--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5301,31 +5301,117 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4375</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4396.8</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4293</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4340</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-68.90000000000001</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="H58" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4216.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4305.25</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4351.8</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4398.35</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4466</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4533.65</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4559.1</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>4216.5</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>4305.25</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>4351.8</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>4398.35</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>4466</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>4533.65</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>4559.1</v>
+      <c r="I59" s="13" t="n">
+        <v>4189.2</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>4233.75</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>4288.1</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>4342.45</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>4391.9</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>4441.35</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>4500.6</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -666,25 +669,25 @@
         <v>67.59999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3273.9</v>
+        <v>3294.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3270.8</v>
+        <v>3296.43</v>
       </c>
       <c r="K2" t="n">
-        <v>3308.5</v>
+        <v>3318.75</v>
       </c>
       <c r="L2" t="n">
-        <v>3346.2</v>
+        <v>3341.07</v>
       </c>
       <c r="M2" t="n">
-        <v>3363.5</v>
+        <v>3353.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3380.8</v>
+        <v>3365.43</v>
       </c>
       <c r="O2" t="n">
-        <v>3438.9</v>
+        <v>3397.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,8 +695,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -720,7 +725,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5307,25 +5312,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C58" t="n">
-        <v>4396.8</v>
+        <v>4347</v>
       </c>
       <c r="D58" t="n">
-        <v>4293</v>
+        <v>4323.8</v>
       </c>
       <c r="E58" t="n">
-        <v>4340</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>-68.90000000000001</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0156</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>103.8</v>
+        <v>23.2</v>
       </c>
       <c r="I58" t="n">
         <v>4216.5</v>
@@ -5348,22 +5353,22 @@
       <c r="O58" t="n">
         <v>4559.1</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5382,36 +5387,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="13" t="n">
-        <v>4189.2</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>4233.75</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>4288.1</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>4342.45</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>4391.9</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>4441.35</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>4500.6</v>
+      <c r="I59" s="14" t="n">
+        <v>4300.6</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>4370.2</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5315,7 +5315,7 @@
         <v>4340.3</v>
       </c>
       <c r="C58" t="n">
-        <v>4347</v>
+        <v>4352.1</v>
       </c>
       <c r="D58" t="n">
         <v>4323.8</v>
@@ -5330,7 +5330,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>23.2</v>
+        <v>28.3</v>
       </c>
       <c r="I58" t="n">
         <v>4216.5</v>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>4300.6</v>
+        <v>4295.5</v>
       </c>
       <c r="J59" s="14" t="n">
         <v/>
@@ -5416,7 +5416,7 @@
         <v/>
       </c>
       <c r="O59" s="14" t="n">
-        <v>4370.2</v>
+        <v>4380.4</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5312,25 +5309,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4340.3</v>
+        <v>4375</v>
       </c>
       <c r="C58" t="n">
-        <v>4352.1</v>
+        <v>4396.8</v>
       </c>
       <c r="D58" t="n">
-        <v>4323.8</v>
+        <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>4351.9</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-57</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0129</v>
       </c>
       <c r="H58" t="n">
-        <v>28.3</v>
+        <v>103.8</v>
       </c>
       <c r="I58" t="n">
         <v>4216.5</v>
@@ -5353,22 +5350,22 @@
       <c r="O58" t="n">
         <v>4559.1</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5387,36 +5384,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
-        <v>4295.5</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
-        <v>4380.4</v>
+      <c r="I59" s="13" t="n">
+        <v>4189.2</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>4251.6</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>4300</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>4348.4</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>4403.8</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>4459.2</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>4500.6</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5318,13 +5318,13 @@
         <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4351.9</v>
+        <v>4343.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-57</v>
+        <v>-65.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0149</v>
       </c>
       <c r="H58" t="n">
         <v>103.8</v>
@@ -5398,19 +5398,19 @@
         <v>4189.2</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4251.6</v>
+        <v>4238.55</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4300</v>
+        <v>4291.3</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4348.4</v>
+        <v>4344.05</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4403.8</v>
+        <v>4395.1</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4459.2</v>
+        <v>4446.15</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4500.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -645,46 +645,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3333.5</v>
+        <v>3382.4</v>
       </c>
       <c r="C2" t="n">
-        <v>3377.7</v>
+        <v>3423.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3310.1</v>
+        <v>3353.4</v>
       </c>
       <c r="E2" t="n">
-        <v>3374.4</v>
+        <v>3418.5</v>
       </c>
       <c r="F2" t="n">
-        <v>38.4</v>
+        <v>35.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0106</v>
       </c>
       <c r="H2" t="n">
-        <v>67.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="I2" t="n">
-        <v>3294.4</v>
+        <v>3327.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3296.43</v>
+        <v>3325.78</v>
       </c>
       <c r="K2" t="n">
-        <v>3318.75</v>
+        <v>3358.45</v>
       </c>
       <c r="L2" t="n">
-        <v>3341.07</v>
+        <v>3391.13</v>
       </c>
       <c r="M2" t="n">
-        <v>3353.25</v>
+        <v>3406.75</v>
       </c>
       <c r="N2" t="n">
-        <v>3365.43</v>
+        <v>3422.38</v>
       </c>
       <c r="O2" t="n">
-        <v>3397.9</v>
+        <v>3472.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -722,7 +722,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -733,46 +733,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3366</v>
+        <v>3417.6</v>
       </c>
       <c r="C3" t="n">
-        <v>3475.6</v>
+        <v>3518.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3366</v>
+        <v>3396.1</v>
       </c>
       <c r="E3" t="n">
-        <v>3473.7</v>
+        <v>3516.1</v>
       </c>
       <c r="F3" t="n">
-        <v>99.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0294</v>
+        <v>0.0286</v>
       </c>
       <c r="H3" t="n">
-        <v>109.6</v>
+        <v>122.4</v>
       </c>
       <c r="I3" t="n">
-        <v>3242.5</v>
+        <v>3283.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3322.05</v>
+        <v>3363.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3340.6</v>
+        <v>3383.5</v>
       </c>
       <c r="L3" t="n">
-        <v>3359.15</v>
+        <v>3403.45</v>
       </c>
       <c r="M3" t="n">
-        <v>3408.2</v>
+        <v>3453.5</v>
       </c>
       <c r="N3" t="n">
-        <v>3457.25</v>
+        <v>3503.55</v>
       </c>
       <c r="O3" t="n">
-        <v>3445.3</v>
+        <v>3493.4</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -817,46 +817,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3485.7</v>
+        <v>3517.9</v>
       </c>
       <c r="C4" t="n">
-        <v>3613.2</v>
+        <v>3655.5</v>
       </c>
       <c r="D4" t="n">
-        <v>3485.7</v>
+        <v>3506</v>
       </c>
       <c r="E4" t="n">
-        <v>3613.2</v>
+        <v>3653.3</v>
       </c>
       <c r="F4" t="n">
-        <v>139.5</v>
+        <v>137.2</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0402</v>
+        <v>0.039</v>
       </c>
       <c r="H4" t="n">
-        <v>127.5</v>
+        <v>149.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3256.4</v>
+        <v>3273.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3390.55</v>
+        <v>3423.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3418.9</v>
+        <v>3454.9</v>
       </c>
       <c r="L4" t="n">
-        <v>3447.25</v>
+        <v>3486.7</v>
       </c>
       <c r="M4" t="n">
-        <v>3528.5</v>
+        <v>3577.3</v>
       </c>
       <c r="N4" t="n">
-        <v>3609.75</v>
+        <v>3667.9</v>
       </c>
       <c r="O4" t="n">
-        <v>3585.2</v>
+        <v>3640.9</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -877,14 +877,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
@@ -901,46 +899,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3594.5</v>
+        <v>3635</v>
       </c>
       <c r="C5" t="n">
-        <v>3670.4</v>
+        <v>3715.2</v>
       </c>
       <c r="D5" t="n">
-        <v>3590</v>
+        <v>3621.7</v>
       </c>
       <c r="E5" t="n">
-        <v>3649.4</v>
+        <v>3686.4</v>
       </c>
       <c r="F5" t="n">
-        <v>36.2</v>
+        <v>33.1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0091</v>
       </c>
       <c r="H5" t="n">
-        <v>80.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3358.2</v>
+        <v>3356.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3517.57</v>
+        <v>3540.08</v>
       </c>
       <c r="K5" t="n">
-        <v>3549.45</v>
+        <v>3578.55</v>
       </c>
       <c r="L5" t="n">
-        <v>3581.32</v>
+        <v>3617.03</v>
       </c>
       <c r="M5" t="n">
-        <v>3676.95</v>
+        <v>3728.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3772.57</v>
+        <v>3839.08</v>
       </c>
       <c r="O5" t="n">
-        <v>3740.7</v>
+        <v>3805</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -981,46 +979,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3640</v>
+        <v>3680.2</v>
       </c>
       <c r="C6" t="n">
-        <v>3698.6</v>
+        <v>3744</v>
       </c>
       <c r="D6" t="n">
-        <v>3635.1</v>
+        <v>3660.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3671.5</v>
+        <v>3705.8</v>
       </c>
       <c r="F6" t="n">
-        <v>22.1</v>
+        <v>19.4</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0061</v>
+        <v>0.0053</v>
       </c>
       <c r="H6" t="n">
-        <v>63.5</v>
+        <v>83.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3509.6</v>
+        <v>3528.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3578.6</v>
+        <v>3601.87</v>
       </c>
       <c r="K6" t="n">
-        <v>3609.2</v>
+        <v>3639.65</v>
       </c>
       <c r="L6" t="n">
-        <v>3639.8</v>
+        <v>3677.42</v>
       </c>
       <c r="M6" t="n">
-        <v>3689.6</v>
+        <v>3733.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3739.4</v>
+        <v>3788.87</v>
       </c>
       <c r="O6" t="n">
-        <v>3750.8</v>
+        <v>3808.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1061,46 +1059,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3688.2</v>
+        <v>3721.3</v>
       </c>
       <c r="C7" t="n">
-        <v>3786</v>
+        <v>3824.6</v>
       </c>
       <c r="D7" t="n">
-        <v>3688</v>
+        <v>3718.1</v>
       </c>
       <c r="E7" t="n">
-        <v>3775.3</v>
+        <v>3809</v>
       </c>
       <c r="F7" t="n">
-        <v>103.8</v>
+        <v>103.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.0278</v>
       </c>
       <c r="H7" t="n">
-        <v>98</v>
+        <v>106.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3571.6</v>
+        <v>3577</v>
       </c>
       <c r="J7" t="n">
-        <v>3610.32</v>
+        <v>3624.08</v>
       </c>
       <c r="K7" t="n">
-        <v>3639.75</v>
+        <v>3664.05</v>
       </c>
       <c r="L7" t="n">
-        <v>3669.18</v>
+        <v>3704.03</v>
       </c>
       <c r="M7" t="n">
-        <v>3703.25</v>
+        <v>3747.55</v>
       </c>
       <c r="N7" t="n">
-        <v>3737.32</v>
+        <v>3791.08</v>
       </c>
       <c r="O7" t="n">
-        <v>3762.1</v>
+        <v>3827.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1123,13 +1121,11 @@
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1145,46 +1141,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3754.8</v>
+        <v>3788.8</v>
       </c>
       <c r="C8" t="n">
-        <v>3891.9</v>
+        <v>3923.3</v>
       </c>
       <c r="D8" t="n">
-        <v>3754.8</v>
+        <v>3785.5</v>
       </c>
       <c r="E8" t="n">
-        <v>3880.8</v>
+        <v>3908.9</v>
       </c>
       <c r="F8" t="n">
-        <v>105.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0279</v>
+        <v>0.0262</v>
       </c>
       <c r="H8" t="n">
-        <v>137.1</v>
+        <v>137.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3590</v>
+        <v>3611.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3696.45</v>
+        <v>3721.32</v>
       </c>
       <c r="K8" t="n">
-        <v>3726.3</v>
+        <v>3755.75</v>
       </c>
       <c r="L8" t="n">
-        <v>3756.15</v>
+        <v>3790.18</v>
       </c>
       <c r="M8" t="n">
-        <v>3824.3</v>
+        <v>3862.25</v>
       </c>
       <c r="N8" t="n">
-        <v>3892.45</v>
+        <v>3934.32</v>
       </c>
       <c r="O8" t="n">
-        <v>3884</v>
+        <v>3931.1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1227,46 +1223,46 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3931.3</v>
+        <v>3913.5</v>
       </c>
       <c r="C9" t="n">
-        <v>4049.2</v>
+        <v>4081</v>
       </c>
       <c r="D9" t="n">
-        <v>3926.8</v>
+        <v>3909.2</v>
       </c>
       <c r="E9" t="n">
-        <v>3975.9</v>
+        <v>4000.4</v>
       </c>
       <c r="F9" t="n">
-        <v>95.09999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0245</v>
+        <v>0.0234</v>
       </c>
       <c r="H9" t="n">
-        <v>122.4</v>
+        <v>171.8</v>
       </c>
       <c r="I9" t="n">
-        <v>3617.7</v>
+        <v>3647.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3772.43</v>
+        <v>3798.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3812.25</v>
+        <v>3840</v>
       </c>
       <c r="L9" t="n">
-        <v>3852.08</v>
+        <v>3881.65</v>
       </c>
       <c r="M9" t="n">
-        <v>3949.35</v>
+        <v>3977.8</v>
       </c>
       <c r="N9" t="n">
-        <v>4046.62</v>
+        <v>4073.95</v>
       </c>
       <c r="O9" t="n">
-        <v>4029</v>
+        <v>4061.1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1311,46 +1307,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4016</v>
+        <v>4018.3</v>
       </c>
       <c r="C10" t="n">
-        <v>4358</v>
+        <v>4392</v>
       </c>
       <c r="D10" t="n">
-        <v>4016</v>
+        <v>4011.3</v>
       </c>
       <c r="E10" t="n">
-        <v>4189.9</v>
+        <v>4213.3</v>
       </c>
       <c r="F10" t="n">
-        <v>214</v>
+        <v>212.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0538</v>
+        <v>0.0532</v>
       </c>
       <c r="H10" t="n">
-        <v>342</v>
+        <v>380.7</v>
       </c>
       <c r="I10" t="n">
-        <v>3804.4</v>
+        <v>3737.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3847.45</v>
+        <v>3831.25</v>
       </c>
       <c r="K10" t="n">
-        <v>3914.7</v>
+        <v>3914.5</v>
       </c>
       <c r="L10" t="n">
-        <v>3981.95</v>
+        <v>3997.75</v>
       </c>
       <c r="M10" t="n">
-        <v>4037.1</v>
+        <v>4086.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4092.25</v>
+        <v>4174.85</v>
       </c>
       <c r="O10" t="n">
-        <v>4171.6</v>
+        <v>4252.8</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1373,12 +1369,12 @@
       </c>
       <c r="U10" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
@@ -1395,46 +1391,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4244.1</v>
+        <v>4269</v>
       </c>
       <c r="C11" t="n">
-        <v>4356.6</v>
+        <v>4398</v>
       </c>
       <c r="D11" t="n">
-        <v>4006</v>
+        <v>4021.2</v>
       </c>
       <c r="E11" t="n">
-        <v>4118.4</v>
+        <v>4137.8</v>
       </c>
       <c r="F11" t="n">
-        <v>-71.5</v>
+        <v>-75.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0171</v>
+        <v>-0.0179</v>
       </c>
       <c r="H11" t="n">
-        <v>350.6</v>
+        <v>376.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3674</v>
+        <v>3630.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3849.35</v>
+        <v>3838.42</v>
       </c>
       <c r="K11" t="n">
-        <v>4018.9</v>
+        <v>4022.95</v>
       </c>
       <c r="L11" t="n">
-        <v>4188.45</v>
+        <v>4207.47</v>
       </c>
       <c r="M11" t="n">
-        <v>4360.9</v>
+        <v>4403.65</v>
       </c>
       <c r="N11" t="n">
-        <v>4533.35</v>
+        <v>4599.82</v>
       </c>
       <c r="O11" t="n">
-        <v>4700</v>
+        <v>4772.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1468,7 +1464,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -1479,46 +1475,46 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4060</v>
+        <v>4103.2</v>
       </c>
       <c r="C12" t="n">
-        <v>4078.6</v>
+        <v>4123.8</v>
       </c>
       <c r="D12" t="n">
-        <v>3913.7</v>
+        <v>3901.3</v>
       </c>
       <c r="E12" t="n">
-        <v>3982.2</v>
+        <v>3996.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-136.2</v>
+        <v>-141.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0331</v>
+        <v>-0.0341</v>
       </c>
       <c r="H12" t="n">
-        <v>164.9</v>
+        <v>222.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3655.4</v>
+        <v>3644.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3736.35</v>
+        <v>3725.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3943.1</v>
+        <v>3949.4</v>
       </c>
       <c r="L12" t="n">
-        <v>4149.85</v>
+        <v>4173.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4293.7</v>
+        <v>4326.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4437.55</v>
+        <v>4478.7</v>
       </c>
       <c r="O12" t="n">
-        <v>4707.2</v>
+        <v>4774.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1563,46 +1559,46 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3976.2</v>
+        <v>4001</v>
       </c>
       <c r="C13" t="n">
-        <v>4020</v>
+        <v>4043.1</v>
       </c>
       <c r="D13" t="n">
-        <v>3927.4</v>
+        <v>3935.7</v>
       </c>
       <c r="E13" t="n">
-        <v>3999.4</v>
+        <v>4009.8</v>
       </c>
       <c r="F13" t="n">
-        <v>17.2</v>
+        <v>13.3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0033</v>
       </c>
       <c r="H13" t="n">
-        <v>92.59999999999999</v>
+        <v>107.4</v>
       </c>
       <c r="I13" t="n">
-        <v>3748.8</v>
+        <v>3678.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3810.32</v>
+        <v>3765.98</v>
       </c>
       <c r="K13" t="n">
-        <v>3899.75</v>
+        <v>3885.25</v>
       </c>
       <c r="L13" t="n">
-        <v>3989.17</v>
+        <v>4004.52</v>
       </c>
       <c r="M13" t="n">
-        <v>4064.65</v>
+        <v>4107.75</v>
       </c>
       <c r="N13" t="n">
-        <v>4140.13</v>
+        <v>4210.97</v>
       </c>
       <c r="O13" t="n">
-        <v>4243.5</v>
+        <v>4346.3</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1645,46 +1641,46 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4060</v>
+        <v>4007.2</v>
       </c>
       <c r="C14" t="n">
-        <v>4228.7</v>
+        <v>4250</v>
       </c>
       <c r="D14" t="n">
-        <v>4047</v>
+        <v>4004.2</v>
       </c>
       <c r="E14" t="n">
-        <v>4087.6</v>
+        <v>4094.2</v>
       </c>
       <c r="F14" t="n">
-        <v>88.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0221</v>
+        <v>0.021</v>
       </c>
       <c r="H14" t="n">
-        <v>181.7</v>
+        <v>245.8</v>
       </c>
       <c r="I14" t="n">
-        <v>3834.8</v>
+        <v>3828.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3919.65</v>
+        <v>3912.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3953.1</v>
+        <v>3956.1</v>
       </c>
       <c r="L14" t="n">
-        <v>3986.55</v>
+        <v>3999.6</v>
       </c>
       <c r="M14" t="n">
-        <v>4045.7</v>
+        <v>4063.5</v>
       </c>
       <c r="N14" t="n">
-        <v>4104.85</v>
+        <v>4127.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4112.6</v>
+        <v>4150.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1702,12 +1698,12 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V14" s="8" t="inlineStr">
@@ -1729,46 +1725,46 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4070</v>
+        <v>4084.4</v>
       </c>
       <c r="C15" t="n">
-        <v>4122.7</v>
+        <v>4134.3</v>
       </c>
       <c r="D15" t="n">
-        <v>4019.4</v>
+        <v>3997.4</v>
       </c>
       <c r="E15" t="n">
-        <v>4076.7</v>
+        <v>4079.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.9</v>
+        <v>-14.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0036</v>
       </c>
       <c r="H15" t="n">
-        <v>103.3</v>
+        <v>136.9</v>
       </c>
       <c r="I15" t="n">
-        <v>3865.3</v>
+        <v>3758.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3880.77</v>
+        <v>3831.95</v>
       </c>
       <c r="K15" t="n">
-        <v>3996.75</v>
+        <v>3971.3</v>
       </c>
       <c r="L15" t="n">
-        <v>4112.73</v>
+        <v>4110.65</v>
       </c>
       <c r="M15" t="n">
-        <v>4178.45</v>
+        <v>4217.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4244.18</v>
+        <v>4323.55</v>
       </c>
       <c r="O15" t="n">
-        <v>4410.4</v>
+        <v>4495.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1811,46 +1807,46 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4060.5</v>
+        <v>4069.2</v>
       </c>
       <c r="C16" t="n">
-        <v>4223.9</v>
+        <v>4263.1</v>
       </c>
       <c r="D16" t="n">
-        <v>4060.5</v>
+        <v>4036.4</v>
       </c>
       <c r="E16" t="n">
-        <v>4218.3</v>
+        <v>4254.9</v>
       </c>
       <c r="F16" t="n">
-        <v>141.6</v>
+        <v>175.4</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0347</v>
+        <v>0.043</v>
       </c>
       <c r="H16" t="n">
-        <v>163.4</v>
+        <v>226.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3916.1</v>
+        <v>3860.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3976.22</v>
+        <v>3949.43</v>
       </c>
       <c r="K16" t="n">
-        <v>4025.05</v>
+        <v>4011.05</v>
       </c>
       <c r="L16" t="n">
-        <v>4073.88</v>
+        <v>4072.67</v>
       </c>
       <c r="M16" t="n">
-        <v>4128.35</v>
+        <v>4147.95</v>
       </c>
       <c r="N16" t="n">
-        <v>4182.83</v>
+        <v>4223.22</v>
       </c>
       <c r="O16" t="n">
-        <v>4226</v>
+        <v>4271.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1895,46 +1891,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4218.5</v>
+        <v>4258.5</v>
       </c>
       <c r="C17" t="n">
-        <v>4262.1</v>
+        <v>4299.6</v>
       </c>
       <c r="D17" t="n">
-        <v>4167</v>
+        <v>4194</v>
       </c>
       <c r="E17" t="n">
-        <v>4212.9</v>
+        <v>4243</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0013</v>
+        <v>-0.0028</v>
       </c>
       <c r="H17" t="n">
-        <v>95.09999999999999</v>
+        <v>105.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3897.1</v>
+        <v>3809.7</v>
       </c>
       <c r="J17" t="n">
-        <v>4092.95</v>
+        <v>4080.77</v>
       </c>
       <c r="K17" t="n">
-        <v>4136.6</v>
+        <v>4141.55</v>
       </c>
       <c r="L17" t="n">
-        <v>4180.25</v>
+        <v>4202.32</v>
       </c>
       <c r="M17" t="n">
-        <v>4300</v>
+        <v>4368.25</v>
       </c>
       <c r="N17" t="n">
-        <v>4419.75</v>
+        <v>4534.18</v>
       </c>
       <c r="O17" t="n">
-        <v>4387.3</v>
+        <v>4489.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1977,46 +1973,46 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4205.5</v>
+        <v>4228.1</v>
       </c>
       <c r="C18" t="n">
-        <v>4355</v>
+        <v>4387.8</v>
       </c>
       <c r="D18" t="n">
-        <v>4175.5</v>
+        <v>4197.8</v>
       </c>
       <c r="E18" t="n">
-        <v>4300.1</v>
+        <v>4328.3</v>
       </c>
       <c r="F18" t="n">
-        <v>87.2</v>
+        <v>85.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0207</v>
+        <v>0.0201</v>
       </c>
       <c r="H18" t="n">
-        <v>179.5</v>
+        <v>190</v>
       </c>
       <c r="I18" t="n">
-        <v>4071.9</v>
+        <v>4088.4</v>
       </c>
       <c r="J18" t="n">
-        <v>4116.97</v>
+        <v>4135.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4165.35</v>
+        <v>4190.2</v>
       </c>
       <c r="L18" t="n">
-        <v>4213.72</v>
+        <v>4244.9</v>
       </c>
       <c r="M18" t="n">
-        <v>4260.45</v>
+        <v>4295.8</v>
       </c>
       <c r="N18" t="n">
-        <v>4307.17</v>
+        <v>4346.7</v>
       </c>
       <c r="O18" t="n">
-        <v>4357.2</v>
+        <v>4405.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2059,46 +2055,46 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4308.3</v>
+        <v>4330</v>
       </c>
       <c r="C19" t="n">
-        <v>4361.4</v>
+        <v>4409.5</v>
       </c>
       <c r="D19" t="n">
-        <v>4270.5</v>
+        <v>4297.4</v>
       </c>
       <c r="E19" t="n">
-        <v>4361.4</v>
+        <v>4387.3</v>
       </c>
       <c r="F19" t="n">
-        <v>61.3</v>
+        <v>59</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0136</v>
       </c>
       <c r="H19" t="n">
-        <v>90.90000000000001</v>
+        <v>112.1</v>
       </c>
       <c r="I19" t="n">
-        <v>3996</v>
+        <v>4007.8</v>
       </c>
       <c r="J19" t="n">
-        <v>4138.03</v>
+        <v>4156.05</v>
       </c>
       <c r="K19" t="n">
-        <v>4210.35</v>
+        <v>4233.3</v>
       </c>
       <c r="L19" t="n">
-        <v>4282.68</v>
+        <v>4310.55</v>
       </c>
       <c r="M19" t="n">
-        <v>4389.85</v>
+        <v>4423.3</v>
       </c>
       <c r="N19" t="n">
-        <v>4497.03</v>
+        <v>4536.05</v>
       </c>
       <c r="O19" t="n">
-        <v>4534.5</v>
+        <v>4577.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2139,46 +2135,46 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4371.1</v>
+        <v>4369.9</v>
       </c>
       <c r="C20" t="n">
-        <v>4556.3</v>
+        <v>4584</v>
       </c>
       <c r="D20" t="n">
-        <v>4371.1</v>
+        <v>4367.9</v>
       </c>
       <c r="E20" t="n">
-        <v>4529.1</v>
+        <v>4552.7</v>
       </c>
       <c r="F20" t="n">
-        <v>167.7</v>
+        <v>165.4</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0385</v>
+        <v>0.0377</v>
       </c>
       <c r="H20" t="n">
-        <v>185.2</v>
+        <v>216.1</v>
       </c>
       <c r="I20" t="n">
-        <v>4179.6</v>
+        <v>4185.3</v>
       </c>
       <c r="J20" t="n">
-        <v>4293.22</v>
+        <v>4292.12</v>
       </c>
       <c r="K20" t="n">
-        <v>4315.95</v>
+        <v>4331.25</v>
       </c>
       <c r="L20" t="n">
-        <v>4338.67</v>
+        <v>4370.37</v>
       </c>
       <c r="M20" t="n">
-        <v>4406.85</v>
+        <v>4443.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4475.02</v>
+        <v>4516.32</v>
       </c>
       <c r="O20" t="n">
-        <v>4452.3</v>
+        <v>4521.6</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2201,12 +2197,12 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
@@ -2223,46 +2219,46 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4371.5</v>
+        <v>4568</v>
       </c>
       <c r="C21" t="n">
-        <v>4403.6</v>
+        <v>4581.3</v>
       </c>
       <c r="D21" t="n">
-        <v>4285</v>
+        <v>4284.3</v>
       </c>
       <c r="E21" t="n">
-        <v>4314.4</v>
+        <v>4329.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-214.7</v>
+        <v>-223.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0474</v>
+        <v>-0.049</v>
       </c>
       <c r="H21" t="n">
-        <v>118.6</v>
+        <v>297</v>
       </c>
       <c r="I21" t="n">
-        <v>4185.9</v>
+        <v>4151.8</v>
       </c>
       <c r="J21" t="n">
-        <v>4376.6</v>
+        <v>4374.98</v>
       </c>
       <c r="K21" t="n">
-        <v>4436.5</v>
+        <v>4444.65</v>
       </c>
       <c r="L21" t="n">
-        <v>4496.4</v>
+        <v>4514.33</v>
       </c>
       <c r="M21" t="n">
-        <v>4621.7</v>
+        <v>4660.75</v>
       </c>
       <c r="N21" t="n">
-        <v>4747</v>
+        <v>4807.18</v>
       </c>
       <c r="O21" t="n">
-        <v>4741.5</v>
+        <v>4800.1</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2305,46 +2301,46 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4386.7</v>
+        <v>4368.3</v>
       </c>
       <c r="C22" t="n">
-        <v>4490.3</v>
+        <v>4527</v>
       </c>
       <c r="D22" t="n">
-        <v>4384.8</v>
+        <v>4354.6</v>
       </c>
       <c r="E22" t="n">
-        <v>4490.3</v>
+        <v>4500.9</v>
       </c>
       <c r="F22" t="n">
-        <v>175.9</v>
+        <v>171.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0408</v>
+        <v>0.0396</v>
       </c>
       <c r="H22" t="n">
-        <v>105.5</v>
+        <v>172.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4166.4</v>
+        <v>3987.3</v>
       </c>
       <c r="J22" t="n">
-        <v>4180.85</v>
+        <v>3981</v>
       </c>
       <c r="K22" t="n">
-        <v>4255.1</v>
+        <v>4181.1</v>
       </c>
       <c r="L22" t="n">
-        <v>4329.35</v>
+        <v>4381.2</v>
       </c>
       <c r="M22" t="n">
-        <v>4373.7</v>
+        <v>4478.1</v>
       </c>
       <c r="N22" t="n">
-        <v>4418.05</v>
+        <v>4575</v>
       </c>
       <c r="O22" t="n">
-        <v>4522.2</v>
+        <v>4878.3</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2362,25 +2358,25 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2389,46 +2385,46 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4579.1</v>
+        <v>4529.1</v>
       </c>
       <c r="C23" t="n">
-        <v>4635</v>
+        <v>4650.5</v>
       </c>
       <c r="D23" t="n">
-        <v>4577.8</v>
+        <v>4520.8</v>
       </c>
       <c r="E23" t="n">
-        <v>4588.4</v>
+        <v>4595.4</v>
       </c>
       <c r="F23" t="n">
-        <v>98.09999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0218</v>
+        <v>0.021</v>
       </c>
       <c r="H23" t="n">
-        <v>57.2</v>
+        <v>129.7</v>
       </c>
       <c r="I23" t="n">
-        <v>4279.3</v>
+        <v>4182.2</v>
       </c>
       <c r="J23" t="n">
-        <v>4411.17</v>
+        <v>4358.55</v>
       </c>
       <c r="K23" t="n">
-        <v>4437.55</v>
+        <v>4414.7</v>
       </c>
       <c r="L23" t="n">
-        <v>4463.92</v>
+        <v>4470.85</v>
       </c>
       <c r="M23" t="n">
-        <v>4543.05</v>
+        <v>4587.1</v>
       </c>
       <c r="N23" t="n">
-        <v>4622.17</v>
+        <v>4703.35</v>
       </c>
       <c r="O23" t="n">
-        <v>4595.8</v>
+        <v>4699.4</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2446,25 +2442,25 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2473,46 +2469,46 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4662.2</v>
+        <v>4633.7</v>
       </c>
       <c r="C24" t="n">
-        <v>4976.2</v>
+        <v>4991.4</v>
       </c>
       <c r="D24" t="n">
-        <v>4661.8</v>
+        <v>4622.2</v>
       </c>
       <c r="E24" t="n">
-        <v>4976.2</v>
+        <v>4979.7</v>
       </c>
       <c r="F24" t="n">
-        <v>387.8</v>
+        <v>384.3</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>314.4</v>
+        <v>369.2</v>
       </c>
       <c r="I24" t="n">
-        <v>4520.6</v>
+        <v>4391.1</v>
       </c>
       <c r="J24" t="n">
-        <v>4522.2</v>
+        <v>4470.57</v>
       </c>
       <c r="K24" t="n">
-        <v>4559.8</v>
+        <v>4530.55</v>
       </c>
       <c r="L24" t="n">
-        <v>4597.4</v>
+        <v>4590.52</v>
       </c>
       <c r="M24" t="n">
-        <v>4617</v>
+        <v>4660.25</v>
       </c>
       <c r="N24" t="n">
-        <v>4636.6</v>
+        <v>4729.98</v>
       </c>
       <c r="O24" t="n">
-        <v>4692.2</v>
+        <v>4780.2</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2557,46 +2553,46 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5081.5</v>
+        <v>5013.4</v>
       </c>
       <c r="C25" t="n">
         <v>5586.2</v>
       </c>
       <c r="D25" t="n">
-        <v>4700</v>
+        <v>4700.4</v>
       </c>
       <c r="E25" t="n">
-        <v>4713.9</v>
+        <v>4745.1</v>
       </c>
       <c r="F25" t="n">
-        <v>-262.3</v>
+        <v>-234.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0527</v>
+        <v>-0.0471</v>
       </c>
       <c r="H25" t="n">
-        <v>886.2</v>
+        <v>885.8</v>
       </c>
       <c r="I25" t="n">
-        <v>4347.4</v>
+        <v>4253</v>
       </c>
       <c r="J25" t="n">
-        <v>4740.4</v>
+        <v>4696.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4819</v>
+        <v>4795.1</v>
       </c>
       <c r="L25" t="n">
-        <v>4897.6</v>
+        <v>4893.25</v>
       </c>
       <c r="M25" t="n">
-        <v>5133.4</v>
+        <v>5164.3</v>
       </c>
       <c r="N25" t="n">
-        <v>5369.2</v>
+        <v>5435.35</v>
       </c>
       <c r="O25" t="n">
-        <v>5290.6</v>
+        <v>5360.6</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2631,14 +2627,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -2649,46 +2645,46 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4807.7</v>
+        <v>4816</v>
       </c>
       <c r="C26" t="n">
-        <v>5082.2</v>
+        <v>5113.9</v>
       </c>
       <c r="D26" t="n">
-        <v>4400</v>
+        <v>4423.2</v>
       </c>
       <c r="E26" t="n">
-        <v>4951.2</v>
+        <v>4979.8</v>
       </c>
       <c r="F26" t="n">
-        <v>237.3</v>
+        <v>234.7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0503</v>
+        <v>0.0495</v>
       </c>
       <c r="H26" t="n">
-        <v>682.2</v>
+        <v>690.7</v>
       </c>
       <c r="I26" t="n">
-        <v>3813.8</v>
+        <v>3814.6</v>
       </c>
       <c r="J26" t="n">
-        <v>3613.1</v>
+        <v>3660.2</v>
       </c>
       <c r="K26" t="n">
-        <v>4270.8</v>
+        <v>4302.2</v>
       </c>
       <c r="L26" t="n">
-        <v>4928.5</v>
+        <v>4944.2</v>
       </c>
       <c r="M26" t="n">
-        <v>5157</v>
+        <v>5188</v>
       </c>
       <c r="N26" t="n">
-        <v>5385.5</v>
+        <v>5431.8</v>
       </c>
       <c r="O26" t="n">
-        <v>6472.4</v>
+        <v>6472</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2713,14 +2709,14 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -2731,46 +2727,46 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5017.4</v>
+        <v>5003.6</v>
       </c>
       <c r="C27" t="n">
-        <v>5111.3</v>
+        <v>5144.5</v>
       </c>
       <c r="D27" t="n">
-        <v>4892</v>
+        <v>4900</v>
       </c>
       <c r="E27" t="n">
-        <v>5022</v>
+        <v>5046.3</v>
       </c>
       <c r="F27" t="n">
-        <v>70.8</v>
+        <v>66.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0143</v>
+        <v>0.0134</v>
       </c>
       <c r="H27" t="n">
-        <v>219.3</v>
+        <v>244.5</v>
       </c>
       <c r="I27" t="n">
-        <v>3717.8</v>
+        <v>3732.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4374.05</v>
+        <v>4394.72</v>
       </c>
       <c r="K27" t="n">
-        <v>4610.1</v>
+        <v>4634.45</v>
       </c>
       <c r="L27" t="n">
-        <v>4846.15</v>
+        <v>4874.17</v>
       </c>
       <c r="M27" t="n">
-        <v>5292.3</v>
+        <v>5325.15</v>
       </c>
       <c r="N27" t="n">
-        <v>5738.45</v>
+        <v>5776.12</v>
       </c>
       <c r="O27" t="n">
-        <v>5764.4</v>
+        <v>5804.6</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2795,16 +2791,12 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2813,46 +2805,46 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5020</v>
+        <v>5050</v>
       </c>
       <c r="C28" t="n">
-        <v>5072.7</v>
+        <v>5131</v>
       </c>
       <c r="D28" t="n">
-        <v>4847.8</v>
+        <v>4854.2</v>
       </c>
       <c r="E28" t="n">
-        <v>5059.3</v>
+        <v>5080.9</v>
       </c>
       <c r="F28" t="n">
-        <v>37.3</v>
+        <v>34.6</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0074</v>
+        <v>0.0069</v>
       </c>
       <c r="H28" t="n">
-        <v>224.9</v>
+        <v>276.8</v>
       </c>
       <c r="I28" t="n">
-        <v>4672.7</v>
+        <v>4655.5</v>
       </c>
       <c r="J28" t="n">
-        <v>4812.88</v>
+        <v>4813.82</v>
       </c>
       <c r="K28" t="n">
-        <v>4912.35</v>
+        <v>4924.05</v>
       </c>
       <c r="L28" t="n">
-        <v>5011.82</v>
+        <v>5034.27</v>
       </c>
       <c r="M28" t="n">
-        <v>5131.65</v>
+        <v>5168.55</v>
       </c>
       <c r="N28" t="n">
-        <v>5251.47</v>
+        <v>5302.82</v>
       </c>
       <c r="O28" t="n">
-        <v>5330.6</v>
+        <v>5389</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2879,14 +2871,14 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -2897,46 +2889,46 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5120.3</v>
+        <v>5128.8</v>
       </c>
       <c r="C29" t="n">
-        <v>5280</v>
+        <v>5299</v>
       </c>
       <c r="D29" t="n">
-        <v>5112.7</v>
+        <v>5109.5</v>
       </c>
       <c r="E29" t="n">
-        <v>5230.5</v>
+        <v>5247.9</v>
       </c>
       <c r="F29" t="n">
-        <v>171.2</v>
+        <v>167</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0338</v>
+        <v>0.0329</v>
       </c>
       <c r="H29" t="n">
-        <v>167.3</v>
+        <v>189.5</v>
       </c>
       <c r="I29" t="n">
-        <v>4622.9</v>
+        <v>4577.4</v>
       </c>
       <c r="J29" t="n">
-        <v>4883.92</v>
+        <v>4848.25</v>
       </c>
       <c r="K29" t="n">
-        <v>4946.85</v>
+        <v>4942.5</v>
       </c>
       <c r="L29" t="n">
-        <v>5009.77</v>
+        <v>5036.75</v>
       </c>
       <c r="M29" t="n">
-        <v>5171.75</v>
+        <v>5219.3</v>
       </c>
       <c r="N29" t="n">
-        <v>5333.73</v>
+        <v>5401.85</v>
       </c>
       <c r="O29" t="n">
-        <v>5297.6</v>
+        <v>5407.8</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2963,16 +2955,12 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2981,46 +2969,46 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5346.6</v>
+        <v>5360</v>
       </c>
       <c r="C30" t="n">
-        <v>5405</v>
+        <v>5434.1</v>
       </c>
       <c r="D30" t="n">
-        <v>5023</v>
+        <v>5005</v>
       </c>
       <c r="E30" t="n">
-        <v>5146.1</v>
+        <v>5158.7</v>
       </c>
       <c r="F30" t="n">
-        <v>-84.40000000000001</v>
+        <v>-89.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.017</v>
       </c>
       <c r="H30" t="n">
-        <v>382</v>
+        <v>429.1</v>
       </c>
       <c r="I30" t="n">
-        <v>4945.4</v>
+        <v>4920</v>
       </c>
       <c r="J30" t="n">
-        <v>5080.28</v>
+        <v>5080.22</v>
       </c>
       <c r="K30" t="n">
-        <v>5146.85</v>
+        <v>5153.15</v>
       </c>
       <c r="L30" t="n">
-        <v>5213.43</v>
+        <v>5226.07</v>
       </c>
       <c r="M30" t="n">
-        <v>5314.15</v>
+        <v>5342.65</v>
       </c>
       <c r="N30" t="n">
-        <v>5414.87</v>
+        <v>5459.22</v>
       </c>
       <c r="O30" t="n">
-        <v>5447.3</v>
+        <v>5488.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3051,14 +3039,14 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -3069,46 +3057,46 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5155</v>
+        <v>5186.7</v>
       </c>
       <c r="C31" t="n">
-        <v>5229.7</v>
+        <v>5248.7</v>
       </c>
       <c r="D31" t="n">
-        <v>5009.5</v>
+        <v>5014.1</v>
       </c>
       <c r="E31" t="n">
-        <v>5052.5</v>
+        <v>5061.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-93.59999999999999</v>
+        <v>-97</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0182</v>
+        <v>-0.0188</v>
       </c>
       <c r="H31" t="n">
-        <v>220.2</v>
+        <v>234.6</v>
       </c>
       <c r="I31" t="n">
-        <v>4641</v>
+        <v>4575.9</v>
       </c>
       <c r="J31" t="n">
-        <v>4730.15</v>
+        <v>4699.18</v>
       </c>
       <c r="K31" t="n">
-        <v>4955.1</v>
+        <v>4944.15</v>
       </c>
       <c r="L31" t="n">
-        <v>5180.05</v>
+        <v>5189.13</v>
       </c>
       <c r="M31" t="n">
-        <v>5337.1</v>
+        <v>5373.25</v>
       </c>
       <c r="N31" t="n">
-        <v>5494.15</v>
+        <v>5557.38</v>
       </c>
       <c r="O31" t="n">
-        <v>5787</v>
+        <v>5863.2</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3135,12 +3123,16 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3149,46 +3141,46 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5001.6</v>
+        <v>5010</v>
       </c>
       <c r="C32" t="n">
-        <v>5017.6</v>
+        <v>5049.4</v>
       </c>
       <c r="D32" t="n">
-        <v>4554</v>
+        <v>4478.4</v>
       </c>
       <c r="E32" t="n">
-        <v>4570.4</v>
+        <v>4574.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-482.1</v>
+        <v>-486.8</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0954</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>463.6</v>
+        <v>571</v>
       </c>
       <c r="I32" t="n">
-        <v>4789.3</v>
+        <v>4779.5</v>
       </c>
       <c r="J32" t="n">
-        <v>4798.75</v>
+        <v>4792.25</v>
       </c>
       <c r="K32" t="n">
-        <v>4942.4</v>
+        <v>4944.4</v>
       </c>
       <c r="L32" t="n">
-        <v>5086.05</v>
+        <v>5096.55</v>
       </c>
       <c r="M32" t="n">
-        <v>5162.6</v>
+        <v>5179</v>
       </c>
       <c r="N32" t="n">
-        <v>5239.15</v>
+        <v>5261.45</v>
       </c>
       <c r="O32" t="n">
-        <v>5449.9</v>
+        <v>5483.3</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -3233,46 +3225,46 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4353</v>
+        <v>4450</v>
       </c>
       <c r="C33" t="n">
-        <v>4551.9</v>
+        <v>4601</v>
       </c>
       <c r="D33" t="n">
-        <v>4100.8</v>
+        <v>4100</v>
       </c>
       <c r="E33" t="n">
-        <v>4492</v>
+        <v>4492.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-78.40000000000001</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0172</v>
+        <v>-0.018</v>
       </c>
       <c r="H33" t="n">
-        <v>451.1</v>
+        <v>501</v>
       </c>
       <c r="I33" t="n">
-        <v>4090.4</v>
+        <v>3907.4</v>
       </c>
       <c r="J33" t="n">
-        <v>3999.1</v>
+        <v>3909.4</v>
       </c>
       <c r="K33" t="n">
-        <v>4338.6</v>
+        <v>4289.4</v>
       </c>
       <c r="L33" t="n">
-        <v>4678.1</v>
+        <v>4669.4</v>
       </c>
       <c r="M33" t="n">
-        <v>4802.2</v>
+        <v>4860.4</v>
       </c>
       <c r="N33" t="n">
-        <v>4926.3</v>
+        <v>5051.4</v>
       </c>
       <c r="O33" t="n">
-        <v>5481.2</v>
+        <v>5620.4</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3282,12 +3274,12 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3316,43 +3308,43 @@
         <v>4482.8</v>
       </c>
       <c r="C34" t="n">
-        <v>4789.1</v>
+        <v>4825.9</v>
       </c>
       <c r="D34" t="n">
         <v>4413.4</v>
       </c>
       <c r="E34" t="n">
-        <v>4651.5</v>
+        <v>4679.7</v>
       </c>
       <c r="F34" t="n">
-        <v>159.5</v>
+        <v>187.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0355</v>
+        <v>0.0417</v>
       </c>
       <c r="H34" t="n">
-        <v>375.7</v>
+        <v>412.5</v>
       </c>
       <c r="I34" t="n">
-        <v>3649.7</v>
+        <v>3599</v>
       </c>
       <c r="J34" t="n">
-        <v>4123.72</v>
+        <v>4062.5</v>
       </c>
       <c r="K34" t="n">
-        <v>4266.45</v>
+        <v>4242</v>
       </c>
       <c r="L34" t="n">
-        <v>4409.17</v>
+        <v>4421.5</v>
       </c>
       <c r="M34" t="n">
-        <v>4717.55</v>
+        <v>4743</v>
       </c>
       <c r="N34" t="n">
-        <v>5025.93</v>
+        <v>5064.5</v>
       </c>
       <c r="O34" t="n">
-        <v>5003</v>
+        <v>5102</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3397,46 +3389,46 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4656.1</v>
+        <v>4675</v>
       </c>
       <c r="C35" t="n">
-        <v>4851</v>
+        <v>4888</v>
       </c>
       <c r="D35" t="n">
-        <v>4605</v>
+        <v>4626.2</v>
       </c>
       <c r="E35" t="n">
-        <v>4761.9</v>
+        <v>4787.4</v>
       </c>
       <c r="F35" t="n">
-        <v>110.4</v>
+        <v>107.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0237</v>
+        <v>0.023</v>
       </c>
       <c r="H35" t="n">
-        <v>246</v>
+        <v>261.8</v>
       </c>
       <c r="I35" t="n">
-        <v>4037.7</v>
+        <v>4000.9</v>
       </c>
       <c r="J35" t="n">
-        <v>4300.92</v>
+        <v>4297.23</v>
       </c>
       <c r="K35" t="n">
-        <v>4463.65</v>
+        <v>4473.45</v>
       </c>
       <c r="L35" t="n">
-        <v>4626.38</v>
+        <v>4649.68</v>
       </c>
       <c r="M35" t="n">
-        <v>4839.35</v>
+        <v>4885.95</v>
       </c>
       <c r="N35" t="n">
-        <v>5052.33</v>
+        <v>5122.23</v>
       </c>
       <c r="O35" t="n">
-        <v>5164.8</v>
+        <v>5238.4</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3481,46 +3473,46 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4704</v>
+        <v>4710</v>
       </c>
       <c r="C36" t="n">
-        <v>4879.7</v>
+        <v>4917.7</v>
       </c>
       <c r="D36" t="n">
-        <v>4704</v>
+        <v>4626</v>
       </c>
       <c r="E36" t="n">
-        <v>4857.6</v>
+        <v>4879.6</v>
       </c>
       <c r="F36" t="n">
-        <v>95.7</v>
+        <v>92.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0193</v>
       </c>
       <c r="H36" t="n">
-        <v>175.7</v>
+        <v>291.7</v>
       </c>
       <c r="I36" t="n">
-        <v>4359</v>
+        <v>4364.4</v>
       </c>
       <c r="J36" t="n">
-        <v>4532.85</v>
+        <v>4540.75</v>
       </c>
       <c r="K36" t="n">
-        <v>4638.9</v>
+        <v>4656.5</v>
       </c>
       <c r="L36" t="n">
-        <v>4744.95</v>
+        <v>4772.25</v>
       </c>
       <c r="M36" t="n">
-        <v>4884.9</v>
+        <v>4918.3</v>
       </c>
       <c r="N36" t="n">
-        <v>5024.85</v>
+        <v>5064.35</v>
       </c>
       <c r="O36" t="n">
-        <v>5097</v>
+        <v>5149.8</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3528,8 +3520,10 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
@@ -3554,7 +3548,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -3565,60 +3559,58 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4793.9</v>
+        <v>4811.8</v>
       </c>
       <c r="C37" t="n">
-        <v>4811</v>
+        <v>4854.8</v>
       </c>
       <c r="D37" t="n">
-        <v>4657.5</v>
+        <v>4672.2</v>
       </c>
       <c r="E37" t="n">
-        <v>4722.3</v>
+        <v>4740.9</v>
       </c>
       <c r="F37" t="n">
-        <v>-135.3</v>
+        <v>-138.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0279</v>
+        <v>-0.0284</v>
       </c>
       <c r="H37" t="n">
-        <v>153.5</v>
+        <v>182.6</v>
       </c>
       <c r="I37" t="n">
-        <v>4528.3</v>
+        <v>4334.3</v>
       </c>
       <c r="J37" t="n">
-        <v>4714.77</v>
+        <v>4641.77</v>
       </c>
       <c r="K37" t="n">
-        <v>4769.75</v>
+        <v>4733.75</v>
       </c>
       <c r="L37" t="n">
-        <v>4824.73</v>
+        <v>4825.73</v>
       </c>
       <c r="M37" t="n">
-        <v>4945.45</v>
+        <v>5025.45</v>
       </c>
       <c r="N37" t="n">
-        <v>5066.18</v>
+        <v>5225.18</v>
       </c>
       <c r="O37" t="n">
-        <v>5055.4</v>
+        <v>5209.4</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3638,7 +3630,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3647,46 +3643,46 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4707.6</v>
+        <v>4713.1</v>
       </c>
       <c r="C38" t="n">
-        <v>4711.1</v>
+        <v>4745.8</v>
       </c>
       <c r="D38" t="n">
-        <v>4515.7</v>
+        <v>4522.2</v>
       </c>
       <c r="E38" t="n">
-        <v>4629.9</v>
+        <v>4644.5</v>
       </c>
       <c r="F38" t="n">
-        <v>-92.40000000000001</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.0203</v>
       </c>
       <c r="H38" t="n">
-        <v>195.4</v>
+        <v>223.6</v>
       </c>
       <c r="I38" t="n">
-        <v>4504</v>
+        <v>4489.6</v>
       </c>
       <c r="J38" t="n">
-        <v>4562.82</v>
+        <v>4547</v>
       </c>
       <c r="K38" t="n">
-        <v>4645.55</v>
+        <v>4649.6</v>
       </c>
       <c r="L38" t="n">
-        <v>4728.27</v>
+        <v>4752.2</v>
       </c>
       <c r="M38" t="n">
-        <v>4799.05</v>
+        <v>4832.2</v>
       </c>
       <c r="N38" t="n">
-        <v>4869.82</v>
+        <v>4912.2</v>
       </c>
       <c r="O38" t="n">
-        <v>4964.5</v>
+        <v>5037.4</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3729,46 +3725,46 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4581.2</v>
+        <v>4644</v>
       </c>
       <c r="C39" t="n">
-        <v>4736.2</v>
+        <v>4775.2</v>
       </c>
       <c r="D39" t="n">
-        <v>4512.7</v>
+        <v>4510.1</v>
       </c>
       <c r="E39" t="n">
-        <v>4720.4</v>
+        <v>4730.7</v>
       </c>
       <c r="F39" t="n">
-        <v>90.5</v>
+        <v>86.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0195</v>
+        <v>0.0186</v>
       </c>
       <c r="H39" t="n">
-        <v>223.5</v>
+        <v>265.1</v>
       </c>
       <c r="I39" t="n">
-        <v>4320.3</v>
+        <v>4298.6</v>
       </c>
       <c r="J39" t="n">
-        <v>4442.75</v>
+        <v>4426.15</v>
       </c>
       <c r="K39" t="n">
-        <v>4532.2</v>
+        <v>4532.7</v>
       </c>
       <c r="L39" t="n">
-        <v>4621.65</v>
+        <v>4639.25</v>
       </c>
       <c r="M39" t="n">
-        <v>4727.6</v>
+        <v>4756.3</v>
       </c>
       <c r="N39" t="n">
-        <v>4833.55</v>
+        <v>4873.35</v>
       </c>
       <c r="O39" t="n">
-        <v>4906.5</v>
+        <v>4969.4</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3815,58 +3811,56 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4729.5</v>
+        <v>4690</v>
       </c>
       <c r="C40" t="n">
-        <v>4765.2</v>
+        <v>4783.4</v>
       </c>
       <c r="D40" t="n">
-        <v>4524.3</v>
+        <v>4513.8</v>
       </c>
       <c r="E40" t="n">
-        <v>4555.8</v>
+        <v>4561.9</v>
       </c>
       <c r="F40" t="n">
-        <v>-164.6</v>
+        <v>-168.8</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0349</v>
+        <v>-0.0357</v>
       </c>
       <c r="H40" t="n">
-        <v>240.9</v>
+        <v>269.6</v>
       </c>
       <c r="I40" t="n">
-        <v>4289.2</v>
+        <v>4245</v>
       </c>
       <c r="J40" t="n">
-        <v>4544.87</v>
+        <v>4509.63</v>
       </c>
       <c r="K40" t="n">
-        <v>4608.65</v>
+        <v>4598.15</v>
       </c>
       <c r="L40" t="n">
-        <v>4672.43</v>
+        <v>4686.68</v>
       </c>
       <c r="M40" t="n">
-        <v>4832.15</v>
+        <v>4863.25</v>
       </c>
       <c r="N40" t="n">
-        <v>4991.87</v>
+        <v>5039.83</v>
       </c>
       <c r="O40" t="n">
-        <v>4959.7</v>
+        <v>5040.3</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
@@ -3901,46 +3895,46 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4563</v>
+        <v>4547.6</v>
       </c>
       <c r="C41" t="n">
-        <v>4570.3</v>
+        <v>4593.2</v>
       </c>
       <c r="D41" t="n">
-        <v>4465.1</v>
+        <v>4455</v>
       </c>
       <c r="E41" t="n">
-        <v>4521</v>
+        <v>4523.2</v>
       </c>
       <c r="F41" t="n">
-        <v>-34.8</v>
+        <v>-38.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>105.2</v>
+        <v>138.2</v>
       </c>
       <c r="I41" t="n">
-        <v>4283.4</v>
+        <v>4244.2</v>
       </c>
       <c r="J41" t="n">
-        <v>4270.42</v>
+        <v>4248.95</v>
       </c>
       <c r="K41" t="n">
-        <v>4435.35</v>
+        <v>4427.1</v>
       </c>
       <c r="L41" t="n">
-        <v>4600.27</v>
+        <v>4605.25</v>
       </c>
       <c r="M41" t="n">
-        <v>4676.25</v>
+        <v>4696.7</v>
       </c>
       <c r="N41" t="n">
-        <v>4752.23</v>
+        <v>4788.15</v>
       </c>
       <c r="O41" t="n">
-        <v>5006.1</v>
+        <v>5053</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3979,46 +3973,46 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4572.8</v>
+        <v>4532</v>
       </c>
       <c r="C42" t="n">
-        <v>4591.8</v>
+        <v>4627.1</v>
       </c>
       <c r="D42" t="n">
         <v>4363.5</v>
       </c>
       <c r="E42" t="n">
-        <v>4560.5</v>
+        <v>4593</v>
       </c>
       <c r="F42" t="n">
-        <v>39.5</v>
+        <v>69.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0154</v>
       </c>
       <c r="H42" t="n">
-        <v>228.3</v>
+        <v>263.6</v>
       </c>
       <c r="I42" t="n">
-        <v>4359.9</v>
+        <v>4316.8</v>
       </c>
       <c r="J42" t="n">
-        <v>4417.45</v>
+        <v>4384.55</v>
       </c>
       <c r="K42" t="n">
-        <v>4468.4</v>
+        <v>4454.1</v>
       </c>
       <c r="L42" t="n">
-        <v>4519.35</v>
+        <v>4523.65</v>
       </c>
       <c r="M42" t="n">
-        <v>4573.6</v>
+        <v>4592.3</v>
       </c>
       <c r="N42" t="n">
-        <v>4627.85</v>
+        <v>4660.95</v>
       </c>
       <c r="O42" t="n">
-        <v>4675.5</v>
+        <v>4731.4</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4067,46 +4061,46 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4523.5</v>
+        <v>4575.2</v>
       </c>
       <c r="C43" t="n">
-        <v>4541.4</v>
+        <v>4577.3</v>
       </c>
       <c r="D43" t="n">
-        <v>4319.1</v>
+        <v>4336.6</v>
       </c>
       <c r="E43" t="n">
-        <v>4337.1</v>
+        <v>4365.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-223.4</v>
+        <v>-227.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.049</v>
+        <v>-0.0496</v>
       </c>
       <c r="H43" t="n">
-        <v>222.3</v>
+        <v>240.7</v>
       </c>
       <c r="I43" t="n">
-        <v>4135.2</v>
+        <v>4099.9</v>
       </c>
       <c r="J43" t="n">
-        <v>4373.63</v>
+        <v>4378.25</v>
       </c>
       <c r="K43" t="n">
-        <v>4446.35</v>
+        <v>4461.2</v>
       </c>
       <c r="L43" t="n">
-        <v>4519.07</v>
+        <v>4544.15</v>
       </c>
       <c r="M43" t="n">
-        <v>4674.65</v>
+        <v>4724.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4830.22</v>
+        <v>4905.45</v>
       </c>
       <c r="O43" t="n">
-        <v>4820.1</v>
+        <v>4890.7</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4149,46 +4143,46 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4324.2</v>
+        <v>4354</v>
       </c>
       <c r="C44" t="n">
-        <v>4344.5</v>
+        <v>4388.6</v>
       </c>
       <c r="D44" t="n">
-        <v>4031</v>
+        <v>4046.2</v>
       </c>
       <c r="E44" t="n">
-        <v>4215</v>
+        <v>4238.8</v>
       </c>
       <c r="F44" t="n">
-        <v>-122.1</v>
+        <v>-126.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0282</v>
+        <v>-0.029</v>
       </c>
       <c r="H44" t="n">
-        <v>313.5</v>
+        <v>342.4</v>
       </c>
       <c r="I44" t="n">
-        <v>4096.8</v>
+        <v>4095.9</v>
       </c>
       <c r="J44" t="n">
-        <v>4068.23</v>
+        <v>4078.78</v>
       </c>
       <c r="K44" t="n">
-        <v>4225.95</v>
+        <v>4244.95</v>
       </c>
       <c r="L44" t="n">
-        <v>4383.68</v>
+        <v>4411.12</v>
       </c>
       <c r="M44" t="n">
-        <v>4448.25</v>
+        <v>4485.65</v>
       </c>
       <c r="N44" t="n">
-        <v>4512.82</v>
+        <v>4560.17</v>
       </c>
       <c r="O44" t="n">
-        <v>4763.7</v>
+        <v>4818</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -4233,46 +4227,46 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4271.2</v>
+        <v>4289.4</v>
       </c>
       <c r="C45" t="n">
-        <v>4377</v>
+        <v>4403.6</v>
       </c>
       <c r="D45" t="n">
-        <v>4141.1</v>
+        <v>4138.7</v>
       </c>
       <c r="E45" t="n">
-        <v>4145.3</v>
+        <v>4172.9</v>
       </c>
       <c r="F45" t="n">
-        <v>-69.7</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0165</v>
+        <v>-0.0155</v>
       </c>
       <c r="H45" t="n">
-        <v>235.9</v>
+        <v>264.9</v>
       </c>
       <c r="I45" t="n">
-        <v>3717.5</v>
+        <v>3703.8</v>
       </c>
       <c r="J45" t="n">
-        <v>3915.12</v>
+        <v>3907.1</v>
       </c>
       <c r="K45" t="n">
-        <v>4058.25</v>
+        <v>4067.6</v>
       </c>
       <c r="L45" t="n">
-        <v>4201.38</v>
+        <v>4228.1</v>
       </c>
       <c r="M45" t="n">
-        <v>4371.75</v>
+        <v>4410</v>
       </c>
       <c r="N45" t="n">
-        <v>4542.12</v>
+        <v>4591.9</v>
       </c>
       <c r="O45" t="n">
-        <v>4658</v>
+        <v>4731</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4288,10 +4282,8 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4317,46 +4309,46 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4138.8</v>
+        <v>4163.9</v>
       </c>
       <c r="C46" t="n">
-        <v>4216.4</v>
+        <v>4238.1</v>
       </c>
       <c r="D46" t="n">
-        <v>3963.3</v>
+        <v>3975.7</v>
       </c>
       <c r="E46" t="n">
-        <v>4078.7</v>
+        <v>4096.3</v>
       </c>
       <c r="F46" t="n">
-        <v>-66.59999999999999</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0184</v>
       </c>
       <c r="H46" t="n">
-        <v>253.1</v>
+        <v>262.4</v>
       </c>
       <c r="I46" t="n">
-        <v>3905.2</v>
+        <v>3873.8</v>
       </c>
       <c r="J46" t="n">
-        <v>3852.52</v>
+        <v>3858.87</v>
       </c>
       <c r="K46" t="n">
-        <v>4027.35</v>
+        <v>4040.45</v>
       </c>
       <c r="L46" t="n">
-        <v>4202.17</v>
+        <v>4222.03</v>
       </c>
       <c r="M46" t="n">
-        <v>4263.25</v>
+        <v>4305.35</v>
       </c>
       <c r="N46" t="n">
-        <v>4324.32</v>
+        <v>4388.67</v>
       </c>
       <c r="O46" t="n">
-        <v>4612.9</v>
+        <v>4668.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4397,46 +4389,46 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4057.5</v>
+        <v>4101.1</v>
       </c>
       <c r="C47" t="n">
-        <v>4174.6</v>
+        <v>4208.3</v>
       </c>
       <c r="D47" t="n">
-        <v>3962.5</v>
+        <v>3955.4</v>
       </c>
       <c r="E47" t="n">
-        <v>4174.6</v>
+        <v>4187.3</v>
       </c>
       <c r="F47" t="n">
-        <v>95.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0235</v>
+        <v>0.0222</v>
       </c>
       <c r="H47" t="n">
-        <v>212.1</v>
+        <v>252.9</v>
       </c>
       <c r="I47" t="n">
-        <v>3710.2</v>
+        <v>3713.3</v>
       </c>
       <c r="J47" t="n">
-        <v>3820.03</v>
+        <v>3828.6</v>
       </c>
       <c r="K47" t="n">
-        <v>3952.15</v>
+        <v>3965.1</v>
       </c>
       <c r="L47" t="n">
-        <v>4084.27</v>
+        <v>4101.6</v>
       </c>
       <c r="M47" t="n">
-        <v>4205.25</v>
+        <v>4227.5</v>
       </c>
       <c r="N47" t="n">
-        <v>4326.22</v>
+        <v>4353.4</v>
       </c>
       <c r="O47" t="n">
-        <v>4469.5</v>
+        <v>4500.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4444,8 +4436,10 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
@@ -4481,46 +4475,46 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4175.4</v>
+        <v>4187.5</v>
       </c>
       <c r="C48" t="n">
-        <v>4199.7</v>
+        <v>4215.5</v>
       </c>
       <c r="D48" t="n">
-        <v>4053</v>
+        <v>4032.5</v>
       </c>
       <c r="E48" t="n">
-        <v>4104.1</v>
+        <v>4113.7</v>
       </c>
       <c r="F48" t="n">
-        <v>-70.5</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0176</v>
       </c>
       <c r="H48" t="n">
-        <v>146.7</v>
+        <v>183</v>
       </c>
       <c r="I48" t="n">
-        <v>3750.4</v>
+        <v>3702.5</v>
       </c>
       <c r="J48" t="n">
-        <v>4015.53</v>
+        <v>3987.12</v>
       </c>
       <c r="K48" t="n">
-        <v>4068.55</v>
+        <v>4060.85</v>
       </c>
       <c r="L48" t="n">
-        <v>4121.58</v>
+        <v>4134.57</v>
       </c>
       <c r="M48" t="n">
-        <v>4280.65</v>
+        <v>4313.75</v>
       </c>
       <c r="N48" t="n">
-        <v>4439.73</v>
+        <v>4492.92</v>
       </c>
       <c r="O48" t="n">
-        <v>4386.7</v>
+        <v>4461.2</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4565,46 +4559,46 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4081</v>
+        <v>4106.6</v>
       </c>
       <c r="C49" t="n">
-        <v>4091.2</v>
+        <v>4112.5</v>
       </c>
       <c r="D49" t="n">
-        <v>3964.2</v>
+        <v>3963</v>
       </c>
       <c r="E49" t="n">
-        <v>4012.7</v>
+        <v>4018.8</v>
       </c>
       <c r="F49" t="n">
-        <v>-91.40000000000001</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0223</v>
+        <v>-0.0231</v>
       </c>
       <c r="H49" t="n">
-        <v>127</v>
+        <v>149.5</v>
       </c>
       <c r="I49" t="n">
-        <v>3906.3</v>
+        <v>3849.5</v>
       </c>
       <c r="J49" t="n">
-        <v>3946.27</v>
+        <v>3925.55</v>
       </c>
       <c r="K49" t="n">
-        <v>4030.75</v>
+        <v>4022.2</v>
       </c>
       <c r="L49" t="n">
-        <v>4115.23</v>
+        <v>4118.85</v>
       </c>
       <c r="M49" t="n">
-        <v>4177.45</v>
+        <v>4205.2</v>
       </c>
       <c r="N49" t="n">
-        <v>4239.68</v>
+        <v>4291.55</v>
       </c>
       <c r="O49" t="n">
-        <v>4346.4</v>
+        <v>4398.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4645,46 +4639,46 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4003.4</v>
+        <v>4005.6</v>
       </c>
       <c r="C50" t="n">
-        <v>4152.1</v>
+        <v>4171.4</v>
       </c>
       <c r="D50" t="n">
-        <v>3999.7</v>
+        <v>3986.5</v>
       </c>
       <c r="E50" t="n">
-        <v>4067.6</v>
+        <v>4070.8</v>
       </c>
       <c r="F50" t="n">
-        <v>54.9</v>
+        <v>52</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0137</v>
+        <v>0.0129</v>
       </c>
       <c r="H50" t="n">
-        <v>152.4</v>
+        <v>184.9</v>
       </c>
       <c r="I50" t="n">
-        <v>3837.2</v>
+        <v>3813.5</v>
       </c>
       <c r="J50" t="n">
-        <v>3878.2</v>
+        <v>3859.83</v>
       </c>
       <c r="K50" t="n">
-        <v>3949.2</v>
+        <v>3944.05</v>
       </c>
       <c r="L50" t="n">
-        <v>4020.2</v>
+        <v>4028.28</v>
       </c>
       <c r="M50" t="n">
-        <v>4076.2</v>
+        <v>4093.55</v>
       </c>
       <c r="N50" t="n">
-        <v>4132.2</v>
+        <v>4158.83</v>
       </c>
       <c r="O50" t="n">
-        <v>4218.2</v>
+        <v>4262</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4731,46 +4725,46 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4090.1</v>
+        <v>4097.5</v>
       </c>
       <c r="C51" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D51" t="n">
-        <v>4017.9</v>
+        <v>3993.8</v>
       </c>
       <c r="E51" t="n">
-        <v>4049.1</v>
+        <v>4107</v>
       </c>
       <c r="F51" t="n">
-        <v>-18.5</v>
+        <v>36.2</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0045</v>
+        <v>0.0089</v>
       </c>
       <c r="H51" t="n">
-        <v>100.6</v>
+        <v>176.9</v>
       </c>
       <c r="I51" t="n">
-        <v>3847.3</v>
+        <v>3801.6</v>
       </c>
       <c r="J51" t="n">
-        <v>3911.05</v>
+        <v>3881.83</v>
       </c>
       <c r="K51" t="n">
-        <v>3991.4</v>
+        <v>3978.35</v>
       </c>
       <c r="L51" t="n">
-        <v>4071.75</v>
+        <v>4074.88</v>
       </c>
       <c r="M51" t="n">
-        <v>4143.8</v>
+        <v>4163.25</v>
       </c>
       <c r="N51" t="n">
-        <v>4215.85</v>
+        <v>4251.62</v>
       </c>
       <c r="O51" t="n">
-        <v>4304.5</v>
+        <v>4356.3</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4781,13 +4775,15 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4802,7 +4798,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -4813,46 +4809,46 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4083.4</v>
+        <v>4135.2</v>
       </c>
       <c r="C52" t="n">
-        <v>4371.5</v>
+        <v>4432.3</v>
       </c>
       <c r="D52" t="n">
-        <v>4026.5</v>
+        <v>4074</v>
       </c>
       <c r="E52" t="n">
-        <v>4340.7</v>
+        <v>4399.7</v>
       </c>
       <c r="F52" t="n">
-        <v>291.6</v>
+        <v>292.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0713</v>
       </c>
       <c r="H52" t="n">
-        <v>345</v>
+        <v>358.3</v>
       </c>
       <c r="I52" t="n">
-        <v>3917.3</v>
+        <v>3816.9</v>
       </c>
       <c r="J52" t="n">
-        <v>3938.95</v>
+        <v>3942.47</v>
       </c>
       <c r="K52" t="n">
-        <v>3998.8</v>
+        <v>4018.55</v>
       </c>
       <c r="L52" t="n">
-        <v>4058.65</v>
+        <v>4094.63</v>
       </c>
       <c r="M52" t="n">
-        <v>4099.4</v>
+        <v>4195.45</v>
       </c>
       <c r="N52" t="n">
-        <v>4140.15</v>
+        <v>4296.28</v>
       </c>
       <c r="O52" t="n">
-        <v>4219.1</v>
+        <v>4347.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4897,46 +4893,46 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4336.1</v>
+        <v>4400</v>
       </c>
       <c r="C53" t="n">
-        <v>4445</v>
+        <v>4509.1</v>
       </c>
       <c r="D53" t="n">
-        <v>4315</v>
+        <v>4365.5</v>
       </c>
       <c r="E53" t="n">
-        <v>4380.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F53" t="n">
-        <v>39.7</v>
+        <v>37.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>130</v>
+        <v>143.6</v>
       </c>
       <c r="I53" t="n">
-        <v>3681.5</v>
+        <v>3715.7</v>
       </c>
       <c r="J53" t="n">
-        <v>4066.55</v>
+        <v>4114.68</v>
       </c>
       <c r="K53" t="n">
-        <v>4168.2</v>
+        <v>4220.55</v>
       </c>
       <c r="L53" t="n">
-        <v>4269.85</v>
+        <v>4326.43</v>
       </c>
       <c r="M53" t="n">
-        <v>4513.2</v>
+        <v>4578.85</v>
       </c>
       <c r="N53" t="n">
-        <v>4756.55</v>
+        <v>4831.28</v>
       </c>
       <c r="O53" t="n">
-        <v>4716.5</v>
+        <v>4790.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4975,46 +4971,46 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4394.8</v>
+        <v>4440</v>
       </c>
       <c r="C54" t="n">
-        <v>4624.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D54" t="n">
-        <v>4327.6</v>
+        <v>4378</v>
       </c>
       <c r="E54" t="n">
-        <v>4624.1</v>
+        <v>4680.6</v>
       </c>
       <c r="F54" t="n">
-        <v>243.7</v>
+        <v>243.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0556</v>
+        <v>0.0548</v>
       </c>
       <c r="H54" t="n">
-        <v>296.5</v>
+        <v>312.4</v>
       </c>
       <c r="I54" t="n">
-        <v>4185</v>
+        <v>4221.9</v>
       </c>
       <c r="J54" t="n">
-        <v>4250.6</v>
+        <v>4293.7</v>
       </c>
       <c r="K54" t="n">
-        <v>4315.4</v>
+        <v>4365.5</v>
       </c>
       <c r="L54" t="n">
-        <v>4380.2</v>
+        <v>4437.3</v>
       </c>
       <c r="M54" t="n">
-        <v>4445.4</v>
+        <v>4509.1</v>
       </c>
       <c r="N54" t="n">
-        <v>4510.6</v>
+        <v>4580.9</v>
       </c>
       <c r="O54" t="n">
-        <v>4575</v>
+        <v>4652.7</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5059,46 +5055,46 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4638</v>
+        <v>4673.4</v>
       </c>
       <c r="C55" t="n">
-        <v>4670.9</v>
+        <v>4755</v>
       </c>
       <c r="D55" t="n">
-        <v>4451.8</v>
+        <v>4495</v>
       </c>
       <c r="E55" t="n">
-        <v>4478.1</v>
+        <v>4529.9</v>
       </c>
       <c r="F55" t="n">
-        <v>-146</v>
+        <v>-150.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0316</v>
+        <v>-0.0322</v>
       </c>
       <c r="H55" t="n">
-        <v>219.1</v>
+        <v>260</v>
       </c>
       <c r="I55" t="n">
-        <v>4031.1</v>
+        <v>4065.6</v>
       </c>
       <c r="J55" t="n">
-        <v>4401.73</v>
+        <v>4441.4</v>
       </c>
       <c r="K55" t="n">
-        <v>4475.85</v>
+        <v>4524.4</v>
       </c>
       <c r="L55" t="n">
-        <v>4549.98</v>
+        <v>4607.4</v>
       </c>
       <c r="M55" t="n">
-        <v>4772.35</v>
+        <v>4836.8</v>
       </c>
       <c r="N55" t="n">
-        <v>4994.73</v>
+        <v>5066.2</v>
       </c>
       <c r="O55" t="n">
-        <v>4920.6</v>
+        <v>5002.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5143,46 +5139,46 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4430</v>
+        <v>4483.2</v>
       </c>
       <c r="C56" t="n">
-        <v>4510</v>
+        <v>4558.5</v>
       </c>
       <c r="D56" t="n">
-        <v>4292.2</v>
+        <v>4329.2</v>
       </c>
       <c r="E56" t="n">
-        <v>4429.8</v>
+        <v>4476.6</v>
       </c>
       <c r="F56" t="n">
-        <v>-48.3</v>
+        <v>-53.3</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0108</v>
+        <v>-0.0118</v>
       </c>
       <c r="H56" t="n">
-        <v>217.8</v>
+        <v>229.3</v>
       </c>
       <c r="I56" t="n">
-        <v>4232.7</v>
+        <v>4235</v>
       </c>
       <c r="J56" t="n">
-        <v>4217.38</v>
+        <v>4222.35</v>
       </c>
       <c r="K56" t="n">
-        <v>4368.55</v>
+        <v>4399.9</v>
       </c>
       <c r="L56" t="n">
-        <v>4519.72</v>
+        <v>4577.45</v>
       </c>
       <c r="M56" t="n">
-        <v>4587.65</v>
+        <v>4659.9</v>
       </c>
       <c r="N56" t="n">
-        <v>4655.58</v>
+        <v>4742.35</v>
       </c>
       <c r="O56" t="n">
-        <v>4890</v>
+        <v>5015</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5227,46 +5223,46 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4391.9</v>
+        <v>4466.5</v>
       </c>
       <c r="C57" t="n">
-        <v>4444.9</v>
+        <v>4488.8</v>
       </c>
       <c r="D57" t="n">
-        <v>4330.7</v>
+        <v>4333</v>
       </c>
       <c r="E57" t="n">
         <v>4408.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-20.9</v>
+        <v>-67.7</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0047</v>
+        <v>-0.0151</v>
       </c>
       <c r="H57" t="n">
-        <v>114.2</v>
+        <v>155.8</v>
       </c>
       <c r="I57" t="n">
-        <v>4074.4</v>
+        <v>4099.9</v>
       </c>
       <c r="J57" t="n">
-        <v>4226.35</v>
+        <v>4263.68</v>
       </c>
       <c r="K57" t="n">
-        <v>4320.9</v>
+        <v>4361.95</v>
       </c>
       <c r="L57" t="n">
-        <v>4415.45</v>
+        <v>4460.23</v>
       </c>
       <c r="M57" t="n">
-        <v>4538.7</v>
+        <v>4591.25</v>
       </c>
       <c r="N57" t="n">
-        <v>4661.95</v>
+        <v>4722.27</v>
       </c>
       <c r="O57" t="n">
-        <v>4727.8</v>
+        <v>4787.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5274,12 +5270,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5318,45 +5316,43 @@
         <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4343.2</v>
+        <v>4333.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-65.7</v>
+        <v>-75.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.0171</v>
       </c>
       <c r="H58" t="n">
         <v>103.8</v>
       </c>
       <c r="I58" t="n">
-        <v>4216.5</v>
+        <v>4177.2</v>
       </c>
       <c r="J58" t="n">
-        <v>4305.25</v>
+        <v>4252.1</v>
       </c>
       <c r="K58" t="n">
-        <v>4351.8</v>
+        <v>4331</v>
       </c>
       <c r="L58" t="n">
-        <v>4398.35</v>
+        <v>4409.9</v>
       </c>
       <c r="M58" t="n">
-        <v>4466</v>
+        <v>4486.8</v>
       </c>
       <c r="N58" t="n">
-        <v>4533.65</v>
+        <v>4563.7</v>
       </c>
       <c r="O58" t="n">
-        <v>4559.1</v>
+        <v>4644.6</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
@@ -5398,19 +5394,19 @@
         <v>4189.2</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4238.55</v>
+        <v>4223.85</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4291.3</v>
+        <v>4281.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4344.05</v>
+        <v>4339.15</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4395.1</v>
+        <v>4385.3</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4446.15</v>
+        <v>4431.45</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4500.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5316,13 +5316,13 @@
         <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4333.4</v>
+        <v>4324.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-75.5</v>
+        <v>-84</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0171</v>
+        <v>-0.0191</v>
       </c>
       <c r="H58" t="n">
         <v>103.8</v>
@@ -5394,19 +5394,19 @@
         <v>4189.2</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4223.85</v>
+        <v>4211.1</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4281.5</v>
+        <v>4273</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4339.15</v>
+        <v>4334.9</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4385.3</v>
+        <v>4376.8</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4431.45</v>
+        <v>4418.7</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4500.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5316,13 +5316,13 @@
         <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4324.9</v>
+        <v>4371</v>
       </c>
       <c r="F58" t="n">
-        <v>-84</v>
+        <v>-37.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0191</v>
+        <v>-0.0086</v>
       </c>
       <c r="H58" t="n">
         <v>103.8</v>
@@ -5356,12 +5356,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5394,19 +5394,19 @@
         <v>4189.2</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4211.1</v>
+        <v>4280.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4273</v>
+        <v>4319.1</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4334.9</v>
+        <v>4357.95</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4376.8</v>
+        <v>4422.9</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4418.7</v>
+        <v>4487.85</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4500.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5316,13 +5316,13 @@
         <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4371</v>
+        <v>4389.8</v>
       </c>
       <c r="F58" t="n">
-        <v>-37.9</v>
+        <v>-19.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0086</v>
+        <v>-0.0043</v>
       </c>
       <c r="H58" t="n">
         <v>103.8</v>
@@ -5394,19 +5394,19 @@
         <v>4189.2</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4280.25</v>
+        <v>4308.45</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4319.1</v>
+        <v>4337.9</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4357.95</v>
+        <v>4367.35</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4422.9</v>
+        <v>4441.7</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4487.85</v>
+        <v>4516.05</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4500.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5316,13 +5316,13 @@
         <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4389.8</v>
+        <v>4384.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-19.1</v>
+        <v>-24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0054</v>
       </c>
       <c r="H58" t="n">
         <v>103.8</v>
@@ -5394,19 +5394,19 @@
         <v>4189.2</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4308.45</v>
+        <v>4301.1</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4337.9</v>
+        <v>4333</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4367.35</v>
+        <v>4364.9</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4441.7</v>
+        <v>4436.8</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4516.05</v>
+        <v>4508.7</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4500.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5316,13 +5316,13 @@
         <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4384.9</v>
+        <v>4387.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-24</v>
+        <v>-21.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0054</v>
+        <v>-0.0049</v>
       </c>
       <c r="H58" t="n">
         <v>103.8</v>
@@ -5394,19 +5394,19 @@
         <v>4189.2</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4301.1</v>
+        <v>4305</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4333</v>
+        <v>4335.6</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4364.9</v>
+        <v>4366.2</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4436.8</v>
+        <v>4439.4</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4508.7</v>
+        <v>4512.6</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4500.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5316,13 +5316,13 @@
         <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4387.5</v>
+        <v>4296.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-21.4</v>
+        <v>-112.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0254</v>
       </c>
       <c r="H58" t="n">
         <v>103.8</v>
@@ -5356,12 +5356,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5394,19 +5394,19 @@
         <v>4189.2</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4305</v>
+        <v>4168.8</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4335.6</v>
+        <v>4244.8</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4366.2</v>
+        <v>4320.8</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4439.4</v>
+        <v>4348.6</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4512.6</v>
+        <v>4376.4</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4500.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5316,13 +5316,13 @@
         <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4296.7</v>
+        <v>4318.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-112.2</v>
+        <v>-90.40000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0254</v>
+        <v>-0.0205</v>
       </c>
       <c r="H58" t="n">
         <v>103.8</v>
@@ -5394,19 +5394,19 @@
         <v>4189.2</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4168.8</v>
+        <v>4201.5</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4244.8</v>
+        <v>4266.6</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4320.8</v>
+        <v>4331.7</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4348.6</v>
+        <v>4370.4</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4376.4</v>
+        <v>4409.1</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4500.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5310,22 +5310,22 @@
         <v>4375</v>
       </c>
       <c r="C58" t="n">
-        <v>4396.8</v>
+        <v>4413.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4293</v>
+        <v>4273.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4318.5</v>
+        <v>4382.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-90.40000000000001</v>
+        <v>-26.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0205</v>
+        <v>-0.0061</v>
       </c>
       <c r="H58" t="n">
-        <v>103.8</v>
+        <v>139.8</v>
       </c>
       <c r="I58" t="n">
         <v>4177.2</v>
@@ -5356,12 +5356,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5391,25 +5391,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>4189.2</v>
+        <v>4133.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4201.5</v>
+        <v>4261.9</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4266.6</v>
+        <v>4312.3</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4331.7</v>
+        <v>4362.7</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4370.4</v>
+        <v>4452.1</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4409.1</v>
+        <v>4541.5</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>4500.6</v>
+        <v>4552.9</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5316,13 +5316,13 @@
         <v>4273.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4382.2</v>
+        <v>4383.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-26.7</v>
+        <v>-25.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0059</v>
       </c>
       <c r="H58" t="n">
         <v>139.8</v>
@@ -5394,19 +5394,19 @@
         <v>4133.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>4261.9</v>
+        <v>4263.25</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>4312.3</v>
+        <v>4313.2</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>4362.7</v>
+        <v>4363.15</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>4452.1</v>
+        <v>4453</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>4541.5</v>
+        <v>4542.85</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>4552.9</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,31 +659,35 @@
         <v>70</v>
       </c>
       <c r="I2" t="n">
-        <v>3327.2</v>
+        <v>3360.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3325.78</v>
+        <v>3363.68</v>
       </c>
       <c r="K2" t="n">
-        <v>3358.45</v>
+        <v>3374.05</v>
       </c>
       <c r="L2" t="n">
-        <v>3391.13</v>
+        <v>3384.43</v>
       </c>
       <c r="M2" t="n">
-        <v>3406.75</v>
+        <v>3391.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3422.38</v>
+        <v>3397.88</v>
       </c>
       <c r="O2" t="n">
-        <v>3472.1</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>3411.9</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -709,12 +706,14 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
@@ -722,7 +721,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -5316,13 +5315,13 @@
         <v>4273.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4383.1</v>
+        <v>4391.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-25.8</v>
+        <v>-17.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0059</v>
+        <v>-0.0039</v>
       </c>
       <c r="H58" t="n">
         <v>139.8</v>
@@ -5382,34 +5381,6 @@
         <is>
           <t>強警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>4133.5</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>4263.25</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>4313.2</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>4363.15</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>4453</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>4542.85</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>4552.9</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5315,13 +5315,13 @@
         <v>4273.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4391.6</v>
+        <v>4395.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-17.3</v>
+        <v>-13.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.003</v>
       </c>
       <c r="H58" t="n">
         <v>139.8</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,144 +634,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3382.4</v>
+        <v>3417.6</v>
       </c>
       <c r="C2" t="n">
-        <v>3423.4</v>
+        <v>3518.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3353.4</v>
+        <v>3396.1</v>
       </c>
       <c r="E2" t="n">
-        <v>3418.5</v>
+        <v>3516.1</v>
       </c>
       <c r="F2" t="n">
-        <v>35.9</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0286</v>
       </c>
       <c r="H2" t="n">
-        <v>70</v>
+        <v>122.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3360.6</v>
+        <v>3283.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3363.68</v>
+        <v>3363.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3374.05</v>
+        <v>3383.5</v>
       </c>
       <c r="L2" t="n">
-        <v>3384.43</v>
+        <v>3403.45</v>
       </c>
       <c r="M2" t="n">
-        <v>3391.15</v>
+        <v>3453.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3397.88</v>
+        <v>3503.55</v>
       </c>
       <c r="O2" t="n">
-        <v>3411.9</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>3493.4</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3417.6</v>
+        <v>3517.9</v>
       </c>
       <c r="C3" t="n">
-        <v>3518.5</v>
+        <v>3655.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3396.1</v>
+        <v>3506</v>
       </c>
       <c r="E3" t="n">
-        <v>3516.1</v>
+        <v>3653.3</v>
       </c>
       <c r="F3" t="n">
-        <v>97.59999999999999</v>
+        <v>137.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0286</v>
+        <v>0.039</v>
       </c>
       <c r="H3" t="n">
-        <v>122.4</v>
+        <v>149.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3283.4</v>
+        <v>3273.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3363.55</v>
+        <v>3423.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3383.5</v>
+        <v>3454.9</v>
       </c>
       <c r="L3" t="n">
-        <v>3403.45</v>
+        <v>3486.7</v>
       </c>
       <c r="M3" t="n">
-        <v>3453.5</v>
+        <v>3577.3</v>
       </c>
       <c r="N3" t="n">
-        <v>3503.55</v>
+        <v>3667.9</v>
       </c>
       <c r="O3" t="n">
-        <v>3493.4</v>
+        <v>3640.9</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -792,14 +782,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
@@ -812,50 +800,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3517.9</v>
+        <v>3635</v>
       </c>
       <c r="C4" t="n">
-        <v>3655.5</v>
+        <v>3715.2</v>
       </c>
       <c r="D4" t="n">
-        <v>3506</v>
+        <v>3621.7</v>
       </c>
       <c r="E4" t="n">
-        <v>3653.3</v>
+        <v>3686.4</v>
       </c>
       <c r="F4" t="n">
-        <v>137.2</v>
+        <v>33.1</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.039</v>
+        <v>0.0091</v>
       </c>
       <c r="H4" t="n">
-        <v>149.5</v>
+        <v>93.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3273.7</v>
+        <v>3356.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3423.1</v>
+        <v>3540.08</v>
       </c>
       <c r="K4" t="n">
-        <v>3454.9</v>
+        <v>3578.55</v>
       </c>
       <c r="L4" t="n">
-        <v>3486.7</v>
+        <v>3617.03</v>
       </c>
       <c r="M4" t="n">
-        <v>3577.3</v>
+        <v>3728.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3667.9</v>
+        <v>3839.08</v>
       </c>
       <c r="O4" t="n">
-        <v>3640.9</v>
+        <v>3805</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -873,16 +861,14 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -894,50 +880,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3635</v>
+        <v>3680.2</v>
       </c>
       <c r="C5" t="n">
-        <v>3715.2</v>
+        <v>3744</v>
       </c>
       <c r="D5" t="n">
-        <v>3621.7</v>
+        <v>3660.5</v>
       </c>
       <c r="E5" t="n">
-        <v>3686.4</v>
+        <v>3705.8</v>
       </c>
       <c r="F5" t="n">
-        <v>33.1</v>
+        <v>19.4</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0053</v>
       </c>
       <c r="H5" t="n">
-        <v>93.5</v>
+        <v>83.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3356.5</v>
+        <v>3528.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3540.08</v>
+        <v>3601.87</v>
       </c>
       <c r="K5" t="n">
-        <v>3578.55</v>
+        <v>3639.65</v>
       </c>
       <c r="L5" t="n">
-        <v>3617.03</v>
+        <v>3677.42</v>
       </c>
       <c r="M5" t="n">
-        <v>3728.05</v>
+        <v>3733.15</v>
       </c>
       <c r="N5" t="n">
-        <v>3839.08</v>
+        <v>3788.87</v>
       </c>
       <c r="O5" t="n">
-        <v>3805</v>
+        <v>3808.7</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -974,50 +960,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3680.2</v>
+        <v>3721.3</v>
       </c>
       <c r="C6" t="n">
-        <v>3744</v>
+        <v>3824.6</v>
       </c>
       <c r="D6" t="n">
-        <v>3660.5</v>
+        <v>3718.1</v>
       </c>
       <c r="E6" t="n">
-        <v>3705.8</v>
+        <v>3809</v>
       </c>
       <c r="F6" t="n">
-        <v>19.4</v>
+        <v>103.2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0278</v>
       </c>
       <c r="H6" t="n">
-        <v>83.5</v>
+        <v>106.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3528.2</v>
+        <v>3577</v>
       </c>
       <c r="J6" t="n">
-        <v>3601.87</v>
+        <v>3624.08</v>
       </c>
       <c r="K6" t="n">
-        <v>3639.65</v>
+        <v>3664.05</v>
       </c>
       <c r="L6" t="n">
-        <v>3677.42</v>
+        <v>3704.03</v>
       </c>
       <c r="M6" t="n">
-        <v>3733.15</v>
+        <v>3747.55</v>
       </c>
       <c r="N6" t="n">
-        <v>3788.87</v>
+        <v>3791.08</v>
       </c>
       <c r="O6" t="n">
-        <v>3808.7</v>
+        <v>3827.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1035,11 +1021,13 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1054,50 +1042,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3721.3</v>
+        <v>3788.8</v>
       </c>
       <c r="C7" t="n">
-        <v>3824.6</v>
+        <v>3923.3</v>
       </c>
       <c r="D7" t="n">
-        <v>3718.1</v>
+        <v>3785.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3809</v>
+        <v>3908.9</v>
       </c>
       <c r="F7" t="n">
-        <v>103.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0262</v>
       </c>
       <c r="H7" t="n">
-        <v>106.5</v>
+        <v>137.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3577</v>
+        <v>3611.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3624.08</v>
+        <v>3721.32</v>
       </c>
       <c r="K7" t="n">
-        <v>3664.05</v>
+        <v>3755.75</v>
       </c>
       <c r="L7" t="n">
-        <v>3704.03</v>
+        <v>3790.18</v>
       </c>
       <c r="M7" t="n">
-        <v>3747.55</v>
+        <v>3862.25</v>
       </c>
       <c r="N7" t="n">
-        <v>3791.08</v>
+        <v>3934.32</v>
       </c>
       <c r="O7" t="n">
-        <v>3827.5</v>
+        <v>3931.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1118,13 +1106,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1136,50 +1124,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3788.8</v>
+        <v>3913.5</v>
       </c>
       <c r="C8" t="n">
-        <v>3923.3</v>
+        <v>4081</v>
       </c>
       <c r="D8" t="n">
-        <v>3785.5</v>
+        <v>3909.2</v>
       </c>
       <c r="E8" t="n">
-        <v>3908.9</v>
+        <v>4000.4</v>
       </c>
       <c r="F8" t="n">
-        <v>99.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0262</v>
+        <v>0.0234</v>
       </c>
       <c r="H8" t="n">
-        <v>137.8</v>
+        <v>171.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3611.6</v>
+        <v>3647.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3721.32</v>
+        <v>3798.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3755.75</v>
+        <v>3840</v>
       </c>
       <c r="L8" t="n">
-        <v>3790.18</v>
+        <v>3881.65</v>
       </c>
       <c r="M8" t="n">
-        <v>3862.25</v>
+        <v>3977.8</v>
       </c>
       <c r="N8" t="n">
-        <v>3934.32</v>
+        <v>4073.95</v>
       </c>
       <c r="O8" t="n">
-        <v>3931.1</v>
+        <v>4061.1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1197,15 +1185,17 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
@@ -1218,50 +1208,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3913.5</v>
+        <v>4018.3</v>
       </c>
       <c r="C9" t="n">
-        <v>4081</v>
+        <v>4392</v>
       </c>
       <c r="D9" t="n">
-        <v>3909.2</v>
+        <v>4011.3</v>
       </c>
       <c r="E9" t="n">
-        <v>4000.4</v>
+        <v>4213.3</v>
       </c>
       <c r="F9" t="n">
-        <v>91.5</v>
+        <v>212.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0532</v>
       </c>
       <c r="H9" t="n">
-        <v>171.8</v>
+        <v>380.7</v>
       </c>
       <c r="I9" t="n">
-        <v>3647.7</v>
+        <v>3737.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3798.35</v>
+        <v>3831.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3840</v>
+        <v>3914.5</v>
       </c>
       <c r="L9" t="n">
-        <v>3881.65</v>
+        <v>3997.75</v>
       </c>
       <c r="M9" t="n">
-        <v>3977.8</v>
+        <v>4086.3</v>
       </c>
       <c r="N9" t="n">
-        <v>4073.95</v>
+        <v>4174.85</v>
       </c>
       <c r="O9" t="n">
-        <v>4061.1</v>
+        <v>4252.8</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,12 +1269,12 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V9" s="8" t="inlineStr">
@@ -1302,50 +1292,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4018.3</v>
+        <v>4269</v>
       </c>
       <c r="C10" t="n">
-        <v>4392</v>
+        <v>4398</v>
       </c>
       <c r="D10" t="n">
-        <v>4011.3</v>
+        <v>4021.2</v>
       </c>
       <c r="E10" t="n">
-        <v>4213.3</v>
+        <v>4137.8</v>
       </c>
       <c r="F10" t="n">
-        <v>212.9</v>
+        <v>-75.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0532</v>
+        <v>-0.0179</v>
       </c>
       <c r="H10" t="n">
-        <v>380.7</v>
+        <v>376.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3737.4</v>
+        <v>3630.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3831.25</v>
+        <v>3838.42</v>
       </c>
       <c r="K10" t="n">
-        <v>3914.5</v>
+        <v>4022.95</v>
       </c>
       <c r="L10" t="n">
-        <v>3997.75</v>
+        <v>4207.47</v>
       </c>
       <c r="M10" t="n">
-        <v>4086.3</v>
+        <v>4403.65</v>
       </c>
       <c r="N10" t="n">
-        <v>4174.85</v>
+        <v>4599.82</v>
       </c>
       <c r="O10" t="n">
-        <v>4252.8</v>
+        <v>4772.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,83 +1343,83 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4269</v>
+        <v>4103.2</v>
       </c>
       <c r="C11" t="n">
-        <v>4398</v>
+        <v>4123.8</v>
       </c>
       <c r="D11" t="n">
-        <v>4021.2</v>
+        <v>3901.3</v>
       </c>
       <c r="E11" t="n">
-        <v>4137.8</v>
+        <v>3996.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-75.5</v>
+        <v>-141.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0179</v>
+        <v>-0.0341</v>
       </c>
       <c r="H11" t="n">
-        <v>376.8</v>
+        <v>222.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3630.6</v>
+        <v>3644.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3838.42</v>
+        <v>3725.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4022.95</v>
+        <v>3949.4</v>
       </c>
       <c r="L11" t="n">
-        <v>4207.47</v>
+        <v>4173.7</v>
       </c>
       <c r="M11" t="n">
-        <v>4403.65</v>
+        <v>4326.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4599.82</v>
+        <v>4478.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4772.7</v>
+        <v>4774.8</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1439,12 +1429,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1463,57 +1453,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4103.2</v>
+        <v>4001</v>
       </c>
       <c r="C12" t="n">
-        <v>4123.8</v>
+        <v>4043.1</v>
       </c>
       <c r="D12" t="n">
-        <v>3901.3</v>
+        <v>3935.7</v>
       </c>
       <c r="E12" t="n">
-        <v>3996.5</v>
+        <v>4009.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-141.3</v>
+        <v>13.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0341</v>
+        <v>0.0033</v>
       </c>
       <c r="H12" t="n">
-        <v>222.5</v>
+        <v>107.4</v>
       </c>
       <c r="I12" t="n">
-        <v>3644.4</v>
+        <v>3678.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3725.1</v>
+        <v>3765.98</v>
       </c>
       <c r="K12" t="n">
-        <v>3949.4</v>
+        <v>3885.25</v>
       </c>
       <c r="L12" t="n">
-        <v>4173.7</v>
+        <v>4004.52</v>
       </c>
       <c r="M12" t="n">
-        <v>4326.2</v>
+        <v>4107.75</v>
       </c>
       <c r="N12" t="n">
-        <v>4478.7</v>
+        <v>4210.97</v>
       </c>
       <c r="O12" t="n">
-        <v>4774.8</v>
+        <v>4346.3</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,14 +1511,12 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1547,57 +1535,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4001</v>
+        <v>4007.2</v>
       </c>
       <c r="C13" t="n">
-        <v>4043.1</v>
+        <v>4250</v>
       </c>
       <c r="D13" t="n">
-        <v>3935.7</v>
+        <v>4004.2</v>
       </c>
       <c r="E13" t="n">
-        <v>4009.8</v>
+        <v>4094.2</v>
       </c>
       <c r="F13" t="n">
-        <v>13.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.021</v>
       </c>
       <c r="H13" t="n">
-        <v>107.4</v>
+        <v>245.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3678.8</v>
+        <v>3828.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3765.98</v>
+        <v>3912.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3885.25</v>
+        <v>3956.1</v>
       </c>
       <c r="L13" t="n">
-        <v>4004.52</v>
+        <v>3999.6</v>
       </c>
       <c r="M13" t="n">
-        <v>4107.75</v>
+        <v>4063.5</v>
       </c>
       <c r="N13" t="n">
-        <v>4210.97</v>
+        <v>4127.4</v>
       </c>
       <c r="O13" t="n">
-        <v>4346.3</v>
+        <v>4150.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1610,76 +1598,78 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4007.2</v>
+        <v>4084.4</v>
       </c>
       <c r="C14" t="n">
-        <v>4250</v>
+        <v>4134.3</v>
       </c>
       <c r="D14" t="n">
-        <v>4004.2</v>
+        <v>3997.4</v>
       </c>
       <c r="E14" t="n">
-        <v>4094.2</v>
+        <v>4079.5</v>
       </c>
       <c r="F14" t="n">
-        <v>84.40000000000001</v>
+        <v>-14.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.0036</v>
       </c>
       <c r="H14" t="n">
-        <v>245.8</v>
+        <v>136.9</v>
       </c>
       <c r="I14" t="n">
-        <v>3828.3</v>
+        <v>3758.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3912.6</v>
+        <v>3831.95</v>
       </c>
       <c r="K14" t="n">
-        <v>3956.1</v>
+        <v>3971.3</v>
       </c>
       <c r="L14" t="n">
-        <v>3999.6</v>
+        <v>4110.65</v>
       </c>
       <c r="M14" t="n">
-        <v>4063.5</v>
+        <v>4217.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4127.4</v>
+        <v>4323.55</v>
       </c>
       <c r="O14" t="n">
-        <v>4150.5</v>
+        <v>4495.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1690,80 +1680,78 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4084.4</v>
+        <v>4069.2</v>
       </c>
       <c r="C15" t="n">
-        <v>4134.3</v>
+        <v>4263.1</v>
       </c>
       <c r="D15" t="n">
-        <v>3997.4</v>
+        <v>4036.4</v>
       </c>
       <c r="E15" t="n">
-        <v>4079.5</v>
+        <v>4254.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.7</v>
+        <v>175.4</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.043</v>
       </c>
       <c r="H15" t="n">
-        <v>136.9</v>
+        <v>226.7</v>
       </c>
       <c r="I15" t="n">
-        <v>3758.4</v>
+        <v>3860.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3831.95</v>
+        <v>3949.43</v>
       </c>
       <c r="K15" t="n">
-        <v>3971.3</v>
+        <v>4011.05</v>
       </c>
       <c r="L15" t="n">
-        <v>4110.65</v>
+        <v>4072.67</v>
       </c>
       <c r="M15" t="n">
-        <v>4217.1</v>
+        <v>4147.95</v>
       </c>
       <c r="N15" t="n">
-        <v>4323.55</v>
+        <v>4223.22</v>
       </c>
       <c r="O15" t="n">
-        <v>4495.8</v>
+        <v>4271.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1774,78 +1762,80 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4069.2</v>
+        <v>4258.5</v>
       </c>
       <c r="C16" t="n">
-        <v>4263.1</v>
+        <v>4299.6</v>
       </c>
       <c r="D16" t="n">
-        <v>4036.4</v>
+        <v>4194</v>
       </c>
       <c r="E16" t="n">
-        <v>4254.9</v>
+        <v>4243</v>
       </c>
       <c r="F16" t="n">
-        <v>175.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.043</v>
+        <v>-0.0028</v>
       </c>
       <c r="H16" t="n">
-        <v>226.7</v>
+        <v>105.6</v>
       </c>
       <c r="I16" t="n">
-        <v>3860.5</v>
+        <v>3809.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3949.43</v>
+        <v>4080.77</v>
       </c>
       <c r="K16" t="n">
-        <v>4011.05</v>
+        <v>4141.55</v>
       </c>
       <c r="L16" t="n">
-        <v>4072.67</v>
+        <v>4202.32</v>
       </c>
       <c r="M16" t="n">
-        <v>4147.95</v>
+        <v>4368.25</v>
       </c>
       <c r="N16" t="n">
-        <v>4223.22</v>
+        <v>4534.18</v>
       </c>
       <c r="O16" t="n">
-        <v>4271.2</v>
+        <v>4489.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,78 +1848,76 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4258.5</v>
+        <v>4228.1</v>
       </c>
       <c r="C17" t="n">
-        <v>4299.6</v>
+        <v>4387.8</v>
       </c>
       <c r="D17" t="n">
-        <v>4194</v>
+        <v>4197.8</v>
       </c>
       <c r="E17" t="n">
-        <v>4243</v>
+        <v>4328.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.9</v>
+        <v>85.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0201</v>
       </c>
       <c r="H17" t="n">
-        <v>105.6</v>
+        <v>190</v>
       </c>
       <c r="I17" t="n">
-        <v>3809.7</v>
+        <v>4088.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4080.77</v>
+        <v>4135.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4141.55</v>
+        <v>4190.2</v>
       </c>
       <c r="L17" t="n">
-        <v>4202.32</v>
+        <v>4244.9</v>
       </c>
       <c r="M17" t="n">
-        <v>4368.25</v>
+        <v>4295.8</v>
       </c>
       <c r="N17" t="n">
-        <v>4534.18</v>
+        <v>4346.7</v>
       </c>
       <c r="O17" t="n">
-        <v>4489.8</v>
+        <v>4405.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,14 +1930,18 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1959,59 +1951,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4228.1</v>
+        <v>4330</v>
       </c>
       <c r="C18" t="n">
-        <v>4387.8</v>
+        <v>4409.5</v>
       </c>
       <c r="D18" t="n">
-        <v>4197.8</v>
+        <v>4297.4</v>
       </c>
       <c r="E18" t="n">
-        <v>4328.3</v>
+        <v>4387.3</v>
       </c>
       <c r="F18" t="n">
-        <v>85.3</v>
+        <v>59</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0136</v>
       </c>
       <c r="H18" t="n">
-        <v>190</v>
+        <v>112.1</v>
       </c>
       <c r="I18" t="n">
-        <v>4088.4</v>
+        <v>4007.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4135.5</v>
+        <v>4156.05</v>
       </c>
       <c r="K18" t="n">
-        <v>4190.2</v>
+        <v>4233.3</v>
       </c>
       <c r="L18" t="n">
-        <v>4244.9</v>
+        <v>4310.55</v>
       </c>
       <c r="M18" t="n">
-        <v>4295.8</v>
+        <v>4423.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4346.7</v>
+        <v>4536.05</v>
       </c>
       <c r="O18" t="n">
-        <v>4405.2</v>
+        <v>4577.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,13 +2017,11 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2050,50 +2036,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4330</v>
+        <v>4369.9</v>
       </c>
       <c r="C19" t="n">
-        <v>4409.5</v>
+        <v>4584</v>
       </c>
       <c r="D19" t="n">
-        <v>4297.4</v>
+        <v>4367.9</v>
       </c>
       <c r="E19" t="n">
-        <v>4387.3</v>
+        <v>4552.7</v>
       </c>
       <c r="F19" t="n">
-        <v>59</v>
+        <v>165.4</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0377</v>
       </c>
       <c r="H19" t="n">
-        <v>112.1</v>
+        <v>216.1</v>
       </c>
       <c r="I19" t="n">
-        <v>4007.8</v>
+        <v>4185.3</v>
       </c>
       <c r="J19" t="n">
-        <v>4156.05</v>
+        <v>4292.12</v>
       </c>
       <c r="K19" t="n">
-        <v>4233.3</v>
+        <v>4331.25</v>
       </c>
       <c r="L19" t="n">
-        <v>4310.55</v>
+        <v>4370.37</v>
       </c>
       <c r="M19" t="n">
-        <v>4423.3</v>
+        <v>4443.35</v>
       </c>
       <c r="N19" t="n">
-        <v>4536.05</v>
+        <v>4516.32</v>
       </c>
       <c r="O19" t="n">
-        <v>4577.8</v>
+        <v>4521.6</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2111,14 +2097,18 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2130,83 +2120,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4369.9</v>
+        <v>4568</v>
       </c>
       <c r="C20" t="n">
-        <v>4584</v>
+        <v>4581.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4367.9</v>
+        <v>4284.3</v>
       </c>
       <c r="E20" t="n">
-        <v>4552.7</v>
+        <v>4329.6</v>
       </c>
       <c r="F20" t="n">
-        <v>165.4</v>
+        <v>-223.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.049</v>
       </c>
       <c r="H20" t="n">
-        <v>216.1</v>
+        <v>297</v>
       </c>
       <c r="I20" t="n">
-        <v>4185.3</v>
+        <v>4151.8</v>
       </c>
       <c r="J20" t="n">
-        <v>4292.12</v>
+        <v>4374.98</v>
       </c>
       <c r="K20" t="n">
-        <v>4331.25</v>
+        <v>4444.65</v>
       </c>
       <c r="L20" t="n">
-        <v>4370.37</v>
+        <v>4514.33</v>
       </c>
       <c r="M20" t="n">
-        <v>4443.35</v>
+        <v>4660.75</v>
       </c>
       <c r="N20" t="n">
-        <v>4516.32</v>
+        <v>4807.18</v>
       </c>
       <c r="O20" t="n">
-        <v>4521.6</v>
+        <v>4800.1</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2214,72 +2202,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4568</v>
+        <v>4368.3</v>
       </c>
       <c r="C21" t="n">
-        <v>4581.3</v>
+        <v>4527</v>
       </c>
       <c r="D21" t="n">
-        <v>4284.3</v>
+        <v>4354.6</v>
       </c>
       <c r="E21" t="n">
-        <v>4329.6</v>
+        <v>4500.9</v>
       </c>
       <c r="F21" t="n">
-        <v>-223.1</v>
+        <v>171.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.049</v>
+        <v>0.0396</v>
       </c>
       <c r="H21" t="n">
-        <v>297</v>
+        <v>172.4</v>
       </c>
       <c r="I21" t="n">
-        <v>4151.8</v>
+        <v>3987.3</v>
       </c>
       <c r="J21" t="n">
-        <v>4374.98</v>
+        <v>3981</v>
       </c>
       <c r="K21" t="n">
-        <v>4444.65</v>
+        <v>4181.1</v>
       </c>
       <c r="L21" t="n">
-        <v>4514.33</v>
+        <v>4381.2</v>
       </c>
       <c r="M21" t="n">
-        <v>4660.75</v>
+        <v>4478.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4807.18</v>
+        <v>4575</v>
       </c>
       <c r="O21" t="n">
-        <v>4800.1</v>
+        <v>4878.3</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2291,55 +2277,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4368.3</v>
+        <v>4529.1</v>
       </c>
       <c r="C22" t="n">
-        <v>4527</v>
+        <v>4650.5</v>
       </c>
       <c r="D22" t="n">
-        <v>4354.6</v>
+        <v>4520.8</v>
       </c>
       <c r="E22" t="n">
-        <v>4500.9</v>
+        <v>4595.4</v>
       </c>
       <c r="F22" t="n">
-        <v>171.3</v>
+        <v>94.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.021</v>
       </c>
       <c r="H22" t="n">
-        <v>172.4</v>
+        <v>129.7</v>
       </c>
       <c r="I22" t="n">
-        <v>3987.3</v>
+        <v>4182.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3981</v>
+        <v>4358.55</v>
       </c>
       <c r="K22" t="n">
-        <v>4181.1</v>
+        <v>4414.7</v>
       </c>
       <c r="L22" t="n">
-        <v>4381.2</v>
+        <v>4470.85</v>
       </c>
       <c r="M22" t="n">
-        <v>4478.1</v>
+        <v>4587.1</v>
       </c>
       <c r="N22" t="n">
-        <v>4575</v>
+        <v>4703.35</v>
       </c>
       <c r="O22" t="n">
-        <v>4878.3</v>
+        <v>4699.4</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2373,57 +2363,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4529.1</v>
+        <v>4633.7</v>
       </c>
       <c r="C23" t="n">
-        <v>4650.5</v>
+        <v>4991.4</v>
       </c>
       <c r="D23" t="n">
-        <v>4520.8</v>
+        <v>4622.2</v>
       </c>
       <c r="E23" t="n">
-        <v>4595.4</v>
+        <v>4979.7</v>
       </c>
       <c r="F23" t="n">
-        <v>94.5</v>
+        <v>384.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.021</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>129.7</v>
+        <v>369.2</v>
       </c>
       <c r="I23" t="n">
-        <v>4182.2</v>
+        <v>4391.1</v>
       </c>
       <c r="J23" t="n">
-        <v>4358.55</v>
+        <v>4470.57</v>
       </c>
       <c r="K23" t="n">
-        <v>4414.7</v>
+        <v>4530.55</v>
       </c>
       <c r="L23" t="n">
-        <v>4470.85</v>
+        <v>4590.52</v>
       </c>
       <c r="M23" t="n">
-        <v>4587.1</v>
+        <v>4660.25</v>
       </c>
       <c r="N23" t="n">
-        <v>4703.35</v>
+        <v>4729.98</v>
       </c>
       <c r="O23" t="n">
-        <v>4699.4</v>
+        <v>4780.2</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2441,86 +2431,90 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4633.7</v>
+        <v>5013.4</v>
       </c>
       <c r="C24" t="n">
-        <v>4991.4</v>
+        <v>5586.2</v>
       </c>
       <c r="D24" t="n">
-        <v>4622.2</v>
+        <v>4700.4</v>
       </c>
       <c r="E24" t="n">
-        <v>4979.7</v>
+        <v>4745.1</v>
       </c>
       <c r="F24" t="n">
-        <v>384.3</v>
+        <v>-234.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.0471</v>
       </c>
       <c r="H24" t="n">
-        <v>369.2</v>
+        <v>885.8</v>
       </c>
       <c r="I24" t="n">
-        <v>4391.1</v>
+        <v>4253</v>
       </c>
       <c r="J24" t="n">
-        <v>4470.57</v>
+        <v>4696.95</v>
       </c>
       <c r="K24" t="n">
-        <v>4530.55</v>
+        <v>4795.1</v>
       </c>
       <c r="L24" t="n">
-        <v>4590.52</v>
+        <v>4893.25</v>
       </c>
       <c r="M24" t="n">
-        <v>4660.25</v>
+        <v>5164.3</v>
       </c>
       <c r="N24" t="n">
-        <v>4729.98</v>
+        <v>5435.35</v>
       </c>
       <c r="O24" t="n">
-        <v>4780.2</v>
+        <v>5360.6</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2535,7 +2529,7 @@
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W24" s="9" t="inlineStr">
@@ -2543,88 +2537,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5013.4</v>
+        <v>4816</v>
       </c>
       <c r="C25" t="n">
-        <v>5586.2</v>
+        <v>5113.9</v>
       </c>
       <c r="D25" t="n">
-        <v>4700.4</v>
+        <v>4423.2</v>
       </c>
       <c r="E25" t="n">
-        <v>4745.1</v>
+        <v>4979.8</v>
       </c>
       <c r="F25" t="n">
-        <v>-234.6</v>
+        <v>234.7</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0471</v>
+        <v>0.0495</v>
       </c>
       <c r="H25" t="n">
-        <v>885.8</v>
+        <v>690.7</v>
       </c>
       <c r="I25" t="n">
-        <v>4253</v>
+        <v>3814.6</v>
       </c>
       <c r="J25" t="n">
-        <v>4696.95</v>
+        <v>3660.2</v>
       </c>
       <c r="K25" t="n">
-        <v>4795.1</v>
+        <v>4302.2</v>
       </c>
       <c r="L25" t="n">
-        <v>4893.25</v>
+        <v>4944.2</v>
       </c>
       <c r="M25" t="n">
-        <v>5164.3</v>
+        <v>5188</v>
       </c>
       <c r="N25" t="n">
-        <v>5435.35</v>
+        <v>5431.8</v>
       </c>
       <c r="O25" t="n">
-        <v>5360.6</v>
+        <v>6472</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2633,57 +2621,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4816</v>
+        <v>5003.6</v>
       </c>
       <c r="C26" t="n">
-        <v>5113.9</v>
+        <v>5144.5</v>
       </c>
       <c r="D26" t="n">
-        <v>4423.2</v>
+        <v>4900</v>
       </c>
       <c r="E26" t="n">
-        <v>4979.8</v>
+        <v>5046.3</v>
       </c>
       <c r="F26" t="n">
-        <v>234.7</v>
+        <v>66.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0495</v>
+        <v>0.0134</v>
       </c>
       <c r="H26" t="n">
-        <v>690.7</v>
+        <v>244.5</v>
       </c>
       <c r="I26" t="n">
-        <v>3814.6</v>
+        <v>3732.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3660.2</v>
+        <v>4394.72</v>
       </c>
       <c r="K26" t="n">
-        <v>4302.2</v>
+        <v>4634.45</v>
       </c>
       <c r="L26" t="n">
-        <v>4944.2</v>
+        <v>4874.17</v>
       </c>
       <c r="M26" t="n">
-        <v>5188</v>
+        <v>5325.15</v>
       </c>
       <c r="N26" t="n">
-        <v>5431.8</v>
+        <v>5776.12</v>
       </c>
       <c r="O26" t="n">
-        <v>6472</v>
+        <v>5804.6</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2713,59 +2701,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5003.6</v>
+        <v>5050</v>
       </c>
       <c r="C27" t="n">
-        <v>5144.5</v>
+        <v>5131</v>
       </c>
       <c r="D27" t="n">
-        <v>4900</v>
+        <v>4854.2</v>
       </c>
       <c r="E27" t="n">
-        <v>5046.3</v>
+        <v>5080.9</v>
       </c>
       <c r="F27" t="n">
-        <v>66.5</v>
+        <v>34.6</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0069</v>
       </c>
       <c r="H27" t="n">
-        <v>244.5</v>
+        <v>276.8</v>
       </c>
       <c r="I27" t="n">
-        <v>3732.5</v>
+        <v>4655.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4394.72</v>
+        <v>4813.82</v>
       </c>
       <c r="K27" t="n">
-        <v>4634.45</v>
+        <v>4924.05</v>
       </c>
       <c r="L27" t="n">
-        <v>4874.17</v>
+        <v>5034.27</v>
       </c>
       <c r="M27" t="n">
-        <v>5325.15</v>
+        <v>5168.55</v>
       </c>
       <c r="N27" t="n">
-        <v>5776.12</v>
+        <v>5302.82</v>
       </c>
       <c r="O27" t="n">
-        <v>5804.6</v>
+        <v>5389</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2773,8 +2757,10 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
@@ -2795,55 +2781,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5050</v>
+        <v>5128.8</v>
       </c>
       <c r="C28" t="n">
-        <v>5131</v>
+        <v>5299</v>
       </c>
       <c r="D28" t="n">
-        <v>4854.2</v>
+        <v>5109.5</v>
       </c>
       <c r="E28" t="n">
-        <v>5080.9</v>
+        <v>5247.9</v>
       </c>
       <c r="F28" t="n">
-        <v>34.6</v>
+        <v>167</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0329</v>
       </c>
       <c r="H28" t="n">
-        <v>276.8</v>
+        <v>189.5</v>
       </c>
       <c r="I28" t="n">
-        <v>4655.5</v>
+        <v>4577.4</v>
       </c>
       <c r="J28" t="n">
-        <v>4813.82</v>
+        <v>4848.25</v>
       </c>
       <c r="K28" t="n">
-        <v>4924.05</v>
+        <v>4942.5</v>
       </c>
       <c r="L28" t="n">
-        <v>5034.27</v>
+        <v>5036.75</v>
       </c>
       <c r="M28" t="n">
-        <v>5168.55</v>
+        <v>5219.3</v>
       </c>
       <c r="N28" t="n">
-        <v>5302.82</v>
+        <v>5401.85</v>
       </c>
       <c r="O28" t="n">
-        <v>5389</v>
+        <v>5407.8</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2851,18 +2841,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2875,77 +2865,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5128.8</v>
+        <v>5360</v>
       </c>
       <c r="C29" t="n">
-        <v>5299</v>
+        <v>5434.1</v>
       </c>
       <c r="D29" t="n">
-        <v>5109.5</v>
+        <v>5005</v>
       </c>
       <c r="E29" t="n">
-        <v>5247.9</v>
+        <v>5158.7</v>
       </c>
       <c r="F29" t="n">
-        <v>167</v>
+        <v>-89.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0329</v>
+        <v>-0.017</v>
       </c>
       <c r="H29" t="n">
-        <v>189.5</v>
+        <v>429.1</v>
       </c>
       <c r="I29" t="n">
-        <v>4577.4</v>
+        <v>4920</v>
       </c>
       <c r="J29" t="n">
-        <v>4848.25</v>
+        <v>5080.22</v>
       </c>
       <c r="K29" t="n">
-        <v>4942.5</v>
+        <v>5153.15</v>
       </c>
       <c r="L29" t="n">
-        <v>5036.75</v>
+        <v>5226.07</v>
       </c>
       <c r="M29" t="n">
-        <v>5219.3</v>
+        <v>5342.65</v>
       </c>
       <c r="N29" t="n">
-        <v>5401.85</v>
+        <v>5459.22</v>
       </c>
       <c r="O29" t="n">
-        <v>5407.8</v>
+        <v>5488.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2959,63 +2949,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5360</v>
+        <v>5186.7</v>
       </c>
       <c r="C30" t="n">
-        <v>5434.1</v>
+        <v>5248.7</v>
       </c>
       <c r="D30" t="n">
-        <v>5005</v>
+        <v>5014.1</v>
       </c>
       <c r="E30" t="n">
-        <v>5158.7</v>
+        <v>5061.7</v>
       </c>
       <c r="F30" t="n">
-        <v>-89.2</v>
+        <v>-97</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0188</v>
       </c>
       <c r="H30" t="n">
-        <v>429.1</v>
+        <v>234.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4920</v>
+        <v>4575.9</v>
       </c>
       <c r="J30" t="n">
-        <v>5080.22</v>
+        <v>4699.18</v>
       </c>
       <c r="K30" t="n">
-        <v>5153.15</v>
+        <v>4944.15</v>
       </c>
       <c r="L30" t="n">
-        <v>5226.07</v>
+        <v>5189.13</v>
       </c>
       <c r="M30" t="n">
-        <v>5342.65</v>
+        <v>5373.25</v>
       </c>
       <c r="N30" t="n">
-        <v>5459.22</v>
+        <v>5557.38</v>
       </c>
       <c r="O30" t="n">
-        <v>5488.5</v>
+        <v>5863.2</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q30" s="6" t="n">
+        <v/>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
@@ -3027,10 +3019,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3052,60 +3042,64 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5186.7</v>
+        <v>5010</v>
       </c>
       <c r="C31" t="n">
-        <v>5248.7</v>
+        <v>5049.4</v>
       </c>
       <c r="D31" t="n">
-        <v>5014.1</v>
+        <v>4478.4</v>
       </c>
       <c r="E31" t="n">
-        <v>5061.7</v>
+        <v>4574.9</v>
       </c>
       <c r="F31" t="n">
-        <v>-97</v>
+        <v>-486.8</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0188</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>234.6</v>
+        <v>571</v>
       </c>
       <c r="I31" t="n">
-        <v>4575.9</v>
+        <v>4779.5</v>
       </c>
       <c r="J31" t="n">
-        <v>4699.18</v>
+        <v>4792.25</v>
       </c>
       <c r="K31" t="n">
-        <v>4944.15</v>
+        <v>4944.4</v>
       </c>
       <c r="L31" t="n">
-        <v>5189.13</v>
+        <v>5096.55</v>
       </c>
       <c r="M31" t="n">
-        <v>5373.25</v>
+        <v>5179</v>
       </c>
       <c r="N31" t="n">
-        <v>5557.38</v>
+        <v>5261.45</v>
       </c>
       <c r="O31" t="n">
-        <v>5863.2</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+        <v>5483.3</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
@@ -3122,83 +3116,75 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>5010</v>
+        <v>4450</v>
       </c>
       <c r="C32" t="n">
-        <v>5049.4</v>
+        <v>4601</v>
       </c>
       <c r="D32" t="n">
-        <v>4478.4</v>
+        <v>4100</v>
       </c>
       <c r="E32" t="n">
-        <v>4574.9</v>
+        <v>4492.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-486.8</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="H32" t="n">
-        <v>571</v>
+        <v>501</v>
       </c>
       <c r="I32" t="n">
-        <v>4779.5</v>
+        <v>3907.4</v>
       </c>
       <c r="J32" t="n">
-        <v>4792.25</v>
+        <v>3909.4</v>
       </c>
       <c r="K32" t="n">
-        <v>4944.4</v>
+        <v>4289.4</v>
       </c>
       <c r="L32" t="n">
-        <v>5096.55</v>
+        <v>4669.4</v>
       </c>
       <c r="M32" t="n">
-        <v>5179</v>
+        <v>4860.4</v>
       </c>
       <c r="N32" t="n">
-        <v>5261.45</v>
+        <v>5051.4</v>
       </c>
       <c r="O32" t="n">
-        <v>5483.3</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>5620.4</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3220,50 +3206,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4450</v>
+        <v>4482.8</v>
       </c>
       <c r="C33" t="n">
-        <v>4601</v>
+        <v>4825.9</v>
       </c>
       <c r="D33" t="n">
-        <v>4100</v>
+        <v>4413.4</v>
       </c>
       <c r="E33" t="n">
-        <v>4492.5</v>
+        <v>4679.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-82.40000000000001</v>
+        <v>187.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0417</v>
       </c>
       <c r="H33" t="n">
-        <v>501</v>
+        <v>412.5</v>
       </c>
       <c r="I33" t="n">
-        <v>3907.4</v>
+        <v>3599</v>
       </c>
       <c r="J33" t="n">
-        <v>3909.4</v>
+        <v>4062.5</v>
       </c>
       <c r="K33" t="n">
-        <v>4289.4</v>
+        <v>4242</v>
       </c>
       <c r="L33" t="n">
-        <v>4669.4</v>
+        <v>4421.5</v>
       </c>
       <c r="M33" t="n">
-        <v>4860.4</v>
+        <v>4743</v>
       </c>
       <c r="N33" t="n">
-        <v>5051.4</v>
+        <v>5064.5</v>
       </c>
       <c r="O33" t="n">
-        <v>5620.4</v>
+        <v>5102</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3271,18 +3257,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3295,55 +3281,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4482.8</v>
+        <v>4675</v>
       </c>
       <c r="C34" t="n">
-        <v>4825.9</v>
+        <v>4888</v>
       </c>
       <c r="D34" t="n">
-        <v>4413.4</v>
+        <v>4626.2</v>
       </c>
       <c r="E34" t="n">
-        <v>4679.7</v>
+        <v>4787.4</v>
       </c>
       <c r="F34" t="n">
-        <v>187.2</v>
+        <v>107.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0417</v>
+        <v>0.023</v>
       </c>
       <c r="H34" t="n">
-        <v>412.5</v>
+        <v>261.8</v>
       </c>
       <c r="I34" t="n">
-        <v>3599</v>
+        <v>4000.9</v>
       </c>
       <c r="J34" t="n">
-        <v>4062.5</v>
+        <v>4297.23</v>
       </c>
       <c r="K34" t="n">
-        <v>4242</v>
+        <v>4473.45</v>
       </c>
       <c r="L34" t="n">
-        <v>4421.5</v>
+        <v>4649.68</v>
       </c>
       <c r="M34" t="n">
-        <v>4743</v>
+        <v>4885.95</v>
       </c>
       <c r="N34" t="n">
-        <v>5064.5</v>
+        <v>5122.23</v>
       </c>
       <c r="O34" t="n">
-        <v>5102</v>
+        <v>5238.4</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3384,50 +3374,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4675</v>
+        <v>4710</v>
       </c>
       <c r="C35" t="n">
-        <v>4888</v>
+        <v>4917.7</v>
       </c>
       <c r="D35" t="n">
-        <v>4626.2</v>
+        <v>4626</v>
       </c>
       <c r="E35" t="n">
-        <v>4787.4</v>
+        <v>4879.6</v>
       </c>
       <c r="F35" t="n">
-        <v>107.7</v>
+        <v>92.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0193</v>
       </c>
       <c r="H35" t="n">
-        <v>261.8</v>
+        <v>291.7</v>
       </c>
       <c r="I35" t="n">
-        <v>4000.9</v>
+        <v>4364.4</v>
       </c>
       <c r="J35" t="n">
-        <v>4297.23</v>
+        <v>4540.75</v>
       </c>
       <c r="K35" t="n">
-        <v>4473.45</v>
+        <v>4656.5</v>
       </c>
       <c r="L35" t="n">
-        <v>4649.68</v>
+        <v>4772.25</v>
       </c>
       <c r="M35" t="n">
-        <v>4885.95</v>
+        <v>4918.3</v>
       </c>
       <c r="N35" t="n">
-        <v>5122.23</v>
+        <v>5064.35</v>
       </c>
       <c r="O35" t="n">
-        <v>5238.4</v>
+        <v>5149.8</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3435,8 +3425,10 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
@@ -3461,57 +3453,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4710</v>
+        <v>4811.8</v>
       </c>
       <c r="C36" t="n">
-        <v>4917.7</v>
+        <v>4854.8</v>
       </c>
       <c r="D36" t="n">
-        <v>4626</v>
+        <v>4672.2</v>
       </c>
       <c r="E36" t="n">
-        <v>4879.6</v>
+        <v>4740.9</v>
       </c>
       <c r="F36" t="n">
-        <v>92.2</v>
+        <v>-138.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0193</v>
+        <v>-0.0284</v>
       </c>
       <c r="H36" t="n">
-        <v>291.7</v>
+        <v>182.6</v>
       </c>
       <c r="I36" t="n">
-        <v>4364.4</v>
+        <v>4334.3</v>
       </c>
       <c r="J36" t="n">
-        <v>4540.75</v>
+        <v>4641.77</v>
       </c>
       <c r="K36" t="n">
-        <v>4656.5</v>
+        <v>4733.75</v>
       </c>
       <c r="L36" t="n">
-        <v>4772.25</v>
+        <v>4825.73</v>
       </c>
       <c r="M36" t="n">
-        <v>4918.3</v>
+        <v>5025.45</v>
       </c>
       <c r="N36" t="n">
-        <v>5064.35</v>
+        <v>5225.18</v>
       </c>
       <c r="O36" t="n">
-        <v>5149.8</v>
+        <v>5209.4</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3521,19 +3513,17 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3547,63 +3537,65 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4811.8</v>
+        <v>4713.1</v>
       </c>
       <c r="C37" t="n">
-        <v>4854.8</v>
+        <v>4745.8</v>
       </c>
       <c r="D37" t="n">
-        <v>4672.2</v>
+        <v>4522.2</v>
       </c>
       <c r="E37" t="n">
-        <v>4740.9</v>
+        <v>4644.5</v>
       </c>
       <c r="F37" t="n">
-        <v>-138.7</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0284</v>
+        <v>-0.0203</v>
       </c>
       <c r="H37" t="n">
-        <v>182.6</v>
+        <v>223.6</v>
       </c>
       <c r="I37" t="n">
-        <v>4334.3</v>
+        <v>4489.6</v>
       </c>
       <c r="J37" t="n">
-        <v>4641.77</v>
+        <v>4547</v>
       </c>
       <c r="K37" t="n">
-        <v>4733.75</v>
+        <v>4649.6</v>
       </c>
       <c r="L37" t="n">
-        <v>4825.73</v>
+        <v>4752.2</v>
       </c>
       <c r="M37" t="n">
-        <v>5025.45</v>
+        <v>4832.2</v>
       </c>
       <c r="N37" t="n">
-        <v>5225.18</v>
+        <v>4912.2</v>
       </c>
       <c r="O37" t="n">
-        <v>5209.4</v>
+        <v>5037.4</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3629,81 +3621,77 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4713.1</v>
+        <v>4644</v>
       </c>
       <c r="C38" t="n">
-        <v>4745.8</v>
+        <v>4775.2</v>
       </c>
       <c r="D38" t="n">
-        <v>4522.2</v>
+        <v>4510.1</v>
       </c>
       <c r="E38" t="n">
-        <v>4644.5</v>
+        <v>4730.7</v>
       </c>
       <c r="F38" t="n">
-        <v>-96.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0186</v>
       </c>
       <c r="H38" t="n">
-        <v>223.6</v>
+        <v>265.1</v>
       </c>
       <c r="I38" t="n">
-        <v>4489.6</v>
+        <v>4298.6</v>
       </c>
       <c r="J38" t="n">
-        <v>4547</v>
+        <v>4426.15</v>
       </c>
       <c r="K38" t="n">
-        <v>4649.6</v>
+        <v>4532.7</v>
       </c>
       <c r="L38" t="n">
-        <v>4752.2</v>
+        <v>4639.25</v>
       </c>
       <c r="M38" t="n">
-        <v>4832.2</v>
+        <v>4756.3</v>
       </c>
       <c r="N38" t="n">
-        <v>4912.2</v>
+        <v>4873.35</v>
       </c>
       <c r="O38" t="n">
-        <v>5037.4</v>
+        <v>4969.4</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3715,55 +3703,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4644</v>
+        <v>4690</v>
       </c>
       <c r="C39" t="n">
-        <v>4775.2</v>
+        <v>4783.4</v>
       </c>
       <c r="D39" t="n">
-        <v>4510.1</v>
+        <v>4513.8</v>
       </c>
       <c r="E39" t="n">
-        <v>4730.7</v>
+        <v>4561.9</v>
       </c>
       <c r="F39" t="n">
-        <v>86.2</v>
+        <v>-168.8</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0357</v>
       </c>
       <c r="H39" t="n">
-        <v>265.1</v>
+        <v>269.6</v>
       </c>
       <c r="I39" t="n">
-        <v>4298.6</v>
+        <v>4245</v>
       </c>
       <c r="J39" t="n">
-        <v>4426.15</v>
+        <v>4509.63</v>
       </c>
       <c r="K39" t="n">
-        <v>4532.7</v>
+        <v>4598.15</v>
       </c>
       <c r="L39" t="n">
-        <v>4639.25</v>
+        <v>4686.68</v>
       </c>
       <c r="M39" t="n">
-        <v>4756.3</v>
+        <v>4863.25</v>
       </c>
       <c r="N39" t="n">
-        <v>4873.35</v>
+        <v>5039.83</v>
       </c>
       <c r="O39" t="n">
-        <v>4969.4</v>
+        <v>5040.3</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3773,18 +3765,16 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3806,50 +3796,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4690</v>
+        <v>4547.6</v>
       </c>
       <c r="C40" t="n">
-        <v>4783.4</v>
+        <v>4593.2</v>
       </c>
       <c r="D40" t="n">
-        <v>4513.8</v>
+        <v>4455</v>
       </c>
       <c r="E40" t="n">
-        <v>4561.9</v>
+        <v>4523.2</v>
       </c>
       <c r="F40" t="n">
-        <v>-168.8</v>
+        <v>-38.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0357</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>269.6</v>
+        <v>138.2</v>
       </c>
       <c r="I40" t="n">
-        <v>4245</v>
+        <v>4244.2</v>
       </c>
       <c r="J40" t="n">
-        <v>4509.63</v>
+        <v>4248.95</v>
       </c>
       <c r="K40" t="n">
-        <v>4598.15</v>
+        <v>4427.1</v>
       </c>
       <c r="L40" t="n">
-        <v>4686.68</v>
+        <v>4605.25</v>
       </c>
       <c r="M40" t="n">
-        <v>4863.25</v>
+        <v>4696.7</v>
       </c>
       <c r="N40" t="n">
-        <v>5039.83</v>
+        <v>4788.15</v>
       </c>
       <c r="O40" t="n">
-        <v>5040.3</v>
+        <v>5053</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3857,14 +3847,12 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3881,76 +3869,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4547.6</v>
+        <v>4532</v>
       </c>
       <c r="C41" t="n">
-        <v>4593.2</v>
+        <v>4627.1</v>
       </c>
       <c r="D41" t="n">
-        <v>4455</v>
+        <v>4363.5</v>
       </c>
       <c r="E41" t="n">
-        <v>4523.2</v>
+        <v>4593</v>
       </c>
       <c r="F41" t="n">
-        <v>-38.7</v>
+        <v>69.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H41" t="n">
-        <v>138.2</v>
+        <v>263.6</v>
       </c>
       <c r="I41" t="n">
-        <v>4244.2</v>
+        <v>4316.8</v>
       </c>
       <c r="J41" t="n">
-        <v>4248.95</v>
+        <v>4384.55</v>
       </c>
       <c r="K41" t="n">
-        <v>4427.1</v>
+        <v>4454.1</v>
       </c>
       <c r="L41" t="n">
-        <v>4605.25</v>
+        <v>4523.65</v>
       </c>
       <c r="M41" t="n">
-        <v>4696.7</v>
+        <v>4592.3</v>
       </c>
       <c r="N41" t="n">
-        <v>4788.15</v>
+        <v>4660.95</v>
       </c>
       <c r="O41" t="n">
-        <v>5053</v>
+        <v>4731.4</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3963,78 +3953,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4532</v>
+        <v>4575.2</v>
       </c>
       <c r="C42" t="n">
-        <v>4627.1</v>
+        <v>4577.3</v>
       </c>
       <c r="D42" t="n">
-        <v>4363.5</v>
+        <v>4336.6</v>
       </c>
       <c r="E42" t="n">
-        <v>4593</v>
+        <v>4365.3</v>
       </c>
       <c r="F42" t="n">
-        <v>69.8</v>
+        <v>-227.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0154</v>
+        <v>-0.0496</v>
       </c>
       <c r="H42" t="n">
-        <v>263.6</v>
+        <v>240.7</v>
       </c>
       <c r="I42" t="n">
-        <v>4316.8</v>
+        <v>4099.9</v>
       </c>
       <c r="J42" t="n">
-        <v>4384.55</v>
+        <v>4378.25</v>
       </c>
       <c r="K42" t="n">
-        <v>4454.1</v>
+        <v>4461.2</v>
       </c>
       <c r="L42" t="n">
-        <v>4523.65</v>
+        <v>4544.15</v>
       </c>
       <c r="M42" t="n">
-        <v>4592.3</v>
+        <v>4724.8</v>
       </c>
       <c r="N42" t="n">
-        <v>4660.95</v>
+        <v>4905.45</v>
       </c>
       <c r="O42" t="n">
-        <v>4731.4</v>
+        <v>4890.7</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4047,71 +4039,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4575.2</v>
+        <v>4354</v>
       </c>
       <c r="C43" t="n">
-        <v>4577.3</v>
+        <v>4388.6</v>
       </c>
       <c r="D43" t="n">
-        <v>4336.6</v>
+        <v>4046.2</v>
       </c>
       <c r="E43" t="n">
-        <v>4365.3</v>
+        <v>4238.8</v>
       </c>
       <c r="F43" t="n">
-        <v>-227.7</v>
+        <v>-126.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0496</v>
+        <v>-0.029</v>
       </c>
       <c r="H43" t="n">
-        <v>240.7</v>
+        <v>342.4</v>
       </c>
       <c r="I43" t="n">
-        <v>4099.9</v>
+        <v>4095.9</v>
       </c>
       <c r="J43" t="n">
-        <v>4378.25</v>
+        <v>4078.78</v>
       </c>
       <c r="K43" t="n">
-        <v>4461.2</v>
+        <v>4244.95</v>
       </c>
       <c r="L43" t="n">
-        <v>4544.15</v>
+        <v>4411.12</v>
       </c>
       <c r="M43" t="n">
-        <v>4724.8</v>
+        <v>4485.65</v>
       </c>
       <c r="N43" t="n">
-        <v>4905.45</v>
+        <v>4560.17</v>
       </c>
       <c r="O43" t="n">
-        <v>4890.7</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
+        <v>4818</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
@@ -4138,69 +4128,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4354</v>
+        <v>4289.4</v>
       </c>
       <c r="C44" t="n">
-        <v>4388.6</v>
+        <v>4403.6</v>
       </c>
       <c r="D44" t="n">
-        <v>4046.2</v>
+        <v>4138.7</v>
       </c>
       <c r="E44" t="n">
-        <v>4238.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F44" t="n">
-        <v>-126.5</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0155</v>
       </c>
       <c r="H44" t="n">
-        <v>342.4</v>
+        <v>264.9</v>
       </c>
       <c r="I44" t="n">
-        <v>4095.9</v>
+        <v>3703.8</v>
       </c>
       <c r="J44" t="n">
-        <v>4078.78</v>
+        <v>3907.1</v>
       </c>
       <c r="K44" t="n">
-        <v>4244.95</v>
+        <v>4067.6</v>
       </c>
       <c r="L44" t="n">
-        <v>4411.12</v>
+        <v>4228.1</v>
       </c>
       <c r="M44" t="n">
-        <v>4485.65</v>
+        <v>4410</v>
       </c>
       <c r="N44" t="n">
-        <v>4560.17</v>
+        <v>4591.9</v>
       </c>
       <c r="O44" t="n">
-        <v>4818</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4731</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4217,55 +4201,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4289.4</v>
+        <v>4163.9</v>
       </c>
       <c r="C45" t="n">
-        <v>4403.6</v>
+        <v>4238.1</v>
       </c>
       <c r="D45" t="n">
-        <v>4138.7</v>
+        <v>3975.7</v>
       </c>
       <c r="E45" t="n">
-        <v>4172.9</v>
+        <v>4096.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-65.90000000000001</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0184</v>
       </c>
       <c r="H45" t="n">
-        <v>264.9</v>
+        <v>262.4</v>
       </c>
       <c r="I45" t="n">
-        <v>3703.8</v>
+        <v>3873.8</v>
       </c>
       <c r="J45" t="n">
-        <v>3907.1</v>
+        <v>3858.87</v>
       </c>
       <c r="K45" t="n">
-        <v>4067.6</v>
+        <v>4040.45</v>
       </c>
       <c r="L45" t="n">
-        <v>4228.1</v>
+        <v>4222.03</v>
       </c>
       <c r="M45" t="n">
-        <v>4410</v>
+        <v>4305.35</v>
       </c>
       <c r="N45" t="n">
-        <v>4591.9</v>
+        <v>4388.67</v>
       </c>
       <c r="O45" t="n">
-        <v>4731</v>
+        <v>4668.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4273,12 +4261,14 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4295,59 +4285,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4163.9</v>
+        <v>4101.1</v>
       </c>
       <c r="C46" t="n">
-        <v>4238.1</v>
+        <v>4208.3</v>
       </c>
       <c r="D46" t="n">
-        <v>3975.7</v>
+        <v>3955.4</v>
       </c>
       <c r="E46" t="n">
-        <v>4096.3</v>
+        <v>4187.3</v>
       </c>
       <c r="F46" t="n">
-        <v>-76.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0222</v>
       </c>
       <c r="H46" t="n">
-        <v>262.4</v>
+        <v>252.9</v>
       </c>
       <c r="I46" t="n">
-        <v>3873.8</v>
+        <v>3713.3</v>
       </c>
       <c r="J46" t="n">
-        <v>3858.87</v>
+        <v>3828.6</v>
       </c>
       <c r="K46" t="n">
-        <v>4040.45</v>
+        <v>3965.1</v>
       </c>
       <c r="L46" t="n">
-        <v>4222.03</v>
+        <v>4101.6</v>
       </c>
       <c r="M46" t="n">
-        <v>4305.35</v>
+        <v>4227.5</v>
       </c>
       <c r="N46" t="n">
-        <v>4388.67</v>
+        <v>4353.4</v>
       </c>
       <c r="O46" t="n">
-        <v>4668.5</v>
+        <v>4500.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4357,17 +4343,19 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4379,55 +4367,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4101.1</v>
+        <v>4187.5</v>
       </c>
       <c r="C47" t="n">
-        <v>4208.3</v>
+        <v>4215.5</v>
       </c>
       <c r="D47" t="n">
-        <v>3955.4</v>
+        <v>4032.5</v>
       </c>
       <c r="E47" t="n">
-        <v>4187.3</v>
+        <v>4113.7</v>
       </c>
       <c r="F47" t="n">
-        <v>91</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0176</v>
       </c>
       <c r="H47" t="n">
-        <v>252.9</v>
+        <v>183</v>
       </c>
       <c r="I47" t="n">
-        <v>3713.3</v>
+        <v>3702.5</v>
       </c>
       <c r="J47" t="n">
-        <v>3828.6</v>
+        <v>3987.12</v>
       </c>
       <c r="K47" t="n">
-        <v>3965.1</v>
+        <v>4060.85</v>
       </c>
       <c r="L47" t="n">
-        <v>4101.6</v>
+        <v>4134.57</v>
       </c>
       <c r="M47" t="n">
-        <v>4227.5</v>
+        <v>4313.75</v>
       </c>
       <c r="N47" t="n">
-        <v>4353.4</v>
+        <v>4492.92</v>
       </c>
       <c r="O47" t="n">
-        <v>4500.5</v>
+        <v>4461.2</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4440,15 +4432,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4463,57 +4453,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4187.5</v>
+        <v>4106.6</v>
       </c>
       <c r="C48" t="n">
-        <v>4215.5</v>
+        <v>4112.5</v>
       </c>
       <c r="D48" t="n">
-        <v>4032.5</v>
+        <v>3963</v>
       </c>
       <c r="E48" t="n">
-        <v>4113.7</v>
+        <v>4018.8</v>
       </c>
       <c r="F48" t="n">
-        <v>-73.59999999999999</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0176</v>
+        <v>-0.0231</v>
       </c>
       <c r="H48" t="n">
-        <v>183</v>
+        <v>149.5</v>
       </c>
       <c r="I48" t="n">
-        <v>3702.5</v>
+        <v>3849.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3987.12</v>
+        <v>3925.55</v>
       </c>
       <c r="K48" t="n">
-        <v>4060.85</v>
+        <v>4022.2</v>
       </c>
       <c r="L48" t="n">
-        <v>4134.57</v>
+        <v>4118.85</v>
       </c>
       <c r="M48" t="n">
-        <v>4313.75</v>
+        <v>4205.2</v>
       </c>
       <c r="N48" t="n">
-        <v>4492.92</v>
+        <v>4291.55</v>
       </c>
       <c r="O48" t="n">
-        <v>4461.2</v>
+        <v>4398.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4523,12 +4513,12 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4545,59 +4535,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4106.6</v>
+        <v>4005.6</v>
       </c>
       <c r="C49" t="n">
-        <v>4112.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D49" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E49" t="n">
-        <v>4018.8</v>
+        <v>4070.8</v>
       </c>
       <c r="F49" t="n">
-        <v>-94.90000000000001</v>
+        <v>52</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0129</v>
       </c>
       <c r="H49" t="n">
-        <v>149.5</v>
+        <v>184.9</v>
       </c>
       <c r="I49" t="n">
-        <v>3849.5</v>
+        <v>3813.5</v>
       </c>
       <c r="J49" t="n">
-        <v>3925.55</v>
+        <v>3859.83</v>
       </c>
       <c r="K49" t="n">
-        <v>4022.2</v>
+        <v>3944.05</v>
       </c>
       <c r="L49" t="n">
-        <v>4118.85</v>
+        <v>4028.28</v>
       </c>
       <c r="M49" t="n">
-        <v>4205.2</v>
+        <v>4093.55</v>
       </c>
       <c r="N49" t="n">
-        <v>4291.55</v>
+        <v>4158.83</v>
       </c>
       <c r="O49" t="n">
-        <v>4398.5</v>
+        <v>4262</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4605,21 +4591,23 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4629,55 +4617,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4005.6</v>
+        <v>4097.5</v>
       </c>
       <c r="C50" t="n">
-        <v>4171.4</v>
+        <v>4170.7</v>
       </c>
       <c r="D50" t="n">
-        <v>3986.5</v>
+        <v>3993.8</v>
       </c>
       <c r="E50" t="n">
-        <v>4070.8</v>
+        <v>4107</v>
       </c>
       <c r="F50" t="n">
-        <v>52</v>
+        <v>36.2</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0089</v>
       </c>
       <c r="H50" t="n">
-        <v>184.9</v>
+        <v>176.9</v>
       </c>
       <c r="I50" t="n">
-        <v>3813.5</v>
+        <v>3801.6</v>
       </c>
       <c r="J50" t="n">
-        <v>3859.83</v>
+        <v>3881.83</v>
       </c>
       <c r="K50" t="n">
-        <v>3944.05</v>
+        <v>3978.35</v>
       </c>
       <c r="L50" t="n">
-        <v>4028.28</v>
+        <v>4074.88</v>
       </c>
       <c r="M50" t="n">
-        <v>4093.55</v>
+        <v>4163.25</v>
       </c>
       <c r="N50" t="n">
-        <v>4158.83</v>
+        <v>4251.62</v>
       </c>
       <c r="O50" t="n">
-        <v>4262</v>
+        <v>4356.3</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4690,19 +4682,17 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4713,57 +4703,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4097.5</v>
+        <v>4135.2</v>
       </c>
       <c r="C51" t="n">
-        <v>4170.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D51" t="n">
-        <v>3993.8</v>
+        <v>4074</v>
       </c>
       <c r="E51" t="n">
-        <v>4107</v>
+        <v>4399.7</v>
       </c>
       <c r="F51" t="n">
-        <v>36.2</v>
+        <v>292.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0089</v>
+        <v>0.0713</v>
       </c>
       <c r="H51" t="n">
-        <v>176.9</v>
+        <v>358.3</v>
       </c>
       <c r="I51" t="n">
-        <v>3801.6</v>
+        <v>3816.9</v>
       </c>
       <c r="J51" t="n">
-        <v>3881.83</v>
+        <v>3942.47</v>
       </c>
       <c r="K51" t="n">
-        <v>3978.35</v>
+        <v>4018.55</v>
       </c>
       <c r="L51" t="n">
-        <v>4074.88</v>
+        <v>4094.63</v>
       </c>
       <c r="M51" t="n">
-        <v>4163.25</v>
+        <v>4195.45</v>
       </c>
       <c r="N51" t="n">
-        <v>4251.62</v>
+        <v>4296.28</v>
       </c>
       <c r="O51" t="n">
-        <v>4356.3</v>
+        <v>4347.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4776,7 +4766,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4784,70 +4774,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4135.2</v>
+        <v>4400</v>
       </c>
       <c r="C52" t="n">
-        <v>4432.3</v>
+        <v>4509.1</v>
       </c>
       <c r="D52" t="n">
-        <v>4074</v>
+        <v>4365.5</v>
       </c>
       <c r="E52" t="n">
-        <v>4399.7</v>
+        <v>4437.3</v>
       </c>
       <c r="F52" t="n">
-        <v>292.7</v>
+        <v>37.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0713</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>358.3</v>
+        <v>143.6</v>
       </c>
       <c r="I52" t="n">
-        <v>3816.9</v>
+        <v>3715.7</v>
       </c>
       <c r="J52" t="n">
-        <v>3942.47</v>
+        <v>4114.68</v>
       </c>
       <c r="K52" t="n">
-        <v>4018.55</v>
+        <v>4220.55</v>
       </c>
       <c r="L52" t="n">
-        <v>4094.63</v>
+        <v>4326.43</v>
       </c>
       <c r="M52" t="n">
-        <v>4195.45</v>
+        <v>4578.85</v>
       </c>
       <c r="N52" t="n">
-        <v>4296.28</v>
+        <v>4831.28</v>
       </c>
       <c r="O52" t="n">
-        <v>4347.6</v>
+        <v>4790.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4860,23 +4850,17 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4888,50 +4872,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4400</v>
+        <v>4440</v>
       </c>
       <c r="C53" t="n">
+        <v>4690.4</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4378</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4680.6</v>
+      </c>
+      <c r="F53" t="n">
+        <v>243.3</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H53" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="I53" t="n">
+        <v>4221.9</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4293.7</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4365.5</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4437.3</v>
+      </c>
+      <c r="M53" t="n">
         <v>4509.1</v>
       </c>
-      <c r="D53" t="n">
-        <v>4365.5</v>
-      </c>
-      <c r="E53" t="n">
-        <v>4437.3</v>
-      </c>
-      <c r="F53" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="H53" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3715.7</v>
-      </c>
-      <c r="J53" t="n">
-        <v>4114.68</v>
-      </c>
-      <c r="K53" t="n">
-        <v>4220.55</v>
-      </c>
-      <c r="L53" t="n">
-        <v>4326.43</v>
-      </c>
-      <c r="M53" t="n">
-        <v>4578.85</v>
-      </c>
       <c r="N53" t="n">
-        <v>4831.28</v>
+        <v>4580.9</v>
       </c>
       <c r="O53" t="n">
-        <v>4790.6</v>
+        <v>4652.7</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4944,17 +4928,23 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
@@ -4966,50 +4956,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4440</v>
+        <v>4673.4</v>
       </c>
       <c r="C54" t="n">
-        <v>4690.4</v>
+        <v>4755</v>
       </c>
       <c r="D54" t="n">
-        <v>4378</v>
+        <v>4495</v>
       </c>
       <c r="E54" t="n">
-        <v>4680.6</v>
+        <v>4529.9</v>
       </c>
       <c r="F54" t="n">
-        <v>243.3</v>
+        <v>-150.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0548</v>
+        <v>-0.0322</v>
       </c>
       <c r="H54" t="n">
-        <v>312.4</v>
+        <v>260</v>
       </c>
       <c r="I54" t="n">
-        <v>4221.9</v>
+        <v>4065.6</v>
       </c>
       <c r="J54" t="n">
-        <v>4293.7</v>
+        <v>4441.4</v>
       </c>
       <c r="K54" t="n">
-        <v>4365.5</v>
+        <v>4524.4</v>
       </c>
       <c r="L54" t="n">
-        <v>4437.3</v>
+        <v>4607.4</v>
       </c>
       <c r="M54" t="n">
-        <v>4509.1</v>
+        <v>4836.8</v>
       </c>
       <c r="N54" t="n">
-        <v>4580.9</v>
+        <v>5066.2</v>
       </c>
       <c r="O54" t="n">
-        <v>4652.7</v>
+        <v>5002.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5017,83 +5007,83 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4673.4</v>
+        <v>4483.2</v>
       </c>
       <c r="C55" t="n">
-        <v>4755</v>
+        <v>4558.5</v>
       </c>
       <c r="D55" t="n">
-        <v>4495</v>
+        <v>4329.2</v>
       </c>
       <c r="E55" t="n">
-        <v>4529.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F55" t="n">
-        <v>-150.7</v>
+        <v>-53.3</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0118</v>
       </c>
       <c r="H55" t="n">
-        <v>260</v>
+        <v>229.3</v>
       </c>
       <c r="I55" t="n">
-        <v>4065.6</v>
+        <v>4235</v>
       </c>
       <c r="J55" t="n">
-        <v>4441.4</v>
+        <v>4222.35</v>
       </c>
       <c r="K55" t="n">
-        <v>4524.4</v>
+        <v>4399.9</v>
       </c>
       <c r="L55" t="n">
-        <v>4607.4</v>
+        <v>4577.45</v>
       </c>
       <c r="M55" t="n">
-        <v>4836.8</v>
+        <v>4659.9</v>
       </c>
       <c r="N55" t="n">
-        <v>5066.2</v>
+        <v>4742.35</v>
       </c>
       <c r="O55" t="n">
-        <v>5002.8</v>
+        <v>5015</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5127,57 +5117,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4483.2</v>
+        <v>4466.5</v>
       </c>
       <c r="C56" t="n">
-        <v>4558.5</v>
+        <v>4488.8</v>
       </c>
       <c r="D56" t="n">
-        <v>4329.2</v>
+        <v>4333</v>
       </c>
       <c r="E56" t="n">
-        <v>4476.6</v>
+        <v>4408.9</v>
       </c>
       <c r="F56" t="n">
-        <v>-53.3</v>
+        <v>-67.7</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0151</v>
       </c>
       <c r="H56" t="n">
-        <v>229.3</v>
+        <v>155.8</v>
       </c>
       <c r="I56" t="n">
-        <v>4235</v>
+        <v>4099.9</v>
       </c>
       <c r="J56" t="n">
-        <v>4222.35</v>
+        <v>4263.68</v>
       </c>
       <c r="K56" t="n">
-        <v>4399.9</v>
+        <v>4361.95</v>
       </c>
       <c r="L56" t="n">
-        <v>4577.45</v>
+        <v>4460.23</v>
       </c>
       <c r="M56" t="n">
-        <v>4659.9</v>
+        <v>4591.25</v>
       </c>
       <c r="N56" t="n">
-        <v>4742.35</v>
+        <v>4722.27</v>
       </c>
       <c r="O56" t="n">
-        <v>5015</v>
+        <v>4787.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5211,57 +5201,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4466.5</v>
+        <v>4375</v>
       </c>
       <c r="C57" t="n">
-        <v>4488.8</v>
+        <v>4439.8</v>
       </c>
       <c r="D57" t="n">
-        <v>4333</v>
+        <v>4273.3</v>
       </c>
       <c r="E57" t="n">
-        <v>4408.9</v>
+        <v>4424.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-67.7</v>
+        <v>16</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0151</v>
+        <v>0.0036</v>
       </c>
       <c r="H57" t="n">
-        <v>155.8</v>
+        <v>166.5</v>
       </c>
       <c r="I57" t="n">
-        <v>4099.9</v>
+        <v>4177.2</v>
       </c>
       <c r="J57" t="n">
-        <v>4263.68</v>
+        <v>4252.1</v>
       </c>
       <c r="K57" t="n">
-        <v>4361.95</v>
+        <v>4331</v>
       </c>
       <c r="L57" t="n">
-        <v>4460.23</v>
+        <v>4409.9</v>
       </c>
       <c r="M57" t="n">
-        <v>4591.25</v>
+        <v>4486.8</v>
       </c>
       <c r="N57" t="n">
-        <v>4722.27</v>
+        <v>4563.7</v>
       </c>
       <c r="O57" t="n">
-        <v>4787.8</v>
+        <v>4644.6</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5271,12 +5261,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5296,90 +5286,6 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4375</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4413.1</v>
-      </c>
-      <c r="D58" t="n">
-        <v>4273.3</v>
-      </c>
-      <c r="E58" t="n">
-        <v>4395.6</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-13.3</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="H58" t="n">
-        <v>139.8</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4177.2</v>
-      </c>
-      <c r="J58" t="n">
-        <v>4252.1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4331</v>
-      </c>
-      <c r="L58" t="n">
-        <v>4409.9</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4486.8</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4563.7</v>
-      </c>
-      <c r="O58" t="n">
-        <v>4644.6</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5289,6 +5289,88 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4382.5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4386.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4382</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4385.2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-39.7</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4106.8</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4292.57</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4341.65</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4390.72</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4508.15</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4625.57</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4606.3</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5296,25 +5296,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4382.5</v>
+        <v>4413</v>
       </c>
       <c r="C58" t="n">
-        <v>4386.5</v>
+        <v>4422.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4382</v>
+        <v>4327.6</v>
       </c>
       <c r="E58" t="n">
-        <v>4385.2</v>
+        <v>4374.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-39.7</v>
+        <v>-50.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.0113</v>
       </c>
       <c r="H58" t="n">
-        <v>4.5</v>
+        <v>94.5</v>
       </c>
       <c r="I58" t="n">
         <v>4106.8</v>
@@ -5343,8 +5343,10 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5305,13 +5305,13 @@
         <v>4327.6</v>
       </c>
       <c r="E58" t="n">
-        <v>4374.7</v>
+        <v>4359.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-50.2</v>
+        <v>-65.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.0147</v>
       </c>
       <c r="H58" t="n">
         <v>94.5</v>
@@ -5345,12 +5345,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5302,19 +5302,19 @@
         <v>4422.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4327.6</v>
+        <v>4360.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4359.7</v>
+        <v>4399.8</v>
       </c>
       <c r="F58" t="n">
-        <v>-65.2</v>
+        <v>-25.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0147</v>
+        <v>-0.0057</v>
       </c>
       <c r="H58" t="n">
-        <v>94.5</v>
+        <v>61.8</v>
       </c>
       <c r="I58" t="n">
         <v>4106.8</v>
@@ -5343,14 +5343,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5305,13 +5305,13 @@
         <v>4360.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4399.8</v>
+        <v>4381.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-25.1</v>
+        <v>-43.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>61.8</v>
@@ -5346,9 +5346,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5305,13 +5305,13 @@
         <v>4360.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4381.1</v>
+        <v>4382.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-43.8</v>
+        <v>-42.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0097</v>
       </c>
       <c r="H58" t="n">
         <v>61.8</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5302,19 +5302,19 @@
         <v>4422.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4360.3</v>
+        <v>4327.6</v>
       </c>
       <c r="E58" t="n">
-        <v>4382.1</v>
+        <v>4374</v>
       </c>
       <c r="F58" t="n">
-        <v>-42.8</v>
+        <v>-50.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0097</v>
+        <v>-0.0115</v>
       </c>
       <c r="H58" t="n">
-        <v>61.8</v>
+        <v>94.5</v>
       </c>
       <c r="I58" t="n">
         <v>4106.8</v>
@@ -5343,8 +5343,10 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5305,10 +5305,10 @@
         <v>4327.6</v>
       </c>
       <c r="E58" t="n">
-        <v>4374</v>
+        <v>4373.8</v>
       </c>
       <c r="F58" t="n">
-        <v>-50.9</v>
+        <v>-51.1</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>-0.0115</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5305,13 +5305,13 @@
         <v>4327.6</v>
       </c>
       <c r="E58" t="n">
-        <v>4373.8</v>
+        <v>4336.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-51.1</v>
+        <v>-88.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0115</v>
+        <v>-0.02</v>
       </c>
       <c r="H58" t="n">
         <v>94.5</v>
@@ -5345,12 +5345,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5302,19 +5302,19 @@
         <v>4422.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4327.6</v>
+        <v>4324</v>
       </c>
       <c r="E58" t="n">
-        <v>4336.6</v>
+        <v>4327.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-88.3</v>
+        <v>-97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.02</v>
+        <v>-0.0219</v>
       </c>
       <c r="H58" t="n">
-        <v>94.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I58" t="n">
         <v>4106.8</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>122.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3283.4</v>
+        <v>3302.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3363.55</v>
+        <v>3370.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3383.5</v>
+        <v>3388.2</v>
       </c>
       <c r="L2" t="n">
-        <v>3403.45</v>
+        <v>3405.8</v>
       </c>
       <c r="M2" t="n">
-        <v>3453.5</v>
+        <v>3448.8</v>
       </c>
       <c r="N2" t="n">
-        <v>3503.55</v>
+        <v>3491.8</v>
       </c>
       <c r="O2" t="n">
-        <v>3493.4</v>
+        <v>3484</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5302,19 +5302,19 @@
         <v>4422.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4324</v>
+        <v>4307.1</v>
       </c>
       <c r="E58" t="n">
-        <v>4327.9</v>
+        <v>4308.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-97</v>
+        <v>-116.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0219</v>
+        <v>-0.0264</v>
       </c>
       <c r="H58" t="n">
-        <v>98.09999999999999</v>
+        <v>115</v>
       </c>
       <c r="I58" t="n">
         <v>4106.8</v>
@@ -5340,12 +5340,14 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3417.6</v>
+        <v>3517.9</v>
       </c>
       <c r="C2" t="n">
-        <v>3518.5</v>
+        <v>3655.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3396.1</v>
+        <v>3506</v>
       </c>
       <c r="E2" t="n">
-        <v>3516.1</v>
+        <v>3653.3</v>
       </c>
       <c r="F2" t="n">
-        <v>97.59999999999999</v>
+        <v>137.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0286</v>
+        <v>0.039</v>
       </c>
       <c r="H2" t="n">
-        <v>122.4</v>
+        <v>149.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3302.2</v>
+        <v>3273.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3370.6</v>
+        <v>3423.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3388.2</v>
+        <v>3454.9</v>
       </c>
       <c r="L2" t="n">
-        <v>3405.8</v>
+        <v>3486.7</v>
       </c>
       <c r="M2" t="n">
-        <v>3448.8</v>
+        <v>3577.3</v>
       </c>
       <c r="N2" t="n">
-        <v>3491.8</v>
+        <v>3667.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3484</v>
+        <v>3640.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,14 +698,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -718,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3517.9</v>
+        <v>3635</v>
       </c>
       <c r="C3" t="n">
-        <v>3655.5</v>
+        <v>3715.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3506</v>
+        <v>3621.7</v>
       </c>
       <c r="E3" t="n">
-        <v>3653.3</v>
+        <v>3686.4</v>
       </c>
       <c r="F3" t="n">
-        <v>137.2</v>
+        <v>33.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.039</v>
+        <v>0.0091</v>
       </c>
       <c r="H3" t="n">
-        <v>149.5</v>
+        <v>93.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3273.7</v>
+        <v>3356.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3423.1</v>
+        <v>3540.08</v>
       </c>
       <c r="K3" t="n">
-        <v>3454.9</v>
+        <v>3578.55</v>
       </c>
       <c r="L3" t="n">
-        <v>3486.7</v>
+        <v>3617.03</v>
       </c>
       <c r="M3" t="n">
-        <v>3577.3</v>
+        <v>3728.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3667.9</v>
+        <v>3839.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3640.9</v>
+        <v>3805</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,16 +777,14 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -800,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3635</v>
+        <v>3680.2</v>
       </c>
       <c r="C4" t="n">
-        <v>3715.2</v>
+        <v>3744</v>
       </c>
       <c r="D4" t="n">
-        <v>3621.7</v>
+        <v>3660.5</v>
       </c>
       <c r="E4" t="n">
-        <v>3686.4</v>
+        <v>3705.8</v>
       </c>
       <c r="F4" t="n">
-        <v>33.1</v>
+        <v>19.4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0053</v>
       </c>
       <c r="H4" t="n">
-        <v>93.5</v>
+        <v>83.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3356.5</v>
+        <v>3528.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3540.08</v>
+        <v>3601.87</v>
       </c>
       <c r="K4" t="n">
-        <v>3578.55</v>
+        <v>3639.65</v>
       </c>
       <c r="L4" t="n">
-        <v>3617.03</v>
+        <v>3677.42</v>
       </c>
       <c r="M4" t="n">
-        <v>3728.05</v>
+        <v>3733.15</v>
       </c>
       <c r="N4" t="n">
-        <v>3839.08</v>
+        <v>3788.87</v>
       </c>
       <c r="O4" t="n">
-        <v>3805</v>
+        <v>3808.7</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -880,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3680.2</v>
+        <v>3721.3</v>
       </c>
       <c r="C5" t="n">
-        <v>3744</v>
+        <v>3824.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3660.5</v>
+        <v>3718.1</v>
       </c>
       <c r="E5" t="n">
-        <v>3705.8</v>
+        <v>3809</v>
       </c>
       <c r="F5" t="n">
-        <v>19.4</v>
+        <v>103.2</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0278</v>
       </c>
       <c r="H5" t="n">
-        <v>83.5</v>
+        <v>106.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3528.2</v>
+        <v>3577</v>
       </c>
       <c r="J5" t="n">
-        <v>3601.87</v>
+        <v>3624.08</v>
       </c>
       <c r="K5" t="n">
-        <v>3639.65</v>
+        <v>3664.05</v>
       </c>
       <c r="L5" t="n">
-        <v>3677.42</v>
+        <v>3704.03</v>
       </c>
       <c r="M5" t="n">
-        <v>3733.15</v>
+        <v>3747.55</v>
       </c>
       <c r="N5" t="n">
-        <v>3788.87</v>
+        <v>3791.08</v>
       </c>
       <c r="O5" t="n">
-        <v>3808.7</v>
+        <v>3827.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,11 +937,13 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -960,50 +958,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3721.3</v>
+        <v>3788.8</v>
       </c>
       <c r="C6" t="n">
-        <v>3824.6</v>
+        <v>3923.3</v>
       </c>
       <c r="D6" t="n">
-        <v>3718.1</v>
+        <v>3785.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3809</v>
+        <v>3908.9</v>
       </c>
       <c r="F6" t="n">
-        <v>103.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0262</v>
       </c>
       <c r="H6" t="n">
-        <v>106.5</v>
+        <v>137.8</v>
       </c>
       <c r="I6" t="n">
-        <v>3577</v>
+        <v>3611.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3624.08</v>
+        <v>3721.32</v>
       </c>
       <c r="K6" t="n">
-        <v>3664.05</v>
+        <v>3755.75</v>
       </c>
       <c r="L6" t="n">
-        <v>3704.03</v>
+        <v>3790.18</v>
       </c>
       <c r="M6" t="n">
-        <v>3747.55</v>
+        <v>3862.25</v>
       </c>
       <c r="N6" t="n">
-        <v>3791.08</v>
+        <v>3934.32</v>
       </c>
       <c r="O6" t="n">
-        <v>3827.5</v>
+        <v>3931.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1024,13 +1022,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1042,50 +1040,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3788.8</v>
+        <v>3913.5</v>
       </c>
       <c r="C7" t="n">
-        <v>3923.3</v>
+        <v>4081</v>
       </c>
       <c r="D7" t="n">
-        <v>3785.5</v>
+        <v>3909.2</v>
       </c>
       <c r="E7" t="n">
-        <v>3908.9</v>
+        <v>4000.4</v>
       </c>
       <c r="F7" t="n">
-        <v>99.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0262</v>
+        <v>0.0234</v>
       </c>
       <c r="H7" t="n">
-        <v>137.8</v>
+        <v>171.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3611.6</v>
+        <v>3647.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3721.32</v>
+        <v>3798.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3755.75</v>
+        <v>3840</v>
       </c>
       <c r="L7" t="n">
-        <v>3790.18</v>
+        <v>3881.65</v>
       </c>
       <c r="M7" t="n">
-        <v>3862.25</v>
+        <v>3977.8</v>
       </c>
       <c r="N7" t="n">
-        <v>3934.32</v>
+        <v>4073.95</v>
       </c>
       <c r="O7" t="n">
-        <v>3931.1</v>
+        <v>4061.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,15 +1101,17 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
@@ -1124,50 +1124,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3913.5</v>
+        <v>4018.3</v>
       </c>
       <c r="C8" t="n">
-        <v>4081</v>
+        <v>4392</v>
       </c>
       <c r="D8" t="n">
-        <v>3909.2</v>
+        <v>4011.3</v>
       </c>
       <c r="E8" t="n">
-        <v>4000.4</v>
+        <v>4213.3</v>
       </c>
       <c r="F8" t="n">
-        <v>91.5</v>
+        <v>212.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0532</v>
       </c>
       <c r="H8" t="n">
-        <v>171.8</v>
+        <v>380.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3647.7</v>
+        <v>3737.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3798.35</v>
+        <v>3831.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3840</v>
+        <v>3914.5</v>
       </c>
       <c r="L8" t="n">
-        <v>3881.65</v>
+        <v>3997.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3977.8</v>
+        <v>4086.3</v>
       </c>
       <c r="N8" t="n">
-        <v>4073.95</v>
+        <v>4174.85</v>
       </c>
       <c r="O8" t="n">
-        <v>4061.1</v>
+        <v>4252.8</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V8" s="8" t="inlineStr">
@@ -1208,50 +1208,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4018.3</v>
+        <v>4269</v>
       </c>
       <c r="C9" t="n">
-        <v>4392</v>
+        <v>4398</v>
       </c>
       <c r="D9" t="n">
-        <v>4011.3</v>
+        <v>4021.2</v>
       </c>
       <c r="E9" t="n">
-        <v>4213.3</v>
+        <v>4137.8</v>
       </c>
       <c r="F9" t="n">
-        <v>212.9</v>
+        <v>-75.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0532</v>
+        <v>-0.0179</v>
       </c>
       <c r="H9" t="n">
-        <v>380.7</v>
+        <v>376.8</v>
       </c>
       <c r="I9" t="n">
-        <v>3737.4</v>
+        <v>3630.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3831.25</v>
+        <v>3838.42</v>
       </c>
       <c r="K9" t="n">
-        <v>3914.5</v>
+        <v>4022.95</v>
       </c>
       <c r="L9" t="n">
-        <v>3997.75</v>
+        <v>4207.47</v>
       </c>
       <c r="M9" t="n">
-        <v>4086.3</v>
+        <v>4403.65</v>
       </c>
       <c r="N9" t="n">
-        <v>4174.85</v>
+        <v>4599.82</v>
       </c>
       <c r="O9" t="n">
-        <v>4252.8</v>
+        <v>4772.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1259,83 +1259,83 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4269</v>
+        <v>4103.2</v>
       </c>
       <c r="C10" t="n">
-        <v>4398</v>
+        <v>4123.8</v>
       </c>
       <c r="D10" t="n">
-        <v>4021.2</v>
+        <v>3901.3</v>
       </c>
       <c r="E10" t="n">
-        <v>4137.8</v>
+        <v>3996.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-75.5</v>
+        <v>-141.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0179</v>
+        <v>-0.0341</v>
       </c>
       <c r="H10" t="n">
-        <v>376.8</v>
+        <v>222.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3630.6</v>
+        <v>3644.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3838.42</v>
+        <v>3725.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4022.95</v>
+        <v>3949.4</v>
       </c>
       <c r="L10" t="n">
-        <v>4207.47</v>
+        <v>4173.7</v>
       </c>
       <c r="M10" t="n">
-        <v>4403.65</v>
+        <v>4326.2</v>
       </c>
       <c r="N10" t="n">
-        <v>4599.82</v>
+        <v>4478.7</v>
       </c>
       <c r="O10" t="n">
-        <v>4772.7</v>
+        <v>4774.8</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1369,57 +1369,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4103.2</v>
+        <v>4001</v>
       </c>
       <c r="C11" t="n">
-        <v>4123.8</v>
+        <v>4043.1</v>
       </c>
       <c r="D11" t="n">
-        <v>3901.3</v>
+        <v>3935.7</v>
       </c>
       <c r="E11" t="n">
-        <v>3996.5</v>
+        <v>4009.8</v>
       </c>
       <c r="F11" t="n">
-        <v>-141.3</v>
+        <v>13.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0341</v>
+        <v>0.0033</v>
       </c>
       <c r="H11" t="n">
-        <v>222.5</v>
+        <v>107.4</v>
       </c>
       <c r="I11" t="n">
-        <v>3644.4</v>
+        <v>3678.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3725.1</v>
+        <v>3765.98</v>
       </c>
       <c r="K11" t="n">
-        <v>3949.4</v>
+        <v>3885.25</v>
       </c>
       <c r="L11" t="n">
-        <v>4173.7</v>
+        <v>4004.52</v>
       </c>
       <c r="M11" t="n">
-        <v>4326.2</v>
+        <v>4107.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4478.7</v>
+        <v>4210.97</v>
       </c>
       <c r="O11" t="n">
-        <v>4774.8</v>
+        <v>4346.3</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1427,14 +1427,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1453,57 +1451,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4001</v>
+        <v>4007.2</v>
       </c>
       <c r="C12" t="n">
-        <v>4043.1</v>
+        <v>4250</v>
       </c>
       <c r="D12" t="n">
-        <v>3935.7</v>
+        <v>4004.2</v>
       </c>
       <c r="E12" t="n">
-        <v>4009.8</v>
+        <v>4094.2</v>
       </c>
       <c r="F12" t="n">
-        <v>13.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.021</v>
       </c>
       <c r="H12" t="n">
-        <v>107.4</v>
+        <v>245.8</v>
       </c>
       <c r="I12" t="n">
-        <v>3678.8</v>
+        <v>3828.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3765.98</v>
+        <v>3912.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3885.25</v>
+        <v>3956.1</v>
       </c>
       <c r="L12" t="n">
-        <v>4004.52</v>
+        <v>3999.6</v>
       </c>
       <c r="M12" t="n">
-        <v>4107.75</v>
+        <v>4063.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4210.97</v>
+        <v>4127.4</v>
       </c>
       <c r="O12" t="n">
-        <v>4346.3</v>
+        <v>4150.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1516,76 +1514,78 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4007.2</v>
+        <v>4084.4</v>
       </c>
       <c r="C13" t="n">
-        <v>4250</v>
+        <v>4134.3</v>
       </c>
       <c r="D13" t="n">
-        <v>4004.2</v>
+        <v>3997.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4094.2</v>
+        <v>4079.5</v>
       </c>
       <c r="F13" t="n">
-        <v>84.40000000000001</v>
+        <v>-14.7</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.0036</v>
       </c>
       <c r="H13" t="n">
-        <v>245.8</v>
+        <v>136.9</v>
       </c>
       <c r="I13" t="n">
-        <v>3828.3</v>
+        <v>3758.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3912.6</v>
+        <v>3831.95</v>
       </c>
       <c r="K13" t="n">
-        <v>3956.1</v>
+        <v>3971.3</v>
       </c>
       <c r="L13" t="n">
-        <v>3999.6</v>
+        <v>4110.65</v>
       </c>
       <c r="M13" t="n">
-        <v>4063.5</v>
+        <v>4217.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4127.4</v>
+        <v>4323.55</v>
       </c>
       <c r="O13" t="n">
-        <v>4150.5</v>
+        <v>4495.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1596,80 +1596,78 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4084.4</v>
+        <v>4069.2</v>
       </c>
       <c r="C14" t="n">
-        <v>4134.3</v>
+        <v>4263.1</v>
       </c>
       <c r="D14" t="n">
-        <v>3997.4</v>
+        <v>4036.4</v>
       </c>
       <c r="E14" t="n">
-        <v>4079.5</v>
+        <v>4254.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.7</v>
+        <v>175.4</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.043</v>
       </c>
       <c r="H14" t="n">
-        <v>136.9</v>
+        <v>226.7</v>
       </c>
       <c r="I14" t="n">
-        <v>3758.4</v>
+        <v>3860.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3831.95</v>
+        <v>3949.43</v>
       </c>
       <c r="K14" t="n">
-        <v>3971.3</v>
+        <v>4011.05</v>
       </c>
       <c r="L14" t="n">
-        <v>4110.65</v>
+        <v>4072.67</v>
       </c>
       <c r="M14" t="n">
-        <v>4217.1</v>
+        <v>4147.95</v>
       </c>
       <c r="N14" t="n">
-        <v>4323.55</v>
+        <v>4223.22</v>
       </c>
       <c r="O14" t="n">
-        <v>4495.8</v>
+        <v>4271.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1680,78 +1678,80 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4069.2</v>
+        <v>4258.5</v>
       </c>
       <c r="C15" t="n">
-        <v>4263.1</v>
+        <v>4299.6</v>
       </c>
       <c r="D15" t="n">
-        <v>4036.4</v>
+        <v>4194</v>
       </c>
       <c r="E15" t="n">
-        <v>4254.9</v>
+        <v>4243</v>
       </c>
       <c r="F15" t="n">
-        <v>175.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.043</v>
+        <v>-0.0028</v>
       </c>
       <c r="H15" t="n">
-        <v>226.7</v>
+        <v>105.6</v>
       </c>
       <c r="I15" t="n">
-        <v>3860.5</v>
+        <v>3809.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3949.43</v>
+        <v>4080.77</v>
       </c>
       <c r="K15" t="n">
-        <v>4011.05</v>
+        <v>4141.55</v>
       </c>
       <c r="L15" t="n">
-        <v>4072.67</v>
+        <v>4202.32</v>
       </c>
       <c r="M15" t="n">
-        <v>4147.95</v>
+        <v>4368.25</v>
       </c>
       <c r="N15" t="n">
-        <v>4223.22</v>
+        <v>4534.18</v>
       </c>
       <c r="O15" t="n">
-        <v>4271.2</v>
+        <v>4489.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1764,78 +1764,76 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4258.5</v>
+        <v>4228.1</v>
       </c>
       <c r="C16" t="n">
-        <v>4299.6</v>
+        <v>4387.8</v>
       </c>
       <c r="D16" t="n">
-        <v>4194</v>
+        <v>4197.8</v>
       </c>
       <c r="E16" t="n">
-        <v>4243</v>
+        <v>4328.3</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.9</v>
+        <v>85.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0201</v>
       </c>
       <c r="H16" t="n">
-        <v>105.6</v>
+        <v>190</v>
       </c>
       <c r="I16" t="n">
-        <v>3809.7</v>
+        <v>4088.4</v>
       </c>
       <c r="J16" t="n">
-        <v>4080.77</v>
+        <v>4135.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4141.55</v>
+        <v>4190.2</v>
       </c>
       <c r="L16" t="n">
-        <v>4202.32</v>
+        <v>4244.9</v>
       </c>
       <c r="M16" t="n">
-        <v>4368.25</v>
+        <v>4295.8</v>
       </c>
       <c r="N16" t="n">
-        <v>4534.18</v>
+        <v>4346.7</v>
       </c>
       <c r="O16" t="n">
-        <v>4489.8</v>
+        <v>4405.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1848,14 +1846,18 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1865,59 +1867,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4228.1</v>
+        <v>4330</v>
       </c>
       <c r="C17" t="n">
-        <v>4387.8</v>
+        <v>4409.5</v>
       </c>
       <c r="D17" t="n">
-        <v>4197.8</v>
+        <v>4297.4</v>
       </c>
       <c r="E17" t="n">
-        <v>4328.3</v>
+        <v>4387.3</v>
       </c>
       <c r="F17" t="n">
-        <v>85.3</v>
+        <v>59</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0136</v>
       </c>
       <c r="H17" t="n">
-        <v>190</v>
+        <v>112.1</v>
       </c>
       <c r="I17" t="n">
-        <v>4088.4</v>
+        <v>4007.8</v>
       </c>
       <c r="J17" t="n">
-        <v>4135.5</v>
+        <v>4156.05</v>
       </c>
       <c r="K17" t="n">
-        <v>4190.2</v>
+        <v>4233.3</v>
       </c>
       <c r="L17" t="n">
-        <v>4244.9</v>
+        <v>4310.55</v>
       </c>
       <c r="M17" t="n">
-        <v>4295.8</v>
+        <v>4423.3</v>
       </c>
       <c r="N17" t="n">
-        <v>4346.7</v>
+        <v>4536.05</v>
       </c>
       <c r="O17" t="n">
-        <v>4405.2</v>
+        <v>4577.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1935,13 +1933,11 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1956,50 +1952,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4330</v>
+        <v>4369.9</v>
       </c>
       <c r="C18" t="n">
-        <v>4409.5</v>
+        <v>4584</v>
       </c>
       <c r="D18" t="n">
-        <v>4297.4</v>
+        <v>4367.9</v>
       </c>
       <c r="E18" t="n">
-        <v>4387.3</v>
+        <v>4552.7</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>165.4</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0377</v>
       </c>
       <c r="H18" t="n">
-        <v>112.1</v>
+        <v>216.1</v>
       </c>
       <c r="I18" t="n">
-        <v>4007.8</v>
+        <v>4185.3</v>
       </c>
       <c r="J18" t="n">
-        <v>4156.05</v>
+        <v>4292.12</v>
       </c>
       <c r="K18" t="n">
-        <v>4233.3</v>
+        <v>4331.25</v>
       </c>
       <c r="L18" t="n">
-        <v>4310.55</v>
+        <v>4370.37</v>
       </c>
       <c r="M18" t="n">
-        <v>4423.3</v>
+        <v>4443.35</v>
       </c>
       <c r="N18" t="n">
-        <v>4536.05</v>
+        <v>4516.32</v>
       </c>
       <c r="O18" t="n">
-        <v>4577.8</v>
+        <v>4521.6</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2017,14 +2013,18 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2036,83 +2036,81 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4369.9</v>
+        <v>4568</v>
       </c>
       <c r="C19" t="n">
-        <v>4584</v>
+        <v>4581.3</v>
       </c>
       <c r="D19" t="n">
-        <v>4367.9</v>
+        <v>4284.3</v>
       </c>
       <c r="E19" t="n">
-        <v>4552.7</v>
+        <v>4329.6</v>
       </c>
       <c r="F19" t="n">
-        <v>165.4</v>
+        <v>-223.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.049</v>
       </c>
       <c r="H19" t="n">
-        <v>216.1</v>
+        <v>297</v>
       </c>
       <c r="I19" t="n">
-        <v>4185.3</v>
+        <v>4151.8</v>
       </c>
       <c r="J19" t="n">
-        <v>4292.12</v>
+        <v>4374.98</v>
       </c>
       <c r="K19" t="n">
-        <v>4331.25</v>
+        <v>4444.65</v>
       </c>
       <c r="L19" t="n">
-        <v>4370.37</v>
+        <v>4514.33</v>
       </c>
       <c r="M19" t="n">
-        <v>4443.35</v>
+        <v>4660.75</v>
       </c>
       <c r="N19" t="n">
-        <v>4516.32</v>
+        <v>4807.18</v>
       </c>
       <c r="O19" t="n">
-        <v>4521.6</v>
+        <v>4800.1</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2120,72 +2118,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4568</v>
+        <v>4368.3</v>
       </c>
       <c r="C20" t="n">
-        <v>4581.3</v>
+        <v>4527</v>
       </c>
       <c r="D20" t="n">
-        <v>4284.3</v>
+        <v>4354.6</v>
       </c>
       <c r="E20" t="n">
-        <v>4329.6</v>
+        <v>4500.9</v>
       </c>
       <c r="F20" t="n">
-        <v>-223.1</v>
+        <v>171.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.049</v>
+        <v>0.0396</v>
       </c>
       <c r="H20" t="n">
-        <v>297</v>
+        <v>172.4</v>
       </c>
       <c r="I20" t="n">
-        <v>4151.8</v>
+        <v>3987.3</v>
       </c>
       <c r="J20" t="n">
-        <v>4374.98</v>
+        <v>3981</v>
       </c>
       <c r="K20" t="n">
-        <v>4444.65</v>
+        <v>4181.1</v>
       </c>
       <c r="L20" t="n">
-        <v>4514.33</v>
+        <v>4381.2</v>
       </c>
       <c r="M20" t="n">
-        <v>4660.75</v>
+        <v>4478.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4807.18</v>
+        <v>4575</v>
       </c>
       <c r="O20" t="n">
-        <v>4800.1</v>
+        <v>4878.3</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2197,55 +2193,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4368.3</v>
+        <v>4529.1</v>
       </c>
       <c r="C21" t="n">
-        <v>4527</v>
+        <v>4650.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4354.6</v>
+        <v>4520.8</v>
       </c>
       <c r="E21" t="n">
-        <v>4500.9</v>
+        <v>4595.4</v>
       </c>
       <c r="F21" t="n">
-        <v>171.3</v>
+        <v>94.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.021</v>
       </c>
       <c r="H21" t="n">
-        <v>172.4</v>
+        <v>129.7</v>
       </c>
       <c r="I21" t="n">
-        <v>3987.3</v>
+        <v>4182.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3981</v>
+        <v>4358.55</v>
       </c>
       <c r="K21" t="n">
-        <v>4181.1</v>
+        <v>4414.7</v>
       </c>
       <c r="L21" t="n">
-        <v>4381.2</v>
+        <v>4470.85</v>
       </c>
       <c r="M21" t="n">
-        <v>4478.1</v>
+        <v>4587.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4575</v>
+        <v>4703.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4878.3</v>
+        <v>4699.4</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,57 +2279,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4529.1</v>
+        <v>4633.7</v>
       </c>
       <c r="C22" t="n">
-        <v>4650.5</v>
+        <v>4991.4</v>
       </c>
       <c r="D22" t="n">
-        <v>4520.8</v>
+        <v>4622.2</v>
       </c>
       <c r="E22" t="n">
-        <v>4595.4</v>
+        <v>4979.7</v>
       </c>
       <c r="F22" t="n">
-        <v>94.5</v>
+        <v>384.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.021</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>129.7</v>
+        <v>369.2</v>
       </c>
       <c r="I22" t="n">
-        <v>4182.2</v>
+        <v>4391.1</v>
       </c>
       <c r="J22" t="n">
-        <v>4358.55</v>
+        <v>4470.57</v>
       </c>
       <c r="K22" t="n">
-        <v>4414.7</v>
+        <v>4530.55</v>
       </c>
       <c r="L22" t="n">
-        <v>4470.85</v>
+        <v>4590.52</v>
       </c>
       <c r="M22" t="n">
-        <v>4587.1</v>
+        <v>4660.25</v>
       </c>
       <c r="N22" t="n">
-        <v>4703.35</v>
+        <v>4729.98</v>
       </c>
       <c r="O22" t="n">
-        <v>4699.4</v>
+        <v>4780.2</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2347,86 +2347,90 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4633.7</v>
+        <v>5013.4</v>
       </c>
       <c r="C23" t="n">
-        <v>4991.4</v>
+        <v>5586.2</v>
       </c>
       <c r="D23" t="n">
-        <v>4622.2</v>
+        <v>4700.4</v>
       </c>
       <c r="E23" t="n">
-        <v>4979.7</v>
+        <v>4745.1</v>
       </c>
       <c r="F23" t="n">
-        <v>384.3</v>
+        <v>-234.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.0471</v>
       </c>
       <c r="H23" t="n">
-        <v>369.2</v>
+        <v>885.8</v>
       </c>
       <c r="I23" t="n">
-        <v>4391.1</v>
+        <v>4253</v>
       </c>
       <c r="J23" t="n">
-        <v>4470.57</v>
+        <v>4696.95</v>
       </c>
       <c r="K23" t="n">
-        <v>4530.55</v>
+        <v>4795.1</v>
       </c>
       <c r="L23" t="n">
-        <v>4590.52</v>
+        <v>4893.25</v>
       </c>
       <c r="M23" t="n">
-        <v>4660.25</v>
+        <v>5164.3</v>
       </c>
       <c r="N23" t="n">
-        <v>4729.98</v>
+        <v>5435.35</v>
       </c>
       <c r="O23" t="n">
-        <v>4780.2</v>
+        <v>5360.6</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2441,7 +2445,7 @@
       </c>
       <c r="V23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
@@ -2449,88 +2453,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5013.4</v>
+        <v>4816</v>
       </c>
       <c r="C24" t="n">
-        <v>5586.2</v>
+        <v>5113.9</v>
       </c>
       <c r="D24" t="n">
-        <v>4700.4</v>
+        <v>4423.2</v>
       </c>
       <c r="E24" t="n">
-        <v>4745.1</v>
+        <v>4979.8</v>
       </c>
       <c r="F24" t="n">
-        <v>-234.6</v>
+        <v>234.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0471</v>
+        <v>0.0495</v>
       </c>
       <c r="H24" t="n">
-        <v>885.8</v>
+        <v>690.7</v>
       </c>
       <c r="I24" t="n">
-        <v>4253</v>
+        <v>3814.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4696.95</v>
+        <v>3660.2</v>
       </c>
       <c r="K24" t="n">
-        <v>4795.1</v>
+        <v>4302.2</v>
       </c>
       <c r="L24" t="n">
-        <v>4893.25</v>
+        <v>4944.2</v>
       </c>
       <c r="M24" t="n">
-        <v>5164.3</v>
+        <v>5188</v>
       </c>
       <c r="N24" t="n">
-        <v>5435.35</v>
+        <v>5431.8</v>
       </c>
       <c r="O24" t="n">
-        <v>5360.6</v>
+        <v>6472</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2539,57 +2537,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4816</v>
+        <v>5003.6</v>
       </c>
       <c r="C25" t="n">
-        <v>5113.9</v>
+        <v>5144.5</v>
       </c>
       <c r="D25" t="n">
-        <v>4423.2</v>
+        <v>4900</v>
       </c>
       <c r="E25" t="n">
-        <v>4979.8</v>
+        <v>5046.3</v>
       </c>
       <c r="F25" t="n">
-        <v>234.7</v>
+        <v>66.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0495</v>
+        <v>0.0134</v>
       </c>
       <c r="H25" t="n">
-        <v>690.7</v>
+        <v>244.5</v>
       </c>
       <c r="I25" t="n">
-        <v>3814.6</v>
+        <v>3732.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3660.2</v>
+        <v>4394.72</v>
       </c>
       <c r="K25" t="n">
-        <v>4302.2</v>
+        <v>4634.45</v>
       </c>
       <c r="L25" t="n">
-        <v>4944.2</v>
+        <v>4874.17</v>
       </c>
       <c r="M25" t="n">
-        <v>5188</v>
+        <v>5325.15</v>
       </c>
       <c r="N25" t="n">
-        <v>5431.8</v>
+        <v>5776.12</v>
       </c>
       <c r="O25" t="n">
-        <v>6472</v>
+        <v>5804.6</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2619,59 +2617,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5003.6</v>
+        <v>5050</v>
       </c>
       <c r="C26" t="n">
-        <v>5144.5</v>
+        <v>5131</v>
       </c>
       <c r="D26" t="n">
-        <v>4900</v>
+        <v>4854.2</v>
       </c>
       <c r="E26" t="n">
-        <v>5046.3</v>
+        <v>5080.9</v>
       </c>
       <c r="F26" t="n">
-        <v>66.5</v>
+        <v>34.6</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0069</v>
       </c>
       <c r="H26" t="n">
-        <v>244.5</v>
+        <v>276.8</v>
       </c>
       <c r="I26" t="n">
-        <v>3732.5</v>
+        <v>4655.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4394.72</v>
+        <v>4813.82</v>
       </c>
       <c r="K26" t="n">
-        <v>4634.45</v>
+        <v>4924.05</v>
       </c>
       <c r="L26" t="n">
-        <v>4874.17</v>
+        <v>5034.27</v>
       </c>
       <c r="M26" t="n">
-        <v>5325.15</v>
+        <v>5168.55</v>
       </c>
       <c r="N26" t="n">
-        <v>5776.12</v>
+        <v>5302.82</v>
       </c>
       <c r="O26" t="n">
-        <v>5804.6</v>
+        <v>5389</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2679,8 +2673,10 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
@@ -2701,55 +2697,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5050</v>
+        <v>5128.8</v>
       </c>
       <c r="C27" t="n">
-        <v>5131</v>
+        <v>5299</v>
       </c>
       <c r="D27" t="n">
-        <v>4854.2</v>
+        <v>5109.5</v>
       </c>
       <c r="E27" t="n">
-        <v>5080.9</v>
+        <v>5247.9</v>
       </c>
       <c r="F27" t="n">
-        <v>34.6</v>
+        <v>167</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0329</v>
       </c>
       <c r="H27" t="n">
-        <v>276.8</v>
+        <v>189.5</v>
       </c>
       <c r="I27" t="n">
-        <v>4655.5</v>
+        <v>4577.4</v>
       </c>
       <c r="J27" t="n">
-        <v>4813.82</v>
+        <v>4848.25</v>
       </c>
       <c r="K27" t="n">
-        <v>4924.05</v>
+        <v>4942.5</v>
       </c>
       <c r="L27" t="n">
-        <v>5034.27</v>
+        <v>5036.75</v>
       </c>
       <c r="M27" t="n">
-        <v>5168.55</v>
+        <v>5219.3</v>
       </c>
       <c r="N27" t="n">
-        <v>5302.82</v>
+        <v>5401.85</v>
       </c>
       <c r="O27" t="n">
-        <v>5389</v>
+        <v>5407.8</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2757,18 +2757,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2781,77 +2781,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5128.8</v>
+        <v>5360</v>
       </c>
       <c r="C28" t="n">
-        <v>5299</v>
+        <v>5434.1</v>
       </c>
       <c r="D28" t="n">
-        <v>5109.5</v>
+        <v>5005</v>
       </c>
       <c r="E28" t="n">
-        <v>5247.9</v>
+        <v>5158.7</v>
       </c>
       <c r="F28" t="n">
-        <v>167</v>
+        <v>-89.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0329</v>
+        <v>-0.017</v>
       </c>
       <c r="H28" t="n">
-        <v>189.5</v>
+        <v>429.1</v>
       </c>
       <c r="I28" t="n">
-        <v>4577.4</v>
+        <v>4920</v>
       </c>
       <c r="J28" t="n">
-        <v>4848.25</v>
+        <v>5080.22</v>
       </c>
       <c r="K28" t="n">
-        <v>4942.5</v>
+        <v>5153.15</v>
       </c>
       <c r="L28" t="n">
-        <v>5036.75</v>
+        <v>5226.07</v>
       </c>
       <c r="M28" t="n">
-        <v>5219.3</v>
+        <v>5342.65</v>
       </c>
       <c r="N28" t="n">
-        <v>5401.85</v>
+        <v>5459.22</v>
       </c>
       <c r="O28" t="n">
-        <v>5407.8</v>
+        <v>5488.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
@@ -2865,63 +2865,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5360</v>
+        <v>5186.7</v>
       </c>
       <c r="C29" t="n">
-        <v>5434.1</v>
+        <v>5248.7</v>
       </c>
       <c r="D29" t="n">
-        <v>5005</v>
+        <v>5014.1</v>
       </c>
       <c r="E29" t="n">
-        <v>5158.7</v>
+        <v>5061.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-89.2</v>
+        <v>-97</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0188</v>
       </c>
       <c r="H29" t="n">
-        <v>429.1</v>
+        <v>234.6</v>
       </c>
       <c r="I29" t="n">
-        <v>4920</v>
+        <v>4575.9</v>
       </c>
       <c r="J29" t="n">
-        <v>5080.22</v>
+        <v>4699.18</v>
       </c>
       <c r="K29" t="n">
-        <v>5153.15</v>
+        <v>4944.15</v>
       </c>
       <c r="L29" t="n">
-        <v>5226.07</v>
+        <v>5189.13</v>
       </c>
       <c r="M29" t="n">
-        <v>5342.65</v>
+        <v>5373.25</v>
       </c>
       <c r="N29" t="n">
-        <v>5459.22</v>
+        <v>5557.38</v>
       </c>
       <c r="O29" t="n">
-        <v>5488.5</v>
+        <v>5863.2</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
@@ -2933,10 +2935,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2958,60 +2958,64 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5186.7</v>
+        <v>5010</v>
       </c>
       <c r="C30" t="n">
-        <v>5248.7</v>
+        <v>5049.4</v>
       </c>
       <c r="D30" t="n">
-        <v>5014.1</v>
+        <v>4478.4</v>
       </c>
       <c r="E30" t="n">
-        <v>5061.7</v>
+        <v>4574.9</v>
       </c>
       <c r="F30" t="n">
-        <v>-97</v>
+        <v>-486.8</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0188</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>234.6</v>
+        <v>571</v>
       </c>
       <c r="I30" t="n">
-        <v>4575.9</v>
+        <v>4779.5</v>
       </c>
       <c r="J30" t="n">
-        <v>4699.18</v>
+        <v>4792.25</v>
       </c>
       <c r="K30" t="n">
-        <v>4944.15</v>
+        <v>4944.4</v>
       </c>
       <c r="L30" t="n">
-        <v>5189.13</v>
+        <v>5096.55</v>
       </c>
       <c r="M30" t="n">
-        <v>5373.25</v>
+        <v>5179</v>
       </c>
       <c r="N30" t="n">
-        <v>5557.38</v>
+        <v>5261.45</v>
       </c>
       <c r="O30" t="n">
-        <v>5863.2</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+        <v>5483.3</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
@@ -3028,83 +3032,75 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5010</v>
+        <v>4450</v>
       </c>
       <c r="C31" t="n">
-        <v>5049.4</v>
+        <v>4601</v>
       </c>
       <c r="D31" t="n">
-        <v>4478.4</v>
+        <v>4100</v>
       </c>
       <c r="E31" t="n">
-        <v>4574.9</v>
+        <v>4492.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-486.8</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="H31" t="n">
-        <v>571</v>
+        <v>501</v>
       </c>
       <c r="I31" t="n">
-        <v>4779.5</v>
+        <v>3907.4</v>
       </c>
       <c r="J31" t="n">
-        <v>4792.25</v>
+        <v>3909.4</v>
       </c>
       <c r="K31" t="n">
-        <v>4944.4</v>
+        <v>4289.4</v>
       </c>
       <c r="L31" t="n">
-        <v>5096.55</v>
+        <v>4669.4</v>
       </c>
       <c r="M31" t="n">
-        <v>5179</v>
+        <v>4860.4</v>
       </c>
       <c r="N31" t="n">
-        <v>5261.45</v>
+        <v>5051.4</v>
       </c>
       <c r="O31" t="n">
-        <v>5483.3</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
+        <v>5620.4</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3126,50 +3122,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4450</v>
+        <v>4482.8</v>
       </c>
       <c r="C32" t="n">
-        <v>4601</v>
+        <v>4825.9</v>
       </c>
       <c r="D32" t="n">
-        <v>4100</v>
+        <v>4413.4</v>
       </c>
       <c r="E32" t="n">
-        <v>4492.5</v>
+        <v>4679.7</v>
       </c>
       <c r="F32" t="n">
-        <v>-82.40000000000001</v>
+        <v>187.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0417</v>
       </c>
       <c r="H32" t="n">
-        <v>501</v>
+        <v>412.5</v>
       </c>
       <c r="I32" t="n">
-        <v>3907.4</v>
+        <v>3599</v>
       </c>
       <c r="J32" t="n">
-        <v>3909.4</v>
+        <v>4062.5</v>
       </c>
       <c r="K32" t="n">
-        <v>4289.4</v>
+        <v>4242</v>
       </c>
       <c r="L32" t="n">
-        <v>4669.4</v>
+        <v>4421.5</v>
       </c>
       <c r="M32" t="n">
-        <v>4860.4</v>
+        <v>4743</v>
       </c>
       <c r="N32" t="n">
-        <v>5051.4</v>
+        <v>5064.5</v>
       </c>
       <c r="O32" t="n">
-        <v>5620.4</v>
+        <v>5102</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3177,18 +3173,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3201,55 +3197,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4482.8</v>
+        <v>4675</v>
       </c>
       <c r="C33" t="n">
-        <v>4825.9</v>
+        <v>4888</v>
       </c>
       <c r="D33" t="n">
-        <v>4413.4</v>
+        <v>4626.2</v>
       </c>
       <c r="E33" t="n">
-        <v>4679.7</v>
+        <v>4787.4</v>
       </c>
       <c r="F33" t="n">
-        <v>187.2</v>
+        <v>107.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0417</v>
+        <v>0.023</v>
       </c>
       <c r="H33" t="n">
-        <v>412.5</v>
+        <v>261.8</v>
       </c>
       <c r="I33" t="n">
-        <v>3599</v>
+        <v>4000.9</v>
       </c>
       <c r="J33" t="n">
-        <v>4062.5</v>
+        <v>4297.23</v>
       </c>
       <c r="K33" t="n">
-        <v>4242</v>
+        <v>4473.45</v>
       </c>
       <c r="L33" t="n">
-        <v>4421.5</v>
+        <v>4649.68</v>
       </c>
       <c r="M33" t="n">
-        <v>4743</v>
+        <v>4885.95</v>
       </c>
       <c r="N33" t="n">
-        <v>5064.5</v>
+        <v>5122.23</v>
       </c>
       <c r="O33" t="n">
-        <v>5102</v>
+        <v>5238.4</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3290,50 +3290,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4675</v>
+        <v>4710</v>
       </c>
       <c r="C34" t="n">
-        <v>4888</v>
+        <v>4917.7</v>
       </c>
       <c r="D34" t="n">
-        <v>4626.2</v>
+        <v>4626</v>
       </c>
       <c r="E34" t="n">
-        <v>4787.4</v>
+        <v>4879.6</v>
       </c>
       <c r="F34" t="n">
-        <v>107.7</v>
+        <v>92.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0193</v>
       </c>
       <c r="H34" t="n">
-        <v>261.8</v>
+        <v>291.7</v>
       </c>
       <c r="I34" t="n">
-        <v>4000.9</v>
+        <v>4364.4</v>
       </c>
       <c r="J34" t="n">
-        <v>4297.23</v>
+        <v>4540.75</v>
       </c>
       <c r="K34" t="n">
-        <v>4473.45</v>
+        <v>4656.5</v>
       </c>
       <c r="L34" t="n">
-        <v>4649.68</v>
+        <v>4772.25</v>
       </c>
       <c r="M34" t="n">
-        <v>4885.95</v>
+        <v>4918.3</v>
       </c>
       <c r="N34" t="n">
-        <v>5122.23</v>
+        <v>5064.35</v>
       </c>
       <c r="O34" t="n">
-        <v>5238.4</v>
+        <v>5149.8</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3341,8 +3341,10 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
@@ -3367,57 +3369,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4710</v>
+        <v>4811.8</v>
       </c>
       <c r="C35" t="n">
-        <v>4917.7</v>
+        <v>4854.8</v>
       </c>
       <c r="D35" t="n">
-        <v>4626</v>
+        <v>4672.2</v>
       </c>
       <c r="E35" t="n">
-        <v>4879.6</v>
+        <v>4740.9</v>
       </c>
       <c r="F35" t="n">
-        <v>92.2</v>
+        <v>-138.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0193</v>
+        <v>-0.0284</v>
       </c>
       <c r="H35" t="n">
-        <v>291.7</v>
+        <v>182.6</v>
       </c>
       <c r="I35" t="n">
-        <v>4364.4</v>
+        <v>4334.3</v>
       </c>
       <c r="J35" t="n">
-        <v>4540.75</v>
+        <v>4641.77</v>
       </c>
       <c r="K35" t="n">
-        <v>4656.5</v>
+        <v>4733.75</v>
       </c>
       <c r="L35" t="n">
-        <v>4772.25</v>
+        <v>4825.73</v>
       </c>
       <c r="M35" t="n">
-        <v>4918.3</v>
+        <v>5025.45</v>
       </c>
       <c r="N35" t="n">
-        <v>5064.35</v>
+        <v>5225.18</v>
       </c>
       <c r="O35" t="n">
-        <v>5149.8</v>
+        <v>5209.4</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3427,19 +3429,17 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3453,63 +3453,65 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4811.8</v>
+        <v>4713.1</v>
       </c>
       <c r="C36" t="n">
-        <v>4854.8</v>
+        <v>4745.8</v>
       </c>
       <c r="D36" t="n">
-        <v>4672.2</v>
+        <v>4522.2</v>
       </c>
       <c r="E36" t="n">
-        <v>4740.9</v>
+        <v>4644.5</v>
       </c>
       <c r="F36" t="n">
-        <v>-138.7</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0284</v>
+        <v>-0.0203</v>
       </c>
       <c r="H36" t="n">
-        <v>182.6</v>
+        <v>223.6</v>
       </c>
       <c r="I36" t="n">
-        <v>4334.3</v>
+        <v>4489.6</v>
       </c>
       <c r="J36" t="n">
-        <v>4641.77</v>
+        <v>4547</v>
       </c>
       <c r="K36" t="n">
-        <v>4733.75</v>
+        <v>4649.6</v>
       </c>
       <c r="L36" t="n">
-        <v>4825.73</v>
+        <v>4752.2</v>
       </c>
       <c r="M36" t="n">
-        <v>5025.45</v>
+        <v>4832.2</v>
       </c>
       <c r="N36" t="n">
-        <v>5225.18</v>
+        <v>4912.2</v>
       </c>
       <c r="O36" t="n">
-        <v>5209.4</v>
+        <v>5037.4</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
@@ -3535,81 +3537,77 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4713.1</v>
+        <v>4644</v>
       </c>
       <c r="C37" t="n">
-        <v>4745.8</v>
+        <v>4775.2</v>
       </c>
       <c r="D37" t="n">
-        <v>4522.2</v>
+        <v>4510.1</v>
       </c>
       <c r="E37" t="n">
-        <v>4644.5</v>
+        <v>4730.7</v>
       </c>
       <c r="F37" t="n">
-        <v>-96.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0186</v>
       </c>
       <c r="H37" t="n">
-        <v>223.6</v>
+        <v>265.1</v>
       </c>
       <c r="I37" t="n">
-        <v>4489.6</v>
+        <v>4298.6</v>
       </c>
       <c r="J37" t="n">
-        <v>4547</v>
+        <v>4426.15</v>
       </c>
       <c r="K37" t="n">
-        <v>4649.6</v>
+        <v>4532.7</v>
       </c>
       <c r="L37" t="n">
-        <v>4752.2</v>
+        <v>4639.25</v>
       </c>
       <c r="M37" t="n">
-        <v>4832.2</v>
+        <v>4756.3</v>
       </c>
       <c r="N37" t="n">
-        <v>4912.2</v>
+        <v>4873.35</v>
       </c>
       <c r="O37" t="n">
-        <v>5037.4</v>
+        <v>4969.4</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3621,55 +3619,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4644</v>
+        <v>4690</v>
       </c>
       <c r="C38" t="n">
-        <v>4775.2</v>
+        <v>4783.4</v>
       </c>
       <c r="D38" t="n">
-        <v>4510.1</v>
+        <v>4513.8</v>
       </c>
       <c r="E38" t="n">
-        <v>4730.7</v>
+        <v>4561.9</v>
       </c>
       <c r="F38" t="n">
-        <v>86.2</v>
+        <v>-168.8</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0357</v>
       </c>
       <c r="H38" t="n">
-        <v>265.1</v>
+        <v>269.6</v>
       </c>
       <c r="I38" t="n">
-        <v>4298.6</v>
+        <v>4245</v>
       </c>
       <c r="J38" t="n">
-        <v>4426.15</v>
+        <v>4509.63</v>
       </c>
       <c r="K38" t="n">
-        <v>4532.7</v>
+        <v>4598.15</v>
       </c>
       <c r="L38" t="n">
-        <v>4639.25</v>
+        <v>4686.68</v>
       </c>
       <c r="M38" t="n">
-        <v>4756.3</v>
+        <v>4863.25</v>
       </c>
       <c r="N38" t="n">
-        <v>4873.35</v>
+        <v>5039.83</v>
       </c>
       <c r="O38" t="n">
-        <v>4969.4</v>
+        <v>5040.3</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3679,18 +3681,16 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3712,50 +3712,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4690</v>
+        <v>4547.6</v>
       </c>
       <c r="C39" t="n">
-        <v>4783.4</v>
+        <v>4593.2</v>
       </c>
       <c r="D39" t="n">
-        <v>4513.8</v>
+        <v>4455</v>
       </c>
       <c r="E39" t="n">
-        <v>4561.9</v>
+        <v>4523.2</v>
       </c>
       <c r="F39" t="n">
-        <v>-168.8</v>
+        <v>-38.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0357</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>269.6</v>
+        <v>138.2</v>
       </c>
       <c r="I39" t="n">
-        <v>4245</v>
+        <v>4244.2</v>
       </c>
       <c r="J39" t="n">
-        <v>4509.63</v>
+        <v>4248.95</v>
       </c>
       <c r="K39" t="n">
-        <v>4598.15</v>
+        <v>4427.1</v>
       </c>
       <c r="L39" t="n">
-        <v>4686.68</v>
+        <v>4605.25</v>
       </c>
       <c r="M39" t="n">
-        <v>4863.25</v>
+        <v>4696.7</v>
       </c>
       <c r="N39" t="n">
-        <v>5039.83</v>
+        <v>4788.15</v>
       </c>
       <c r="O39" t="n">
-        <v>5040.3</v>
+        <v>5053</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3763,14 +3763,12 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3787,76 +3785,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4547.6</v>
+        <v>4532</v>
       </c>
       <c r="C40" t="n">
-        <v>4593.2</v>
+        <v>4627.1</v>
       </c>
       <c r="D40" t="n">
-        <v>4455</v>
+        <v>4363.5</v>
       </c>
       <c r="E40" t="n">
-        <v>4523.2</v>
+        <v>4593</v>
       </c>
       <c r="F40" t="n">
-        <v>-38.7</v>
+        <v>69.8</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H40" t="n">
-        <v>138.2</v>
+        <v>263.6</v>
       </c>
       <c r="I40" t="n">
-        <v>4244.2</v>
+        <v>4316.8</v>
       </c>
       <c r="J40" t="n">
-        <v>4248.95</v>
+        <v>4384.55</v>
       </c>
       <c r="K40" t="n">
-        <v>4427.1</v>
+        <v>4454.1</v>
       </c>
       <c r="L40" t="n">
-        <v>4605.25</v>
+        <v>4523.65</v>
       </c>
       <c r="M40" t="n">
-        <v>4696.7</v>
+        <v>4592.3</v>
       </c>
       <c r="N40" t="n">
-        <v>4788.15</v>
+        <v>4660.95</v>
       </c>
       <c r="O40" t="n">
-        <v>5053</v>
+        <v>4731.4</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3869,78 +3869,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4532</v>
+        <v>4575.2</v>
       </c>
       <c r="C41" t="n">
-        <v>4627.1</v>
+        <v>4577.3</v>
       </c>
       <c r="D41" t="n">
-        <v>4363.5</v>
+        <v>4336.6</v>
       </c>
       <c r="E41" t="n">
-        <v>4593</v>
+        <v>4365.3</v>
       </c>
       <c r="F41" t="n">
-        <v>69.8</v>
+        <v>-227.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0154</v>
+        <v>-0.0496</v>
       </c>
       <c r="H41" t="n">
-        <v>263.6</v>
+        <v>240.7</v>
       </c>
       <c r="I41" t="n">
-        <v>4316.8</v>
+        <v>4099.9</v>
       </c>
       <c r="J41" t="n">
-        <v>4384.55</v>
+        <v>4378.25</v>
       </c>
       <c r="K41" t="n">
-        <v>4454.1</v>
+        <v>4461.2</v>
       </c>
       <c r="L41" t="n">
-        <v>4523.65</v>
+        <v>4544.15</v>
       </c>
       <c r="M41" t="n">
-        <v>4592.3</v>
+        <v>4724.8</v>
       </c>
       <c r="N41" t="n">
-        <v>4660.95</v>
+        <v>4905.45</v>
       </c>
       <c r="O41" t="n">
-        <v>4731.4</v>
+        <v>4890.7</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3953,71 +3955,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4575.2</v>
+        <v>4354</v>
       </c>
       <c r="C42" t="n">
-        <v>4577.3</v>
+        <v>4388.6</v>
       </c>
       <c r="D42" t="n">
-        <v>4336.6</v>
+        <v>4046.2</v>
       </c>
       <c r="E42" t="n">
-        <v>4365.3</v>
+        <v>4238.8</v>
       </c>
       <c r="F42" t="n">
-        <v>-227.7</v>
+        <v>-126.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0496</v>
+        <v>-0.029</v>
       </c>
       <c r="H42" t="n">
-        <v>240.7</v>
+        <v>342.4</v>
       </c>
       <c r="I42" t="n">
-        <v>4099.9</v>
+        <v>4095.9</v>
       </c>
       <c r="J42" t="n">
-        <v>4378.25</v>
+        <v>4078.78</v>
       </c>
       <c r="K42" t="n">
-        <v>4461.2</v>
+        <v>4244.95</v>
       </c>
       <c r="L42" t="n">
-        <v>4544.15</v>
+        <v>4411.12</v>
       </c>
       <c r="M42" t="n">
-        <v>4724.8</v>
+        <v>4485.65</v>
       </c>
       <c r="N42" t="n">
-        <v>4905.45</v>
+        <v>4560.17</v>
       </c>
       <c r="O42" t="n">
-        <v>4890.7</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
+        <v>4818</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4044,69 +4044,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4354</v>
+        <v>4289.4</v>
       </c>
       <c r="C43" t="n">
-        <v>4388.6</v>
+        <v>4403.6</v>
       </c>
       <c r="D43" t="n">
-        <v>4046.2</v>
+        <v>4138.7</v>
       </c>
       <c r="E43" t="n">
-        <v>4238.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F43" t="n">
-        <v>-126.5</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0155</v>
       </c>
       <c r="H43" t="n">
-        <v>342.4</v>
+        <v>264.9</v>
       </c>
       <c r="I43" t="n">
-        <v>4095.9</v>
+        <v>3703.8</v>
       </c>
       <c r="J43" t="n">
-        <v>4078.78</v>
+        <v>3907.1</v>
       </c>
       <c r="K43" t="n">
-        <v>4244.95</v>
+        <v>4067.6</v>
       </c>
       <c r="L43" t="n">
-        <v>4411.12</v>
+        <v>4228.1</v>
       </c>
       <c r="M43" t="n">
-        <v>4485.65</v>
+        <v>4410</v>
       </c>
       <c r="N43" t="n">
-        <v>4560.17</v>
+        <v>4591.9</v>
       </c>
       <c r="O43" t="n">
-        <v>4818</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4731</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4123,55 +4117,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4289.4</v>
+        <v>4163.9</v>
       </c>
       <c r="C44" t="n">
-        <v>4403.6</v>
+        <v>4238.1</v>
       </c>
       <c r="D44" t="n">
-        <v>4138.7</v>
+        <v>3975.7</v>
       </c>
       <c r="E44" t="n">
-        <v>4172.9</v>
+        <v>4096.3</v>
       </c>
       <c r="F44" t="n">
-        <v>-65.90000000000001</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0184</v>
       </c>
       <c r="H44" t="n">
-        <v>264.9</v>
+        <v>262.4</v>
       </c>
       <c r="I44" t="n">
-        <v>3703.8</v>
+        <v>3873.8</v>
       </c>
       <c r="J44" t="n">
-        <v>3907.1</v>
+        <v>3858.87</v>
       </c>
       <c r="K44" t="n">
-        <v>4067.6</v>
+        <v>4040.45</v>
       </c>
       <c r="L44" t="n">
-        <v>4228.1</v>
+        <v>4222.03</v>
       </c>
       <c r="M44" t="n">
-        <v>4410</v>
+        <v>4305.35</v>
       </c>
       <c r="N44" t="n">
-        <v>4591.9</v>
+        <v>4388.67</v>
       </c>
       <c r="O44" t="n">
-        <v>4731</v>
+        <v>4668.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4179,12 +4177,14 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4201,59 +4201,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4163.9</v>
+        <v>4101.1</v>
       </c>
       <c r="C45" t="n">
-        <v>4238.1</v>
+        <v>4208.3</v>
       </c>
       <c r="D45" t="n">
-        <v>3975.7</v>
+        <v>3955.4</v>
       </c>
       <c r="E45" t="n">
-        <v>4096.3</v>
+        <v>4187.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-76.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0222</v>
       </c>
       <c r="H45" t="n">
-        <v>262.4</v>
+        <v>252.9</v>
       </c>
       <c r="I45" t="n">
-        <v>3873.8</v>
+        <v>3713.3</v>
       </c>
       <c r="J45" t="n">
-        <v>3858.87</v>
+        <v>3828.6</v>
       </c>
       <c r="K45" t="n">
-        <v>4040.45</v>
+        <v>3965.1</v>
       </c>
       <c r="L45" t="n">
-        <v>4222.03</v>
+        <v>4101.6</v>
       </c>
       <c r="M45" t="n">
-        <v>4305.35</v>
+        <v>4227.5</v>
       </c>
       <c r="N45" t="n">
-        <v>4388.67</v>
+        <v>4353.4</v>
       </c>
       <c r="O45" t="n">
-        <v>4668.5</v>
+        <v>4500.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4263,17 +4259,19 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4285,55 +4283,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4101.1</v>
+        <v>4187.5</v>
       </c>
       <c r="C46" t="n">
-        <v>4208.3</v>
+        <v>4215.5</v>
       </c>
       <c r="D46" t="n">
-        <v>3955.4</v>
+        <v>4032.5</v>
       </c>
       <c r="E46" t="n">
-        <v>4187.3</v>
+        <v>4113.7</v>
       </c>
       <c r="F46" t="n">
-        <v>91</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0176</v>
       </c>
       <c r="H46" t="n">
-        <v>252.9</v>
+        <v>183</v>
       </c>
       <c r="I46" t="n">
-        <v>3713.3</v>
+        <v>3702.5</v>
       </c>
       <c r="J46" t="n">
-        <v>3828.6</v>
+        <v>3987.12</v>
       </c>
       <c r="K46" t="n">
-        <v>3965.1</v>
+        <v>4060.85</v>
       </c>
       <c r="L46" t="n">
-        <v>4101.6</v>
+        <v>4134.57</v>
       </c>
       <c r="M46" t="n">
-        <v>4227.5</v>
+        <v>4313.75</v>
       </c>
       <c r="N46" t="n">
-        <v>4353.4</v>
+        <v>4492.92</v>
       </c>
       <c r="O46" t="n">
-        <v>4500.5</v>
+        <v>4461.2</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4346,15 +4348,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4369,57 +4369,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4187.5</v>
+        <v>4106.6</v>
       </c>
       <c r="C47" t="n">
-        <v>4215.5</v>
+        <v>4112.5</v>
       </c>
       <c r="D47" t="n">
-        <v>4032.5</v>
+        <v>3963</v>
       </c>
       <c r="E47" t="n">
-        <v>4113.7</v>
+        <v>4018.8</v>
       </c>
       <c r="F47" t="n">
-        <v>-73.59999999999999</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0176</v>
+        <v>-0.0231</v>
       </c>
       <c r="H47" t="n">
-        <v>183</v>
+        <v>149.5</v>
       </c>
       <c r="I47" t="n">
-        <v>3702.5</v>
+        <v>3849.5</v>
       </c>
       <c r="J47" t="n">
-        <v>3987.12</v>
+        <v>3925.55</v>
       </c>
       <c r="K47" t="n">
-        <v>4060.85</v>
+        <v>4022.2</v>
       </c>
       <c r="L47" t="n">
-        <v>4134.57</v>
+        <v>4118.85</v>
       </c>
       <c r="M47" t="n">
-        <v>4313.75</v>
+        <v>4205.2</v>
       </c>
       <c r="N47" t="n">
-        <v>4492.92</v>
+        <v>4291.55</v>
       </c>
       <c r="O47" t="n">
-        <v>4461.2</v>
+        <v>4398.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4451,59 +4451,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4106.6</v>
+        <v>4005.6</v>
       </c>
       <c r="C48" t="n">
-        <v>4112.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D48" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E48" t="n">
-        <v>4018.8</v>
+        <v>4070.8</v>
       </c>
       <c r="F48" t="n">
-        <v>-94.90000000000001</v>
+        <v>52</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0129</v>
       </c>
       <c r="H48" t="n">
-        <v>149.5</v>
+        <v>184.9</v>
       </c>
       <c r="I48" t="n">
-        <v>3849.5</v>
+        <v>3813.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3925.55</v>
+        <v>3859.83</v>
       </c>
       <c r="K48" t="n">
-        <v>4022.2</v>
+        <v>3944.05</v>
       </c>
       <c r="L48" t="n">
-        <v>4118.85</v>
+        <v>4028.28</v>
       </c>
       <c r="M48" t="n">
-        <v>4205.2</v>
+        <v>4093.55</v>
       </c>
       <c r="N48" t="n">
-        <v>4291.55</v>
+        <v>4158.83</v>
       </c>
       <c r="O48" t="n">
-        <v>4398.5</v>
+        <v>4262</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4511,21 +4507,23 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4535,55 +4533,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4005.6</v>
+        <v>4097.5</v>
       </c>
       <c r="C49" t="n">
-        <v>4171.4</v>
+        <v>4170.7</v>
       </c>
       <c r="D49" t="n">
-        <v>3986.5</v>
+        <v>3993.8</v>
       </c>
       <c r="E49" t="n">
-        <v>4070.8</v>
+        <v>4107</v>
       </c>
       <c r="F49" t="n">
-        <v>52</v>
+        <v>36.2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0089</v>
       </c>
       <c r="H49" t="n">
-        <v>184.9</v>
+        <v>176.9</v>
       </c>
       <c r="I49" t="n">
-        <v>3813.5</v>
+        <v>3801.6</v>
       </c>
       <c r="J49" t="n">
-        <v>3859.83</v>
+        <v>3881.83</v>
       </c>
       <c r="K49" t="n">
-        <v>3944.05</v>
+        <v>3978.35</v>
       </c>
       <c r="L49" t="n">
-        <v>4028.28</v>
+        <v>4074.88</v>
       </c>
       <c r="M49" t="n">
-        <v>4093.55</v>
+        <v>4163.25</v>
       </c>
       <c r="N49" t="n">
-        <v>4158.83</v>
+        <v>4251.62</v>
       </c>
       <c r="O49" t="n">
-        <v>4262</v>
+        <v>4356.3</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4596,19 +4598,17 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4619,57 +4619,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4097.5</v>
+        <v>4135.2</v>
       </c>
       <c r="C50" t="n">
-        <v>4170.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D50" t="n">
-        <v>3993.8</v>
+        <v>4074</v>
       </c>
       <c r="E50" t="n">
-        <v>4107</v>
+        <v>4399.7</v>
       </c>
       <c r="F50" t="n">
-        <v>36.2</v>
+        <v>292.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0089</v>
+        <v>0.0713</v>
       </c>
       <c r="H50" t="n">
-        <v>176.9</v>
+        <v>358.3</v>
       </c>
       <c r="I50" t="n">
-        <v>3801.6</v>
+        <v>3816.9</v>
       </c>
       <c r="J50" t="n">
-        <v>3881.83</v>
+        <v>3942.47</v>
       </c>
       <c r="K50" t="n">
-        <v>3978.35</v>
+        <v>4018.55</v>
       </c>
       <c r="L50" t="n">
-        <v>4074.88</v>
+        <v>4094.63</v>
       </c>
       <c r="M50" t="n">
-        <v>4163.25</v>
+        <v>4195.45</v>
       </c>
       <c r="N50" t="n">
-        <v>4251.62</v>
+        <v>4296.28</v>
       </c>
       <c r="O50" t="n">
-        <v>4356.3</v>
+        <v>4347.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -4690,70 +4690,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4135.2</v>
+        <v>4400</v>
       </c>
       <c r="C51" t="n">
-        <v>4432.3</v>
+        <v>4509.1</v>
       </c>
       <c r="D51" t="n">
-        <v>4074</v>
+        <v>4365.5</v>
       </c>
       <c r="E51" t="n">
-        <v>4399.7</v>
+        <v>4437.3</v>
       </c>
       <c r="F51" t="n">
-        <v>292.7</v>
+        <v>37.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0713</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>358.3</v>
+        <v>143.6</v>
       </c>
       <c r="I51" t="n">
-        <v>3816.9</v>
+        <v>3715.7</v>
       </c>
       <c r="J51" t="n">
-        <v>3942.47</v>
+        <v>4114.68</v>
       </c>
       <c r="K51" t="n">
-        <v>4018.55</v>
+        <v>4220.55</v>
       </c>
       <c r="L51" t="n">
-        <v>4094.63</v>
+        <v>4326.43</v>
       </c>
       <c r="M51" t="n">
-        <v>4195.45</v>
+        <v>4578.85</v>
       </c>
       <c r="N51" t="n">
-        <v>4296.28</v>
+        <v>4831.28</v>
       </c>
       <c r="O51" t="n">
-        <v>4347.6</v>
+        <v>4790.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4766,23 +4766,17 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
@@ -4794,50 +4788,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4400</v>
+        <v>4440</v>
       </c>
       <c r="C52" t="n">
+        <v>4690.4</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4378</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4680.6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>243.3</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H52" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4221.9</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4293.7</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4365.5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>4437.3</v>
+      </c>
+      <c r="M52" t="n">
         <v>4509.1</v>
       </c>
-      <c r="D52" t="n">
-        <v>4365.5</v>
-      </c>
-      <c r="E52" t="n">
-        <v>4437.3</v>
-      </c>
-      <c r="F52" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="H52" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="I52" t="n">
-        <v>3715.7</v>
-      </c>
-      <c r="J52" t="n">
-        <v>4114.68</v>
-      </c>
-      <c r="K52" t="n">
-        <v>4220.55</v>
-      </c>
-      <c r="L52" t="n">
-        <v>4326.43</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4578.85</v>
-      </c>
       <c r="N52" t="n">
-        <v>4831.28</v>
+        <v>4580.9</v>
       </c>
       <c r="O52" t="n">
-        <v>4790.6</v>
+        <v>4652.7</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4850,17 +4844,23 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4872,50 +4872,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4440</v>
+        <v>4673.4</v>
       </c>
       <c r="C53" t="n">
-        <v>4690.4</v>
+        <v>4755</v>
       </c>
       <c r="D53" t="n">
-        <v>4378</v>
+        <v>4495</v>
       </c>
       <c r="E53" t="n">
-        <v>4680.6</v>
+        <v>4529.9</v>
       </c>
       <c r="F53" t="n">
-        <v>243.3</v>
+        <v>-150.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0548</v>
+        <v>-0.0322</v>
       </c>
       <c r="H53" t="n">
-        <v>312.4</v>
+        <v>260</v>
       </c>
       <c r="I53" t="n">
-        <v>4221.9</v>
+        <v>4065.6</v>
       </c>
       <c r="J53" t="n">
-        <v>4293.7</v>
+        <v>4441.4</v>
       </c>
       <c r="K53" t="n">
-        <v>4365.5</v>
+        <v>4524.4</v>
       </c>
       <c r="L53" t="n">
-        <v>4437.3</v>
+        <v>4607.4</v>
       </c>
       <c r="M53" t="n">
-        <v>4509.1</v>
+        <v>4836.8</v>
       </c>
       <c r="N53" t="n">
-        <v>4580.9</v>
+        <v>5066.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4652.7</v>
+        <v>5002.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4923,83 +4923,83 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4673.4</v>
+        <v>4483.2</v>
       </c>
       <c r="C54" t="n">
-        <v>4755</v>
+        <v>4558.5</v>
       </c>
       <c r="D54" t="n">
-        <v>4495</v>
+        <v>4329.2</v>
       </c>
       <c r="E54" t="n">
-        <v>4529.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F54" t="n">
-        <v>-150.7</v>
+        <v>-53.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0118</v>
       </c>
       <c r="H54" t="n">
-        <v>260</v>
+        <v>229.3</v>
       </c>
       <c r="I54" t="n">
-        <v>4065.6</v>
+        <v>4235</v>
       </c>
       <c r="J54" t="n">
-        <v>4441.4</v>
+        <v>4222.35</v>
       </c>
       <c r="K54" t="n">
-        <v>4524.4</v>
+        <v>4399.9</v>
       </c>
       <c r="L54" t="n">
-        <v>4607.4</v>
+        <v>4577.45</v>
       </c>
       <c r="M54" t="n">
-        <v>4836.8</v>
+        <v>4659.9</v>
       </c>
       <c r="N54" t="n">
-        <v>5066.2</v>
+        <v>4742.35</v>
       </c>
       <c r="O54" t="n">
-        <v>5002.8</v>
+        <v>5015</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5033,57 +5033,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4483.2</v>
+        <v>4466.5</v>
       </c>
       <c r="C55" t="n">
-        <v>4558.5</v>
+        <v>4488.8</v>
       </c>
       <c r="D55" t="n">
-        <v>4329.2</v>
+        <v>4333</v>
       </c>
       <c r="E55" t="n">
-        <v>4476.6</v>
+        <v>4408.9</v>
       </c>
       <c r="F55" t="n">
-        <v>-53.3</v>
+        <v>-67.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0151</v>
       </c>
       <c r="H55" t="n">
-        <v>229.3</v>
+        <v>155.8</v>
       </c>
       <c r="I55" t="n">
-        <v>4235</v>
+        <v>4099.9</v>
       </c>
       <c r="J55" t="n">
-        <v>4222.35</v>
+        <v>4263.68</v>
       </c>
       <c r="K55" t="n">
-        <v>4399.9</v>
+        <v>4361.95</v>
       </c>
       <c r="L55" t="n">
-        <v>4577.45</v>
+        <v>4460.23</v>
       </c>
       <c r="M55" t="n">
-        <v>4659.9</v>
+        <v>4591.25</v>
       </c>
       <c r="N55" t="n">
-        <v>4742.35</v>
+        <v>4722.27</v>
       </c>
       <c r="O55" t="n">
-        <v>5015</v>
+        <v>4787.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5117,57 +5117,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4466.5</v>
+        <v>4375</v>
       </c>
       <c r="C56" t="n">
-        <v>4488.8</v>
+        <v>4439.8</v>
       </c>
       <c r="D56" t="n">
-        <v>4333</v>
+        <v>4273.3</v>
       </c>
       <c r="E56" t="n">
-        <v>4408.9</v>
+        <v>4424.9</v>
       </c>
       <c r="F56" t="n">
-        <v>-67.7</v>
+        <v>16</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0151</v>
+        <v>0.0036</v>
       </c>
       <c r="H56" t="n">
-        <v>155.8</v>
+        <v>166.5</v>
       </c>
       <c r="I56" t="n">
-        <v>4099.9</v>
+        <v>4177.2</v>
       </c>
       <c r="J56" t="n">
-        <v>4263.68</v>
+        <v>4252.1</v>
       </c>
       <c r="K56" t="n">
-        <v>4361.95</v>
+        <v>4331</v>
       </c>
       <c r="L56" t="n">
-        <v>4460.23</v>
+        <v>4409.9</v>
       </c>
       <c r="M56" t="n">
-        <v>4591.25</v>
+        <v>4486.8</v>
       </c>
       <c r="N56" t="n">
-        <v>4722.27</v>
+        <v>4563.7</v>
       </c>
       <c r="O56" t="n">
-        <v>4787.8</v>
+        <v>4644.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5177,12 +5177,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5208,65 +5208,67 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4375</v>
+        <v>4413</v>
       </c>
       <c r="C57" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D57" t="n">
-        <v>4273.3</v>
+        <v>4278.3</v>
       </c>
       <c r="E57" t="n">
-        <v>4424.9</v>
+        <v>4321.2</v>
       </c>
       <c r="F57" t="n">
-        <v>16</v>
+        <v>-103.7</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0234</v>
       </c>
       <c r="H57" t="n">
-        <v>166.5</v>
+        <v>143.8</v>
       </c>
       <c r="I57" t="n">
-        <v>4177.2</v>
+        <v>4106.8</v>
       </c>
       <c r="J57" t="n">
-        <v>4252.1</v>
+        <v>4292.57</v>
       </c>
       <c r="K57" t="n">
-        <v>4331</v>
+        <v>4341.65</v>
       </c>
       <c r="L57" t="n">
-        <v>4409.9</v>
+        <v>4390.72</v>
       </c>
       <c r="M57" t="n">
-        <v>4486.8</v>
+        <v>4508.15</v>
       </c>
       <c r="N57" t="n">
-        <v>4563.7</v>
+        <v>4625.57</v>
       </c>
       <c r="O57" t="n">
-        <v>4644.6</v>
+        <v>4606.3</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5284,92 +5286,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4413</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4422.1</v>
-      </c>
-      <c r="D58" t="n">
-        <v>4307.1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>4308.1</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-116.8</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0264</v>
-      </c>
-      <c r="H58" t="n">
-        <v>115</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4106.8</v>
-      </c>
-      <c r="J58" t="n">
-        <v>4292.57</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4341.65</v>
-      </c>
-      <c r="L58" t="n">
-        <v>4390.72</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4508.15</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4625.57</v>
-      </c>
-      <c r="O58" t="n">
-        <v>4606.3</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5291,6 +5291,88 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4150.1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4153.9</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4147.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4153.7</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-167.5</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0388</v>
+      </c>
+      <c r="H58" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4134.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4162.9</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4249.3</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4335.7</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4393.1</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4450.5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4565.9</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5298,25 +5298,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4150.1</v>
+        <v>4216.2</v>
       </c>
       <c r="C58" t="n">
-        <v>4153.9</v>
+        <v>4217.3</v>
       </c>
       <c r="D58" t="n">
-        <v>4147.8</v>
+        <v>4212.8</v>
       </c>
       <c r="E58" t="n">
-        <v>4153.7</v>
+        <v>4214.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-167.5</v>
+        <v>-106.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0388</v>
+        <v>-0.0246</v>
       </c>
       <c r="H58" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="I58" t="n">
         <v>4134.5</v>
@@ -5342,16 +5342,14 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5366,12 +5364,16 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>149.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3273.7</v>
+        <v>3325.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3423.1</v>
+        <v>3442.68</v>
       </c>
       <c r="K2" t="n">
-        <v>3454.9</v>
+        <v>3467.95</v>
       </c>
       <c r="L2" t="n">
-        <v>3486.7</v>
+        <v>3493.23</v>
       </c>
       <c r="M2" t="n">
-        <v>3577.3</v>
+        <v>3564.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3667.9</v>
+        <v>3635.28</v>
       </c>
       <c r="O2" t="n">
-        <v>3640.9</v>
+        <v>3614.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,12 +698,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5298,25 +5300,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4216.2</v>
+        <v>4315</v>
       </c>
       <c r="C58" t="n">
-        <v>4217.3</v>
+        <v>4315.6</v>
       </c>
       <c r="D58" t="n">
-        <v>4212.8</v>
+        <v>4143.1</v>
       </c>
       <c r="E58" t="n">
-        <v>4214.9</v>
+        <v>4190.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-106.3</v>
+        <v>-130.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0246</v>
+        <v>-0.0302</v>
       </c>
       <c r="H58" t="n">
-        <v>4.5</v>
+        <v>172.5</v>
       </c>
       <c r="I58" t="n">
         <v>4134.5</v>
@@ -5342,12 +5344,14 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>149.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3325.9</v>
+        <v>3366.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3442.68</v>
+        <v>3457.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3467.95</v>
+        <v>3478.1</v>
       </c>
       <c r="L2" t="n">
-        <v>3493.23</v>
+        <v>3498.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3564.25</v>
+        <v>3554.1</v>
       </c>
       <c r="N2" t="n">
-        <v>3635.28</v>
+        <v>3609.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3614.8</v>
+        <v>3594.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5309,13 +5309,13 @@
         <v>4143.1</v>
       </c>
       <c r="E58" t="n">
-        <v>4190.6</v>
+        <v>4205.3</v>
       </c>
       <c r="F58" t="n">
-        <v>-130.6</v>
+        <v>-115.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0302</v>
+        <v>-0.0268</v>
       </c>
       <c r="H58" t="n">
         <v>172.5</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3517.9</v>
+        <v>3635</v>
       </c>
       <c r="C2" t="n">
-        <v>3655.5</v>
+        <v>3715.2</v>
       </c>
       <c r="D2" t="n">
-        <v>3506</v>
+        <v>3621.7</v>
       </c>
       <c r="E2" t="n">
-        <v>3653.3</v>
+        <v>3686.4</v>
       </c>
       <c r="F2" t="n">
-        <v>137.2</v>
+        <v>33.1</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.039</v>
+        <v>0.0091</v>
       </c>
       <c r="H2" t="n">
-        <v>149.5</v>
+        <v>93.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3366.5</v>
+        <v>3356.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3457.9</v>
+        <v>3540.08</v>
       </c>
       <c r="K2" t="n">
-        <v>3478.1</v>
+        <v>3578.55</v>
       </c>
       <c r="L2" t="n">
-        <v>3498.3</v>
+        <v>3617.03</v>
       </c>
       <c r="M2" t="n">
-        <v>3554.1</v>
+        <v>3728.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3609.9</v>
+        <v>3839.08</v>
       </c>
       <c r="O2" t="n">
-        <v>3594.5</v>
+        <v>3805</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,18 +695,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -718,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3635</v>
+        <v>3680.2</v>
       </c>
       <c r="C3" t="n">
-        <v>3715.2</v>
+        <v>3744</v>
       </c>
       <c r="D3" t="n">
-        <v>3621.7</v>
+        <v>3660.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3686.4</v>
+        <v>3705.8</v>
       </c>
       <c r="F3" t="n">
-        <v>33.1</v>
+        <v>19.4</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0053</v>
       </c>
       <c r="H3" t="n">
-        <v>93.5</v>
+        <v>83.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3356.5</v>
+        <v>3528.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3540.08</v>
+        <v>3601.87</v>
       </c>
       <c r="K3" t="n">
-        <v>3578.55</v>
+        <v>3639.65</v>
       </c>
       <c r="L3" t="n">
-        <v>3617.03</v>
+        <v>3677.42</v>
       </c>
       <c r="M3" t="n">
-        <v>3728.05</v>
+        <v>3733.15</v>
       </c>
       <c r="N3" t="n">
-        <v>3839.08</v>
+        <v>3788.87</v>
       </c>
       <c r="O3" t="n">
-        <v>3805</v>
+        <v>3808.7</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -798,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3680.2</v>
+        <v>3721.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3744</v>
+        <v>3824.6</v>
       </c>
       <c r="D4" t="n">
-        <v>3660.5</v>
+        <v>3718.1</v>
       </c>
       <c r="E4" t="n">
-        <v>3705.8</v>
+        <v>3809</v>
       </c>
       <c r="F4" t="n">
-        <v>19.4</v>
+        <v>103.2</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0278</v>
       </c>
       <c r="H4" t="n">
-        <v>83.5</v>
+        <v>106.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3528.2</v>
+        <v>3577</v>
       </c>
       <c r="J4" t="n">
-        <v>3601.87</v>
+        <v>3624.08</v>
       </c>
       <c r="K4" t="n">
-        <v>3639.65</v>
+        <v>3664.05</v>
       </c>
       <c r="L4" t="n">
-        <v>3677.42</v>
+        <v>3704.03</v>
       </c>
       <c r="M4" t="n">
-        <v>3733.15</v>
+        <v>3747.55</v>
       </c>
       <c r="N4" t="n">
-        <v>3788.87</v>
+        <v>3791.08</v>
       </c>
       <c r="O4" t="n">
-        <v>3808.7</v>
+        <v>3827.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,11 +855,13 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -878,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3721.3</v>
+        <v>3788.8</v>
       </c>
       <c r="C5" t="n">
-        <v>3824.6</v>
+        <v>3923.3</v>
       </c>
       <c r="D5" t="n">
-        <v>3718.1</v>
+        <v>3785.5</v>
       </c>
       <c r="E5" t="n">
-        <v>3809</v>
+        <v>3908.9</v>
       </c>
       <c r="F5" t="n">
-        <v>103.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0262</v>
       </c>
       <c r="H5" t="n">
-        <v>106.5</v>
+        <v>137.8</v>
       </c>
       <c r="I5" t="n">
-        <v>3577</v>
+        <v>3611.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3624.08</v>
+        <v>3721.32</v>
       </c>
       <c r="K5" t="n">
-        <v>3664.05</v>
+        <v>3755.75</v>
       </c>
       <c r="L5" t="n">
-        <v>3704.03</v>
+        <v>3790.18</v>
       </c>
       <c r="M5" t="n">
-        <v>3747.55</v>
+        <v>3862.25</v>
       </c>
       <c r="N5" t="n">
-        <v>3791.08</v>
+        <v>3934.32</v>
       </c>
       <c r="O5" t="n">
-        <v>3827.5</v>
+        <v>3931.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,13 +940,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -960,50 +958,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3788.8</v>
+        <v>3913.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3923.3</v>
+        <v>4081</v>
       </c>
       <c r="D6" t="n">
-        <v>3785.5</v>
+        <v>3909.2</v>
       </c>
       <c r="E6" t="n">
-        <v>3908.9</v>
+        <v>4000.4</v>
       </c>
       <c r="F6" t="n">
-        <v>99.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0262</v>
+        <v>0.0234</v>
       </c>
       <c r="H6" t="n">
-        <v>137.8</v>
+        <v>171.8</v>
       </c>
       <c r="I6" t="n">
-        <v>3611.6</v>
+        <v>3647.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3721.32</v>
+        <v>3798.35</v>
       </c>
       <c r="K6" t="n">
-        <v>3755.75</v>
+        <v>3840</v>
       </c>
       <c r="L6" t="n">
-        <v>3790.18</v>
+        <v>3881.65</v>
       </c>
       <c r="M6" t="n">
-        <v>3862.25</v>
+        <v>3977.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3934.32</v>
+        <v>4073.95</v>
       </c>
       <c r="O6" t="n">
-        <v>3931.1</v>
+        <v>4061.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,15 +1019,17 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
@@ -1042,50 +1042,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3913.5</v>
+        <v>4018.3</v>
       </c>
       <c r="C7" t="n">
-        <v>4081</v>
+        <v>4392</v>
       </c>
       <c r="D7" t="n">
-        <v>3909.2</v>
+        <v>4011.3</v>
       </c>
       <c r="E7" t="n">
-        <v>4000.4</v>
+        <v>4213.3</v>
       </c>
       <c r="F7" t="n">
-        <v>91.5</v>
+        <v>212.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0532</v>
       </c>
       <c r="H7" t="n">
-        <v>171.8</v>
+        <v>380.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3647.7</v>
+        <v>3737.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3798.35</v>
+        <v>3831.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3840</v>
+        <v>3914.5</v>
       </c>
       <c r="L7" t="n">
-        <v>3881.65</v>
+        <v>3997.75</v>
       </c>
       <c r="M7" t="n">
-        <v>3977.8</v>
+        <v>4086.3</v>
       </c>
       <c r="N7" t="n">
-        <v>4073.95</v>
+        <v>4174.85</v>
       </c>
       <c r="O7" t="n">
-        <v>4061.1</v>
+        <v>4252.8</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V7" s="8" t="inlineStr">
@@ -1126,50 +1126,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4018.3</v>
+        <v>4269</v>
       </c>
       <c r="C8" t="n">
-        <v>4392</v>
+        <v>4398</v>
       </c>
       <c r="D8" t="n">
-        <v>4011.3</v>
+        <v>4021.2</v>
       </c>
       <c r="E8" t="n">
-        <v>4213.3</v>
+        <v>4137.8</v>
       </c>
       <c r="F8" t="n">
-        <v>212.9</v>
+        <v>-75.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0532</v>
+        <v>-0.0179</v>
       </c>
       <c r="H8" t="n">
-        <v>380.7</v>
+        <v>376.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3737.4</v>
+        <v>3630.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3831.25</v>
+        <v>3838.42</v>
       </c>
       <c r="K8" t="n">
-        <v>3914.5</v>
+        <v>4022.95</v>
       </c>
       <c r="L8" t="n">
-        <v>3997.75</v>
+        <v>4207.47</v>
       </c>
       <c r="M8" t="n">
-        <v>4086.3</v>
+        <v>4403.65</v>
       </c>
       <c r="N8" t="n">
-        <v>4174.85</v>
+        <v>4599.82</v>
       </c>
       <c r="O8" t="n">
-        <v>4252.8</v>
+        <v>4772.7</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1177,83 +1177,83 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4269</v>
+        <v>4103.2</v>
       </c>
       <c r="C9" t="n">
-        <v>4398</v>
+        <v>4123.8</v>
       </c>
       <c r="D9" t="n">
-        <v>4021.2</v>
+        <v>3901.3</v>
       </c>
       <c r="E9" t="n">
-        <v>4137.8</v>
+        <v>3996.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-75.5</v>
+        <v>-141.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0179</v>
+        <v>-0.0341</v>
       </c>
       <c r="H9" t="n">
-        <v>376.8</v>
+        <v>222.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3630.6</v>
+        <v>3644.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3838.42</v>
+        <v>3725.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4022.95</v>
+        <v>3949.4</v>
       </c>
       <c r="L9" t="n">
-        <v>4207.47</v>
+        <v>4173.7</v>
       </c>
       <c r="M9" t="n">
-        <v>4403.65</v>
+        <v>4326.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4599.82</v>
+        <v>4478.7</v>
       </c>
       <c r="O9" t="n">
-        <v>4772.7</v>
+        <v>4774.8</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1287,57 +1287,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4103.2</v>
+        <v>4001</v>
       </c>
       <c r="C10" t="n">
-        <v>4123.8</v>
+        <v>4043.1</v>
       </c>
       <c r="D10" t="n">
-        <v>3901.3</v>
+        <v>3935.7</v>
       </c>
       <c r="E10" t="n">
-        <v>3996.5</v>
+        <v>4009.8</v>
       </c>
       <c r="F10" t="n">
-        <v>-141.3</v>
+        <v>13.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0341</v>
+        <v>0.0033</v>
       </c>
       <c r="H10" t="n">
-        <v>222.5</v>
+        <v>107.4</v>
       </c>
       <c r="I10" t="n">
-        <v>3644.4</v>
+        <v>3678.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3725.1</v>
+        <v>3765.98</v>
       </c>
       <c r="K10" t="n">
-        <v>3949.4</v>
+        <v>3885.25</v>
       </c>
       <c r="L10" t="n">
-        <v>4173.7</v>
+        <v>4004.52</v>
       </c>
       <c r="M10" t="n">
-        <v>4326.2</v>
+        <v>4107.75</v>
       </c>
       <c r="N10" t="n">
-        <v>4478.7</v>
+        <v>4210.97</v>
       </c>
       <c r="O10" t="n">
-        <v>4774.8</v>
+        <v>4346.3</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1345,14 +1345,12 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1371,57 +1369,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4001</v>
+        <v>4007.2</v>
       </c>
       <c r="C11" t="n">
-        <v>4043.1</v>
+        <v>4250</v>
       </c>
       <c r="D11" t="n">
-        <v>3935.7</v>
+        <v>4004.2</v>
       </c>
       <c r="E11" t="n">
-        <v>4009.8</v>
+        <v>4094.2</v>
       </c>
       <c r="F11" t="n">
-        <v>13.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.021</v>
       </c>
       <c r="H11" t="n">
-        <v>107.4</v>
+        <v>245.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3678.8</v>
+        <v>3828.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3765.98</v>
+        <v>3912.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3885.25</v>
+        <v>3956.1</v>
       </c>
       <c r="L11" t="n">
-        <v>4004.52</v>
+        <v>3999.6</v>
       </c>
       <c r="M11" t="n">
-        <v>4107.75</v>
+        <v>4063.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4210.97</v>
+        <v>4127.4</v>
       </c>
       <c r="O11" t="n">
-        <v>4346.3</v>
+        <v>4150.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1434,76 +1432,78 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4007.2</v>
+        <v>4084.4</v>
       </c>
       <c r="C12" t="n">
-        <v>4250</v>
+        <v>4134.3</v>
       </c>
       <c r="D12" t="n">
-        <v>4004.2</v>
+        <v>3997.4</v>
       </c>
       <c r="E12" t="n">
-        <v>4094.2</v>
+        <v>4079.5</v>
       </c>
       <c r="F12" t="n">
-        <v>84.40000000000001</v>
+        <v>-14.7</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.0036</v>
       </c>
       <c r="H12" t="n">
-        <v>245.8</v>
+        <v>136.9</v>
       </c>
       <c r="I12" t="n">
-        <v>3828.3</v>
+        <v>3758.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3912.6</v>
+        <v>3831.95</v>
       </c>
       <c r="K12" t="n">
-        <v>3956.1</v>
+        <v>3971.3</v>
       </c>
       <c r="L12" t="n">
-        <v>3999.6</v>
+        <v>4110.65</v>
       </c>
       <c r="M12" t="n">
-        <v>4063.5</v>
+        <v>4217.1</v>
       </c>
       <c r="N12" t="n">
-        <v>4127.4</v>
+        <v>4323.55</v>
       </c>
       <c r="O12" t="n">
-        <v>4150.5</v>
+        <v>4495.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1514,80 +1514,78 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4084.4</v>
+        <v>4069.2</v>
       </c>
       <c r="C13" t="n">
-        <v>4134.3</v>
+        <v>4263.1</v>
       </c>
       <c r="D13" t="n">
-        <v>3997.4</v>
+        <v>4036.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4079.5</v>
+        <v>4254.9</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.7</v>
+        <v>175.4</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.043</v>
       </c>
       <c r="H13" t="n">
-        <v>136.9</v>
+        <v>226.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3758.4</v>
+        <v>3860.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3831.95</v>
+        <v>3949.43</v>
       </c>
       <c r="K13" t="n">
-        <v>3971.3</v>
+        <v>4011.05</v>
       </c>
       <c r="L13" t="n">
-        <v>4110.65</v>
+        <v>4072.67</v>
       </c>
       <c r="M13" t="n">
-        <v>4217.1</v>
+        <v>4147.95</v>
       </c>
       <c r="N13" t="n">
-        <v>4323.55</v>
+        <v>4223.22</v>
       </c>
       <c r="O13" t="n">
-        <v>4495.8</v>
+        <v>4271.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1598,78 +1596,80 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4069.2</v>
+        <v>4258.5</v>
       </c>
       <c r="C14" t="n">
-        <v>4263.1</v>
+        <v>4299.6</v>
       </c>
       <c r="D14" t="n">
-        <v>4036.4</v>
+        <v>4194</v>
       </c>
       <c r="E14" t="n">
-        <v>4254.9</v>
+        <v>4243</v>
       </c>
       <c r="F14" t="n">
-        <v>175.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.043</v>
+        <v>-0.0028</v>
       </c>
       <c r="H14" t="n">
-        <v>226.7</v>
+        <v>105.6</v>
       </c>
       <c r="I14" t="n">
-        <v>3860.5</v>
+        <v>3809.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3949.43</v>
+        <v>4080.77</v>
       </c>
       <c r="K14" t="n">
-        <v>4011.05</v>
+        <v>4141.55</v>
       </c>
       <c r="L14" t="n">
-        <v>4072.67</v>
+        <v>4202.32</v>
       </c>
       <c r="M14" t="n">
-        <v>4147.95</v>
+        <v>4368.25</v>
       </c>
       <c r="N14" t="n">
-        <v>4223.22</v>
+        <v>4534.18</v>
       </c>
       <c r="O14" t="n">
-        <v>4271.2</v>
+        <v>4489.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1682,78 +1682,76 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4258.5</v>
+        <v>4228.1</v>
       </c>
       <c r="C15" t="n">
-        <v>4299.6</v>
+        <v>4387.8</v>
       </c>
       <c r="D15" t="n">
-        <v>4194</v>
+        <v>4197.8</v>
       </c>
       <c r="E15" t="n">
-        <v>4243</v>
+        <v>4328.3</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.9</v>
+        <v>85.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0201</v>
       </c>
       <c r="H15" t="n">
-        <v>105.6</v>
+        <v>190</v>
       </c>
       <c r="I15" t="n">
-        <v>3809.7</v>
+        <v>4088.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4080.77</v>
+        <v>4135.5</v>
       </c>
       <c r="K15" t="n">
-        <v>4141.55</v>
+        <v>4190.2</v>
       </c>
       <c r="L15" t="n">
-        <v>4202.32</v>
+        <v>4244.9</v>
       </c>
       <c r="M15" t="n">
-        <v>4368.25</v>
+        <v>4295.8</v>
       </c>
       <c r="N15" t="n">
-        <v>4534.18</v>
+        <v>4346.7</v>
       </c>
       <c r="O15" t="n">
-        <v>4489.8</v>
+        <v>4405.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1766,14 +1764,18 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1783,59 +1785,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4228.1</v>
+        <v>4330</v>
       </c>
       <c r="C16" t="n">
-        <v>4387.8</v>
+        <v>4409.5</v>
       </c>
       <c r="D16" t="n">
-        <v>4197.8</v>
+        <v>4297.4</v>
       </c>
       <c r="E16" t="n">
-        <v>4328.3</v>
+        <v>4387.3</v>
       </c>
       <c r="F16" t="n">
-        <v>85.3</v>
+        <v>59</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0136</v>
       </c>
       <c r="H16" t="n">
-        <v>190</v>
+        <v>112.1</v>
       </c>
       <c r="I16" t="n">
-        <v>4088.4</v>
+        <v>4007.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4135.5</v>
+        <v>4156.05</v>
       </c>
       <c r="K16" t="n">
-        <v>4190.2</v>
+        <v>4233.3</v>
       </c>
       <c r="L16" t="n">
-        <v>4244.9</v>
+        <v>4310.55</v>
       </c>
       <c r="M16" t="n">
-        <v>4295.8</v>
+        <v>4423.3</v>
       </c>
       <c r="N16" t="n">
-        <v>4346.7</v>
+        <v>4536.05</v>
       </c>
       <c r="O16" t="n">
-        <v>4405.2</v>
+        <v>4577.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,13 +1851,11 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1874,50 +1870,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4330</v>
+        <v>4369.9</v>
       </c>
       <c r="C17" t="n">
-        <v>4409.5</v>
+        <v>4584</v>
       </c>
       <c r="D17" t="n">
-        <v>4297.4</v>
+        <v>4367.9</v>
       </c>
       <c r="E17" t="n">
-        <v>4387.3</v>
+        <v>4552.7</v>
       </c>
       <c r="F17" t="n">
-        <v>59</v>
+        <v>165.4</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0377</v>
       </c>
       <c r="H17" t="n">
-        <v>112.1</v>
+        <v>216.1</v>
       </c>
       <c r="I17" t="n">
-        <v>4007.8</v>
+        <v>4185.3</v>
       </c>
       <c r="J17" t="n">
-        <v>4156.05</v>
+        <v>4292.12</v>
       </c>
       <c r="K17" t="n">
-        <v>4233.3</v>
+        <v>4331.25</v>
       </c>
       <c r="L17" t="n">
-        <v>4310.55</v>
+        <v>4370.37</v>
       </c>
       <c r="M17" t="n">
-        <v>4423.3</v>
+        <v>4443.35</v>
       </c>
       <c r="N17" t="n">
-        <v>4536.05</v>
+        <v>4516.32</v>
       </c>
       <c r="O17" t="n">
-        <v>4577.8</v>
+        <v>4521.6</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1935,14 +1931,18 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1954,83 +1954,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4369.9</v>
+        <v>4568</v>
       </c>
       <c r="C18" t="n">
-        <v>4584</v>
+        <v>4581.3</v>
       </c>
       <c r="D18" t="n">
-        <v>4367.9</v>
+        <v>4284.3</v>
       </c>
       <c r="E18" t="n">
-        <v>4552.7</v>
+        <v>4329.6</v>
       </c>
       <c r="F18" t="n">
-        <v>165.4</v>
+        <v>-223.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.049</v>
       </c>
       <c r="H18" t="n">
-        <v>216.1</v>
+        <v>297</v>
       </c>
       <c r="I18" t="n">
-        <v>4185.3</v>
+        <v>4151.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4292.12</v>
+        <v>4374.98</v>
       </c>
       <c r="K18" t="n">
-        <v>4331.25</v>
+        <v>4444.65</v>
       </c>
       <c r="L18" t="n">
-        <v>4370.37</v>
+        <v>4514.33</v>
       </c>
       <c r="M18" t="n">
-        <v>4443.35</v>
+        <v>4660.75</v>
       </c>
       <c r="N18" t="n">
-        <v>4516.32</v>
+        <v>4807.18</v>
       </c>
       <c r="O18" t="n">
-        <v>4521.6</v>
+        <v>4800.1</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2038,72 +2036,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4568</v>
+        <v>4368.3</v>
       </c>
       <c r="C19" t="n">
-        <v>4581.3</v>
+        <v>4527</v>
       </c>
       <c r="D19" t="n">
-        <v>4284.3</v>
+        <v>4354.6</v>
       </c>
       <c r="E19" t="n">
-        <v>4329.6</v>
+        <v>4500.9</v>
       </c>
       <c r="F19" t="n">
-        <v>-223.1</v>
+        <v>171.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.049</v>
+        <v>0.0396</v>
       </c>
       <c r="H19" t="n">
-        <v>297</v>
+        <v>172.4</v>
       </c>
       <c r="I19" t="n">
-        <v>4151.8</v>
+        <v>3987.3</v>
       </c>
       <c r="J19" t="n">
-        <v>4374.98</v>
+        <v>3981</v>
       </c>
       <c r="K19" t="n">
-        <v>4444.65</v>
+        <v>4181.1</v>
       </c>
       <c r="L19" t="n">
-        <v>4514.33</v>
+        <v>4381.2</v>
       </c>
       <c r="M19" t="n">
-        <v>4660.75</v>
+        <v>4478.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4807.18</v>
+        <v>4575</v>
       </c>
       <c r="O19" t="n">
-        <v>4800.1</v>
+        <v>4878.3</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2115,55 +2111,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4368.3</v>
+        <v>4529.1</v>
       </c>
       <c r="C20" t="n">
-        <v>4527</v>
+        <v>4650.5</v>
       </c>
       <c r="D20" t="n">
-        <v>4354.6</v>
+        <v>4520.8</v>
       </c>
       <c r="E20" t="n">
-        <v>4500.9</v>
+        <v>4595.4</v>
       </c>
       <c r="F20" t="n">
-        <v>171.3</v>
+        <v>94.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.021</v>
       </c>
       <c r="H20" t="n">
-        <v>172.4</v>
+        <v>129.7</v>
       </c>
       <c r="I20" t="n">
-        <v>3987.3</v>
+        <v>4182.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3981</v>
+        <v>4358.55</v>
       </c>
       <c r="K20" t="n">
-        <v>4181.1</v>
+        <v>4414.7</v>
       </c>
       <c r="L20" t="n">
-        <v>4381.2</v>
+        <v>4470.85</v>
       </c>
       <c r="M20" t="n">
-        <v>4478.1</v>
+        <v>4587.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4575</v>
+        <v>4703.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4878.3</v>
+        <v>4699.4</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2197,57 +2197,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4529.1</v>
+        <v>4633.7</v>
       </c>
       <c r="C21" t="n">
-        <v>4650.5</v>
+        <v>4991.4</v>
       </c>
       <c r="D21" t="n">
-        <v>4520.8</v>
+        <v>4622.2</v>
       </c>
       <c r="E21" t="n">
-        <v>4595.4</v>
+        <v>4979.7</v>
       </c>
       <c r="F21" t="n">
-        <v>94.5</v>
+        <v>384.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.021</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>129.7</v>
+        <v>369.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4182.2</v>
+        <v>4391.1</v>
       </c>
       <c r="J21" t="n">
-        <v>4358.55</v>
+        <v>4470.57</v>
       </c>
       <c r="K21" t="n">
-        <v>4414.7</v>
+        <v>4530.55</v>
       </c>
       <c r="L21" t="n">
-        <v>4470.85</v>
+        <v>4590.52</v>
       </c>
       <c r="M21" t="n">
-        <v>4587.1</v>
+        <v>4660.25</v>
       </c>
       <c r="N21" t="n">
-        <v>4703.35</v>
+        <v>4729.98</v>
       </c>
       <c r="O21" t="n">
-        <v>4699.4</v>
+        <v>4780.2</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2265,86 +2265,90 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4633.7</v>
+        <v>5013.4</v>
       </c>
       <c r="C22" t="n">
-        <v>4991.4</v>
+        <v>5586.2</v>
       </c>
       <c r="D22" t="n">
-        <v>4622.2</v>
+        <v>4700.4</v>
       </c>
       <c r="E22" t="n">
-        <v>4979.7</v>
+        <v>4745.1</v>
       </c>
       <c r="F22" t="n">
-        <v>384.3</v>
+        <v>-234.6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.0471</v>
       </c>
       <c r="H22" t="n">
-        <v>369.2</v>
+        <v>885.8</v>
       </c>
       <c r="I22" t="n">
-        <v>4391.1</v>
+        <v>4253</v>
       </c>
       <c r="J22" t="n">
-        <v>4470.57</v>
+        <v>4696.95</v>
       </c>
       <c r="K22" t="n">
-        <v>4530.55</v>
+        <v>4795.1</v>
       </c>
       <c r="L22" t="n">
-        <v>4590.52</v>
+        <v>4893.25</v>
       </c>
       <c r="M22" t="n">
-        <v>4660.25</v>
+        <v>5164.3</v>
       </c>
       <c r="N22" t="n">
-        <v>4729.98</v>
+        <v>5435.35</v>
       </c>
       <c r="O22" t="n">
-        <v>4780.2</v>
+        <v>5360.6</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2359,7 +2363,7 @@
       </c>
       <c r="V22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
@@ -2367,88 +2371,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5013.4</v>
+        <v>4816</v>
       </c>
       <c r="C23" t="n">
-        <v>5586.2</v>
+        <v>5113.9</v>
       </c>
       <c r="D23" t="n">
-        <v>4700.4</v>
+        <v>4423.2</v>
       </c>
       <c r="E23" t="n">
-        <v>4745.1</v>
+        <v>4979.8</v>
       </c>
       <c r="F23" t="n">
-        <v>-234.6</v>
+        <v>234.7</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0471</v>
+        <v>0.0495</v>
       </c>
       <c r="H23" t="n">
-        <v>885.8</v>
+        <v>690.7</v>
       </c>
       <c r="I23" t="n">
-        <v>4253</v>
+        <v>3814.6</v>
       </c>
       <c r="J23" t="n">
-        <v>4696.95</v>
+        <v>3660.2</v>
       </c>
       <c r="K23" t="n">
-        <v>4795.1</v>
+        <v>4302.2</v>
       </c>
       <c r="L23" t="n">
-        <v>4893.25</v>
+        <v>4944.2</v>
       </c>
       <c r="M23" t="n">
-        <v>5164.3</v>
+        <v>5188</v>
       </c>
       <c r="N23" t="n">
-        <v>5435.35</v>
+        <v>5431.8</v>
       </c>
       <c r="O23" t="n">
-        <v>5360.6</v>
+        <v>6472</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2457,57 +2455,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4816</v>
+        <v>5003.6</v>
       </c>
       <c r="C24" t="n">
-        <v>5113.9</v>
+        <v>5144.5</v>
       </c>
       <c r="D24" t="n">
-        <v>4423.2</v>
+        <v>4900</v>
       </c>
       <c r="E24" t="n">
-        <v>4979.8</v>
+        <v>5046.3</v>
       </c>
       <c r="F24" t="n">
-        <v>234.7</v>
+        <v>66.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0495</v>
+        <v>0.0134</v>
       </c>
       <c r="H24" t="n">
-        <v>690.7</v>
+        <v>244.5</v>
       </c>
       <c r="I24" t="n">
-        <v>3814.6</v>
+        <v>3732.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3660.2</v>
+        <v>4394.72</v>
       </c>
       <c r="K24" t="n">
-        <v>4302.2</v>
+        <v>4634.45</v>
       </c>
       <c r="L24" t="n">
-        <v>4944.2</v>
+        <v>4874.17</v>
       </c>
       <c r="M24" t="n">
-        <v>5188</v>
+        <v>5325.15</v>
       </c>
       <c r="N24" t="n">
-        <v>5431.8</v>
+        <v>5776.12</v>
       </c>
       <c r="O24" t="n">
-        <v>6472</v>
+        <v>5804.6</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2537,59 +2535,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5003.6</v>
+        <v>5050</v>
       </c>
       <c r="C25" t="n">
-        <v>5144.5</v>
+        <v>5131</v>
       </c>
       <c r="D25" t="n">
-        <v>4900</v>
+        <v>4854.2</v>
       </c>
       <c r="E25" t="n">
-        <v>5046.3</v>
+        <v>5080.9</v>
       </c>
       <c r="F25" t="n">
-        <v>66.5</v>
+        <v>34.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0069</v>
       </c>
       <c r="H25" t="n">
-        <v>244.5</v>
+        <v>276.8</v>
       </c>
       <c r="I25" t="n">
-        <v>3732.5</v>
+        <v>4655.5</v>
       </c>
       <c r="J25" t="n">
-        <v>4394.72</v>
+        <v>4813.82</v>
       </c>
       <c r="K25" t="n">
-        <v>4634.45</v>
+        <v>4924.05</v>
       </c>
       <c r="L25" t="n">
-        <v>4874.17</v>
+        <v>5034.27</v>
       </c>
       <c r="M25" t="n">
-        <v>5325.15</v>
+        <v>5168.55</v>
       </c>
       <c r="N25" t="n">
-        <v>5776.12</v>
+        <v>5302.82</v>
       </c>
       <c r="O25" t="n">
-        <v>5804.6</v>
+        <v>5389</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2597,8 +2591,10 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
@@ -2619,55 +2615,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5050</v>
+        <v>5128.8</v>
       </c>
       <c r="C26" t="n">
-        <v>5131</v>
+        <v>5299</v>
       </c>
       <c r="D26" t="n">
-        <v>4854.2</v>
+        <v>5109.5</v>
       </c>
       <c r="E26" t="n">
-        <v>5080.9</v>
+        <v>5247.9</v>
       </c>
       <c r="F26" t="n">
-        <v>34.6</v>
+        <v>167</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0329</v>
       </c>
       <c r="H26" t="n">
-        <v>276.8</v>
+        <v>189.5</v>
       </c>
       <c r="I26" t="n">
-        <v>4655.5</v>
+        <v>4577.4</v>
       </c>
       <c r="J26" t="n">
-        <v>4813.82</v>
+        <v>4848.25</v>
       </c>
       <c r="K26" t="n">
-        <v>4924.05</v>
+        <v>4942.5</v>
       </c>
       <c r="L26" t="n">
-        <v>5034.27</v>
+        <v>5036.75</v>
       </c>
       <c r="M26" t="n">
-        <v>5168.55</v>
+        <v>5219.3</v>
       </c>
       <c r="N26" t="n">
-        <v>5302.82</v>
+        <v>5401.85</v>
       </c>
       <c r="O26" t="n">
-        <v>5389</v>
+        <v>5407.8</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2675,18 +2675,18 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2699,77 +2699,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5128.8</v>
+        <v>5360</v>
       </c>
       <c r="C27" t="n">
-        <v>5299</v>
+        <v>5434.1</v>
       </c>
       <c r="D27" t="n">
-        <v>5109.5</v>
+        <v>5005</v>
       </c>
       <c r="E27" t="n">
-        <v>5247.9</v>
+        <v>5158.7</v>
       </c>
       <c r="F27" t="n">
-        <v>167</v>
+        <v>-89.2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0329</v>
+        <v>-0.017</v>
       </c>
       <c r="H27" t="n">
-        <v>189.5</v>
+        <v>429.1</v>
       </c>
       <c r="I27" t="n">
-        <v>4577.4</v>
+        <v>4920</v>
       </c>
       <c r="J27" t="n">
-        <v>4848.25</v>
+        <v>5080.22</v>
       </c>
       <c r="K27" t="n">
-        <v>4942.5</v>
+        <v>5153.15</v>
       </c>
       <c r="L27" t="n">
-        <v>5036.75</v>
+        <v>5226.07</v>
       </c>
       <c r="M27" t="n">
-        <v>5219.3</v>
+        <v>5342.65</v>
       </c>
       <c r="N27" t="n">
-        <v>5401.85</v>
+        <v>5459.22</v>
       </c>
       <c r="O27" t="n">
-        <v>5407.8</v>
+        <v>5488.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
@@ -2783,63 +2783,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5360</v>
+        <v>5186.7</v>
       </c>
       <c r="C28" t="n">
-        <v>5434.1</v>
+        <v>5248.7</v>
       </c>
       <c r="D28" t="n">
-        <v>5005</v>
+        <v>5014.1</v>
       </c>
       <c r="E28" t="n">
-        <v>5158.7</v>
+        <v>5061.7</v>
       </c>
       <c r="F28" t="n">
-        <v>-89.2</v>
+        <v>-97</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0188</v>
       </c>
       <c r="H28" t="n">
-        <v>429.1</v>
+        <v>234.6</v>
       </c>
       <c r="I28" t="n">
-        <v>4920</v>
+        <v>4575.9</v>
       </c>
       <c r="J28" t="n">
-        <v>5080.22</v>
+        <v>4699.18</v>
       </c>
       <c r="K28" t="n">
-        <v>5153.15</v>
+        <v>4944.15</v>
       </c>
       <c r="L28" t="n">
-        <v>5226.07</v>
+        <v>5189.13</v>
       </c>
       <c r="M28" t="n">
-        <v>5342.65</v>
+        <v>5373.25</v>
       </c>
       <c r="N28" t="n">
-        <v>5459.22</v>
+        <v>5557.38</v>
       </c>
       <c r="O28" t="n">
-        <v>5488.5</v>
+        <v>5863.2</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q28" s="6" t="n">
+        <v/>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
@@ -2851,10 +2853,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2876,60 +2876,64 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5186.7</v>
+        <v>5010</v>
       </c>
       <c r="C29" t="n">
-        <v>5248.7</v>
+        <v>5049.4</v>
       </c>
       <c r="D29" t="n">
-        <v>5014.1</v>
+        <v>4478.4</v>
       </c>
       <c r="E29" t="n">
-        <v>5061.7</v>
+        <v>4574.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-97</v>
+        <v>-486.8</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0188</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>234.6</v>
+        <v>571</v>
       </c>
       <c r="I29" t="n">
-        <v>4575.9</v>
+        <v>4779.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4699.18</v>
+        <v>4792.25</v>
       </c>
       <c r="K29" t="n">
-        <v>4944.15</v>
+        <v>4944.4</v>
       </c>
       <c r="L29" t="n">
-        <v>5189.13</v>
+        <v>5096.55</v>
       </c>
       <c r="M29" t="n">
-        <v>5373.25</v>
+        <v>5179</v>
       </c>
       <c r="N29" t="n">
-        <v>5557.38</v>
+        <v>5261.45</v>
       </c>
       <c r="O29" t="n">
-        <v>5863.2</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+        <v>5483.3</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
@@ -2946,83 +2950,75 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5010</v>
+        <v>4450</v>
       </c>
       <c r="C30" t="n">
-        <v>5049.4</v>
+        <v>4601</v>
       </c>
       <c r="D30" t="n">
-        <v>4478.4</v>
+        <v>4100</v>
       </c>
       <c r="E30" t="n">
-        <v>4574.9</v>
+        <v>4492.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-486.8</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="H30" t="n">
-        <v>571</v>
+        <v>501</v>
       </c>
       <c r="I30" t="n">
-        <v>4779.5</v>
+        <v>3907.4</v>
       </c>
       <c r="J30" t="n">
-        <v>4792.25</v>
+        <v>3909.4</v>
       </c>
       <c r="K30" t="n">
-        <v>4944.4</v>
+        <v>4289.4</v>
       </c>
       <c r="L30" t="n">
-        <v>5096.55</v>
+        <v>4669.4</v>
       </c>
       <c r="M30" t="n">
-        <v>5179</v>
+        <v>4860.4</v>
       </c>
       <c r="N30" t="n">
-        <v>5261.45</v>
+        <v>5051.4</v>
       </c>
       <c r="O30" t="n">
-        <v>5483.3</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
+        <v>5620.4</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3044,50 +3040,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4450</v>
+        <v>4482.8</v>
       </c>
       <c r="C31" t="n">
-        <v>4601</v>
+        <v>4825.9</v>
       </c>
       <c r="D31" t="n">
-        <v>4100</v>
+        <v>4413.4</v>
       </c>
       <c r="E31" t="n">
-        <v>4492.5</v>
+        <v>4679.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-82.40000000000001</v>
+        <v>187.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0417</v>
       </c>
       <c r="H31" t="n">
-        <v>501</v>
+        <v>412.5</v>
       </c>
       <c r="I31" t="n">
-        <v>3907.4</v>
+        <v>3599</v>
       </c>
       <c r="J31" t="n">
-        <v>3909.4</v>
+        <v>4062.5</v>
       </c>
       <c r="K31" t="n">
-        <v>4289.4</v>
+        <v>4242</v>
       </c>
       <c r="L31" t="n">
-        <v>4669.4</v>
+        <v>4421.5</v>
       </c>
       <c r="M31" t="n">
-        <v>4860.4</v>
+        <v>4743</v>
       </c>
       <c r="N31" t="n">
-        <v>5051.4</v>
+        <v>5064.5</v>
       </c>
       <c r="O31" t="n">
-        <v>5620.4</v>
+        <v>5102</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3095,18 +3091,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3119,55 +3115,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4482.8</v>
+        <v>4675</v>
       </c>
       <c r="C32" t="n">
-        <v>4825.9</v>
+        <v>4888</v>
       </c>
       <c r="D32" t="n">
-        <v>4413.4</v>
+        <v>4626.2</v>
       </c>
       <c r="E32" t="n">
-        <v>4679.7</v>
+        <v>4787.4</v>
       </c>
       <c r="F32" t="n">
-        <v>187.2</v>
+        <v>107.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0417</v>
+        <v>0.023</v>
       </c>
       <c r="H32" t="n">
-        <v>412.5</v>
+        <v>261.8</v>
       </c>
       <c r="I32" t="n">
-        <v>3599</v>
+        <v>4000.9</v>
       </c>
       <c r="J32" t="n">
-        <v>4062.5</v>
+        <v>4297.23</v>
       </c>
       <c r="K32" t="n">
-        <v>4242</v>
+        <v>4473.45</v>
       </c>
       <c r="L32" t="n">
-        <v>4421.5</v>
+        <v>4649.68</v>
       </c>
       <c r="M32" t="n">
-        <v>4743</v>
+        <v>4885.95</v>
       </c>
       <c r="N32" t="n">
-        <v>5064.5</v>
+        <v>5122.23</v>
       </c>
       <c r="O32" t="n">
-        <v>5102</v>
+        <v>5238.4</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3208,50 +3208,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4675</v>
+        <v>4710</v>
       </c>
       <c r="C33" t="n">
-        <v>4888</v>
+        <v>4917.7</v>
       </c>
       <c r="D33" t="n">
-        <v>4626.2</v>
+        <v>4626</v>
       </c>
       <c r="E33" t="n">
-        <v>4787.4</v>
+        <v>4879.6</v>
       </c>
       <c r="F33" t="n">
-        <v>107.7</v>
+        <v>92.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0193</v>
       </c>
       <c r="H33" t="n">
-        <v>261.8</v>
+        <v>291.7</v>
       </c>
       <c r="I33" t="n">
-        <v>4000.9</v>
+        <v>4364.4</v>
       </c>
       <c r="J33" t="n">
-        <v>4297.23</v>
+        <v>4540.75</v>
       </c>
       <c r="K33" t="n">
-        <v>4473.45</v>
+        <v>4656.5</v>
       </c>
       <c r="L33" t="n">
-        <v>4649.68</v>
+        <v>4772.25</v>
       </c>
       <c r="M33" t="n">
-        <v>4885.95</v>
+        <v>4918.3</v>
       </c>
       <c r="N33" t="n">
-        <v>5122.23</v>
+        <v>5064.35</v>
       </c>
       <c r="O33" t="n">
-        <v>5238.4</v>
+        <v>5149.8</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3259,8 +3259,10 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
@@ -3285,57 +3287,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4710</v>
+        <v>4811.8</v>
       </c>
       <c r="C34" t="n">
-        <v>4917.7</v>
+        <v>4854.8</v>
       </c>
       <c r="D34" t="n">
-        <v>4626</v>
+        <v>4672.2</v>
       </c>
       <c r="E34" t="n">
-        <v>4879.6</v>
+        <v>4740.9</v>
       </c>
       <c r="F34" t="n">
-        <v>92.2</v>
+        <v>-138.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0193</v>
+        <v>-0.0284</v>
       </c>
       <c r="H34" t="n">
-        <v>291.7</v>
+        <v>182.6</v>
       </c>
       <c r="I34" t="n">
-        <v>4364.4</v>
+        <v>4334.3</v>
       </c>
       <c r="J34" t="n">
-        <v>4540.75</v>
+        <v>4641.77</v>
       </c>
       <c r="K34" t="n">
-        <v>4656.5</v>
+        <v>4733.75</v>
       </c>
       <c r="L34" t="n">
-        <v>4772.25</v>
+        <v>4825.73</v>
       </c>
       <c r="M34" t="n">
-        <v>4918.3</v>
+        <v>5025.45</v>
       </c>
       <c r="N34" t="n">
-        <v>5064.35</v>
+        <v>5225.18</v>
       </c>
       <c r="O34" t="n">
-        <v>5149.8</v>
+        <v>5209.4</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3345,19 +3347,17 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3371,63 +3371,65 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4811.8</v>
+        <v>4713.1</v>
       </c>
       <c r="C35" t="n">
-        <v>4854.8</v>
+        <v>4745.8</v>
       </c>
       <c r="D35" t="n">
-        <v>4672.2</v>
+        <v>4522.2</v>
       </c>
       <c r="E35" t="n">
-        <v>4740.9</v>
+        <v>4644.5</v>
       </c>
       <c r="F35" t="n">
-        <v>-138.7</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0284</v>
+        <v>-0.0203</v>
       </c>
       <c r="H35" t="n">
-        <v>182.6</v>
+        <v>223.6</v>
       </c>
       <c r="I35" t="n">
-        <v>4334.3</v>
+        <v>4489.6</v>
       </c>
       <c r="J35" t="n">
-        <v>4641.77</v>
+        <v>4547</v>
       </c>
       <c r="K35" t="n">
-        <v>4733.75</v>
+        <v>4649.6</v>
       </c>
       <c r="L35" t="n">
-        <v>4825.73</v>
+        <v>4752.2</v>
       </c>
       <c r="M35" t="n">
-        <v>5025.45</v>
+        <v>4832.2</v>
       </c>
       <c r="N35" t="n">
-        <v>5225.18</v>
+        <v>4912.2</v>
       </c>
       <c r="O35" t="n">
-        <v>5209.4</v>
+        <v>5037.4</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
@@ -3453,81 +3455,77 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4713.1</v>
+        <v>4644</v>
       </c>
       <c r="C36" t="n">
-        <v>4745.8</v>
+        <v>4775.2</v>
       </c>
       <c r="D36" t="n">
-        <v>4522.2</v>
+        <v>4510.1</v>
       </c>
       <c r="E36" t="n">
-        <v>4644.5</v>
+        <v>4730.7</v>
       </c>
       <c r="F36" t="n">
-        <v>-96.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0186</v>
       </c>
       <c r="H36" t="n">
-        <v>223.6</v>
+        <v>265.1</v>
       </c>
       <c r="I36" t="n">
-        <v>4489.6</v>
+        <v>4298.6</v>
       </c>
       <c r="J36" t="n">
-        <v>4547</v>
+        <v>4426.15</v>
       </c>
       <c r="K36" t="n">
-        <v>4649.6</v>
+        <v>4532.7</v>
       </c>
       <c r="L36" t="n">
-        <v>4752.2</v>
+        <v>4639.25</v>
       </c>
       <c r="M36" t="n">
-        <v>4832.2</v>
+        <v>4756.3</v>
       </c>
       <c r="N36" t="n">
-        <v>4912.2</v>
+        <v>4873.35</v>
       </c>
       <c r="O36" t="n">
-        <v>5037.4</v>
+        <v>4969.4</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3539,55 +3537,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4644</v>
+        <v>4690</v>
       </c>
       <c r="C37" t="n">
-        <v>4775.2</v>
+        <v>4783.4</v>
       </c>
       <c r="D37" t="n">
-        <v>4510.1</v>
+        <v>4513.8</v>
       </c>
       <c r="E37" t="n">
-        <v>4730.7</v>
+        <v>4561.9</v>
       </c>
       <c r="F37" t="n">
-        <v>86.2</v>
+        <v>-168.8</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0357</v>
       </c>
       <c r="H37" t="n">
-        <v>265.1</v>
+        <v>269.6</v>
       </c>
       <c r="I37" t="n">
-        <v>4298.6</v>
+        <v>4245</v>
       </c>
       <c r="J37" t="n">
-        <v>4426.15</v>
+        <v>4509.63</v>
       </c>
       <c r="K37" t="n">
-        <v>4532.7</v>
+        <v>4598.15</v>
       </c>
       <c r="L37" t="n">
-        <v>4639.25</v>
+        <v>4686.68</v>
       </c>
       <c r="M37" t="n">
-        <v>4756.3</v>
+        <v>4863.25</v>
       </c>
       <c r="N37" t="n">
-        <v>4873.35</v>
+        <v>5039.83</v>
       </c>
       <c r="O37" t="n">
-        <v>4969.4</v>
+        <v>5040.3</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3597,18 +3599,16 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3630,50 +3630,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4690</v>
+        <v>4547.6</v>
       </c>
       <c r="C38" t="n">
-        <v>4783.4</v>
+        <v>4593.2</v>
       </c>
       <c r="D38" t="n">
-        <v>4513.8</v>
+        <v>4455</v>
       </c>
       <c r="E38" t="n">
-        <v>4561.9</v>
+        <v>4523.2</v>
       </c>
       <c r="F38" t="n">
-        <v>-168.8</v>
+        <v>-38.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0357</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>269.6</v>
+        <v>138.2</v>
       </c>
       <c r="I38" t="n">
-        <v>4245</v>
+        <v>4244.2</v>
       </c>
       <c r="J38" t="n">
-        <v>4509.63</v>
+        <v>4248.95</v>
       </c>
       <c r="K38" t="n">
-        <v>4598.15</v>
+        <v>4427.1</v>
       </c>
       <c r="L38" t="n">
-        <v>4686.68</v>
+        <v>4605.25</v>
       </c>
       <c r="M38" t="n">
-        <v>4863.25</v>
+        <v>4696.7</v>
       </c>
       <c r="N38" t="n">
-        <v>5039.83</v>
+        <v>4788.15</v>
       </c>
       <c r="O38" t="n">
-        <v>5040.3</v>
+        <v>5053</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3681,14 +3681,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3705,76 +3703,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4547.6</v>
+        <v>4532</v>
       </c>
       <c r="C39" t="n">
-        <v>4593.2</v>
+        <v>4627.1</v>
       </c>
       <c r="D39" t="n">
-        <v>4455</v>
+        <v>4363.5</v>
       </c>
       <c r="E39" t="n">
-        <v>4523.2</v>
+        <v>4593</v>
       </c>
       <c r="F39" t="n">
-        <v>-38.7</v>
+        <v>69.8</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H39" t="n">
-        <v>138.2</v>
+        <v>263.6</v>
       </c>
       <c r="I39" t="n">
-        <v>4244.2</v>
+        <v>4316.8</v>
       </c>
       <c r="J39" t="n">
-        <v>4248.95</v>
+        <v>4384.55</v>
       </c>
       <c r="K39" t="n">
-        <v>4427.1</v>
+        <v>4454.1</v>
       </c>
       <c r="L39" t="n">
-        <v>4605.25</v>
+        <v>4523.65</v>
       </c>
       <c r="M39" t="n">
-        <v>4696.7</v>
+        <v>4592.3</v>
       </c>
       <c r="N39" t="n">
-        <v>4788.15</v>
+        <v>4660.95</v>
       </c>
       <c r="O39" t="n">
-        <v>5053</v>
+        <v>4731.4</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3787,78 +3787,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4532</v>
+        <v>4575.2</v>
       </c>
       <c r="C40" t="n">
-        <v>4627.1</v>
+        <v>4577.3</v>
       </c>
       <c r="D40" t="n">
-        <v>4363.5</v>
+        <v>4336.6</v>
       </c>
       <c r="E40" t="n">
-        <v>4593</v>
+        <v>4365.3</v>
       </c>
       <c r="F40" t="n">
-        <v>69.8</v>
+        <v>-227.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0154</v>
+        <v>-0.0496</v>
       </c>
       <c r="H40" t="n">
-        <v>263.6</v>
+        <v>240.7</v>
       </c>
       <c r="I40" t="n">
-        <v>4316.8</v>
+        <v>4099.9</v>
       </c>
       <c r="J40" t="n">
-        <v>4384.55</v>
+        <v>4378.25</v>
       </c>
       <c r="K40" t="n">
-        <v>4454.1</v>
+        <v>4461.2</v>
       </c>
       <c r="L40" t="n">
-        <v>4523.65</v>
+        <v>4544.15</v>
       </c>
       <c r="M40" t="n">
-        <v>4592.3</v>
+        <v>4724.8</v>
       </c>
       <c r="N40" t="n">
-        <v>4660.95</v>
+        <v>4905.45</v>
       </c>
       <c r="O40" t="n">
-        <v>4731.4</v>
+        <v>4890.7</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3871,71 +3873,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4575.2</v>
+        <v>4354</v>
       </c>
       <c r="C41" t="n">
-        <v>4577.3</v>
+        <v>4388.6</v>
       </c>
       <c r="D41" t="n">
-        <v>4336.6</v>
+        <v>4046.2</v>
       </c>
       <c r="E41" t="n">
-        <v>4365.3</v>
+        <v>4238.8</v>
       </c>
       <c r="F41" t="n">
-        <v>-227.7</v>
+        <v>-126.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0496</v>
+        <v>-0.029</v>
       </c>
       <c r="H41" t="n">
-        <v>240.7</v>
+        <v>342.4</v>
       </c>
       <c r="I41" t="n">
-        <v>4099.9</v>
+        <v>4095.9</v>
       </c>
       <c r="J41" t="n">
-        <v>4378.25</v>
+        <v>4078.78</v>
       </c>
       <c r="K41" t="n">
-        <v>4461.2</v>
+        <v>4244.95</v>
       </c>
       <c r="L41" t="n">
-        <v>4544.15</v>
+        <v>4411.12</v>
       </c>
       <c r="M41" t="n">
-        <v>4724.8</v>
+        <v>4485.65</v>
       </c>
       <c r="N41" t="n">
-        <v>4905.45</v>
+        <v>4560.17</v>
       </c>
       <c r="O41" t="n">
-        <v>4890.7</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
+        <v>4818</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
@@ -3962,69 +3962,63 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4354</v>
+        <v>4289.4</v>
       </c>
       <c r="C42" t="n">
-        <v>4388.6</v>
+        <v>4403.6</v>
       </c>
       <c r="D42" t="n">
-        <v>4046.2</v>
+        <v>4138.7</v>
       </c>
       <c r="E42" t="n">
-        <v>4238.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F42" t="n">
-        <v>-126.5</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0155</v>
       </c>
       <c r="H42" t="n">
-        <v>342.4</v>
+        <v>264.9</v>
       </c>
       <c r="I42" t="n">
-        <v>4095.9</v>
+        <v>3703.8</v>
       </c>
       <c r="J42" t="n">
-        <v>4078.78</v>
+        <v>3907.1</v>
       </c>
       <c r="K42" t="n">
-        <v>4244.95</v>
+        <v>4067.6</v>
       </c>
       <c r="L42" t="n">
-        <v>4411.12</v>
+        <v>4228.1</v>
       </c>
       <c r="M42" t="n">
-        <v>4485.65</v>
+        <v>4410</v>
       </c>
       <c r="N42" t="n">
-        <v>4560.17</v>
+        <v>4591.9</v>
       </c>
       <c r="O42" t="n">
-        <v>4818</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4731</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4041,55 +4035,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4289.4</v>
+        <v>4163.9</v>
       </c>
       <c r="C43" t="n">
-        <v>4403.6</v>
+        <v>4238.1</v>
       </c>
       <c r="D43" t="n">
-        <v>4138.7</v>
+        <v>3975.7</v>
       </c>
       <c r="E43" t="n">
-        <v>4172.9</v>
+        <v>4096.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-65.90000000000001</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0184</v>
       </c>
       <c r="H43" t="n">
-        <v>264.9</v>
+        <v>262.4</v>
       </c>
       <c r="I43" t="n">
-        <v>3703.8</v>
+        <v>3873.8</v>
       </c>
       <c r="J43" t="n">
-        <v>3907.1</v>
+        <v>3858.87</v>
       </c>
       <c r="K43" t="n">
-        <v>4067.6</v>
+        <v>4040.45</v>
       </c>
       <c r="L43" t="n">
-        <v>4228.1</v>
+        <v>4222.03</v>
       </c>
       <c r="M43" t="n">
-        <v>4410</v>
+        <v>4305.35</v>
       </c>
       <c r="N43" t="n">
-        <v>4591.9</v>
+        <v>4388.67</v>
       </c>
       <c r="O43" t="n">
-        <v>4731</v>
+        <v>4668.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4097,12 +4095,14 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4119,59 +4119,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4163.9</v>
+        <v>4101.1</v>
       </c>
       <c r="C44" t="n">
-        <v>4238.1</v>
+        <v>4208.3</v>
       </c>
       <c r="D44" t="n">
-        <v>3975.7</v>
+        <v>3955.4</v>
       </c>
       <c r="E44" t="n">
-        <v>4096.3</v>
+        <v>4187.3</v>
       </c>
       <c r="F44" t="n">
-        <v>-76.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0222</v>
       </c>
       <c r="H44" t="n">
-        <v>262.4</v>
+        <v>252.9</v>
       </c>
       <c r="I44" t="n">
-        <v>3873.8</v>
+        <v>3713.3</v>
       </c>
       <c r="J44" t="n">
-        <v>3858.87</v>
+        <v>3828.6</v>
       </c>
       <c r="K44" t="n">
-        <v>4040.45</v>
+        <v>3965.1</v>
       </c>
       <c r="L44" t="n">
-        <v>4222.03</v>
+        <v>4101.6</v>
       </c>
       <c r="M44" t="n">
-        <v>4305.35</v>
+        <v>4227.5</v>
       </c>
       <c r="N44" t="n">
-        <v>4388.67</v>
+        <v>4353.4</v>
       </c>
       <c r="O44" t="n">
-        <v>4668.5</v>
+        <v>4500.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4181,17 +4177,19 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4203,55 +4201,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4101.1</v>
+        <v>4187.5</v>
       </c>
       <c r="C45" t="n">
-        <v>4208.3</v>
+        <v>4215.5</v>
       </c>
       <c r="D45" t="n">
-        <v>3955.4</v>
+        <v>4032.5</v>
       </c>
       <c r="E45" t="n">
-        <v>4187.3</v>
+        <v>4113.7</v>
       </c>
       <c r="F45" t="n">
-        <v>91</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0176</v>
       </c>
       <c r="H45" t="n">
-        <v>252.9</v>
+        <v>183</v>
       </c>
       <c r="I45" t="n">
-        <v>3713.3</v>
+        <v>3702.5</v>
       </c>
       <c r="J45" t="n">
-        <v>3828.6</v>
+        <v>3987.12</v>
       </c>
       <c r="K45" t="n">
-        <v>3965.1</v>
+        <v>4060.85</v>
       </c>
       <c r="L45" t="n">
-        <v>4101.6</v>
+        <v>4134.57</v>
       </c>
       <c r="M45" t="n">
-        <v>4227.5</v>
+        <v>4313.75</v>
       </c>
       <c r="N45" t="n">
-        <v>4353.4</v>
+        <v>4492.92</v>
       </c>
       <c r="O45" t="n">
-        <v>4500.5</v>
+        <v>4461.2</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4264,15 +4266,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4287,57 +4287,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4187.5</v>
+        <v>4106.6</v>
       </c>
       <c r="C46" t="n">
-        <v>4215.5</v>
+        <v>4112.5</v>
       </c>
       <c r="D46" t="n">
-        <v>4032.5</v>
+        <v>3963</v>
       </c>
       <c r="E46" t="n">
-        <v>4113.7</v>
+        <v>4018.8</v>
       </c>
       <c r="F46" t="n">
-        <v>-73.59999999999999</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0176</v>
+        <v>-0.0231</v>
       </c>
       <c r="H46" t="n">
-        <v>183</v>
+        <v>149.5</v>
       </c>
       <c r="I46" t="n">
-        <v>3702.5</v>
+        <v>3849.5</v>
       </c>
       <c r="J46" t="n">
-        <v>3987.12</v>
+        <v>3925.55</v>
       </c>
       <c r="K46" t="n">
-        <v>4060.85</v>
+        <v>4022.2</v>
       </c>
       <c r="L46" t="n">
-        <v>4134.57</v>
+        <v>4118.85</v>
       </c>
       <c r="M46" t="n">
-        <v>4313.75</v>
+        <v>4205.2</v>
       </c>
       <c r="N46" t="n">
-        <v>4492.92</v>
+        <v>4291.55</v>
       </c>
       <c r="O46" t="n">
-        <v>4461.2</v>
+        <v>4398.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4347,12 +4347,12 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4369,59 +4369,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4106.6</v>
+        <v>4005.6</v>
       </c>
       <c r="C47" t="n">
-        <v>4112.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D47" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E47" t="n">
-        <v>4018.8</v>
+        <v>4070.8</v>
       </c>
       <c r="F47" t="n">
-        <v>-94.90000000000001</v>
+        <v>52</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0129</v>
       </c>
       <c r="H47" t="n">
-        <v>149.5</v>
+        <v>184.9</v>
       </c>
       <c r="I47" t="n">
-        <v>3849.5</v>
+        <v>3813.5</v>
       </c>
       <c r="J47" t="n">
-        <v>3925.55</v>
+        <v>3859.83</v>
       </c>
       <c r="K47" t="n">
-        <v>4022.2</v>
+        <v>3944.05</v>
       </c>
       <c r="L47" t="n">
-        <v>4118.85</v>
+        <v>4028.28</v>
       </c>
       <c r="M47" t="n">
-        <v>4205.2</v>
+        <v>4093.55</v>
       </c>
       <c r="N47" t="n">
-        <v>4291.55</v>
+        <v>4158.83</v>
       </c>
       <c r="O47" t="n">
-        <v>4398.5</v>
+        <v>4262</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4429,21 +4425,23 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4453,55 +4451,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4005.6</v>
+        <v>4097.5</v>
       </c>
       <c r="C48" t="n">
-        <v>4171.4</v>
+        <v>4170.7</v>
       </c>
       <c r="D48" t="n">
-        <v>3986.5</v>
+        <v>3993.8</v>
       </c>
       <c r="E48" t="n">
-        <v>4070.8</v>
+        <v>4107</v>
       </c>
       <c r="F48" t="n">
-        <v>52</v>
+        <v>36.2</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0089</v>
       </c>
       <c r="H48" t="n">
-        <v>184.9</v>
+        <v>176.9</v>
       </c>
       <c r="I48" t="n">
-        <v>3813.5</v>
+        <v>3801.6</v>
       </c>
       <c r="J48" t="n">
-        <v>3859.83</v>
+        <v>3881.83</v>
       </c>
       <c r="K48" t="n">
-        <v>3944.05</v>
+        <v>3978.35</v>
       </c>
       <c r="L48" t="n">
-        <v>4028.28</v>
+        <v>4074.88</v>
       </c>
       <c r="M48" t="n">
-        <v>4093.55</v>
+        <v>4163.25</v>
       </c>
       <c r="N48" t="n">
-        <v>4158.83</v>
+        <v>4251.62</v>
       </c>
       <c r="O48" t="n">
-        <v>4262</v>
+        <v>4356.3</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4514,19 +4516,17 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4537,57 +4537,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4097.5</v>
+        <v>4135.2</v>
       </c>
       <c r="C49" t="n">
-        <v>4170.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D49" t="n">
-        <v>3993.8</v>
+        <v>4074</v>
       </c>
       <c r="E49" t="n">
-        <v>4107</v>
+        <v>4399.7</v>
       </c>
       <c r="F49" t="n">
-        <v>36.2</v>
+        <v>292.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0089</v>
+        <v>0.0713</v>
       </c>
       <c r="H49" t="n">
-        <v>176.9</v>
+        <v>358.3</v>
       </c>
       <c r="I49" t="n">
-        <v>3801.6</v>
+        <v>3816.9</v>
       </c>
       <c r="J49" t="n">
-        <v>3881.83</v>
+        <v>3942.47</v>
       </c>
       <c r="K49" t="n">
-        <v>3978.35</v>
+        <v>4018.55</v>
       </c>
       <c r="L49" t="n">
-        <v>4074.88</v>
+        <v>4094.63</v>
       </c>
       <c r="M49" t="n">
-        <v>4163.25</v>
+        <v>4195.45</v>
       </c>
       <c r="N49" t="n">
-        <v>4251.62</v>
+        <v>4296.28</v>
       </c>
       <c r="O49" t="n">
-        <v>4356.3</v>
+        <v>4347.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4608,70 +4608,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4135.2</v>
+        <v>4400</v>
       </c>
       <c r="C50" t="n">
-        <v>4432.3</v>
+        <v>4509.1</v>
       </c>
       <c r="D50" t="n">
-        <v>4074</v>
+        <v>4365.5</v>
       </c>
       <c r="E50" t="n">
-        <v>4399.7</v>
+        <v>4437.3</v>
       </c>
       <c r="F50" t="n">
-        <v>292.7</v>
+        <v>37.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0713</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>358.3</v>
+        <v>143.6</v>
       </c>
       <c r="I50" t="n">
-        <v>3816.9</v>
+        <v>3715.7</v>
       </c>
       <c r="J50" t="n">
-        <v>3942.47</v>
+        <v>4114.68</v>
       </c>
       <c r="K50" t="n">
-        <v>4018.55</v>
+        <v>4220.55</v>
       </c>
       <c r="L50" t="n">
-        <v>4094.63</v>
+        <v>4326.43</v>
       </c>
       <c r="M50" t="n">
-        <v>4195.45</v>
+        <v>4578.85</v>
       </c>
       <c r="N50" t="n">
-        <v>4296.28</v>
+        <v>4831.28</v>
       </c>
       <c r="O50" t="n">
-        <v>4347.6</v>
+        <v>4790.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4684,23 +4684,17 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
@@ -4712,50 +4706,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4400</v>
+        <v>4440</v>
       </c>
       <c r="C51" t="n">
+        <v>4690.4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4378</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4680.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>243.3</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H51" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4221.9</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4293.7</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4365.5</v>
+      </c>
+      <c r="L51" t="n">
+        <v>4437.3</v>
+      </c>
+      <c r="M51" t="n">
         <v>4509.1</v>
       </c>
-      <c r="D51" t="n">
-        <v>4365.5</v>
-      </c>
-      <c r="E51" t="n">
-        <v>4437.3</v>
-      </c>
-      <c r="F51" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="H51" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3715.7</v>
-      </c>
-      <c r="J51" t="n">
-        <v>4114.68</v>
-      </c>
-      <c r="K51" t="n">
-        <v>4220.55</v>
-      </c>
-      <c r="L51" t="n">
-        <v>4326.43</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4578.85</v>
-      </c>
       <c r="N51" t="n">
-        <v>4831.28</v>
+        <v>4580.9</v>
       </c>
       <c r="O51" t="n">
-        <v>4790.6</v>
+        <v>4652.7</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4768,17 +4762,23 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
@@ -4790,50 +4790,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4440</v>
+        <v>4673.4</v>
       </c>
       <c r="C52" t="n">
-        <v>4690.4</v>
+        <v>4755</v>
       </c>
       <c r="D52" t="n">
-        <v>4378</v>
+        <v>4495</v>
       </c>
       <c r="E52" t="n">
-        <v>4680.6</v>
+        <v>4529.9</v>
       </c>
       <c r="F52" t="n">
-        <v>243.3</v>
+        <v>-150.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0548</v>
+        <v>-0.0322</v>
       </c>
       <c r="H52" t="n">
-        <v>312.4</v>
+        <v>260</v>
       </c>
       <c r="I52" t="n">
-        <v>4221.9</v>
+        <v>4065.6</v>
       </c>
       <c r="J52" t="n">
-        <v>4293.7</v>
+        <v>4441.4</v>
       </c>
       <c r="K52" t="n">
-        <v>4365.5</v>
+        <v>4524.4</v>
       </c>
       <c r="L52" t="n">
-        <v>4437.3</v>
+        <v>4607.4</v>
       </c>
       <c r="M52" t="n">
-        <v>4509.1</v>
+        <v>4836.8</v>
       </c>
       <c r="N52" t="n">
-        <v>4580.9</v>
+        <v>5066.2</v>
       </c>
       <c r="O52" t="n">
-        <v>4652.7</v>
+        <v>5002.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4841,83 +4841,83 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4673.4</v>
+        <v>4483.2</v>
       </c>
       <c r="C53" t="n">
-        <v>4755</v>
+        <v>4558.5</v>
       </c>
       <c r="D53" t="n">
-        <v>4495</v>
+        <v>4329.2</v>
       </c>
       <c r="E53" t="n">
-        <v>4529.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F53" t="n">
-        <v>-150.7</v>
+        <v>-53.3</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0118</v>
       </c>
       <c r="H53" t="n">
-        <v>260</v>
+        <v>229.3</v>
       </c>
       <c r="I53" t="n">
-        <v>4065.6</v>
+        <v>4235</v>
       </c>
       <c r="J53" t="n">
-        <v>4441.4</v>
+        <v>4222.35</v>
       </c>
       <c r="K53" t="n">
-        <v>4524.4</v>
+        <v>4399.9</v>
       </c>
       <c r="L53" t="n">
-        <v>4607.4</v>
+        <v>4577.45</v>
       </c>
       <c r="M53" t="n">
-        <v>4836.8</v>
+        <v>4659.9</v>
       </c>
       <c r="N53" t="n">
-        <v>5066.2</v>
+        <v>4742.35</v>
       </c>
       <c r="O53" t="n">
-        <v>5002.8</v>
+        <v>5015</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4951,57 +4951,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4483.2</v>
+        <v>4466.5</v>
       </c>
       <c r="C54" t="n">
-        <v>4558.5</v>
+        <v>4488.8</v>
       </c>
       <c r="D54" t="n">
-        <v>4329.2</v>
+        <v>4333</v>
       </c>
       <c r="E54" t="n">
-        <v>4476.6</v>
+        <v>4408.9</v>
       </c>
       <c r="F54" t="n">
-        <v>-53.3</v>
+        <v>-67.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0151</v>
       </c>
       <c r="H54" t="n">
-        <v>229.3</v>
+        <v>155.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4235</v>
+        <v>4099.9</v>
       </c>
       <c r="J54" t="n">
-        <v>4222.35</v>
+        <v>4263.68</v>
       </c>
       <c r="K54" t="n">
-        <v>4399.9</v>
+        <v>4361.95</v>
       </c>
       <c r="L54" t="n">
-        <v>4577.45</v>
+        <v>4460.23</v>
       </c>
       <c r="M54" t="n">
-        <v>4659.9</v>
+        <v>4591.25</v>
       </c>
       <c r="N54" t="n">
-        <v>4742.35</v>
+        <v>4722.27</v>
       </c>
       <c r="O54" t="n">
-        <v>5015</v>
+        <v>4787.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5035,57 +5035,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4466.5</v>
+        <v>4375</v>
       </c>
       <c r="C55" t="n">
-        <v>4488.8</v>
+        <v>4439.8</v>
       </c>
       <c r="D55" t="n">
-        <v>4333</v>
+        <v>4273.3</v>
       </c>
       <c r="E55" t="n">
-        <v>4408.9</v>
+        <v>4424.9</v>
       </c>
       <c r="F55" t="n">
-        <v>-67.7</v>
+        <v>16</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0151</v>
+        <v>0.0036</v>
       </c>
       <c r="H55" t="n">
-        <v>155.8</v>
+        <v>166.5</v>
       </c>
       <c r="I55" t="n">
-        <v>4099.9</v>
+        <v>4177.2</v>
       </c>
       <c r="J55" t="n">
-        <v>4263.68</v>
+        <v>4252.1</v>
       </c>
       <c r="K55" t="n">
-        <v>4361.95</v>
+        <v>4331</v>
       </c>
       <c r="L55" t="n">
-        <v>4460.23</v>
+        <v>4409.9</v>
       </c>
       <c r="M55" t="n">
-        <v>4591.25</v>
+        <v>4486.8</v>
       </c>
       <c r="N55" t="n">
-        <v>4722.27</v>
+        <v>4563.7</v>
       </c>
       <c r="O55" t="n">
-        <v>4787.8</v>
+        <v>4644.6</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5095,12 +5095,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5126,65 +5126,67 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4375</v>
+        <v>4413</v>
       </c>
       <c r="C56" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D56" t="n">
-        <v>4273.3</v>
+        <v>4278.3</v>
       </c>
       <c r="E56" t="n">
-        <v>4424.9</v>
+        <v>4321.2</v>
       </c>
       <c r="F56" t="n">
-        <v>16</v>
+        <v>-103.7</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0234</v>
       </c>
       <c r="H56" t="n">
-        <v>166.5</v>
+        <v>143.8</v>
       </c>
       <c r="I56" t="n">
-        <v>4177.2</v>
+        <v>4106.8</v>
       </c>
       <c r="J56" t="n">
-        <v>4252.1</v>
+        <v>4292.57</v>
       </c>
       <c r="K56" t="n">
-        <v>4331</v>
+        <v>4341.65</v>
       </c>
       <c r="L56" t="n">
-        <v>4409.9</v>
+        <v>4390.72</v>
       </c>
       <c r="M56" t="n">
-        <v>4486.8</v>
+        <v>4508.15</v>
       </c>
       <c r="N56" t="n">
-        <v>4563.7</v>
+        <v>4625.57</v>
       </c>
       <c r="O56" t="n">
-        <v>4644.6</v>
+        <v>4606.3</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5210,64 +5212,64 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4413</v>
+        <v>4315</v>
       </c>
       <c r="C57" t="n">
-        <v>4422.1</v>
+        <v>4315.6</v>
       </c>
       <c r="D57" t="n">
-        <v>4278.3</v>
+        <v>4143.1</v>
       </c>
       <c r="E57" t="n">
-        <v>4321.2</v>
+        <v>4162.3</v>
       </c>
       <c r="F57" t="n">
-        <v>-103.7</v>
+        <v>-158.9</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0234</v>
+        <v>-0.0368</v>
       </c>
       <c r="H57" t="n">
-        <v>143.8</v>
+        <v>172.5</v>
       </c>
       <c r="I57" t="n">
-        <v>4106.8</v>
+        <v>4134.5</v>
       </c>
       <c r="J57" t="n">
-        <v>4292.57</v>
+        <v>4162.9</v>
       </c>
       <c r="K57" t="n">
-        <v>4341.65</v>
+        <v>4249.3</v>
       </c>
       <c r="L57" t="n">
-        <v>4390.72</v>
+        <v>4335.7</v>
       </c>
       <c r="M57" t="n">
-        <v>4508.15</v>
+        <v>4393.1</v>
       </c>
       <c r="N57" t="n">
-        <v>4625.57</v>
+        <v>4450.5</v>
       </c>
       <c r="O57" t="n">
-        <v>4606.3</v>
+        <v>4565.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5282,102 +5284,12 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4315</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4315.6</v>
-      </c>
-      <c r="D58" t="n">
-        <v>4143.1</v>
-      </c>
-      <c r="E58" t="n">
-        <v>4205.3</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-115.9</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0268</v>
-      </c>
-      <c r="H58" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4134.5</v>
-      </c>
-      <c r="J58" t="n">
-        <v>4162.9</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4249.3</v>
-      </c>
-      <c r="L58" t="n">
-        <v>4335.7</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4393.1</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4450.5</v>
-      </c>
-      <c r="O58" t="n">
-        <v>4565.9</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5291,6 +5291,88 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4169.2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4172</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4168.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4170.6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3970.6</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3956.27</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4076.05</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4195.82</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4248.55</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4301.27</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4488.1</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>93.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3356.5</v>
+        <v>3491.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3540.08</v>
+        <v>3590.85</v>
       </c>
       <c r="K2" t="n">
-        <v>3578.55</v>
+        <v>3612.4</v>
       </c>
       <c r="L2" t="n">
-        <v>3617.03</v>
+        <v>3633.95</v>
       </c>
       <c r="M2" t="n">
-        <v>3728.05</v>
+        <v>3694.2</v>
       </c>
       <c r="N2" t="n">
-        <v>3839.08</v>
+        <v>3754.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3805</v>
+        <v>3737.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5298,25 +5298,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4169.2</v>
+        <v>4169.4</v>
       </c>
       <c r="C58" t="n">
-        <v>4172</v>
+        <v>4198.9</v>
       </c>
       <c r="D58" t="n">
-        <v>4168.5</v>
+        <v>4150.4</v>
       </c>
       <c r="E58" t="n">
-        <v>4170.6</v>
+        <v>4179.9</v>
       </c>
       <c r="F58" t="n">
-        <v>8.300000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0042</v>
       </c>
       <c r="H58" t="n">
-        <v>3.5</v>
+        <v>48.5</v>
       </c>
       <c r="I58" t="n">
         <v>3970.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5301,22 +5301,22 @@
         <v>4169.4</v>
       </c>
       <c r="C58" t="n">
-        <v>4198.9</v>
+        <v>4212.4</v>
       </c>
       <c r="D58" t="n">
-        <v>4150.4</v>
+        <v>4128.1</v>
       </c>
       <c r="E58" t="n">
-        <v>4179.9</v>
+        <v>4132.6</v>
       </c>
       <c r="F58" t="n">
-        <v>17.6</v>
+        <v>-29.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.0071</v>
       </c>
       <c r="H58" t="n">
-        <v>48.5</v>
+        <v>84.3</v>
       </c>
       <c r="I58" t="n">
         <v>3970.6</v>
@@ -5345,12 +5345,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5367,11 +5369,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5307,13 +5307,13 @@
         <v>4128.1</v>
       </c>
       <c r="E58" t="n">
-        <v>4132.6</v>
+        <v>4152.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-29.7</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.0024</v>
       </c>
       <c r="H58" t="n">
         <v>84.3</v>
@@ -5345,14 +5345,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>93.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3491.9</v>
+        <v>3535.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3590.85</v>
+        <v>3607.12</v>
       </c>
       <c r="K2" t="n">
-        <v>3612.4</v>
+        <v>3623.25</v>
       </c>
       <c r="L2" t="n">
-        <v>3633.95</v>
+        <v>3639.38</v>
       </c>
       <c r="M2" t="n">
-        <v>3694.2</v>
+        <v>3683.35</v>
       </c>
       <c r="N2" t="n">
-        <v>3754.45</v>
+        <v>3727.33</v>
       </c>
       <c r="O2" t="n">
-        <v>3737.3</v>
+        <v>3715.6</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -5304,19 +5306,19 @@
         <v>4212.4</v>
       </c>
       <c r="D58" t="n">
-        <v>4128.1</v>
+        <v>4091.2</v>
       </c>
       <c r="E58" t="n">
-        <v>4152.5</v>
+        <v>4195.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-9.800000000000001</v>
+        <v>32.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0024</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>84.3</v>
+        <v>121.2</v>
       </c>
       <c r="I58" t="n">
         <v>3970.6</v>
@@ -5367,7 +5369,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3635</v>
+        <v>3680.2</v>
       </c>
       <c r="C2" t="n">
-        <v>3715.2</v>
+        <v>3744</v>
       </c>
       <c r="D2" t="n">
-        <v>3621.7</v>
+        <v>3660.5</v>
       </c>
       <c r="E2" t="n">
-        <v>3686.4</v>
+        <v>3705.8</v>
       </c>
       <c r="F2" t="n">
-        <v>33.1</v>
+        <v>19.4</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0053</v>
       </c>
       <c r="H2" t="n">
-        <v>93.5</v>
+        <v>83.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3535.3</v>
+        <v>3528.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3607.12</v>
+        <v>3601.87</v>
       </c>
       <c r="K2" t="n">
-        <v>3623.25</v>
+        <v>3639.65</v>
       </c>
       <c r="L2" t="n">
-        <v>3639.38</v>
+        <v>3677.42</v>
       </c>
       <c r="M2" t="n">
-        <v>3683.35</v>
+        <v>3733.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3727.33</v>
+        <v>3788.87</v>
       </c>
       <c r="O2" t="n">
-        <v>3715.6</v>
+        <v>3808.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -716,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3680.2</v>
+        <v>3721.3</v>
       </c>
       <c r="C3" t="n">
-        <v>3744</v>
+        <v>3824.6</v>
       </c>
       <c r="D3" t="n">
-        <v>3660.5</v>
+        <v>3718.1</v>
       </c>
       <c r="E3" t="n">
-        <v>3705.8</v>
+        <v>3809</v>
       </c>
       <c r="F3" t="n">
-        <v>19.4</v>
+        <v>103.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0278</v>
       </c>
       <c r="H3" t="n">
-        <v>83.5</v>
+        <v>106.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3528.2</v>
+        <v>3577</v>
       </c>
       <c r="J3" t="n">
-        <v>3601.87</v>
+        <v>3624.08</v>
       </c>
       <c r="K3" t="n">
-        <v>3639.65</v>
+        <v>3664.05</v>
       </c>
       <c r="L3" t="n">
-        <v>3677.42</v>
+        <v>3704.03</v>
       </c>
       <c r="M3" t="n">
-        <v>3733.15</v>
+        <v>3747.55</v>
       </c>
       <c r="N3" t="n">
-        <v>3788.87</v>
+        <v>3791.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3808.7</v>
+        <v>3827.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -777,11 +775,13 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -796,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3721.3</v>
+        <v>3788.8</v>
       </c>
       <c r="C4" t="n">
-        <v>3824.6</v>
+        <v>3923.3</v>
       </c>
       <c r="D4" t="n">
-        <v>3718.1</v>
+        <v>3785.5</v>
       </c>
       <c r="E4" t="n">
-        <v>3809</v>
+        <v>3908.9</v>
       </c>
       <c r="F4" t="n">
-        <v>103.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0262</v>
       </c>
       <c r="H4" t="n">
-        <v>106.5</v>
+        <v>137.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3577</v>
+        <v>3611.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3624.08</v>
+        <v>3721.32</v>
       </c>
       <c r="K4" t="n">
-        <v>3664.05</v>
+        <v>3755.75</v>
       </c>
       <c r="L4" t="n">
-        <v>3704.03</v>
+        <v>3790.18</v>
       </c>
       <c r="M4" t="n">
-        <v>3747.55</v>
+        <v>3862.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3791.08</v>
+        <v>3934.32</v>
       </c>
       <c r="O4" t="n">
-        <v>3827.5</v>
+        <v>3931.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,13 +860,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -878,50 +878,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3788.8</v>
+        <v>3913.5</v>
       </c>
       <c r="C5" t="n">
-        <v>3923.3</v>
+        <v>4081</v>
       </c>
       <c r="D5" t="n">
-        <v>3785.5</v>
+        <v>3909.2</v>
       </c>
       <c r="E5" t="n">
-        <v>3908.9</v>
+        <v>4000.4</v>
       </c>
       <c r="F5" t="n">
-        <v>99.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0262</v>
+        <v>0.0234</v>
       </c>
       <c r="H5" t="n">
-        <v>137.8</v>
+        <v>171.8</v>
       </c>
       <c r="I5" t="n">
-        <v>3611.6</v>
+        <v>3647.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3721.32</v>
+        <v>3798.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3755.75</v>
+        <v>3840</v>
       </c>
       <c r="L5" t="n">
-        <v>3790.18</v>
+        <v>3881.65</v>
       </c>
       <c r="M5" t="n">
-        <v>3862.25</v>
+        <v>3977.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3934.32</v>
+        <v>4073.95</v>
       </c>
       <c r="O5" t="n">
-        <v>3931.1</v>
+        <v>4061.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,15 +939,17 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
@@ -960,50 +962,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3913.5</v>
+        <v>4018.3</v>
       </c>
       <c r="C6" t="n">
-        <v>4081</v>
+        <v>4392</v>
       </c>
       <c r="D6" t="n">
-        <v>3909.2</v>
+        <v>4011.3</v>
       </c>
       <c r="E6" t="n">
-        <v>4000.4</v>
+        <v>4213.3</v>
       </c>
       <c r="F6" t="n">
-        <v>91.5</v>
+        <v>212.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0532</v>
       </c>
       <c r="H6" t="n">
-        <v>171.8</v>
+        <v>380.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3647.7</v>
+        <v>3737.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3798.35</v>
+        <v>3831.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3840</v>
+        <v>3914.5</v>
       </c>
       <c r="L6" t="n">
-        <v>3881.65</v>
+        <v>3997.75</v>
       </c>
       <c r="M6" t="n">
-        <v>3977.8</v>
+        <v>4086.3</v>
       </c>
       <c r="N6" t="n">
-        <v>4073.95</v>
+        <v>4174.85</v>
       </c>
       <c r="O6" t="n">
-        <v>4061.1</v>
+        <v>4252.8</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,12 +1023,12 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V6" s="8" t="inlineStr">
@@ -1044,50 +1046,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4018.3</v>
+        <v>4269</v>
       </c>
       <c r="C7" t="n">
-        <v>4392</v>
+        <v>4398</v>
       </c>
       <c r="D7" t="n">
-        <v>4011.3</v>
+        <v>4021.2</v>
       </c>
       <c r="E7" t="n">
-        <v>4213.3</v>
+        <v>4137.8</v>
       </c>
       <c r="F7" t="n">
-        <v>212.9</v>
+        <v>-75.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0532</v>
+        <v>-0.0179</v>
       </c>
       <c r="H7" t="n">
-        <v>380.7</v>
+        <v>376.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3737.4</v>
+        <v>3630.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3831.25</v>
+        <v>3838.42</v>
       </c>
       <c r="K7" t="n">
-        <v>3914.5</v>
+        <v>4022.95</v>
       </c>
       <c r="L7" t="n">
-        <v>3997.75</v>
+        <v>4207.47</v>
       </c>
       <c r="M7" t="n">
-        <v>4086.3</v>
+        <v>4403.65</v>
       </c>
       <c r="N7" t="n">
-        <v>4174.85</v>
+        <v>4599.82</v>
       </c>
       <c r="O7" t="n">
-        <v>4252.8</v>
+        <v>4772.7</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1095,83 +1097,83 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4269</v>
+        <v>4103.2</v>
       </c>
       <c r="C8" t="n">
-        <v>4398</v>
+        <v>4123.8</v>
       </c>
       <c r="D8" t="n">
-        <v>4021.2</v>
+        <v>3901.3</v>
       </c>
       <c r="E8" t="n">
-        <v>4137.8</v>
+        <v>3996.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-75.5</v>
+        <v>-141.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0179</v>
+        <v>-0.0341</v>
       </c>
       <c r="H8" t="n">
-        <v>376.8</v>
+        <v>222.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3630.6</v>
+        <v>3644.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3838.42</v>
+        <v>3725.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4022.95</v>
+        <v>3949.4</v>
       </c>
       <c r="L8" t="n">
-        <v>4207.47</v>
+        <v>4173.7</v>
       </c>
       <c r="M8" t="n">
-        <v>4403.65</v>
+        <v>4326.2</v>
       </c>
       <c r="N8" t="n">
-        <v>4599.82</v>
+        <v>4478.7</v>
       </c>
       <c r="O8" t="n">
-        <v>4772.7</v>
+        <v>4774.8</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1181,12 +1183,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1205,57 +1207,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4103.2</v>
+        <v>4001</v>
       </c>
       <c r="C9" t="n">
-        <v>4123.8</v>
+        <v>4043.1</v>
       </c>
       <c r="D9" t="n">
-        <v>3901.3</v>
+        <v>3935.7</v>
       </c>
       <c r="E9" t="n">
-        <v>3996.5</v>
+        <v>4009.8</v>
       </c>
       <c r="F9" t="n">
-        <v>-141.3</v>
+        <v>13.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0341</v>
+        <v>0.0033</v>
       </c>
       <c r="H9" t="n">
-        <v>222.5</v>
+        <v>107.4</v>
       </c>
       <c r="I9" t="n">
-        <v>3644.4</v>
+        <v>3678.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3725.1</v>
+        <v>3765.98</v>
       </c>
       <c r="K9" t="n">
-        <v>3949.4</v>
+        <v>3885.25</v>
       </c>
       <c r="L9" t="n">
-        <v>4173.7</v>
+        <v>4004.52</v>
       </c>
       <c r="M9" t="n">
-        <v>4326.2</v>
+        <v>4107.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4478.7</v>
+        <v>4210.97</v>
       </c>
       <c r="O9" t="n">
-        <v>4774.8</v>
+        <v>4346.3</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1263,14 +1265,12 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1289,57 +1289,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4001</v>
+        <v>4007.2</v>
       </c>
       <c r="C10" t="n">
-        <v>4043.1</v>
+        <v>4250</v>
       </c>
       <c r="D10" t="n">
-        <v>3935.7</v>
+        <v>4004.2</v>
       </c>
       <c r="E10" t="n">
-        <v>4009.8</v>
+        <v>4094.2</v>
       </c>
       <c r="F10" t="n">
-        <v>13.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.021</v>
       </c>
       <c r="H10" t="n">
-        <v>107.4</v>
+        <v>245.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3678.8</v>
+        <v>3828.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3765.98</v>
+        <v>3912.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3885.25</v>
+        <v>3956.1</v>
       </c>
       <c r="L10" t="n">
-        <v>4004.52</v>
+        <v>3999.6</v>
       </c>
       <c r="M10" t="n">
-        <v>4107.75</v>
+        <v>4063.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4210.97</v>
+        <v>4127.4</v>
       </c>
       <c r="O10" t="n">
-        <v>4346.3</v>
+        <v>4150.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,76 +1352,78 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4007.2</v>
+        <v>4084.4</v>
       </c>
       <c r="C11" t="n">
-        <v>4250</v>
+        <v>4134.3</v>
       </c>
       <c r="D11" t="n">
-        <v>4004.2</v>
+        <v>3997.4</v>
       </c>
       <c r="E11" t="n">
-        <v>4094.2</v>
+        <v>4079.5</v>
       </c>
       <c r="F11" t="n">
-        <v>84.40000000000001</v>
+        <v>-14.7</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.0036</v>
       </c>
       <c r="H11" t="n">
-        <v>245.8</v>
+        <v>136.9</v>
       </c>
       <c r="I11" t="n">
-        <v>3828.3</v>
+        <v>3758.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3912.6</v>
+        <v>3831.95</v>
       </c>
       <c r="K11" t="n">
-        <v>3956.1</v>
+        <v>3971.3</v>
       </c>
       <c r="L11" t="n">
-        <v>3999.6</v>
+        <v>4110.65</v>
       </c>
       <c r="M11" t="n">
-        <v>4063.5</v>
+        <v>4217.1</v>
       </c>
       <c r="N11" t="n">
-        <v>4127.4</v>
+        <v>4323.55</v>
       </c>
       <c r="O11" t="n">
-        <v>4150.5</v>
+        <v>4495.8</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1432,80 +1434,78 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4084.4</v>
+        <v>4069.2</v>
       </c>
       <c r="C12" t="n">
-        <v>4134.3</v>
+        <v>4263.1</v>
       </c>
       <c r="D12" t="n">
-        <v>3997.4</v>
+        <v>4036.4</v>
       </c>
       <c r="E12" t="n">
-        <v>4079.5</v>
+        <v>4254.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.7</v>
+        <v>175.4</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.043</v>
       </c>
       <c r="H12" t="n">
-        <v>136.9</v>
+        <v>226.7</v>
       </c>
       <c r="I12" t="n">
-        <v>3758.4</v>
+        <v>3860.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3831.95</v>
+        <v>3949.43</v>
       </c>
       <c r="K12" t="n">
-        <v>3971.3</v>
+        <v>4011.05</v>
       </c>
       <c r="L12" t="n">
-        <v>4110.65</v>
+        <v>4072.67</v>
       </c>
       <c r="M12" t="n">
-        <v>4217.1</v>
+        <v>4147.95</v>
       </c>
       <c r="N12" t="n">
-        <v>4323.55</v>
+        <v>4223.22</v>
       </c>
       <c r="O12" t="n">
-        <v>4495.8</v>
+        <v>4271.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1516,78 +1516,80 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4069.2</v>
+        <v>4258.5</v>
       </c>
       <c r="C13" t="n">
-        <v>4263.1</v>
+        <v>4299.6</v>
       </c>
       <c r="D13" t="n">
-        <v>4036.4</v>
+        <v>4194</v>
       </c>
       <c r="E13" t="n">
-        <v>4254.9</v>
+        <v>4243</v>
       </c>
       <c r="F13" t="n">
-        <v>175.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.043</v>
+        <v>-0.0028</v>
       </c>
       <c r="H13" t="n">
-        <v>226.7</v>
+        <v>105.6</v>
       </c>
       <c r="I13" t="n">
-        <v>3860.5</v>
+        <v>3809.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3949.43</v>
+        <v>4080.77</v>
       </c>
       <c r="K13" t="n">
-        <v>4011.05</v>
+        <v>4141.55</v>
       </c>
       <c r="L13" t="n">
-        <v>4072.67</v>
+        <v>4202.32</v>
       </c>
       <c r="M13" t="n">
-        <v>4147.95</v>
+        <v>4368.25</v>
       </c>
       <c r="N13" t="n">
-        <v>4223.22</v>
+        <v>4534.18</v>
       </c>
       <c r="O13" t="n">
-        <v>4271.2</v>
+        <v>4489.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,78 +1602,76 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4258.5</v>
+        <v>4228.1</v>
       </c>
       <c r="C14" t="n">
-        <v>4299.6</v>
+        <v>4387.8</v>
       </c>
       <c r="D14" t="n">
-        <v>4194</v>
+        <v>4197.8</v>
       </c>
       <c r="E14" t="n">
-        <v>4243</v>
+        <v>4328.3</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.9</v>
+        <v>85.3</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0201</v>
       </c>
       <c r="H14" t="n">
-        <v>105.6</v>
+        <v>190</v>
       </c>
       <c r="I14" t="n">
-        <v>3809.7</v>
+        <v>4088.4</v>
       </c>
       <c r="J14" t="n">
-        <v>4080.77</v>
+        <v>4135.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4141.55</v>
+        <v>4190.2</v>
       </c>
       <c r="L14" t="n">
-        <v>4202.32</v>
+        <v>4244.9</v>
       </c>
       <c r="M14" t="n">
-        <v>4368.25</v>
+        <v>4295.8</v>
       </c>
       <c r="N14" t="n">
-        <v>4534.18</v>
+        <v>4346.7</v>
       </c>
       <c r="O14" t="n">
-        <v>4489.8</v>
+        <v>4405.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1684,14 +1684,18 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1701,59 +1705,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4228.1</v>
+        <v>4330</v>
       </c>
       <c r="C15" t="n">
-        <v>4387.8</v>
+        <v>4409.5</v>
       </c>
       <c r="D15" t="n">
-        <v>4197.8</v>
+        <v>4297.4</v>
       </c>
       <c r="E15" t="n">
-        <v>4328.3</v>
+        <v>4387.3</v>
       </c>
       <c r="F15" t="n">
-        <v>85.3</v>
+        <v>59</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0136</v>
       </c>
       <c r="H15" t="n">
-        <v>190</v>
+        <v>112.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4088.4</v>
+        <v>4007.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4135.5</v>
+        <v>4156.05</v>
       </c>
       <c r="K15" t="n">
-        <v>4190.2</v>
+        <v>4233.3</v>
       </c>
       <c r="L15" t="n">
-        <v>4244.9</v>
+        <v>4310.55</v>
       </c>
       <c r="M15" t="n">
-        <v>4295.8</v>
+        <v>4423.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4346.7</v>
+        <v>4536.05</v>
       </c>
       <c r="O15" t="n">
-        <v>4405.2</v>
+        <v>4577.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,13 +1771,11 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1792,50 +1790,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4330</v>
+        <v>4369.9</v>
       </c>
       <c r="C16" t="n">
-        <v>4409.5</v>
+        <v>4584</v>
       </c>
       <c r="D16" t="n">
-        <v>4297.4</v>
+        <v>4367.9</v>
       </c>
       <c r="E16" t="n">
-        <v>4387.3</v>
+        <v>4552.7</v>
       </c>
       <c r="F16" t="n">
-        <v>59</v>
+        <v>165.4</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0377</v>
       </c>
       <c r="H16" t="n">
-        <v>112.1</v>
+        <v>216.1</v>
       </c>
       <c r="I16" t="n">
-        <v>4007.8</v>
+        <v>4185.3</v>
       </c>
       <c r="J16" t="n">
-        <v>4156.05</v>
+        <v>4292.12</v>
       </c>
       <c r="K16" t="n">
-        <v>4233.3</v>
+        <v>4331.25</v>
       </c>
       <c r="L16" t="n">
-        <v>4310.55</v>
+        <v>4370.37</v>
       </c>
       <c r="M16" t="n">
-        <v>4423.3</v>
+        <v>4443.35</v>
       </c>
       <c r="N16" t="n">
-        <v>4536.05</v>
+        <v>4516.32</v>
       </c>
       <c r="O16" t="n">
-        <v>4577.8</v>
+        <v>4521.6</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,14 +1851,18 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1872,83 +1874,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4369.9</v>
+        <v>4568</v>
       </c>
       <c r="C17" t="n">
-        <v>4584</v>
+        <v>4581.3</v>
       </c>
       <c r="D17" t="n">
-        <v>4367.9</v>
+        <v>4284.3</v>
       </c>
       <c r="E17" t="n">
-        <v>4552.7</v>
+        <v>4329.6</v>
       </c>
       <c r="F17" t="n">
-        <v>165.4</v>
+        <v>-223.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.049</v>
       </c>
       <c r="H17" t="n">
-        <v>216.1</v>
+        <v>297</v>
       </c>
       <c r="I17" t="n">
-        <v>4185.3</v>
+        <v>4151.8</v>
       </c>
       <c r="J17" t="n">
-        <v>4292.12</v>
+        <v>4374.98</v>
       </c>
       <c r="K17" t="n">
-        <v>4331.25</v>
+        <v>4444.65</v>
       </c>
       <c r="L17" t="n">
-        <v>4370.37</v>
+        <v>4514.33</v>
       </c>
       <c r="M17" t="n">
-        <v>4443.35</v>
+        <v>4660.75</v>
       </c>
       <c r="N17" t="n">
-        <v>4516.32</v>
+        <v>4807.18</v>
       </c>
       <c r="O17" t="n">
-        <v>4521.6</v>
+        <v>4800.1</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1956,72 +1956,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4568</v>
+        <v>4368.3</v>
       </c>
       <c r="C18" t="n">
-        <v>4581.3</v>
+        <v>4527</v>
       </c>
       <c r="D18" t="n">
-        <v>4284.3</v>
+        <v>4354.6</v>
       </c>
       <c r="E18" t="n">
-        <v>4329.6</v>
+        <v>4500.9</v>
       </c>
       <c r="F18" t="n">
-        <v>-223.1</v>
+        <v>171.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.049</v>
+        <v>0.0396</v>
       </c>
       <c r="H18" t="n">
-        <v>297</v>
+        <v>172.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4151.8</v>
+        <v>3987.3</v>
       </c>
       <c r="J18" t="n">
-        <v>4374.98</v>
+        <v>3981</v>
       </c>
       <c r="K18" t="n">
-        <v>4444.65</v>
+        <v>4181.1</v>
       </c>
       <c r="L18" t="n">
-        <v>4514.33</v>
+        <v>4381.2</v>
       </c>
       <c r="M18" t="n">
-        <v>4660.75</v>
+        <v>4478.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4807.18</v>
+        <v>4575</v>
       </c>
       <c r="O18" t="n">
-        <v>4800.1</v>
+        <v>4878.3</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2033,55 +2031,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4368.3</v>
+        <v>4529.1</v>
       </c>
       <c r="C19" t="n">
-        <v>4527</v>
+        <v>4650.5</v>
       </c>
       <c r="D19" t="n">
-        <v>4354.6</v>
+        <v>4520.8</v>
       </c>
       <c r="E19" t="n">
-        <v>4500.9</v>
+        <v>4595.4</v>
       </c>
       <c r="F19" t="n">
-        <v>171.3</v>
+        <v>94.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.021</v>
       </c>
       <c r="H19" t="n">
-        <v>172.4</v>
+        <v>129.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3987.3</v>
+        <v>4182.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3981</v>
+        <v>4358.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4181.1</v>
+        <v>4414.7</v>
       </c>
       <c r="L19" t="n">
-        <v>4381.2</v>
+        <v>4470.85</v>
       </c>
       <c r="M19" t="n">
-        <v>4478.1</v>
+        <v>4587.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4575</v>
+        <v>4703.35</v>
       </c>
       <c r="O19" t="n">
-        <v>4878.3</v>
+        <v>4699.4</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2115,57 +2117,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4529.1</v>
+        <v>4633.7</v>
       </c>
       <c r="C20" t="n">
-        <v>4650.5</v>
+        <v>4991.4</v>
       </c>
       <c r="D20" t="n">
-        <v>4520.8</v>
+        <v>4622.2</v>
       </c>
       <c r="E20" t="n">
-        <v>4595.4</v>
+        <v>4979.7</v>
       </c>
       <c r="F20" t="n">
-        <v>94.5</v>
+        <v>384.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.021</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>129.7</v>
+        <v>369.2</v>
       </c>
       <c r="I20" t="n">
-        <v>4182.2</v>
+        <v>4391.1</v>
       </c>
       <c r="J20" t="n">
-        <v>4358.55</v>
+        <v>4470.57</v>
       </c>
       <c r="K20" t="n">
-        <v>4414.7</v>
+        <v>4530.55</v>
       </c>
       <c r="L20" t="n">
-        <v>4470.85</v>
+        <v>4590.52</v>
       </c>
       <c r="M20" t="n">
-        <v>4587.1</v>
+        <v>4660.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4703.35</v>
+        <v>4729.98</v>
       </c>
       <c r="O20" t="n">
-        <v>4699.4</v>
+        <v>4780.2</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2183,86 +2185,90 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4633.7</v>
+        <v>5013.4</v>
       </c>
       <c r="C21" t="n">
-        <v>4991.4</v>
+        <v>5586.2</v>
       </c>
       <c r="D21" t="n">
-        <v>4622.2</v>
+        <v>4700.4</v>
       </c>
       <c r="E21" t="n">
-        <v>4979.7</v>
+        <v>4745.1</v>
       </c>
       <c r="F21" t="n">
-        <v>384.3</v>
+        <v>-234.6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.0471</v>
       </c>
       <c r="H21" t="n">
-        <v>369.2</v>
+        <v>885.8</v>
       </c>
       <c r="I21" t="n">
-        <v>4391.1</v>
+        <v>4253</v>
       </c>
       <c r="J21" t="n">
-        <v>4470.57</v>
+        <v>4696.95</v>
       </c>
       <c r="K21" t="n">
-        <v>4530.55</v>
+        <v>4795.1</v>
       </c>
       <c r="L21" t="n">
-        <v>4590.52</v>
+        <v>4893.25</v>
       </c>
       <c r="M21" t="n">
-        <v>4660.25</v>
+        <v>5164.3</v>
       </c>
       <c r="N21" t="n">
-        <v>4729.98</v>
+        <v>5435.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4780.2</v>
+        <v>5360.6</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2277,7 +2283,7 @@
       </c>
       <c r="V21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
@@ -2285,88 +2291,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5013.4</v>
+        <v>4816</v>
       </c>
       <c r="C22" t="n">
-        <v>5586.2</v>
+        <v>5113.9</v>
       </c>
       <c r="D22" t="n">
-        <v>4700.4</v>
+        <v>4423.2</v>
       </c>
       <c r="E22" t="n">
-        <v>4745.1</v>
+        <v>4979.8</v>
       </c>
       <c r="F22" t="n">
-        <v>-234.6</v>
+        <v>234.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0471</v>
+        <v>0.0495</v>
       </c>
       <c r="H22" t="n">
-        <v>885.8</v>
+        <v>690.7</v>
       </c>
       <c r="I22" t="n">
-        <v>4253</v>
+        <v>3814.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4696.95</v>
+        <v>3660.2</v>
       </c>
       <c r="K22" t="n">
-        <v>4795.1</v>
+        <v>4302.2</v>
       </c>
       <c r="L22" t="n">
-        <v>4893.25</v>
+        <v>4944.2</v>
       </c>
       <c r="M22" t="n">
-        <v>5164.3</v>
+        <v>5188</v>
       </c>
       <c r="N22" t="n">
-        <v>5435.35</v>
+        <v>5431.8</v>
       </c>
       <c r="O22" t="n">
-        <v>5360.6</v>
+        <v>6472</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2375,57 +2375,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4816</v>
+        <v>5003.6</v>
       </c>
       <c r="C23" t="n">
-        <v>5113.9</v>
+        <v>5144.5</v>
       </c>
       <c r="D23" t="n">
-        <v>4423.2</v>
+        <v>4900</v>
       </c>
       <c r="E23" t="n">
-        <v>4979.8</v>
+        <v>5046.3</v>
       </c>
       <c r="F23" t="n">
-        <v>234.7</v>
+        <v>66.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0495</v>
+        <v>0.0134</v>
       </c>
       <c r="H23" t="n">
-        <v>690.7</v>
+        <v>244.5</v>
       </c>
       <c r="I23" t="n">
-        <v>3814.6</v>
+        <v>3732.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3660.2</v>
+        <v>4394.72</v>
       </c>
       <c r="K23" t="n">
-        <v>4302.2</v>
+        <v>4634.45</v>
       </c>
       <c r="L23" t="n">
-        <v>4944.2</v>
+        <v>4874.17</v>
       </c>
       <c r="M23" t="n">
-        <v>5188</v>
+        <v>5325.15</v>
       </c>
       <c r="N23" t="n">
-        <v>5431.8</v>
+        <v>5776.12</v>
       </c>
       <c r="O23" t="n">
-        <v>6472</v>
+        <v>5804.6</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2455,59 +2455,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5003.6</v>
+        <v>5050</v>
       </c>
       <c r="C24" t="n">
-        <v>5144.5</v>
+        <v>5131</v>
       </c>
       <c r="D24" t="n">
-        <v>4900</v>
+        <v>4854.2</v>
       </c>
       <c r="E24" t="n">
-        <v>5046.3</v>
+        <v>5080.9</v>
       </c>
       <c r="F24" t="n">
-        <v>66.5</v>
+        <v>34.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0069</v>
       </c>
       <c r="H24" t="n">
-        <v>244.5</v>
+        <v>276.8</v>
       </c>
       <c r="I24" t="n">
-        <v>3732.5</v>
+        <v>4655.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4394.72</v>
+        <v>4813.82</v>
       </c>
       <c r="K24" t="n">
-        <v>4634.45</v>
+        <v>4924.05</v>
       </c>
       <c r="L24" t="n">
-        <v>4874.17</v>
+        <v>5034.27</v>
       </c>
       <c r="M24" t="n">
-        <v>5325.15</v>
+        <v>5168.55</v>
       </c>
       <c r="N24" t="n">
-        <v>5776.12</v>
+        <v>5302.82</v>
       </c>
       <c r="O24" t="n">
-        <v>5804.6</v>
+        <v>5389</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2515,8 +2511,10 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
@@ -2537,55 +2535,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5050</v>
+        <v>5128.8</v>
       </c>
       <c r="C25" t="n">
-        <v>5131</v>
+        <v>5299</v>
       </c>
       <c r="D25" t="n">
-        <v>4854.2</v>
+        <v>5109.5</v>
       </c>
       <c r="E25" t="n">
-        <v>5080.9</v>
+        <v>5247.9</v>
       </c>
       <c r="F25" t="n">
-        <v>34.6</v>
+        <v>167</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0329</v>
       </c>
       <c r="H25" t="n">
-        <v>276.8</v>
+        <v>189.5</v>
       </c>
       <c r="I25" t="n">
-        <v>4655.5</v>
+        <v>4577.4</v>
       </c>
       <c r="J25" t="n">
-        <v>4813.82</v>
+        <v>4848.25</v>
       </c>
       <c r="K25" t="n">
-        <v>4924.05</v>
+        <v>4942.5</v>
       </c>
       <c r="L25" t="n">
-        <v>5034.27</v>
+        <v>5036.75</v>
       </c>
       <c r="M25" t="n">
-        <v>5168.55</v>
+        <v>5219.3</v>
       </c>
       <c r="N25" t="n">
-        <v>5302.82</v>
+        <v>5401.85</v>
       </c>
       <c r="O25" t="n">
-        <v>5389</v>
+        <v>5407.8</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2593,18 +2595,18 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2617,77 +2619,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5128.8</v>
+        <v>5360</v>
       </c>
       <c r="C26" t="n">
-        <v>5299</v>
+        <v>5434.1</v>
       </c>
       <c r="D26" t="n">
-        <v>5109.5</v>
+        <v>5005</v>
       </c>
       <c r="E26" t="n">
-        <v>5247.9</v>
+        <v>5158.7</v>
       </c>
       <c r="F26" t="n">
-        <v>167</v>
+        <v>-89.2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0329</v>
+        <v>-0.017</v>
       </c>
       <c r="H26" t="n">
-        <v>189.5</v>
+        <v>429.1</v>
       </c>
       <c r="I26" t="n">
-        <v>4577.4</v>
+        <v>4920</v>
       </c>
       <c r="J26" t="n">
-        <v>4848.25</v>
+        <v>5080.22</v>
       </c>
       <c r="K26" t="n">
-        <v>4942.5</v>
+        <v>5153.15</v>
       </c>
       <c r="L26" t="n">
-        <v>5036.75</v>
+        <v>5226.07</v>
       </c>
       <c r="M26" t="n">
-        <v>5219.3</v>
+        <v>5342.65</v>
       </c>
       <c r="N26" t="n">
-        <v>5401.85</v>
+        <v>5459.22</v>
       </c>
       <c r="O26" t="n">
-        <v>5407.8</v>
+        <v>5488.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U26" s="8" t="n">
@@ -2701,63 +2703,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5360</v>
+        <v>5186.7</v>
       </c>
       <c r="C27" t="n">
-        <v>5434.1</v>
+        <v>5248.7</v>
       </c>
       <c r="D27" t="n">
-        <v>5005</v>
+        <v>5014.1</v>
       </c>
       <c r="E27" t="n">
-        <v>5158.7</v>
+        <v>5061.7</v>
       </c>
       <c r="F27" t="n">
-        <v>-89.2</v>
+        <v>-97</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0188</v>
       </c>
       <c r="H27" t="n">
-        <v>429.1</v>
+        <v>234.6</v>
       </c>
       <c r="I27" t="n">
-        <v>4920</v>
+        <v>4575.9</v>
       </c>
       <c r="J27" t="n">
-        <v>5080.22</v>
+        <v>4699.18</v>
       </c>
       <c r="K27" t="n">
-        <v>5153.15</v>
+        <v>4944.15</v>
       </c>
       <c r="L27" t="n">
-        <v>5226.07</v>
+        <v>5189.13</v>
       </c>
       <c r="M27" t="n">
-        <v>5342.65</v>
+        <v>5373.25</v>
       </c>
       <c r="N27" t="n">
-        <v>5459.22</v>
+        <v>5557.38</v>
       </c>
       <c r="O27" t="n">
-        <v>5488.5</v>
+        <v>5863.2</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q27" s="6" t="n">
+        <v/>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
@@ -2769,10 +2773,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2794,60 +2796,64 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5186.7</v>
+        <v>5010</v>
       </c>
       <c r="C28" t="n">
-        <v>5248.7</v>
+        <v>5049.4</v>
       </c>
       <c r="D28" t="n">
-        <v>5014.1</v>
+        <v>4478.4</v>
       </c>
       <c r="E28" t="n">
-        <v>5061.7</v>
+        <v>4574.9</v>
       </c>
       <c r="F28" t="n">
-        <v>-97</v>
+        <v>-486.8</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0188</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>234.6</v>
+        <v>571</v>
       </c>
       <c r="I28" t="n">
-        <v>4575.9</v>
+        <v>4779.5</v>
       </c>
       <c r="J28" t="n">
-        <v>4699.18</v>
+        <v>4792.25</v>
       </c>
       <c r="K28" t="n">
-        <v>4944.15</v>
+        <v>4944.4</v>
       </c>
       <c r="L28" t="n">
-        <v>5189.13</v>
+        <v>5096.55</v>
       </c>
       <c r="M28" t="n">
-        <v>5373.25</v>
+        <v>5179</v>
       </c>
       <c r="N28" t="n">
-        <v>5557.38</v>
+        <v>5261.45</v>
       </c>
       <c r="O28" t="n">
-        <v>5863.2</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+        <v>5483.3</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
@@ -2864,83 +2870,75 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5010</v>
+        <v>4450</v>
       </c>
       <c r="C29" t="n">
-        <v>5049.4</v>
+        <v>4601</v>
       </c>
       <c r="D29" t="n">
-        <v>4478.4</v>
+        <v>4100</v>
       </c>
       <c r="E29" t="n">
-        <v>4574.9</v>
+        <v>4492.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-486.8</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="H29" t="n">
-        <v>571</v>
+        <v>501</v>
       </c>
       <c r="I29" t="n">
-        <v>4779.5</v>
+        <v>3907.4</v>
       </c>
       <c r="J29" t="n">
-        <v>4792.25</v>
+        <v>3909.4</v>
       </c>
       <c r="K29" t="n">
-        <v>4944.4</v>
+        <v>4289.4</v>
       </c>
       <c r="L29" t="n">
-        <v>5096.55</v>
+        <v>4669.4</v>
       </c>
       <c r="M29" t="n">
-        <v>5179</v>
+        <v>4860.4</v>
       </c>
       <c r="N29" t="n">
-        <v>5261.45</v>
+        <v>5051.4</v>
       </c>
       <c r="O29" t="n">
-        <v>5483.3</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
+        <v>5620.4</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2962,50 +2960,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4450</v>
+        <v>4482.8</v>
       </c>
       <c r="C30" t="n">
-        <v>4601</v>
+        <v>4825.9</v>
       </c>
       <c r="D30" t="n">
-        <v>4100</v>
+        <v>4413.4</v>
       </c>
       <c r="E30" t="n">
-        <v>4492.5</v>
+        <v>4679.7</v>
       </c>
       <c r="F30" t="n">
-        <v>-82.40000000000001</v>
+        <v>187.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0417</v>
       </c>
       <c r="H30" t="n">
-        <v>501</v>
+        <v>412.5</v>
       </c>
       <c r="I30" t="n">
-        <v>3907.4</v>
+        <v>3599</v>
       </c>
       <c r="J30" t="n">
-        <v>3909.4</v>
+        <v>4062.5</v>
       </c>
       <c r="K30" t="n">
-        <v>4289.4</v>
+        <v>4242</v>
       </c>
       <c r="L30" t="n">
-        <v>4669.4</v>
+        <v>4421.5</v>
       </c>
       <c r="M30" t="n">
-        <v>4860.4</v>
+        <v>4743</v>
       </c>
       <c r="N30" t="n">
-        <v>5051.4</v>
+        <v>5064.5</v>
       </c>
       <c r="O30" t="n">
-        <v>5620.4</v>
+        <v>5102</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3013,18 +3011,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3037,55 +3035,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4482.8</v>
+        <v>4675</v>
       </c>
       <c r="C31" t="n">
-        <v>4825.9</v>
+        <v>4888</v>
       </c>
       <c r="D31" t="n">
-        <v>4413.4</v>
+        <v>4626.2</v>
       </c>
       <c r="E31" t="n">
-        <v>4679.7</v>
+        <v>4787.4</v>
       </c>
       <c r="F31" t="n">
-        <v>187.2</v>
+        <v>107.7</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0417</v>
+        <v>0.023</v>
       </c>
       <c r="H31" t="n">
-        <v>412.5</v>
+        <v>261.8</v>
       </c>
       <c r="I31" t="n">
-        <v>3599</v>
+        <v>4000.9</v>
       </c>
       <c r="J31" t="n">
-        <v>4062.5</v>
+        <v>4297.23</v>
       </c>
       <c r="K31" t="n">
-        <v>4242</v>
+        <v>4473.45</v>
       </c>
       <c r="L31" t="n">
-        <v>4421.5</v>
+        <v>4649.68</v>
       </c>
       <c r="M31" t="n">
-        <v>4743</v>
+        <v>4885.95</v>
       </c>
       <c r="N31" t="n">
-        <v>5064.5</v>
+        <v>5122.23</v>
       </c>
       <c r="O31" t="n">
-        <v>5102</v>
+        <v>5238.4</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3126,50 +3128,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4675</v>
+        <v>4710</v>
       </c>
       <c r="C32" t="n">
-        <v>4888</v>
+        <v>4917.7</v>
       </c>
       <c r="D32" t="n">
-        <v>4626.2</v>
+        <v>4626</v>
       </c>
       <c r="E32" t="n">
-        <v>4787.4</v>
+        <v>4879.6</v>
       </c>
       <c r="F32" t="n">
-        <v>107.7</v>
+        <v>92.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0193</v>
       </c>
       <c r="H32" t="n">
-        <v>261.8</v>
+        <v>291.7</v>
       </c>
       <c r="I32" t="n">
-        <v>4000.9</v>
+        <v>4364.4</v>
       </c>
       <c r="J32" t="n">
-        <v>4297.23</v>
+        <v>4540.75</v>
       </c>
       <c r="K32" t="n">
-        <v>4473.45</v>
+        <v>4656.5</v>
       </c>
       <c r="L32" t="n">
-        <v>4649.68</v>
+        <v>4772.25</v>
       </c>
       <c r="M32" t="n">
-        <v>4885.95</v>
+        <v>4918.3</v>
       </c>
       <c r="N32" t="n">
-        <v>5122.23</v>
+        <v>5064.35</v>
       </c>
       <c r="O32" t="n">
-        <v>5238.4</v>
+        <v>5149.8</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3177,8 +3179,10 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
@@ -3203,57 +3207,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4710</v>
+        <v>4811.8</v>
       </c>
       <c r="C33" t="n">
-        <v>4917.7</v>
+        <v>4854.8</v>
       </c>
       <c r="D33" t="n">
-        <v>4626</v>
+        <v>4672.2</v>
       </c>
       <c r="E33" t="n">
-        <v>4879.6</v>
+        <v>4740.9</v>
       </c>
       <c r="F33" t="n">
-        <v>92.2</v>
+        <v>-138.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0193</v>
+        <v>-0.0284</v>
       </c>
       <c r="H33" t="n">
-        <v>291.7</v>
+        <v>182.6</v>
       </c>
       <c r="I33" t="n">
-        <v>4364.4</v>
+        <v>4334.3</v>
       </c>
       <c r="J33" t="n">
-        <v>4540.75</v>
+        <v>4641.77</v>
       </c>
       <c r="K33" t="n">
-        <v>4656.5</v>
+        <v>4733.75</v>
       </c>
       <c r="L33" t="n">
-        <v>4772.25</v>
+        <v>4825.73</v>
       </c>
       <c r="M33" t="n">
-        <v>4918.3</v>
+        <v>5025.45</v>
       </c>
       <c r="N33" t="n">
-        <v>5064.35</v>
+        <v>5225.18</v>
       </c>
       <c r="O33" t="n">
-        <v>5149.8</v>
+        <v>5209.4</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3263,19 +3267,17 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3289,63 +3291,65 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4811.8</v>
+        <v>4713.1</v>
       </c>
       <c r="C34" t="n">
-        <v>4854.8</v>
+        <v>4745.8</v>
       </c>
       <c r="D34" t="n">
-        <v>4672.2</v>
+        <v>4522.2</v>
       </c>
       <c r="E34" t="n">
-        <v>4740.9</v>
+        <v>4644.5</v>
       </c>
       <c r="F34" t="n">
-        <v>-138.7</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0284</v>
+        <v>-0.0203</v>
       </c>
       <c r="H34" t="n">
-        <v>182.6</v>
+        <v>223.6</v>
       </c>
       <c r="I34" t="n">
-        <v>4334.3</v>
+        <v>4489.6</v>
       </c>
       <c r="J34" t="n">
-        <v>4641.77</v>
+        <v>4547</v>
       </c>
       <c r="K34" t="n">
-        <v>4733.75</v>
+        <v>4649.6</v>
       </c>
       <c r="L34" t="n">
-        <v>4825.73</v>
+        <v>4752.2</v>
       </c>
       <c r="M34" t="n">
-        <v>5025.45</v>
+        <v>4832.2</v>
       </c>
       <c r="N34" t="n">
-        <v>5225.18</v>
+        <v>4912.2</v>
       </c>
       <c r="O34" t="n">
-        <v>5209.4</v>
+        <v>5037.4</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
@@ -3371,81 +3375,77 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4713.1</v>
+        <v>4644</v>
       </c>
       <c r="C35" t="n">
-        <v>4745.8</v>
+        <v>4775.2</v>
       </c>
       <c r="D35" t="n">
-        <v>4522.2</v>
+        <v>4510.1</v>
       </c>
       <c r="E35" t="n">
-        <v>4644.5</v>
+        <v>4730.7</v>
       </c>
       <c r="F35" t="n">
-        <v>-96.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0186</v>
       </c>
       <c r="H35" t="n">
-        <v>223.6</v>
+        <v>265.1</v>
       </c>
       <c r="I35" t="n">
-        <v>4489.6</v>
+        <v>4298.6</v>
       </c>
       <c r="J35" t="n">
-        <v>4547</v>
+        <v>4426.15</v>
       </c>
       <c r="K35" t="n">
-        <v>4649.6</v>
+        <v>4532.7</v>
       </c>
       <c r="L35" t="n">
-        <v>4752.2</v>
+        <v>4639.25</v>
       </c>
       <c r="M35" t="n">
-        <v>4832.2</v>
+        <v>4756.3</v>
       </c>
       <c r="N35" t="n">
-        <v>4912.2</v>
+        <v>4873.35</v>
       </c>
       <c r="O35" t="n">
-        <v>5037.4</v>
+        <v>4969.4</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3457,55 +3457,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4644</v>
+        <v>4690</v>
       </c>
       <c r="C36" t="n">
-        <v>4775.2</v>
+        <v>4783.4</v>
       </c>
       <c r="D36" t="n">
-        <v>4510.1</v>
+        <v>4513.8</v>
       </c>
       <c r="E36" t="n">
-        <v>4730.7</v>
+        <v>4561.9</v>
       </c>
       <c r="F36" t="n">
-        <v>86.2</v>
+        <v>-168.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0357</v>
       </c>
       <c r="H36" t="n">
-        <v>265.1</v>
+        <v>269.6</v>
       </c>
       <c r="I36" t="n">
-        <v>4298.6</v>
+        <v>4245</v>
       </c>
       <c r="J36" t="n">
-        <v>4426.15</v>
+        <v>4509.63</v>
       </c>
       <c r="K36" t="n">
-        <v>4532.7</v>
+        <v>4598.15</v>
       </c>
       <c r="L36" t="n">
-        <v>4639.25</v>
+        <v>4686.68</v>
       </c>
       <c r="M36" t="n">
-        <v>4756.3</v>
+        <v>4863.25</v>
       </c>
       <c r="N36" t="n">
-        <v>4873.35</v>
+        <v>5039.83</v>
       </c>
       <c r="O36" t="n">
-        <v>4969.4</v>
+        <v>5040.3</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3515,18 +3519,16 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3548,50 +3550,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4690</v>
+        <v>4547.6</v>
       </c>
       <c r="C37" t="n">
-        <v>4783.4</v>
+        <v>4593.2</v>
       </c>
       <c r="D37" t="n">
-        <v>4513.8</v>
+        <v>4455</v>
       </c>
       <c r="E37" t="n">
-        <v>4561.9</v>
+        <v>4523.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-168.8</v>
+        <v>-38.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0357</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>269.6</v>
+        <v>138.2</v>
       </c>
       <c r="I37" t="n">
-        <v>4245</v>
+        <v>4244.2</v>
       </c>
       <c r="J37" t="n">
-        <v>4509.63</v>
+        <v>4248.95</v>
       </c>
       <c r="K37" t="n">
-        <v>4598.15</v>
+        <v>4427.1</v>
       </c>
       <c r="L37" t="n">
-        <v>4686.68</v>
+        <v>4605.25</v>
       </c>
       <c r="M37" t="n">
-        <v>4863.25</v>
+        <v>4696.7</v>
       </c>
       <c r="N37" t="n">
-        <v>5039.83</v>
+        <v>4788.15</v>
       </c>
       <c r="O37" t="n">
-        <v>5040.3</v>
+        <v>5053</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3599,14 +3601,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3623,76 +3623,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4547.6</v>
+        <v>4532</v>
       </c>
       <c r="C38" t="n">
-        <v>4593.2</v>
+        <v>4627.1</v>
       </c>
       <c r="D38" t="n">
-        <v>4455</v>
+        <v>4363.5</v>
       </c>
       <c r="E38" t="n">
-        <v>4523.2</v>
+        <v>4593</v>
       </c>
       <c r="F38" t="n">
-        <v>-38.7</v>
+        <v>69.8</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H38" t="n">
-        <v>138.2</v>
+        <v>263.6</v>
       </c>
       <c r="I38" t="n">
-        <v>4244.2</v>
+        <v>4316.8</v>
       </c>
       <c r="J38" t="n">
-        <v>4248.95</v>
+        <v>4384.55</v>
       </c>
       <c r="K38" t="n">
-        <v>4427.1</v>
+        <v>4454.1</v>
       </c>
       <c r="L38" t="n">
-        <v>4605.25</v>
+        <v>4523.65</v>
       </c>
       <c r="M38" t="n">
-        <v>4696.7</v>
+        <v>4592.3</v>
       </c>
       <c r="N38" t="n">
-        <v>4788.15</v>
+        <v>4660.95</v>
       </c>
       <c r="O38" t="n">
-        <v>5053</v>
+        <v>4731.4</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3705,78 +3707,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4532</v>
+        <v>4575.2</v>
       </c>
       <c r="C39" t="n">
-        <v>4627.1</v>
+        <v>4577.3</v>
       </c>
       <c r="D39" t="n">
-        <v>4363.5</v>
+        <v>4336.6</v>
       </c>
       <c r="E39" t="n">
-        <v>4593</v>
+        <v>4365.3</v>
       </c>
       <c r="F39" t="n">
-        <v>69.8</v>
+        <v>-227.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0154</v>
+        <v>-0.0496</v>
       </c>
       <c r="H39" t="n">
-        <v>263.6</v>
+        <v>240.7</v>
       </c>
       <c r="I39" t="n">
-        <v>4316.8</v>
+        <v>4099.9</v>
       </c>
       <c r="J39" t="n">
-        <v>4384.55</v>
+        <v>4378.25</v>
       </c>
       <c r="K39" t="n">
-        <v>4454.1</v>
+        <v>4461.2</v>
       </c>
       <c r="L39" t="n">
-        <v>4523.65</v>
+        <v>4544.15</v>
       </c>
       <c r="M39" t="n">
-        <v>4592.3</v>
+        <v>4724.8</v>
       </c>
       <c r="N39" t="n">
-        <v>4660.95</v>
+        <v>4905.45</v>
       </c>
       <c r="O39" t="n">
-        <v>4731.4</v>
+        <v>4890.7</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3789,71 +3793,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4575.2</v>
+        <v>4354</v>
       </c>
       <c r="C40" t="n">
-        <v>4577.3</v>
+        <v>4388.6</v>
       </c>
       <c r="D40" t="n">
-        <v>4336.6</v>
+        <v>4046.2</v>
       </c>
       <c r="E40" t="n">
-        <v>4365.3</v>
+        <v>4238.8</v>
       </c>
       <c r="F40" t="n">
-        <v>-227.7</v>
+        <v>-126.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0496</v>
+        <v>-0.029</v>
       </c>
       <c r="H40" t="n">
-        <v>240.7</v>
+        <v>342.4</v>
       </c>
       <c r="I40" t="n">
-        <v>4099.9</v>
+        <v>4095.9</v>
       </c>
       <c r="J40" t="n">
-        <v>4378.25</v>
+        <v>4078.78</v>
       </c>
       <c r="K40" t="n">
-        <v>4461.2</v>
+        <v>4244.95</v>
       </c>
       <c r="L40" t="n">
-        <v>4544.15</v>
+        <v>4411.12</v>
       </c>
       <c r="M40" t="n">
-        <v>4724.8</v>
+        <v>4485.65</v>
       </c>
       <c r="N40" t="n">
-        <v>4905.45</v>
+        <v>4560.17</v>
       </c>
       <c r="O40" t="n">
-        <v>4890.7</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
+        <v>4818</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
@@ -3880,69 +3882,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4354</v>
+        <v>4289.4</v>
       </c>
       <c r="C41" t="n">
-        <v>4388.6</v>
+        <v>4403.6</v>
       </c>
       <c r="D41" t="n">
-        <v>4046.2</v>
+        <v>4138.7</v>
       </c>
       <c r="E41" t="n">
-        <v>4238.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F41" t="n">
-        <v>-126.5</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0155</v>
       </c>
       <c r="H41" t="n">
-        <v>342.4</v>
+        <v>264.9</v>
       </c>
       <c r="I41" t="n">
-        <v>4095.9</v>
+        <v>3703.8</v>
       </c>
       <c r="J41" t="n">
-        <v>4078.78</v>
+        <v>3907.1</v>
       </c>
       <c r="K41" t="n">
-        <v>4244.95</v>
+        <v>4067.6</v>
       </c>
       <c r="L41" t="n">
-        <v>4411.12</v>
+        <v>4228.1</v>
       </c>
       <c r="M41" t="n">
-        <v>4485.65</v>
+        <v>4410</v>
       </c>
       <c r="N41" t="n">
-        <v>4560.17</v>
+        <v>4591.9</v>
       </c>
       <c r="O41" t="n">
-        <v>4818</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4731</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3959,55 +3955,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4289.4</v>
+        <v>4163.9</v>
       </c>
       <c r="C42" t="n">
-        <v>4403.6</v>
+        <v>4238.1</v>
       </c>
       <c r="D42" t="n">
-        <v>4138.7</v>
+        <v>3975.7</v>
       </c>
       <c r="E42" t="n">
-        <v>4172.9</v>
+        <v>4096.3</v>
       </c>
       <c r="F42" t="n">
-        <v>-65.90000000000001</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0184</v>
       </c>
       <c r="H42" t="n">
-        <v>264.9</v>
+        <v>262.4</v>
       </c>
       <c r="I42" t="n">
-        <v>3703.8</v>
+        <v>3873.8</v>
       </c>
       <c r="J42" t="n">
-        <v>3907.1</v>
+        <v>3858.87</v>
       </c>
       <c r="K42" t="n">
-        <v>4067.6</v>
+        <v>4040.45</v>
       </c>
       <c r="L42" t="n">
-        <v>4228.1</v>
+        <v>4222.03</v>
       </c>
       <c r="M42" t="n">
-        <v>4410</v>
+        <v>4305.35</v>
       </c>
       <c r="N42" t="n">
-        <v>4591.9</v>
+        <v>4388.67</v>
       </c>
       <c r="O42" t="n">
-        <v>4731</v>
+        <v>4668.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4015,12 +4015,14 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4037,59 +4039,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4163.9</v>
+        <v>4101.1</v>
       </c>
       <c r="C43" t="n">
-        <v>4238.1</v>
+        <v>4208.3</v>
       </c>
       <c r="D43" t="n">
-        <v>3975.7</v>
+        <v>3955.4</v>
       </c>
       <c r="E43" t="n">
-        <v>4096.3</v>
+        <v>4187.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-76.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0222</v>
       </c>
       <c r="H43" t="n">
-        <v>262.4</v>
+        <v>252.9</v>
       </c>
       <c r="I43" t="n">
-        <v>3873.8</v>
+        <v>3713.3</v>
       </c>
       <c r="J43" t="n">
-        <v>3858.87</v>
+        <v>3828.6</v>
       </c>
       <c r="K43" t="n">
-        <v>4040.45</v>
+        <v>3965.1</v>
       </c>
       <c r="L43" t="n">
-        <v>4222.03</v>
+        <v>4101.6</v>
       </c>
       <c r="M43" t="n">
-        <v>4305.35</v>
+        <v>4227.5</v>
       </c>
       <c r="N43" t="n">
-        <v>4388.67</v>
+        <v>4353.4</v>
       </c>
       <c r="O43" t="n">
-        <v>4668.5</v>
+        <v>4500.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4099,17 +4097,19 @@
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4121,55 +4121,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4101.1</v>
+        <v>4187.5</v>
       </c>
       <c r="C44" t="n">
-        <v>4208.3</v>
+        <v>4215.5</v>
       </c>
       <c r="D44" t="n">
-        <v>3955.4</v>
+        <v>4032.5</v>
       </c>
       <c r="E44" t="n">
-        <v>4187.3</v>
+        <v>4113.7</v>
       </c>
       <c r="F44" t="n">
-        <v>91</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0176</v>
       </c>
       <c r="H44" t="n">
-        <v>252.9</v>
+        <v>183</v>
       </c>
       <c r="I44" t="n">
-        <v>3713.3</v>
+        <v>3702.5</v>
       </c>
       <c r="J44" t="n">
-        <v>3828.6</v>
+        <v>3987.12</v>
       </c>
       <c r="K44" t="n">
-        <v>3965.1</v>
+        <v>4060.85</v>
       </c>
       <c r="L44" t="n">
-        <v>4101.6</v>
+        <v>4134.57</v>
       </c>
       <c r="M44" t="n">
-        <v>4227.5</v>
+        <v>4313.75</v>
       </c>
       <c r="N44" t="n">
-        <v>4353.4</v>
+        <v>4492.92</v>
       </c>
       <c r="O44" t="n">
-        <v>4500.5</v>
+        <v>4461.2</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4182,15 +4186,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4205,57 +4207,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4187.5</v>
+        <v>4106.6</v>
       </c>
       <c r="C45" t="n">
-        <v>4215.5</v>
+        <v>4112.5</v>
       </c>
       <c r="D45" t="n">
-        <v>4032.5</v>
+        <v>3963</v>
       </c>
       <c r="E45" t="n">
-        <v>4113.7</v>
+        <v>4018.8</v>
       </c>
       <c r="F45" t="n">
-        <v>-73.59999999999999</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0176</v>
+        <v>-0.0231</v>
       </c>
       <c r="H45" t="n">
-        <v>183</v>
+        <v>149.5</v>
       </c>
       <c r="I45" t="n">
-        <v>3702.5</v>
+        <v>3849.5</v>
       </c>
       <c r="J45" t="n">
-        <v>3987.12</v>
+        <v>3925.55</v>
       </c>
       <c r="K45" t="n">
-        <v>4060.85</v>
+        <v>4022.2</v>
       </c>
       <c r="L45" t="n">
-        <v>4134.57</v>
+        <v>4118.85</v>
       </c>
       <c r="M45" t="n">
-        <v>4313.75</v>
+        <v>4205.2</v>
       </c>
       <c r="N45" t="n">
-        <v>4492.92</v>
+        <v>4291.55</v>
       </c>
       <c r="O45" t="n">
-        <v>4461.2</v>
+        <v>4398.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4265,12 +4267,12 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4287,59 +4289,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4106.6</v>
+        <v>4005.6</v>
       </c>
       <c r="C46" t="n">
-        <v>4112.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D46" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E46" t="n">
-        <v>4018.8</v>
+        <v>4070.8</v>
       </c>
       <c r="F46" t="n">
-        <v>-94.90000000000001</v>
+        <v>52</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0129</v>
       </c>
       <c r="H46" t="n">
-        <v>149.5</v>
+        <v>184.9</v>
       </c>
       <c r="I46" t="n">
-        <v>3849.5</v>
+        <v>3813.5</v>
       </c>
       <c r="J46" t="n">
-        <v>3925.55</v>
+        <v>3859.83</v>
       </c>
       <c r="K46" t="n">
-        <v>4022.2</v>
+        <v>3944.05</v>
       </c>
       <c r="L46" t="n">
-        <v>4118.85</v>
+        <v>4028.28</v>
       </c>
       <c r="M46" t="n">
-        <v>4205.2</v>
+        <v>4093.55</v>
       </c>
       <c r="N46" t="n">
-        <v>4291.55</v>
+        <v>4158.83</v>
       </c>
       <c r="O46" t="n">
-        <v>4398.5</v>
+        <v>4262</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4347,21 +4345,23 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4371,55 +4371,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4005.6</v>
+        <v>4097.5</v>
       </c>
       <c r="C47" t="n">
-        <v>4171.4</v>
+        <v>4170.7</v>
       </c>
       <c r="D47" t="n">
-        <v>3986.5</v>
+        <v>3993.8</v>
       </c>
       <c r="E47" t="n">
-        <v>4070.8</v>
+        <v>4107</v>
       </c>
       <c r="F47" t="n">
-        <v>52</v>
+        <v>36.2</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0089</v>
       </c>
       <c r="H47" t="n">
-        <v>184.9</v>
+        <v>176.9</v>
       </c>
       <c r="I47" t="n">
-        <v>3813.5</v>
+        <v>3801.6</v>
       </c>
       <c r="J47" t="n">
-        <v>3859.83</v>
+        <v>3881.83</v>
       </c>
       <c r="K47" t="n">
-        <v>3944.05</v>
+        <v>3978.35</v>
       </c>
       <c r="L47" t="n">
-        <v>4028.28</v>
+        <v>4074.88</v>
       </c>
       <c r="M47" t="n">
-        <v>4093.55</v>
+        <v>4163.25</v>
       </c>
       <c r="N47" t="n">
-        <v>4158.83</v>
+        <v>4251.62</v>
       </c>
       <c r="O47" t="n">
-        <v>4262</v>
+        <v>4356.3</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4432,19 +4436,17 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4455,57 +4457,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4097.5</v>
+        <v>4135.2</v>
       </c>
       <c r="C48" t="n">
-        <v>4170.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D48" t="n">
-        <v>3993.8</v>
+        <v>4074</v>
       </c>
       <c r="E48" t="n">
-        <v>4107</v>
+        <v>4399.7</v>
       </c>
       <c r="F48" t="n">
-        <v>36.2</v>
+        <v>292.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0089</v>
+        <v>0.0713</v>
       </c>
       <c r="H48" t="n">
-        <v>176.9</v>
+        <v>358.3</v>
       </c>
       <c r="I48" t="n">
-        <v>3801.6</v>
+        <v>3816.9</v>
       </c>
       <c r="J48" t="n">
-        <v>3881.83</v>
+        <v>3942.47</v>
       </c>
       <c r="K48" t="n">
-        <v>3978.35</v>
+        <v>4018.55</v>
       </c>
       <c r="L48" t="n">
-        <v>4074.88</v>
+        <v>4094.63</v>
       </c>
       <c r="M48" t="n">
-        <v>4163.25</v>
+        <v>4195.45</v>
       </c>
       <c r="N48" t="n">
-        <v>4251.62</v>
+        <v>4296.28</v>
       </c>
       <c r="O48" t="n">
-        <v>4356.3</v>
+        <v>4347.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4518,7 +4520,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4526,70 +4528,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4135.2</v>
+        <v>4400</v>
       </c>
       <c r="C49" t="n">
-        <v>4432.3</v>
+        <v>4509.1</v>
       </c>
       <c r="D49" t="n">
-        <v>4074</v>
+        <v>4365.5</v>
       </c>
       <c r="E49" t="n">
-        <v>4399.7</v>
+        <v>4437.3</v>
       </c>
       <c r="F49" t="n">
-        <v>292.7</v>
+        <v>37.6</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0713</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>358.3</v>
+        <v>143.6</v>
       </c>
       <c r="I49" t="n">
-        <v>3816.9</v>
+        <v>3715.7</v>
       </c>
       <c r="J49" t="n">
-        <v>3942.47</v>
+        <v>4114.68</v>
       </c>
       <c r="K49" t="n">
-        <v>4018.55</v>
+        <v>4220.55</v>
       </c>
       <c r="L49" t="n">
-        <v>4094.63</v>
+        <v>4326.43</v>
       </c>
       <c r="M49" t="n">
-        <v>4195.45</v>
+        <v>4578.85</v>
       </c>
       <c r="N49" t="n">
-        <v>4296.28</v>
+        <v>4831.28</v>
       </c>
       <c r="O49" t="n">
-        <v>4347.6</v>
+        <v>4790.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4602,23 +4604,17 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4630,50 +4626,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4400</v>
+        <v>4440</v>
       </c>
       <c r="C50" t="n">
+        <v>4690.4</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4378</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4680.6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>243.3</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H50" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4221.9</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4293.7</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4365.5</v>
+      </c>
+      <c r="L50" t="n">
+        <v>4437.3</v>
+      </c>
+      <c r="M50" t="n">
         <v>4509.1</v>
       </c>
-      <c r="D50" t="n">
-        <v>4365.5</v>
-      </c>
-      <c r="E50" t="n">
-        <v>4437.3</v>
-      </c>
-      <c r="F50" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="H50" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="I50" t="n">
-        <v>3715.7</v>
-      </c>
-      <c r="J50" t="n">
-        <v>4114.68</v>
-      </c>
-      <c r="K50" t="n">
-        <v>4220.55</v>
-      </c>
-      <c r="L50" t="n">
-        <v>4326.43</v>
-      </c>
-      <c r="M50" t="n">
-        <v>4578.85</v>
-      </c>
       <c r="N50" t="n">
-        <v>4831.28</v>
+        <v>4580.9</v>
       </c>
       <c r="O50" t="n">
-        <v>4790.6</v>
+        <v>4652.7</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4686,17 +4682,23 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
@@ -4708,50 +4710,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4440</v>
+        <v>4673.4</v>
       </c>
       <c r="C51" t="n">
-        <v>4690.4</v>
+        <v>4755</v>
       </c>
       <c r="D51" t="n">
-        <v>4378</v>
+        <v>4495</v>
       </c>
       <c r="E51" t="n">
-        <v>4680.6</v>
+        <v>4529.9</v>
       </c>
       <c r="F51" t="n">
-        <v>243.3</v>
+        <v>-150.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0548</v>
+        <v>-0.0322</v>
       </c>
       <c r="H51" t="n">
-        <v>312.4</v>
+        <v>260</v>
       </c>
       <c r="I51" t="n">
-        <v>4221.9</v>
+        <v>4065.6</v>
       </c>
       <c r="J51" t="n">
-        <v>4293.7</v>
+        <v>4441.4</v>
       </c>
       <c r="K51" t="n">
-        <v>4365.5</v>
+        <v>4524.4</v>
       </c>
       <c r="L51" t="n">
-        <v>4437.3</v>
+        <v>4607.4</v>
       </c>
       <c r="M51" t="n">
-        <v>4509.1</v>
+        <v>4836.8</v>
       </c>
       <c r="N51" t="n">
-        <v>4580.9</v>
+        <v>5066.2</v>
       </c>
       <c r="O51" t="n">
-        <v>4652.7</v>
+        <v>5002.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4759,83 +4761,83 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4673.4</v>
+        <v>4483.2</v>
       </c>
       <c r="C52" t="n">
-        <v>4755</v>
+        <v>4558.5</v>
       </c>
       <c r="D52" t="n">
-        <v>4495</v>
+        <v>4329.2</v>
       </c>
       <c r="E52" t="n">
-        <v>4529.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F52" t="n">
-        <v>-150.7</v>
+        <v>-53.3</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0118</v>
       </c>
       <c r="H52" t="n">
-        <v>260</v>
+        <v>229.3</v>
       </c>
       <c r="I52" t="n">
-        <v>4065.6</v>
+        <v>4235</v>
       </c>
       <c r="J52" t="n">
-        <v>4441.4</v>
+        <v>4222.35</v>
       </c>
       <c r="K52" t="n">
-        <v>4524.4</v>
+        <v>4399.9</v>
       </c>
       <c r="L52" t="n">
-        <v>4607.4</v>
+        <v>4577.45</v>
       </c>
       <c r="M52" t="n">
-        <v>4836.8</v>
+        <v>4659.9</v>
       </c>
       <c r="N52" t="n">
-        <v>5066.2</v>
+        <v>4742.35</v>
       </c>
       <c r="O52" t="n">
-        <v>5002.8</v>
+        <v>5015</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4869,57 +4871,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4483.2</v>
+        <v>4466.5</v>
       </c>
       <c r="C53" t="n">
-        <v>4558.5</v>
+        <v>4488.8</v>
       </c>
       <c r="D53" t="n">
-        <v>4329.2</v>
+        <v>4333</v>
       </c>
       <c r="E53" t="n">
-        <v>4476.6</v>
+        <v>4408.9</v>
       </c>
       <c r="F53" t="n">
-        <v>-53.3</v>
+        <v>-67.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0151</v>
       </c>
       <c r="H53" t="n">
-        <v>229.3</v>
+        <v>155.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4235</v>
+        <v>4099.9</v>
       </c>
       <c r="J53" t="n">
-        <v>4222.35</v>
+        <v>4263.68</v>
       </c>
       <c r="K53" t="n">
-        <v>4399.9</v>
+        <v>4361.95</v>
       </c>
       <c r="L53" t="n">
-        <v>4577.45</v>
+        <v>4460.23</v>
       </c>
       <c r="M53" t="n">
-        <v>4659.9</v>
+        <v>4591.25</v>
       </c>
       <c r="N53" t="n">
-        <v>4742.35</v>
+        <v>4722.27</v>
       </c>
       <c r="O53" t="n">
-        <v>5015</v>
+        <v>4787.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4953,57 +4955,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4466.5</v>
+        <v>4375</v>
       </c>
       <c r="C54" t="n">
-        <v>4488.8</v>
+        <v>4439.8</v>
       </c>
       <c r="D54" t="n">
-        <v>4333</v>
+        <v>4273.3</v>
       </c>
       <c r="E54" t="n">
-        <v>4408.9</v>
+        <v>4424.9</v>
       </c>
       <c r="F54" t="n">
-        <v>-67.7</v>
+        <v>16</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0151</v>
+        <v>0.0036</v>
       </c>
       <c r="H54" t="n">
-        <v>155.8</v>
+        <v>166.5</v>
       </c>
       <c r="I54" t="n">
-        <v>4099.9</v>
+        <v>4177.2</v>
       </c>
       <c r="J54" t="n">
-        <v>4263.68</v>
+        <v>4252.1</v>
       </c>
       <c r="K54" t="n">
-        <v>4361.95</v>
+        <v>4331</v>
       </c>
       <c r="L54" t="n">
-        <v>4460.23</v>
+        <v>4409.9</v>
       </c>
       <c r="M54" t="n">
-        <v>4591.25</v>
+        <v>4486.8</v>
       </c>
       <c r="N54" t="n">
-        <v>4722.27</v>
+        <v>4563.7</v>
       </c>
       <c r="O54" t="n">
-        <v>4787.8</v>
+        <v>4644.6</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5013,12 +5015,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5044,65 +5046,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4375</v>
+        <v>4413</v>
       </c>
       <c r="C55" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D55" t="n">
-        <v>4273.3</v>
+        <v>4278.3</v>
       </c>
       <c r="E55" t="n">
-        <v>4424.9</v>
+        <v>4321.2</v>
       </c>
       <c r="F55" t="n">
-        <v>16</v>
+        <v>-103.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0234</v>
       </c>
       <c r="H55" t="n">
-        <v>166.5</v>
+        <v>143.8</v>
       </c>
       <c r="I55" t="n">
-        <v>4177.2</v>
+        <v>4106.8</v>
       </c>
       <c r="J55" t="n">
-        <v>4252.1</v>
+        <v>4292.57</v>
       </c>
       <c r="K55" t="n">
-        <v>4331</v>
+        <v>4341.65</v>
       </c>
       <c r="L55" t="n">
-        <v>4409.9</v>
+        <v>4390.72</v>
       </c>
       <c r="M55" t="n">
-        <v>4486.8</v>
+        <v>4508.15</v>
       </c>
       <c r="N55" t="n">
-        <v>4563.7</v>
+        <v>4625.57</v>
       </c>
       <c r="O55" t="n">
-        <v>4644.6</v>
+        <v>4606.3</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5128,64 +5132,64 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4413</v>
+        <v>4315</v>
       </c>
       <c r="C56" t="n">
-        <v>4422.1</v>
+        <v>4315.6</v>
       </c>
       <c r="D56" t="n">
-        <v>4278.3</v>
+        <v>4143.1</v>
       </c>
       <c r="E56" t="n">
-        <v>4321.2</v>
+        <v>4162.3</v>
       </c>
       <c r="F56" t="n">
-        <v>-103.7</v>
+        <v>-158.9</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0234</v>
+        <v>-0.0368</v>
       </c>
       <c r="H56" t="n">
-        <v>143.8</v>
+        <v>172.5</v>
       </c>
       <c r="I56" t="n">
-        <v>4106.8</v>
+        <v>4134.5</v>
       </c>
       <c r="J56" t="n">
-        <v>4292.57</v>
+        <v>4162.9</v>
       </c>
       <c r="K56" t="n">
-        <v>4341.65</v>
+        <v>4249.3</v>
       </c>
       <c r="L56" t="n">
-        <v>4390.72</v>
+        <v>4335.7</v>
       </c>
       <c r="M56" t="n">
-        <v>4508.15</v>
+        <v>4393.1</v>
       </c>
       <c r="N56" t="n">
-        <v>4625.57</v>
+        <v>4450.5</v>
       </c>
       <c r="O56" t="n">
-        <v>4606.3</v>
+        <v>4565.9</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5200,81 +5204,73 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4315</v>
+        <v>4169.4</v>
       </c>
       <c r="C57" t="n">
-        <v>4315.6</v>
+        <v>4233.7</v>
       </c>
       <c r="D57" t="n">
-        <v>4143.1</v>
+        <v>4091.2</v>
       </c>
       <c r="E57" t="n">
-        <v>4162.3</v>
+        <v>4216.3</v>
       </c>
       <c r="F57" t="n">
-        <v>-158.9</v>
+        <v>54</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0368</v>
+        <v>0.013</v>
       </c>
       <c r="H57" t="n">
-        <v>172.5</v>
+        <v>142.5</v>
       </c>
       <c r="I57" t="n">
-        <v>4134.5</v>
+        <v>3970.6</v>
       </c>
       <c r="J57" t="n">
-        <v>4162.9</v>
+        <v>3956.27</v>
       </c>
       <c r="K57" t="n">
-        <v>4249.3</v>
+        <v>4076.05</v>
       </c>
       <c r="L57" t="n">
-        <v>4335.7</v>
+        <v>4195.82</v>
       </c>
       <c r="M57" t="n">
-        <v>4393.1</v>
+        <v>4248.55</v>
       </c>
       <c r="N57" t="n">
-        <v>4450.5</v>
+        <v>4301.27</v>
       </c>
       <c r="O57" t="n">
-        <v>4565.9</v>
+        <v>4488.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5291,85 +5287,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4169.4</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4212.4</v>
-      </c>
-      <c r="D58" t="n">
-        <v>4091.2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>4195.2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="H58" t="n">
-        <v>121.2</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3970.6</v>
-      </c>
-      <c r="J58" t="n">
-        <v>3956.27</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4076.05</v>
-      </c>
-      <c r="L58" t="n">
-        <v>4195.82</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4248.55</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4301.27</v>
-      </c>
-      <c r="O58" t="n">
-        <v>4488.1</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5221,22 +5221,22 @@
         <v>4169.4</v>
       </c>
       <c r="C57" t="n">
-        <v>4233.7</v>
+        <v>4235.8</v>
       </c>
       <c r="D57" t="n">
         <v>4091.2</v>
       </c>
       <c r="E57" t="n">
-        <v>4216.3</v>
+        <v>4232.2</v>
       </c>
       <c r="F57" t="n">
-        <v>54</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0168</v>
       </c>
       <c r="H57" t="n">
-        <v>142.5</v>
+        <v>144.6</v>
       </c>
       <c r="I57" t="n">
         <v>3970.6</v>
@@ -5270,11 +5270,13 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5221,22 +5221,22 @@
         <v>4169.4</v>
       </c>
       <c r="C57" t="n">
-        <v>4235.8</v>
+        <v>4242.3</v>
       </c>
       <c r="D57" t="n">
         <v>4091.2</v>
       </c>
       <c r="E57" t="n">
-        <v>4232.2</v>
+        <v>4235.3</v>
       </c>
       <c r="F57" t="n">
-        <v>69.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0168</v>
+        <v>0.0175</v>
       </c>
       <c r="H57" t="n">
-        <v>144.6</v>
+        <v>151.1</v>
       </c>
       <c r="I57" t="n">
         <v>3970.6</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +659,25 @@
         <v>83.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3528.2</v>
+        <v>3586.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3601.87</v>
+        <v>3623.85</v>
       </c>
       <c r="K2" t="n">
-        <v>3639.65</v>
+        <v>3654.3</v>
       </c>
       <c r="L2" t="n">
-        <v>3677.42</v>
+        <v>3684.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3733.15</v>
+        <v>3718.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3788.87</v>
+        <v>3752.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3808.7</v>
+        <v>3779.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5221,22 +5221,22 @@
         <v>4169.4</v>
       </c>
       <c r="C57" t="n">
-        <v>4242.3</v>
+        <v>4233.7</v>
       </c>
       <c r="D57" t="n">
         <v>4091.2</v>
       </c>
       <c r="E57" t="n">
-        <v>4235.3</v>
+        <v>4216.3</v>
       </c>
       <c r="F57" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.013</v>
       </c>
       <c r="H57" t="n">
-        <v>151.1</v>
+        <v>142.5</v>
       </c>
       <c r="I57" t="n">
         <v>3970.6</v>
@@ -5270,13 +5270,11 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5292,6 +5290,88 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4220.8</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4242.3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4178.1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4190.6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-25.7</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="H58" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3948.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4100.72</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4145.05</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4189.37</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4287.55</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4385.72</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4376.2</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>83.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3586.8</v>
+        <v>3604.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3623.85</v>
+        <v>3645.97</v>
       </c>
       <c r="K2" t="n">
-        <v>3654.3</v>
+        <v>3663.15</v>
       </c>
       <c r="L2" t="n">
-        <v>3684.75</v>
+        <v>3680.32</v>
       </c>
       <c r="M2" t="n">
-        <v>3718.5</v>
+        <v>3709.65</v>
       </c>
       <c r="N2" t="n">
-        <v>3752.25</v>
+        <v>3738.97</v>
       </c>
       <c r="O2" t="n">
-        <v>3779.4</v>
+        <v>3744</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -698,11 +700,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5306,19 +5312,19 @@
         <v>4242.3</v>
       </c>
       <c r="D58" t="n">
-        <v>4178.1</v>
+        <v>4170</v>
       </c>
       <c r="E58" t="n">
-        <v>4190.6</v>
+        <v>4188.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-25.7</v>
+        <v>-28.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0061</v>
+        <v>-0.0067</v>
       </c>
       <c r="H58" t="n">
-        <v>64.2</v>
+        <v>72.3</v>
       </c>
       <c r="I58" t="n">
         <v>3948.7</v>
@@ -5350,9 +5356,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>83.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3604.5</v>
+        <v>3606.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3645.97</v>
+        <v>3648.47</v>
       </c>
       <c r="K2" t="n">
-        <v>3663.15</v>
+        <v>3664.15</v>
       </c>
       <c r="L2" t="n">
-        <v>3680.32</v>
+        <v>3679.82</v>
       </c>
       <c r="M2" t="n">
-        <v>3709.65</v>
+        <v>3708.65</v>
       </c>
       <c r="N2" t="n">
-        <v>3738.97</v>
+        <v>3737.47</v>
       </c>
       <c r="O2" t="n">
-        <v>3744</v>
+        <v>3740</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5312,19 +5312,19 @@
         <v>4242.3</v>
       </c>
       <c r="D58" t="n">
-        <v>4170</v>
+        <v>4120.9</v>
       </c>
       <c r="E58" t="n">
-        <v>4188.2</v>
+        <v>4163.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-28.1</v>
+        <v>-52.9</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0067</v>
+        <v>-0.0125</v>
       </c>
       <c r="H58" t="n">
-        <v>72.3</v>
+        <v>121.4</v>
       </c>
       <c r="I58" t="n">
         <v>3948.7</v>
@@ -5353,12 +5353,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5315,13 +5315,13 @@
         <v>4120.9</v>
       </c>
       <c r="E58" t="n">
-        <v>4163.4</v>
+        <v>4165.8</v>
       </c>
       <c r="F58" t="n">
-        <v>-52.9</v>
+        <v>-50.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0125</v>
+        <v>-0.012</v>
       </c>
       <c r="H58" t="n">
         <v>121.4</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5315,13 +5315,13 @@
         <v>4120.9</v>
       </c>
       <c r="E58" t="n">
-        <v>4165.8</v>
+        <v>4168.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-50.5</v>
+        <v>-47.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.012</v>
+        <v>-0.0113</v>
       </c>
       <c r="H58" t="n">
         <v>121.4</v>
@@ -5355,12 +5355,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,31 +659,33 @@
         <v>83.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3606.5</v>
+        <v>3639.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3648.47</v>
+        <v>3660.7</v>
       </c>
       <c r="K2" t="n">
-        <v>3664.15</v>
+        <v>3672.3</v>
       </c>
       <c r="L2" t="n">
-        <v>3679.82</v>
+        <v>3683.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3708.65</v>
+        <v>3700.5</v>
       </c>
       <c r="N2" t="n">
-        <v>3737.47</v>
+        <v>3717.1</v>
       </c>
       <c r="O2" t="n">
-        <v>3740</v>
+        <v>3723.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -715,7 +717,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5312,19 +5318,19 @@
         <v>4242.3</v>
       </c>
       <c r="D58" t="n">
-        <v>4120.9</v>
+        <v>4095</v>
       </c>
       <c r="E58" t="n">
-        <v>4168.7</v>
+        <v>4176.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-47.6</v>
+        <v>-39.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>121.4</v>
+        <v>147.3</v>
       </c>
       <c r="I58" t="n">
         <v>3948.7</v>
@@ -5350,8 +5356,10 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,142 +634,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3680.2</v>
+        <v>3721.3</v>
       </c>
       <c r="C2" t="n">
-        <v>3744</v>
+        <v>3824.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3660.5</v>
+        <v>3718.1</v>
       </c>
       <c r="E2" t="n">
-        <v>3705.8</v>
+        <v>3809</v>
       </c>
       <c r="F2" t="n">
-        <v>19.4</v>
+        <v>103.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0053</v>
+        <v>0.0278</v>
       </c>
       <c r="H2" t="n">
-        <v>83.5</v>
+        <v>106.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3639.1</v>
+        <v>3577</v>
       </c>
       <c r="J2" t="n">
-        <v>3660.7</v>
+        <v>3624.08</v>
       </c>
       <c r="K2" t="n">
-        <v>3672.3</v>
+        <v>3664.05</v>
       </c>
       <c r="L2" t="n">
-        <v>3683.9</v>
+        <v>3704.03</v>
       </c>
       <c r="M2" t="n">
-        <v>3700.5</v>
+        <v>3747.55</v>
       </c>
       <c r="N2" t="n">
-        <v>3717.1</v>
+        <v>3791.08</v>
       </c>
       <c r="O2" t="n">
-        <v>3723.7</v>
+        <v>3827.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3721.3</v>
+        <v>3788.8</v>
       </c>
       <c r="C3" t="n">
-        <v>3824.6</v>
+        <v>3923.3</v>
       </c>
       <c r="D3" t="n">
-        <v>3718.1</v>
+        <v>3785.5</v>
       </c>
       <c r="E3" t="n">
-        <v>3809</v>
+        <v>3908.9</v>
       </c>
       <c r="F3" t="n">
-        <v>103.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0262</v>
       </c>
       <c r="H3" t="n">
-        <v>106.5</v>
+        <v>137.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3577</v>
+        <v>3611.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3624.08</v>
+        <v>3721.32</v>
       </c>
       <c r="K3" t="n">
-        <v>3664.05</v>
+        <v>3755.75</v>
       </c>
       <c r="L3" t="n">
-        <v>3704.03</v>
+        <v>3790.18</v>
       </c>
       <c r="M3" t="n">
-        <v>3747.55</v>
+        <v>3862.25</v>
       </c>
       <c r="N3" t="n">
-        <v>3791.08</v>
+        <v>3934.32</v>
       </c>
       <c r="O3" t="n">
-        <v>3827.5</v>
+        <v>3931.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -790,13 +780,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -808,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3788.8</v>
+        <v>3913.5</v>
       </c>
       <c r="C4" t="n">
-        <v>3923.3</v>
+        <v>4081</v>
       </c>
       <c r="D4" t="n">
-        <v>3785.5</v>
+        <v>3909.2</v>
       </c>
       <c r="E4" t="n">
-        <v>3908.9</v>
+        <v>4000.4</v>
       </c>
       <c r="F4" t="n">
-        <v>99.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0262</v>
+        <v>0.0234</v>
       </c>
       <c r="H4" t="n">
-        <v>137.8</v>
+        <v>171.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3611.6</v>
+        <v>3647.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3721.32</v>
+        <v>3798.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3755.75</v>
+        <v>3840</v>
       </c>
       <c r="L4" t="n">
-        <v>3790.18</v>
+        <v>3881.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3862.25</v>
+        <v>3977.8</v>
       </c>
       <c r="N4" t="n">
-        <v>3934.32</v>
+        <v>4073.95</v>
       </c>
       <c r="O4" t="n">
-        <v>3931.1</v>
+        <v>4061.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -869,15 +859,17 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
@@ -890,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3913.5</v>
+        <v>4018.3</v>
       </c>
       <c r="C5" t="n">
-        <v>4081</v>
+        <v>4392</v>
       </c>
       <c r="D5" t="n">
-        <v>3909.2</v>
+        <v>4011.3</v>
       </c>
       <c r="E5" t="n">
-        <v>4000.4</v>
+        <v>4213.3</v>
       </c>
       <c r="F5" t="n">
-        <v>91.5</v>
+        <v>212.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0532</v>
       </c>
       <c r="H5" t="n">
-        <v>171.8</v>
+        <v>380.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3647.7</v>
+        <v>3737.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3798.35</v>
+        <v>3831.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3840</v>
+        <v>3914.5</v>
       </c>
       <c r="L5" t="n">
-        <v>3881.65</v>
+        <v>3997.75</v>
       </c>
       <c r="M5" t="n">
-        <v>3977.8</v>
+        <v>4086.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4073.95</v>
+        <v>4174.85</v>
       </c>
       <c r="O5" t="n">
-        <v>4061.1</v>
+        <v>4252.8</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -951,12 +943,12 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V5" s="8" t="inlineStr">
@@ -974,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4018.3</v>
+        <v>4269</v>
       </c>
       <c r="C6" t="n">
-        <v>4392</v>
+        <v>4398</v>
       </c>
       <c r="D6" t="n">
-        <v>4011.3</v>
+        <v>4021.2</v>
       </c>
       <c r="E6" t="n">
-        <v>4213.3</v>
+        <v>4137.8</v>
       </c>
       <c r="F6" t="n">
-        <v>212.9</v>
+        <v>-75.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0532</v>
+        <v>-0.0179</v>
       </c>
       <c r="H6" t="n">
-        <v>380.7</v>
+        <v>376.8</v>
       </c>
       <c r="I6" t="n">
-        <v>3737.4</v>
+        <v>3630.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3831.25</v>
+        <v>3838.42</v>
       </c>
       <c r="K6" t="n">
-        <v>3914.5</v>
+        <v>4022.95</v>
       </c>
       <c r="L6" t="n">
-        <v>3997.75</v>
+        <v>4207.47</v>
       </c>
       <c r="M6" t="n">
-        <v>4086.3</v>
+        <v>4403.65</v>
       </c>
       <c r="N6" t="n">
-        <v>4174.85</v>
+        <v>4599.82</v>
       </c>
       <c r="O6" t="n">
-        <v>4252.8</v>
+        <v>4772.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,83 +1017,83 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4269</v>
+        <v>4103.2</v>
       </c>
       <c r="C7" t="n">
-        <v>4398</v>
+        <v>4123.8</v>
       </c>
       <c r="D7" t="n">
-        <v>4021.2</v>
+        <v>3901.3</v>
       </c>
       <c r="E7" t="n">
-        <v>4137.8</v>
+        <v>3996.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-75.5</v>
+        <v>-141.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0179</v>
+        <v>-0.0341</v>
       </c>
       <c r="H7" t="n">
-        <v>376.8</v>
+        <v>222.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3630.6</v>
+        <v>3644.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3838.42</v>
+        <v>3725.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4022.95</v>
+        <v>3949.4</v>
       </c>
       <c r="L7" t="n">
-        <v>4207.47</v>
+        <v>4173.7</v>
       </c>
       <c r="M7" t="n">
-        <v>4403.65</v>
+        <v>4326.2</v>
       </c>
       <c r="N7" t="n">
-        <v>4599.82</v>
+        <v>4478.7</v>
       </c>
       <c r="O7" t="n">
-        <v>4772.7</v>
+        <v>4774.8</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,12 +1103,12 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1135,57 +1127,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4103.2</v>
+        <v>4001</v>
       </c>
       <c r="C8" t="n">
-        <v>4123.8</v>
+        <v>4043.1</v>
       </c>
       <c r="D8" t="n">
-        <v>3901.3</v>
+        <v>3935.7</v>
       </c>
       <c r="E8" t="n">
-        <v>3996.5</v>
+        <v>4009.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-141.3</v>
+        <v>13.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0341</v>
+        <v>0.0033</v>
       </c>
       <c r="H8" t="n">
-        <v>222.5</v>
+        <v>107.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3644.4</v>
+        <v>3678.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3725.1</v>
+        <v>3765.98</v>
       </c>
       <c r="K8" t="n">
-        <v>3949.4</v>
+        <v>3885.25</v>
       </c>
       <c r="L8" t="n">
-        <v>4173.7</v>
+        <v>4004.52</v>
       </c>
       <c r="M8" t="n">
-        <v>4326.2</v>
+        <v>4107.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4478.7</v>
+        <v>4210.97</v>
       </c>
       <c r="O8" t="n">
-        <v>4774.8</v>
+        <v>4346.3</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1193,14 +1185,12 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1219,57 +1209,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4001</v>
+        <v>4007.2</v>
       </c>
       <c r="C9" t="n">
-        <v>4043.1</v>
+        <v>4250</v>
       </c>
       <c r="D9" t="n">
-        <v>3935.7</v>
+        <v>4004.2</v>
       </c>
       <c r="E9" t="n">
-        <v>4009.8</v>
+        <v>4094.2</v>
       </c>
       <c r="F9" t="n">
-        <v>13.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.021</v>
       </c>
       <c r="H9" t="n">
-        <v>107.4</v>
+        <v>245.8</v>
       </c>
       <c r="I9" t="n">
-        <v>3678.8</v>
+        <v>3828.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3765.98</v>
+        <v>3912.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3885.25</v>
+        <v>3956.1</v>
       </c>
       <c r="L9" t="n">
-        <v>4004.52</v>
+        <v>3999.6</v>
       </c>
       <c r="M9" t="n">
-        <v>4107.75</v>
+        <v>4063.5</v>
       </c>
       <c r="N9" t="n">
-        <v>4210.97</v>
+        <v>4127.4</v>
       </c>
       <c r="O9" t="n">
-        <v>4346.3</v>
+        <v>4150.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1282,76 +1272,78 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4007.2</v>
+        <v>4084.4</v>
       </c>
       <c r="C10" t="n">
-        <v>4250</v>
+        <v>4134.3</v>
       </c>
       <c r="D10" t="n">
-        <v>4004.2</v>
+        <v>3997.4</v>
       </c>
       <c r="E10" t="n">
-        <v>4094.2</v>
+        <v>4079.5</v>
       </c>
       <c r="F10" t="n">
-        <v>84.40000000000001</v>
+        <v>-14.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.0036</v>
       </c>
       <c r="H10" t="n">
-        <v>245.8</v>
+        <v>136.9</v>
       </c>
       <c r="I10" t="n">
-        <v>3828.3</v>
+        <v>3758.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3912.6</v>
+        <v>3831.95</v>
       </c>
       <c r="K10" t="n">
-        <v>3956.1</v>
+        <v>3971.3</v>
       </c>
       <c r="L10" t="n">
-        <v>3999.6</v>
+        <v>4110.65</v>
       </c>
       <c r="M10" t="n">
-        <v>4063.5</v>
+        <v>4217.1</v>
       </c>
       <c r="N10" t="n">
-        <v>4127.4</v>
+        <v>4323.55</v>
       </c>
       <c r="O10" t="n">
-        <v>4150.5</v>
+        <v>4495.8</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,80 +1354,78 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4084.4</v>
+        <v>4069.2</v>
       </c>
       <c r="C11" t="n">
-        <v>4134.3</v>
+        <v>4263.1</v>
       </c>
       <c r="D11" t="n">
-        <v>3997.4</v>
+        <v>4036.4</v>
       </c>
       <c r="E11" t="n">
-        <v>4079.5</v>
+        <v>4254.9</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.7</v>
+        <v>175.4</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.043</v>
       </c>
       <c r="H11" t="n">
-        <v>136.9</v>
+        <v>226.7</v>
       </c>
       <c r="I11" t="n">
-        <v>3758.4</v>
+        <v>3860.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3831.95</v>
+        <v>3949.43</v>
       </c>
       <c r="K11" t="n">
-        <v>3971.3</v>
+        <v>4011.05</v>
       </c>
       <c r="L11" t="n">
-        <v>4110.65</v>
+        <v>4072.67</v>
       </c>
       <c r="M11" t="n">
-        <v>4217.1</v>
+        <v>4147.95</v>
       </c>
       <c r="N11" t="n">
-        <v>4323.55</v>
+        <v>4223.22</v>
       </c>
       <c r="O11" t="n">
-        <v>4495.8</v>
+        <v>4271.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,78 +1436,80 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4069.2</v>
+        <v>4258.5</v>
       </c>
       <c r="C12" t="n">
-        <v>4263.1</v>
+        <v>4299.6</v>
       </c>
       <c r="D12" t="n">
-        <v>4036.4</v>
+        <v>4194</v>
       </c>
       <c r="E12" t="n">
-        <v>4254.9</v>
+        <v>4243</v>
       </c>
       <c r="F12" t="n">
-        <v>175.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.043</v>
+        <v>-0.0028</v>
       </c>
       <c r="H12" t="n">
-        <v>226.7</v>
+        <v>105.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3860.5</v>
+        <v>3809.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3949.43</v>
+        <v>4080.77</v>
       </c>
       <c r="K12" t="n">
-        <v>4011.05</v>
+        <v>4141.55</v>
       </c>
       <c r="L12" t="n">
-        <v>4072.67</v>
+        <v>4202.32</v>
       </c>
       <c r="M12" t="n">
-        <v>4147.95</v>
+        <v>4368.25</v>
       </c>
       <c r="N12" t="n">
-        <v>4223.22</v>
+        <v>4534.18</v>
       </c>
       <c r="O12" t="n">
-        <v>4271.2</v>
+        <v>4489.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1530,78 +1522,76 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4258.5</v>
+        <v>4228.1</v>
       </c>
       <c r="C13" t="n">
-        <v>4299.6</v>
+        <v>4387.8</v>
       </c>
       <c r="D13" t="n">
-        <v>4194</v>
+        <v>4197.8</v>
       </c>
       <c r="E13" t="n">
-        <v>4243</v>
+        <v>4328.3</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.9</v>
+        <v>85.3</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0201</v>
       </c>
       <c r="H13" t="n">
-        <v>105.6</v>
+        <v>190</v>
       </c>
       <c r="I13" t="n">
-        <v>3809.7</v>
+        <v>4088.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4080.77</v>
+        <v>4135.5</v>
       </c>
       <c r="K13" t="n">
-        <v>4141.55</v>
+        <v>4190.2</v>
       </c>
       <c r="L13" t="n">
-        <v>4202.32</v>
+        <v>4244.9</v>
       </c>
       <c r="M13" t="n">
-        <v>4368.25</v>
+        <v>4295.8</v>
       </c>
       <c r="N13" t="n">
-        <v>4534.18</v>
+        <v>4346.7</v>
       </c>
       <c r="O13" t="n">
-        <v>4489.8</v>
+        <v>4405.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1614,14 +1604,18 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1631,59 +1625,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4228.1</v>
+        <v>4330</v>
       </c>
       <c r="C14" t="n">
-        <v>4387.8</v>
+        <v>4409.5</v>
       </c>
       <c r="D14" t="n">
-        <v>4197.8</v>
+        <v>4297.4</v>
       </c>
       <c r="E14" t="n">
-        <v>4328.3</v>
+        <v>4387.3</v>
       </c>
       <c r="F14" t="n">
-        <v>85.3</v>
+        <v>59</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0136</v>
       </c>
       <c r="H14" t="n">
-        <v>190</v>
+        <v>112.1</v>
       </c>
       <c r="I14" t="n">
-        <v>4088.4</v>
+        <v>4007.8</v>
       </c>
       <c r="J14" t="n">
-        <v>4135.5</v>
+        <v>4156.05</v>
       </c>
       <c r="K14" t="n">
-        <v>4190.2</v>
+        <v>4233.3</v>
       </c>
       <c r="L14" t="n">
-        <v>4244.9</v>
+        <v>4310.55</v>
       </c>
       <c r="M14" t="n">
-        <v>4295.8</v>
+        <v>4423.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4346.7</v>
+        <v>4536.05</v>
       </c>
       <c r="O14" t="n">
-        <v>4405.2</v>
+        <v>4577.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1701,13 +1691,11 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1722,50 +1710,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4330</v>
+        <v>4369.9</v>
       </c>
       <c r="C15" t="n">
-        <v>4409.5</v>
+        <v>4584</v>
       </c>
       <c r="D15" t="n">
-        <v>4297.4</v>
+        <v>4367.9</v>
       </c>
       <c r="E15" t="n">
-        <v>4387.3</v>
+        <v>4552.7</v>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>165.4</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0377</v>
       </c>
       <c r="H15" t="n">
-        <v>112.1</v>
+        <v>216.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4007.8</v>
+        <v>4185.3</v>
       </c>
       <c r="J15" t="n">
-        <v>4156.05</v>
+        <v>4292.12</v>
       </c>
       <c r="K15" t="n">
-        <v>4233.3</v>
+        <v>4331.25</v>
       </c>
       <c r="L15" t="n">
-        <v>4310.55</v>
+        <v>4370.37</v>
       </c>
       <c r="M15" t="n">
-        <v>4423.3</v>
+        <v>4443.35</v>
       </c>
       <c r="N15" t="n">
-        <v>4536.05</v>
+        <v>4516.32</v>
       </c>
       <c r="O15" t="n">
-        <v>4577.8</v>
+        <v>4521.6</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1783,14 +1771,18 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1802,83 +1794,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4369.9</v>
+        <v>4568</v>
       </c>
       <c r="C16" t="n">
-        <v>4584</v>
+        <v>4581.3</v>
       </c>
       <c r="D16" t="n">
-        <v>4367.9</v>
+        <v>4284.3</v>
       </c>
       <c r="E16" t="n">
-        <v>4552.7</v>
+        <v>4329.6</v>
       </c>
       <c r="F16" t="n">
-        <v>165.4</v>
+        <v>-223.1</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.049</v>
       </c>
       <c r="H16" t="n">
-        <v>216.1</v>
+        <v>297</v>
       </c>
       <c r="I16" t="n">
-        <v>4185.3</v>
+        <v>4151.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4292.12</v>
+        <v>4374.98</v>
       </c>
       <c r="K16" t="n">
-        <v>4331.25</v>
+        <v>4444.65</v>
       </c>
       <c r="L16" t="n">
-        <v>4370.37</v>
+        <v>4514.33</v>
       </c>
       <c r="M16" t="n">
-        <v>4443.35</v>
+        <v>4660.75</v>
       </c>
       <c r="N16" t="n">
-        <v>4516.32</v>
+        <v>4807.18</v>
       </c>
       <c r="O16" t="n">
-        <v>4521.6</v>
+        <v>4800.1</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1886,72 +1876,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4568</v>
+        <v>4368.3</v>
       </c>
       <c r="C17" t="n">
-        <v>4581.3</v>
+        <v>4527</v>
       </c>
       <c r="D17" t="n">
-        <v>4284.3</v>
+        <v>4354.6</v>
       </c>
       <c r="E17" t="n">
-        <v>4329.6</v>
+        <v>4500.9</v>
       </c>
       <c r="F17" t="n">
-        <v>-223.1</v>
+        <v>171.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.049</v>
+        <v>0.0396</v>
       </c>
       <c r="H17" t="n">
-        <v>297</v>
+        <v>172.4</v>
       </c>
       <c r="I17" t="n">
-        <v>4151.8</v>
+        <v>3987.3</v>
       </c>
       <c r="J17" t="n">
-        <v>4374.98</v>
+        <v>3981</v>
       </c>
       <c r="K17" t="n">
-        <v>4444.65</v>
+        <v>4181.1</v>
       </c>
       <c r="L17" t="n">
-        <v>4514.33</v>
+        <v>4381.2</v>
       </c>
       <c r="M17" t="n">
-        <v>4660.75</v>
+        <v>4478.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4807.18</v>
+        <v>4575</v>
       </c>
       <c r="O17" t="n">
-        <v>4800.1</v>
+        <v>4878.3</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1963,55 +1951,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4368.3</v>
+        <v>4529.1</v>
       </c>
       <c r="C18" t="n">
-        <v>4527</v>
+        <v>4650.5</v>
       </c>
       <c r="D18" t="n">
-        <v>4354.6</v>
+        <v>4520.8</v>
       </c>
       <c r="E18" t="n">
-        <v>4500.9</v>
+        <v>4595.4</v>
       </c>
       <c r="F18" t="n">
-        <v>171.3</v>
+        <v>94.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.021</v>
       </c>
       <c r="H18" t="n">
-        <v>172.4</v>
+        <v>129.7</v>
       </c>
       <c r="I18" t="n">
-        <v>3987.3</v>
+        <v>4182.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3981</v>
+        <v>4358.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4181.1</v>
+        <v>4414.7</v>
       </c>
       <c r="L18" t="n">
-        <v>4381.2</v>
+        <v>4470.85</v>
       </c>
       <c r="M18" t="n">
-        <v>4478.1</v>
+        <v>4587.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4575</v>
+        <v>4703.35</v>
       </c>
       <c r="O18" t="n">
-        <v>4878.3</v>
+        <v>4699.4</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2045,57 +2037,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4529.1</v>
+        <v>4633.7</v>
       </c>
       <c r="C19" t="n">
-        <v>4650.5</v>
+        <v>4991.4</v>
       </c>
       <c r="D19" t="n">
-        <v>4520.8</v>
+        <v>4622.2</v>
       </c>
       <c r="E19" t="n">
-        <v>4595.4</v>
+        <v>4979.7</v>
       </c>
       <c r="F19" t="n">
-        <v>94.5</v>
+        <v>384.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.021</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>129.7</v>
+        <v>369.2</v>
       </c>
       <c r="I19" t="n">
-        <v>4182.2</v>
+        <v>4391.1</v>
       </c>
       <c r="J19" t="n">
-        <v>4358.55</v>
+        <v>4470.57</v>
       </c>
       <c r="K19" t="n">
-        <v>4414.7</v>
+        <v>4530.55</v>
       </c>
       <c r="L19" t="n">
-        <v>4470.85</v>
+        <v>4590.52</v>
       </c>
       <c r="M19" t="n">
-        <v>4587.1</v>
+        <v>4660.25</v>
       </c>
       <c r="N19" t="n">
-        <v>4703.35</v>
+        <v>4729.98</v>
       </c>
       <c r="O19" t="n">
-        <v>4699.4</v>
+        <v>4780.2</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2113,86 +2105,90 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4633.7</v>
+        <v>5013.4</v>
       </c>
       <c r="C20" t="n">
-        <v>4991.4</v>
+        <v>5586.2</v>
       </c>
       <c r="D20" t="n">
-        <v>4622.2</v>
+        <v>4700.4</v>
       </c>
       <c r="E20" t="n">
-        <v>4979.7</v>
+        <v>4745.1</v>
       </c>
       <c r="F20" t="n">
-        <v>384.3</v>
+        <v>-234.6</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.0471</v>
       </c>
       <c r="H20" t="n">
-        <v>369.2</v>
+        <v>885.8</v>
       </c>
       <c r="I20" t="n">
-        <v>4391.1</v>
+        <v>4253</v>
       </c>
       <c r="J20" t="n">
-        <v>4470.57</v>
+        <v>4696.95</v>
       </c>
       <c r="K20" t="n">
-        <v>4530.55</v>
+        <v>4795.1</v>
       </c>
       <c r="L20" t="n">
-        <v>4590.52</v>
+        <v>4893.25</v>
       </c>
       <c r="M20" t="n">
-        <v>4660.25</v>
+        <v>5164.3</v>
       </c>
       <c r="N20" t="n">
-        <v>4729.98</v>
+        <v>5435.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4780.2</v>
+        <v>5360.6</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2207,7 +2203,7 @@
       </c>
       <c r="V20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
@@ -2215,88 +2211,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5013.4</v>
+        <v>4816</v>
       </c>
       <c r="C21" t="n">
-        <v>5586.2</v>
+        <v>5113.9</v>
       </c>
       <c r="D21" t="n">
-        <v>4700.4</v>
+        <v>4423.2</v>
       </c>
       <c r="E21" t="n">
-        <v>4745.1</v>
+        <v>4979.8</v>
       </c>
       <c r="F21" t="n">
-        <v>-234.6</v>
+        <v>234.7</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0471</v>
+        <v>0.0495</v>
       </c>
       <c r="H21" t="n">
-        <v>885.8</v>
+        <v>690.7</v>
       </c>
       <c r="I21" t="n">
-        <v>4253</v>
+        <v>3814.6</v>
       </c>
       <c r="J21" t="n">
-        <v>4696.95</v>
+        <v>3660.2</v>
       </c>
       <c r="K21" t="n">
-        <v>4795.1</v>
+        <v>4302.2</v>
       </c>
       <c r="L21" t="n">
-        <v>4893.25</v>
+        <v>4944.2</v>
       </c>
       <c r="M21" t="n">
-        <v>5164.3</v>
+        <v>5188</v>
       </c>
       <c r="N21" t="n">
-        <v>5435.35</v>
+        <v>5431.8</v>
       </c>
       <c r="O21" t="n">
-        <v>5360.6</v>
+        <v>6472</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2305,57 +2295,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4816</v>
+        <v>5003.6</v>
       </c>
       <c r="C22" t="n">
-        <v>5113.9</v>
+        <v>5144.5</v>
       </c>
       <c r="D22" t="n">
-        <v>4423.2</v>
+        <v>4900</v>
       </c>
       <c r="E22" t="n">
-        <v>4979.8</v>
+        <v>5046.3</v>
       </c>
       <c r="F22" t="n">
-        <v>234.7</v>
+        <v>66.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0495</v>
+        <v>0.0134</v>
       </c>
       <c r="H22" t="n">
-        <v>690.7</v>
+        <v>244.5</v>
       </c>
       <c r="I22" t="n">
-        <v>3814.6</v>
+        <v>3732.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3660.2</v>
+        <v>4394.72</v>
       </c>
       <c r="K22" t="n">
-        <v>4302.2</v>
+        <v>4634.45</v>
       </c>
       <c r="L22" t="n">
-        <v>4944.2</v>
+        <v>4874.17</v>
       </c>
       <c r="M22" t="n">
-        <v>5188</v>
+        <v>5325.15</v>
       </c>
       <c r="N22" t="n">
-        <v>5431.8</v>
+        <v>5776.12</v>
       </c>
       <c r="O22" t="n">
-        <v>6472</v>
+        <v>5804.6</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2385,59 +2375,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5003.6</v>
+        <v>5050</v>
       </c>
       <c r="C23" t="n">
-        <v>5144.5</v>
+        <v>5131</v>
       </c>
       <c r="D23" t="n">
-        <v>4900</v>
+        <v>4854.2</v>
       </c>
       <c r="E23" t="n">
-        <v>5046.3</v>
+        <v>5080.9</v>
       </c>
       <c r="F23" t="n">
-        <v>66.5</v>
+        <v>34.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0069</v>
       </c>
       <c r="H23" t="n">
-        <v>244.5</v>
+        <v>276.8</v>
       </c>
       <c r="I23" t="n">
-        <v>3732.5</v>
+        <v>4655.5</v>
       </c>
       <c r="J23" t="n">
-        <v>4394.72</v>
+        <v>4813.82</v>
       </c>
       <c r="K23" t="n">
-        <v>4634.45</v>
+        <v>4924.05</v>
       </c>
       <c r="L23" t="n">
-        <v>4874.17</v>
+        <v>5034.27</v>
       </c>
       <c r="M23" t="n">
-        <v>5325.15</v>
+        <v>5168.55</v>
       </c>
       <c r="N23" t="n">
-        <v>5776.12</v>
+        <v>5302.82</v>
       </c>
       <c r="O23" t="n">
-        <v>5804.6</v>
+        <v>5389</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2445,8 +2431,10 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
@@ -2467,55 +2455,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5050</v>
+        <v>5128.8</v>
       </c>
       <c r="C24" t="n">
-        <v>5131</v>
+        <v>5299</v>
       </c>
       <c r="D24" t="n">
-        <v>4854.2</v>
+        <v>5109.5</v>
       </c>
       <c r="E24" t="n">
-        <v>5080.9</v>
+        <v>5247.9</v>
       </c>
       <c r="F24" t="n">
-        <v>34.6</v>
+        <v>167</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0329</v>
       </c>
       <c r="H24" t="n">
-        <v>276.8</v>
+        <v>189.5</v>
       </c>
       <c r="I24" t="n">
-        <v>4655.5</v>
+        <v>4577.4</v>
       </c>
       <c r="J24" t="n">
-        <v>4813.82</v>
+        <v>4848.25</v>
       </c>
       <c r="K24" t="n">
-        <v>4924.05</v>
+        <v>4942.5</v>
       </c>
       <c r="L24" t="n">
-        <v>5034.27</v>
+        <v>5036.75</v>
       </c>
       <c r="M24" t="n">
-        <v>5168.55</v>
+        <v>5219.3</v>
       </c>
       <c r="N24" t="n">
-        <v>5302.82</v>
+        <v>5401.85</v>
       </c>
       <c r="O24" t="n">
-        <v>5389</v>
+        <v>5407.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2523,18 +2515,18 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2547,77 +2539,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5128.8</v>
+        <v>5360</v>
       </c>
       <c r="C25" t="n">
-        <v>5299</v>
+        <v>5434.1</v>
       </c>
       <c r="D25" t="n">
-        <v>5109.5</v>
+        <v>5005</v>
       </c>
       <c r="E25" t="n">
-        <v>5247.9</v>
+        <v>5158.7</v>
       </c>
       <c r="F25" t="n">
-        <v>167</v>
+        <v>-89.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0329</v>
+        <v>-0.017</v>
       </c>
       <c r="H25" t="n">
-        <v>189.5</v>
+        <v>429.1</v>
       </c>
       <c r="I25" t="n">
-        <v>4577.4</v>
+        <v>4920</v>
       </c>
       <c r="J25" t="n">
-        <v>4848.25</v>
+        <v>5080.22</v>
       </c>
       <c r="K25" t="n">
-        <v>4942.5</v>
+        <v>5153.15</v>
       </c>
       <c r="L25" t="n">
-        <v>5036.75</v>
+        <v>5226.07</v>
       </c>
       <c r="M25" t="n">
-        <v>5219.3</v>
+        <v>5342.65</v>
       </c>
       <c r="N25" t="n">
-        <v>5401.85</v>
+        <v>5459.22</v>
       </c>
       <c r="O25" t="n">
-        <v>5407.8</v>
+        <v>5488.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U25" s="8" t="n">
@@ -2631,63 +2623,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5360</v>
+        <v>5186.7</v>
       </c>
       <c r="C26" t="n">
-        <v>5434.1</v>
+        <v>5248.7</v>
       </c>
       <c r="D26" t="n">
-        <v>5005</v>
+        <v>5014.1</v>
       </c>
       <c r="E26" t="n">
-        <v>5158.7</v>
+        <v>5061.7</v>
       </c>
       <c r="F26" t="n">
-        <v>-89.2</v>
+        <v>-97</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0188</v>
       </c>
       <c r="H26" t="n">
-        <v>429.1</v>
+        <v>234.6</v>
       </c>
       <c r="I26" t="n">
-        <v>4920</v>
+        <v>4575.9</v>
       </c>
       <c r="J26" t="n">
-        <v>5080.22</v>
+        <v>4699.18</v>
       </c>
       <c r="K26" t="n">
-        <v>5153.15</v>
+        <v>4944.15</v>
       </c>
       <c r="L26" t="n">
-        <v>5226.07</v>
+        <v>5189.13</v>
       </c>
       <c r="M26" t="n">
-        <v>5342.65</v>
+        <v>5373.25</v>
       </c>
       <c r="N26" t="n">
-        <v>5459.22</v>
+        <v>5557.38</v>
       </c>
       <c r="O26" t="n">
-        <v>5488.5</v>
+        <v>5863.2</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
@@ -2699,10 +2693,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2724,60 +2716,64 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5186.7</v>
+        <v>5010</v>
       </c>
       <c r="C27" t="n">
-        <v>5248.7</v>
+        <v>5049.4</v>
       </c>
       <c r="D27" t="n">
-        <v>5014.1</v>
+        <v>4478.4</v>
       </c>
       <c r="E27" t="n">
-        <v>5061.7</v>
+        <v>4574.9</v>
       </c>
       <c r="F27" t="n">
-        <v>-97</v>
+        <v>-486.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0188</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>234.6</v>
+        <v>571</v>
       </c>
       <c r="I27" t="n">
-        <v>4575.9</v>
+        <v>4779.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4699.18</v>
+        <v>4792.25</v>
       </c>
       <c r="K27" t="n">
-        <v>4944.15</v>
+        <v>4944.4</v>
       </c>
       <c r="L27" t="n">
-        <v>5189.13</v>
+        <v>5096.55</v>
       </c>
       <c r="M27" t="n">
-        <v>5373.25</v>
+        <v>5179</v>
       </c>
       <c r="N27" t="n">
-        <v>5557.38</v>
+        <v>5261.45</v>
       </c>
       <c r="O27" t="n">
-        <v>5863.2</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+        <v>5483.3</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
@@ -2794,83 +2790,75 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5010</v>
+        <v>4450</v>
       </c>
       <c r="C28" t="n">
-        <v>5049.4</v>
+        <v>4601</v>
       </c>
       <c r="D28" t="n">
-        <v>4478.4</v>
+        <v>4100</v>
       </c>
       <c r="E28" t="n">
-        <v>4574.9</v>
+        <v>4492.5</v>
       </c>
       <c r="F28" t="n">
-        <v>-486.8</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="H28" t="n">
-        <v>571</v>
+        <v>501</v>
       </c>
       <c r="I28" t="n">
-        <v>4779.5</v>
+        <v>3907.4</v>
       </c>
       <c r="J28" t="n">
-        <v>4792.25</v>
+        <v>3909.4</v>
       </c>
       <c r="K28" t="n">
-        <v>4944.4</v>
+        <v>4289.4</v>
       </c>
       <c r="L28" t="n">
-        <v>5096.55</v>
+        <v>4669.4</v>
       </c>
       <c r="M28" t="n">
-        <v>5179</v>
+        <v>4860.4</v>
       </c>
       <c r="N28" t="n">
-        <v>5261.45</v>
+        <v>5051.4</v>
       </c>
       <c r="O28" t="n">
-        <v>5483.3</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
+        <v>5620.4</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2892,50 +2880,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4450</v>
+        <v>4482.8</v>
       </c>
       <c r="C29" t="n">
-        <v>4601</v>
+        <v>4825.9</v>
       </c>
       <c r="D29" t="n">
-        <v>4100</v>
+        <v>4413.4</v>
       </c>
       <c r="E29" t="n">
-        <v>4492.5</v>
+        <v>4679.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-82.40000000000001</v>
+        <v>187.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0417</v>
       </c>
       <c r="H29" t="n">
-        <v>501</v>
+        <v>412.5</v>
       </c>
       <c r="I29" t="n">
-        <v>3907.4</v>
+        <v>3599</v>
       </c>
       <c r="J29" t="n">
-        <v>3909.4</v>
+        <v>4062.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4289.4</v>
+        <v>4242</v>
       </c>
       <c r="L29" t="n">
-        <v>4669.4</v>
+        <v>4421.5</v>
       </c>
       <c r="M29" t="n">
-        <v>4860.4</v>
+        <v>4743</v>
       </c>
       <c r="N29" t="n">
-        <v>5051.4</v>
+        <v>5064.5</v>
       </c>
       <c r="O29" t="n">
-        <v>5620.4</v>
+        <v>5102</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2943,18 +2931,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2967,55 +2955,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4482.8</v>
+        <v>4675</v>
       </c>
       <c r="C30" t="n">
-        <v>4825.9</v>
+        <v>4888</v>
       </c>
       <c r="D30" t="n">
-        <v>4413.4</v>
+        <v>4626.2</v>
       </c>
       <c r="E30" t="n">
-        <v>4679.7</v>
+        <v>4787.4</v>
       </c>
       <c r="F30" t="n">
-        <v>187.2</v>
+        <v>107.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0417</v>
+        <v>0.023</v>
       </c>
       <c r="H30" t="n">
-        <v>412.5</v>
+        <v>261.8</v>
       </c>
       <c r="I30" t="n">
-        <v>3599</v>
+        <v>4000.9</v>
       </c>
       <c r="J30" t="n">
-        <v>4062.5</v>
+        <v>4297.23</v>
       </c>
       <c r="K30" t="n">
-        <v>4242</v>
+        <v>4473.45</v>
       </c>
       <c r="L30" t="n">
-        <v>4421.5</v>
+        <v>4649.68</v>
       </c>
       <c r="M30" t="n">
-        <v>4743</v>
+        <v>4885.95</v>
       </c>
       <c r="N30" t="n">
-        <v>5064.5</v>
+        <v>5122.23</v>
       </c>
       <c r="O30" t="n">
-        <v>5102</v>
+        <v>5238.4</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3056,50 +3048,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4675</v>
+        <v>4710</v>
       </c>
       <c r="C31" t="n">
-        <v>4888</v>
+        <v>4917.7</v>
       </c>
       <c r="D31" t="n">
-        <v>4626.2</v>
+        <v>4626</v>
       </c>
       <c r="E31" t="n">
-        <v>4787.4</v>
+        <v>4879.6</v>
       </c>
       <c r="F31" t="n">
-        <v>107.7</v>
+        <v>92.2</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0193</v>
       </c>
       <c r="H31" t="n">
-        <v>261.8</v>
+        <v>291.7</v>
       </c>
       <c r="I31" t="n">
-        <v>4000.9</v>
+        <v>4364.4</v>
       </c>
       <c r="J31" t="n">
-        <v>4297.23</v>
+        <v>4540.75</v>
       </c>
       <c r="K31" t="n">
-        <v>4473.45</v>
+        <v>4656.5</v>
       </c>
       <c r="L31" t="n">
-        <v>4649.68</v>
+        <v>4772.25</v>
       </c>
       <c r="M31" t="n">
-        <v>4885.95</v>
+        <v>4918.3</v>
       </c>
       <c r="N31" t="n">
-        <v>5122.23</v>
+        <v>5064.35</v>
       </c>
       <c r="O31" t="n">
-        <v>5238.4</v>
+        <v>5149.8</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3107,8 +3099,10 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
@@ -3133,57 +3127,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4710</v>
+        <v>4811.8</v>
       </c>
       <c r="C32" t="n">
-        <v>4917.7</v>
+        <v>4854.8</v>
       </c>
       <c r="D32" t="n">
-        <v>4626</v>
+        <v>4672.2</v>
       </c>
       <c r="E32" t="n">
-        <v>4879.6</v>
+        <v>4740.9</v>
       </c>
       <c r="F32" t="n">
-        <v>92.2</v>
+        <v>-138.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0193</v>
+        <v>-0.0284</v>
       </c>
       <c r="H32" t="n">
-        <v>291.7</v>
+        <v>182.6</v>
       </c>
       <c r="I32" t="n">
-        <v>4364.4</v>
+        <v>4334.3</v>
       </c>
       <c r="J32" t="n">
-        <v>4540.75</v>
+        <v>4641.77</v>
       </c>
       <c r="K32" t="n">
-        <v>4656.5</v>
+        <v>4733.75</v>
       </c>
       <c r="L32" t="n">
-        <v>4772.25</v>
+        <v>4825.73</v>
       </c>
       <c r="M32" t="n">
-        <v>4918.3</v>
+        <v>5025.45</v>
       </c>
       <c r="N32" t="n">
-        <v>5064.35</v>
+        <v>5225.18</v>
       </c>
       <c r="O32" t="n">
-        <v>5149.8</v>
+        <v>5209.4</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3193,19 +3187,17 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3219,63 +3211,65 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4811.8</v>
+        <v>4713.1</v>
       </c>
       <c r="C33" t="n">
-        <v>4854.8</v>
+        <v>4745.8</v>
       </c>
       <c r="D33" t="n">
-        <v>4672.2</v>
+        <v>4522.2</v>
       </c>
       <c r="E33" t="n">
-        <v>4740.9</v>
+        <v>4644.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-138.7</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0284</v>
+        <v>-0.0203</v>
       </c>
       <c r="H33" t="n">
-        <v>182.6</v>
+        <v>223.6</v>
       </c>
       <c r="I33" t="n">
-        <v>4334.3</v>
+        <v>4489.6</v>
       </c>
       <c r="J33" t="n">
-        <v>4641.77</v>
+        <v>4547</v>
       </c>
       <c r="K33" t="n">
-        <v>4733.75</v>
+        <v>4649.6</v>
       </c>
       <c r="L33" t="n">
-        <v>4825.73</v>
+        <v>4752.2</v>
       </c>
       <c r="M33" t="n">
-        <v>5025.45</v>
+        <v>4832.2</v>
       </c>
       <c r="N33" t="n">
-        <v>5225.18</v>
+        <v>4912.2</v>
       </c>
       <c r="O33" t="n">
-        <v>5209.4</v>
+        <v>5037.4</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
@@ -3301,81 +3295,77 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4713.1</v>
+        <v>4644</v>
       </c>
       <c r="C34" t="n">
-        <v>4745.8</v>
+        <v>4775.2</v>
       </c>
       <c r="D34" t="n">
-        <v>4522.2</v>
+        <v>4510.1</v>
       </c>
       <c r="E34" t="n">
-        <v>4644.5</v>
+        <v>4730.7</v>
       </c>
       <c r="F34" t="n">
-        <v>-96.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0186</v>
       </c>
       <c r="H34" t="n">
-        <v>223.6</v>
+        <v>265.1</v>
       </c>
       <c r="I34" t="n">
-        <v>4489.6</v>
+        <v>4298.6</v>
       </c>
       <c r="J34" t="n">
-        <v>4547</v>
+        <v>4426.15</v>
       </c>
       <c r="K34" t="n">
-        <v>4649.6</v>
+        <v>4532.7</v>
       </c>
       <c r="L34" t="n">
-        <v>4752.2</v>
+        <v>4639.25</v>
       </c>
       <c r="M34" t="n">
-        <v>4832.2</v>
+        <v>4756.3</v>
       </c>
       <c r="N34" t="n">
-        <v>4912.2</v>
+        <v>4873.35</v>
       </c>
       <c r="O34" t="n">
-        <v>5037.4</v>
+        <v>4969.4</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3387,55 +3377,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4644</v>
+        <v>4690</v>
       </c>
       <c r="C35" t="n">
-        <v>4775.2</v>
+        <v>4783.4</v>
       </c>
       <c r="D35" t="n">
-        <v>4510.1</v>
+        <v>4513.8</v>
       </c>
       <c r="E35" t="n">
-        <v>4730.7</v>
+        <v>4561.9</v>
       </c>
       <c r="F35" t="n">
-        <v>86.2</v>
+        <v>-168.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0357</v>
       </c>
       <c r="H35" t="n">
-        <v>265.1</v>
+        <v>269.6</v>
       </c>
       <c r="I35" t="n">
-        <v>4298.6</v>
+        <v>4245</v>
       </c>
       <c r="J35" t="n">
-        <v>4426.15</v>
+        <v>4509.63</v>
       </c>
       <c r="K35" t="n">
-        <v>4532.7</v>
+        <v>4598.15</v>
       </c>
       <c r="L35" t="n">
-        <v>4639.25</v>
+        <v>4686.68</v>
       </c>
       <c r="M35" t="n">
-        <v>4756.3</v>
+        <v>4863.25</v>
       </c>
       <c r="N35" t="n">
-        <v>4873.35</v>
+        <v>5039.83</v>
       </c>
       <c r="O35" t="n">
-        <v>4969.4</v>
+        <v>5040.3</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3445,18 +3439,16 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3478,50 +3470,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4690</v>
+        <v>4547.6</v>
       </c>
       <c r="C36" t="n">
-        <v>4783.4</v>
+        <v>4593.2</v>
       </c>
       <c r="D36" t="n">
-        <v>4513.8</v>
+        <v>4455</v>
       </c>
       <c r="E36" t="n">
-        <v>4561.9</v>
+        <v>4523.2</v>
       </c>
       <c r="F36" t="n">
-        <v>-168.8</v>
+        <v>-38.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0357</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>269.6</v>
+        <v>138.2</v>
       </c>
       <c r="I36" t="n">
-        <v>4245</v>
+        <v>4244.2</v>
       </c>
       <c r="J36" t="n">
-        <v>4509.63</v>
+        <v>4248.95</v>
       </c>
       <c r="K36" t="n">
-        <v>4598.15</v>
+        <v>4427.1</v>
       </c>
       <c r="L36" t="n">
-        <v>4686.68</v>
+        <v>4605.25</v>
       </c>
       <c r="M36" t="n">
-        <v>4863.25</v>
+        <v>4696.7</v>
       </c>
       <c r="N36" t="n">
-        <v>5039.83</v>
+        <v>4788.15</v>
       </c>
       <c r="O36" t="n">
-        <v>5040.3</v>
+        <v>5053</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3529,14 +3521,12 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3553,76 +3543,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4547.6</v>
+        <v>4532</v>
       </c>
       <c r="C37" t="n">
-        <v>4593.2</v>
+        <v>4627.1</v>
       </c>
       <c r="D37" t="n">
-        <v>4455</v>
+        <v>4363.5</v>
       </c>
       <c r="E37" t="n">
-        <v>4523.2</v>
+        <v>4593</v>
       </c>
       <c r="F37" t="n">
-        <v>-38.7</v>
+        <v>69.8</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H37" t="n">
-        <v>138.2</v>
+        <v>263.6</v>
       </c>
       <c r="I37" t="n">
-        <v>4244.2</v>
+        <v>4316.8</v>
       </c>
       <c r="J37" t="n">
-        <v>4248.95</v>
+        <v>4384.55</v>
       </c>
       <c r="K37" t="n">
-        <v>4427.1</v>
+        <v>4454.1</v>
       </c>
       <c r="L37" t="n">
-        <v>4605.25</v>
+        <v>4523.65</v>
       </c>
       <c r="M37" t="n">
-        <v>4696.7</v>
+        <v>4592.3</v>
       </c>
       <c r="N37" t="n">
-        <v>4788.15</v>
+        <v>4660.95</v>
       </c>
       <c r="O37" t="n">
-        <v>5053</v>
+        <v>4731.4</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3635,78 +3627,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4532</v>
+        <v>4575.2</v>
       </c>
       <c r="C38" t="n">
-        <v>4627.1</v>
+        <v>4577.3</v>
       </c>
       <c r="D38" t="n">
-        <v>4363.5</v>
+        <v>4336.6</v>
       </c>
       <c r="E38" t="n">
-        <v>4593</v>
+        <v>4365.3</v>
       </c>
       <c r="F38" t="n">
-        <v>69.8</v>
+        <v>-227.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0154</v>
+        <v>-0.0496</v>
       </c>
       <c r="H38" t="n">
-        <v>263.6</v>
+        <v>240.7</v>
       </c>
       <c r="I38" t="n">
-        <v>4316.8</v>
+        <v>4099.9</v>
       </c>
       <c r="J38" t="n">
-        <v>4384.55</v>
+        <v>4378.25</v>
       </c>
       <c r="K38" t="n">
-        <v>4454.1</v>
+        <v>4461.2</v>
       </c>
       <c r="L38" t="n">
-        <v>4523.65</v>
+        <v>4544.15</v>
       </c>
       <c r="M38" t="n">
-        <v>4592.3</v>
+        <v>4724.8</v>
       </c>
       <c r="N38" t="n">
-        <v>4660.95</v>
+        <v>4905.45</v>
       </c>
       <c r="O38" t="n">
-        <v>4731.4</v>
+        <v>4890.7</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3719,71 +3713,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4575.2</v>
+        <v>4354</v>
       </c>
       <c r="C39" t="n">
-        <v>4577.3</v>
+        <v>4388.6</v>
       </c>
       <c r="D39" t="n">
-        <v>4336.6</v>
+        <v>4046.2</v>
       </c>
       <c r="E39" t="n">
-        <v>4365.3</v>
+        <v>4238.8</v>
       </c>
       <c r="F39" t="n">
-        <v>-227.7</v>
+        <v>-126.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0496</v>
+        <v>-0.029</v>
       </c>
       <c r="H39" t="n">
-        <v>240.7</v>
+        <v>342.4</v>
       </c>
       <c r="I39" t="n">
-        <v>4099.9</v>
+        <v>4095.9</v>
       </c>
       <c r="J39" t="n">
-        <v>4378.25</v>
+        <v>4078.78</v>
       </c>
       <c r="K39" t="n">
-        <v>4461.2</v>
+        <v>4244.95</v>
       </c>
       <c r="L39" t="n">
-        <v>4544.15</v>
+        <v>4411.12</v>
       </c>
       <c r="M39" t="n">
-        <v>4724.8</v>
+        <v>4485.65</v>
       </c>
       <c r="N39" t="n">
-        <v>4905.45</v>
+        <v>4560.17</v>
       </c>
       <c r="O39" t="n">
-        <v>4890.7</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
+        <v>4818</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
@@ -3810,69 +3802,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4354</v>
+        <v>4289.4</v>
       </c>
       <c r="C40" t="n">
-        <v>4388.6</v>
+        <v>4403.6</v>
       </c>
       <c r="D40" t="n">
-        <v>4046.2</v>
+        <v>4138.7</v>
       </c>
       <c r="E40" t="n">
-        <v>4238.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F40" t="n">
-        <v>-126.5</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0155</v>
       </c>
       <c r="H40" t="n">
-        <v>342.4</v>
+        <v>264.9</v>
       </c>
       <c r="I40" t="n">
-        <v>4095.9</v>
+        <v>3703.8</v>
       </c>
       <c r="J40" t="n">
-        <v>4078.78</v>
+        <v>3907.1</v>
       </c>
       <c r="K40" t="n">
-        <v>4244.95</v>
+        <v>4067.6</v>
       </c>
       <c r="L40" t="n">
-        <v>4411.12</v>
+        <v>4228.1</v>
       </c>
       <c r="M40" t="n">
-        <v>4485.65</v>
+        <v>4410</v>
       </c>
       <c r="N40" t="n">
-        <v>4560.17</v>
+        <v>4591.9</v>
       </c>
       <c r="O40" t="n">
-        <v>4818</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4731</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3889,55 +3875,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4289.4</v>
+        <v>4163.9</v>
       </c>
       <c r="C41" t="n">
-        <v>4403.6</v>
+        <v>4238.1</v>
       </c>
       <c r="D41" t="n">
-        <v>4138.7</v>
+        <v>3975.7</v>
       </c>
       <c r="E41" t="n">
-        <v>4172.9</v>
+        <v>4096.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-65.90000000000001</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0184</v>
       </c>
       <c r="H41" t="n">
-        <v>264.9</v>
+        <v>262.4</v>
       </c>
       <c r="I41" t="n">
-        <v>3703.8</v>
+        <v>3873.8</v>
       </c>
       <c r="J41" t="n">
-        <v>3907.1</v>
+        <v>3858.87</v>
       </c>
       <c r="K41" t="n">
-        <v>4067.6</v>
+        <v>4040.45</v>
       </c>
       <c r="L41" t="n">
-        <v>4228.1</v>
+        <v>4222.03</v>
       </c>
       <c r="M41" t="n">
-        <v>4410</v>
+        <v>4305.35</v>
       </c>
       <c r="N41" t="n">
-        <v>4591.9</v>
+        <v>4388.67</v>
       </c>
       <c r="O41" t="n">
-        <v>4731</v>
+        <v>4668.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3945,12 +3935,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3967,59 +3959,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4163.9</v>
+        <v>4101.1</v>
       </c>
       <c r="C42" t="n">
-        <v>4238.1</v>
+        <v>4208.3</v>
       </c>
       <c r="D42" t="n">
-        <v>3975.7</v>
+        <v>3955.4</v>
       </c>
       <c r="E42" t="n">
-        <v>4096.3</v>
+        <v>4187.3</v>
       </c>
       <c r="F42" t="n">
-        <v>-76.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0222</v>
       </c>
       <c r="H42" t="n">
-        <v>262.4</v>
+        <v>252.9</v>
       </c>
       <c r="I42" t="n">
-        <v>3873.8</v>
+        <v>3713.3</v>
       </c>
       <c r="J42" t="n">
-        <v>3858.87</v>
+        <v>3828.6</v>
       </c>
       <c r="K42" t="n">
-        <v>4040.45</v>
+        <v>3965.1</v>
       </c>
       <c r="L42" t="n">
-        <v>4222.03</v>
+        <v>4101.6</v>
       </c>
       <c r="M42" t="n">
-        <v>4305.35</v>
+        <v>4227.5</v>
       </c>
       <c r="N42" t="n">
-        <v>4388.67</v>
+        <v>4353.4</v>
       </c>
       <c r="O42" t="n">
-        <v>4668.5</v>
+        <v>4500.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4029,17 +4017,19 @@
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4051,55 +4041,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4101.1</v>
+        <v>4187.5</v>
       </c>
       <c r="C43" t="n">
-        <v>4208.3</v>
+        <v>4215.5</v>
       </c>
       <c r="D43" t="n">
-        <v>3955.4</v>
+        <v>4032.5</v>
       </c>
       <c r="E43" t="n">
-        <v>4187.3</v>
+        <v>4113.7</v>
       </c>
       <c r="F43" t="n">
-        <v>91</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0176</v>
       </c>
       <c r="H43" t="n">
-        <v>252.9</v>
+        <v>183</v>
       </c>
       <c r="I43" t="n">
-        <v>3713.3</v>
+        <v>3702.5</v>
       </c>
       <c r="J43" t="n">
-        <v>3828.6</v>
+        <v>3987.12</v>
       </c>
       <c r="K43" t="n">
-        <v>3965.1</v>
+        <v>4060.85</v>
       </c>
       <c r="L43" t="n">
-        <v>4101.6</v>
+        <v>4134.57</v>
       </c>
       <c r="M43" t="n">
-        <v>4227.5</v>
+        <v>4313.75</v>
       </c>
       <c r="N43" t="n">
-        <v>4353.4</v>
+        <v>4492.92</v>
       </c>
       <c r="O43" t="n">
-        <v>4500.5</v>
+        <v>4461.2</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4112,15 +4106,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4135,57 +4127,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4187.5</v>
+        <v>4106.6</v>
       </c>
       <c r="C44" t="n">
-        <v>4215.5</v>
+        <v>4112.5</v>
       </c>
       <c r="D44" t="n">
-        <v>4032.5</v>
+        <v>3963</v>
       </c>
       <c r="E44" t="n">
-        <v>4113.7</v>
+        <v>4018.8</v>
       </c>
       <c r="F44" t="n">
-        <v>-73.59999999999999</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0176</v>
+        <v>-0.0231</v>
       </c>
       <c r="H44" t="n">
-        <v>183</v>
+        <v>149.5</v>
       </c>
       <c r="I44" t="n">
-        <v>3702.5</v>
+        <v>3849.5</v>
       </c>
       <c r="J44" t="n">
-        <v>3987.12</v>
+        <v>3925.55</v>
       </c>
       <c r="K44" t="n">
-        <v>4060.85</v>
+        <v>4022.2</v>
       </c>
       <c r="L44" t="n">
-        <v>4134.57</v>
+        <v>4118.85</v>
       </c>
       <c r="M44" t="n">
-        <v>4313.75</v>
+        <v>4205.2</v>
       </c>
       <c r="N44" t="n">
-        <v>4492.92</v>
+        <v>4291.55</v>
       </c>
       <c r="O44" t="n">
-        <v>4461.2</v>
+        <v>4398.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4195,12 +4187,12 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4217,59 +4209,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4106.6</v>
+        <v>4005.6</v>
       </c>
       <c r="C45" t="n">
-        <v>4112.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D45" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E45" t="n">
-        <v>4018.8</v>
+        <v>4070.8</v>
       </c>
       <c r="F45" t="n">
-        <v>-94.90000000000001</v>
+        <v>52</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0129</v>
       </c>
       <c r="H45" t="n">
-        <v>149.5</v>
+        <v>184.9</v>
       </c>
       <c r="I45" t="n">
-        <v>3849.5</v>
+        <v>3813.5</v>
       </c>
       <c r="J45" t="n">
-        <v>3925.55</v>
+        <v>3859.83</v>
       </c>
       <c r="K45" t="n">
-        <v>4022.2</v>
+        <v>3944.05</v>
       </c>
       <c r="L45" t="n">
-        <v>4118.85</v>
+        <v>4028.28</v>
       </c>
       <c r="M45" t="n">
-        <v>4205.2</v>
+        <v>4093.55</v>
       </c>
       <c r="N45" t="n">
-        <v>4291.55</v>
+        <v>4158.83</v>
       </c>
       <c r="O45" t="n">
-        <v>4398.5</v>
+        <v>4262</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4277,21 +4265,23 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4301,55 +4291,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4005.6</v>
+        <v>4097.5</v>
       </c>
       <c r="C46" t="n">
-        <v>4171.4</v>
+        <v>4170.7</v>
       </c>
       <c r="D46" t="n">
-        <v>3986.5</v>
+        <v>3993.8</v>
       </c>
       <c r="E46" t="n">
-        <v>4070.8</v>
+        <v>4107</v>
       </c>
       <c r="F46" t="n">
-        <v>52</v>
+        <v>36.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0089</v>
       </c>
       <c r="H46" t="n">
-        <v>184.9</v>
+        <v>176.9</v>
       </c>
       <c r="I46" t="n">
-        <v>3813.5</v>
+        <v>3801.6</v>
       </c>
       <c r="J46" t="n">
-        <v>3859.83</v>
+        <v>3881.83</v>
       </c>
       <c r="K46" t="n">
-        <v>3944.05</v>
+        <v>3978.35</v>
       </c>
       <c r="L46" t="n">
-        <v>4028.28</v>
+        <v>4074.88</v>
       </c>
       <c r="M46" t="n">
-        <v>4093.55</v>
+        <v>4163.25</v>
       </c>
       <c r="N46" t="n">
-        <v>4158.83</v>
+        <v>4251.62</v>
       </c>
       <c r="O46" t="n">
-        <v>4262</v>
+        <v>4356.3</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4362,19 +4356,17 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4385,57 +4377,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4097.5</v>
+        <v>4135.2</v>
       </c>
       <c r="C47" t="n">
-        <v>4170.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D47" t="n">
-        <v>3993.8</v>
+        <v>4074</v>
       </c>
       <c r="E47" t="n">
-        <v>4107</v>
+        <v>4399.7</v>
       </c>
       <c r="F47" t="n">
-        <v>36.2</v>
+        <v>292.7</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0089</v>
+        <v>0.0713</v>
       </c>
       <c r="H47" t="n">
-        <v>176.9</v>
+        <v>358.3</v>
       </c>
       <c r="I47" t="n">
-        <v>3801.6</v>
+        <v>3816.9</v>
       </c>
       <c r="J47" t="n">
-        <v>3881.83</v>
+        <v>3942.47</v>
       </c>
       <c r="K47" t="n">
-        <v>3978.35</v>
+        <v>4018.55</v>
       </c>
       <c r="L47" t="n">
-        <v>4074.88</v>
+        <v>4094.63</v>
       </c>
       <c r="M47" t="n">
-        <v>4163.25</v>
+        <v>4195.45</v>
       </c>
       <c r="N47" t="n">
-        <v>4251.62</v>
+        <v>4296.28</v>
       </c>
       <c r="O47" t="n">
-        <v>4356.3</v>
+        <v>4347.6</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4448,7 +4440,7 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4456,70 +4448,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4135.2</v>
+        <v>4400</v>
       </c>
       <c r="C48" t="n">
-        <v>4432.3</v>
+        <v>4509.1</v>
       </c>
       <c r="D48" t="n">
-        <v>4074</v>
+        <v>4365.5</v>
       </c>
       <c r="E48" t="n">
-        <v>4399.7</v>
+        <v>4437.3</v>
       </c>
       <c r="F48" t="n">
-        <v>292.7</v>
+        <v>37.6</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0713</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>358.3</v>
+        <v>143.6</v>
       </c>
       <c r="I48" t="n">
-        <v>3816.9</v>
+        <v>3715.7</v>
       </c>
       <c r="J48" t="n">
-        <v>3942.47</v>
+        <v>4114.68</v>
       </c>
       <c r="K48" t="n">
-        <v>4018.55</v>
+        <v>4220.55</v>
       </c>
       <c r="L48" t="n">
-        <v>4094.63</v>
+        <v>4326.43</v>
       </c>
       <c r="M48" t="n">
-        <v>4195.45</v>
+        <v>4578.85</v>
       </c>
       <c r="N48" t="n">
-        <v>4296.28</v>
+        <v>4831.28</v>
       </c>
       <c r="O48" t="n">
-        <v>4347.6</v>
+        <v>4790.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4532,23 +4524,17 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4560,50 +4546,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4400</v>
+        <v>4440</v>
       </c>
       <c r="C49" t="n">
+        <v>4690.4</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4378</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4680.6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>243.3</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H49" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>4221.9</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4293.7</v>
+      </c>
+      <c r="K49" t="n">
+        <v>4365.5</v>
+      </c>
+      <c r="L49" t="n">
+        <v>4437.3</v>
+      </c>
+      <c r="M49" t="n">
         <v>4509.1</v>
       </c>
-      <c r="D49" t="n">
-        <v>4365.5</v>
-      </c>
-      <c r="E49" t="n">
-        <v>4437.3</v>
-      </c>
-      <c r="F49" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="H49" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="I49" t="n">
-        <v>3715.7</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4114.68</v>
-      </c>
-      <c r="K49" t="n">
-        <v>4220.55</v>
-      </c>
-      <c r="L49" t="n">
-        <v>4326.43</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4578.85</v>
-      </c>
       <c r="N49" t="n">
-        <v>4831.28</v>
+        <v>4580.9</v>
       </c>
       <c r="O49" t="n">
-        <v>4790.6</v>
+        <v>4652.7</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4616,17 +4602,23 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4638,50 +4630,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4440</v>
+        <v>4673.4</v>
       </c>
       <c r="C50" t="n">
-        <v>4690.4</v>
+        <v>4755</v>
       </c>
       <c r="D50" t="n">
-        <v>4378</v>
+        <v>4495</v>
       </c>
       <c r="E50" t="n">
-        <v>4680.6</v>
+        <v>4529.9</v>
       </c>
       <c r="F50" t="n">
-        <v>243.3</v>
+        <v>-150.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0548</v>
+        <v>-0.0322</v>
       </c>
       <c r="H50" t="n">
-        <v>312.4</v>
+        <v>260</v>
       </c>
       <c r="I50" t="n">
-        <v>4221.9</v>
+        <v>4065.6</v>
       </c>
       <c r="J50" t="n">
-        <v>4293.7</v>
+        <v>4441.4</v>
       </c>
       <c r="K50" t="n">
-        <v>4365.5</v>
+        <v>4524.4</v>
       </c>
       <c r="L50" t="n">
-        <v>4437.3</v>
+        <v>4607.4</v>
       </c>
       <c r="M50" t="n">
-        <v>4509.1</v>
+        <v>4836.8</v>
       </c>
       <c r="N50" t="n">
-        <v>4580.9</v>
+        <v>5066.2</v>
       </c>
       <c r="O50" t="n">
-        <v>4652.7</v>
+        <v>5002.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4689,83 +4681,83 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
+      </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4673.4</v>
+        <v>4483.2</v>
       </c>
       <c r="C51" t="n">
-        <v>4755</v>
+        <v>4558.5</v>
       </c>
       <c r="D51" t="n">
-        <v>4495</v>
+        <v>4329.2</v>
       </c>
       <c r="E51" t="n">
-        <v>4529.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F51" t="n">
-        <v>-150.7</v>
+        <v>-53.3</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0118</v>
       </c>
       <c r="H51" t="n">
-        <v>260</v>
+        <v>229.3</v>
       </c>
       <c r="I51" t="n">
-        <v>4065.6</v>
+        <v>4235</v>
       </c>
       <c r="J51" t="n">
-        <v>4441.4</v>
+        <v>4222.35</v>
       </c>
       <c r="K51" t="n">
-        <v>4524.4</v>
+        <v>4399.9</v>
       </c>
       <c r="L51" t="n">
-        <v>4607.4</v>
+        <v>4577.45</v>
       </c>
       <c r="M51" t="n">
-        <v>4836.8</v>
+        <v>4659.9</v>
       </c>
       <c r="N51" t="n">
-        <v>5066.2</v>
+        <v>4742.35</v>
       </c>
       <c r="O51" t="n">
-        <v>5002.8</v>
+        <v>5015</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4799,57 +4791,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4483.2</v>
+        <v>4466.5</v>
       </c>
       <c r="C52" t="n">
-        <v>4558.5</v>
+        <v>4488.8</v>
       </c>
       <c r="D52" t="n">
-        <v>4329.2</v>
+        <v>4333</v>
       </c>
       <c r="E52" t="n">
-        <v>4476.6</v>
+        <v>4408.9</v>
       </c>
       <c r="F52" t="n">
-        <v>-53.3</v>
+        <v>-67.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0151</v>
       </c>
       <c r="H52" t="n">
-        <v>229.3</v>
+        <v>155.8</v>
       </c>
       <c r="I52" t="n">
-        <v>4235</v>
+        <v>4099.9</v>
       </c>
       <c r="J52" t="n">
-        <v>4222.35</v>
+        <v>4263.68</v>
       </c>
       <c r="K52" t="n">
-        <v>4399.9</v>
+        <v>4361.95</v>
       </c>
       <c r="L52" t="n">
-        <v>4577.45</v>
+        <v>4460.23</v>
       </c>
       <c r="M52" t="n">
-        <v>4659.9</v>
+        <v>4591.25</v>
       </c>
       <c r="N52" t="n">
-        <v>4742.35</v>
+        <v>4722.27</v>
       </c>
       <c r="O52" t="n">
-        <v>5015</v>
+        <v>4787.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4883,57 +4875,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4466.5</v>
+        <v>4375</v>
       </c>
       <c r="C53" t="n">
-        <v>4488.8</v>
+        <v>4439.8</v>
       </c>
       <c r="D53" t="n">
-        <v>4333</v>
+        <v>4273.3</v>
       </c>
       <c r="E53" t="n">
-        <v>4408.9</v>
+        <v>4424.9</v>
       </c>
       <c r="F53" t="n">
-        <v>-67.7</v>
+        <v>16</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0151</v>
+        <v>0.0036</v>
       </c>
       <c r="H53" t="n">
-        <v>155.8</v>
+        <v>166.5</v>
       </c>
       <c r="I53" t="n">
-        <v>4099.9</v>
+        <v>4177.2</v>
       </c>
       <c r="J53" t="n">
-        <v>4263.68</v>
+        <v>4252.1</v>
       </c>
       <c r="K53" t="n">
-        <v>4361.95</v>
+        <v>4331</v>
       </c>
       <c r="L53" t="n">
-        <v>4460.23</v>
+        <v>4409.9</v>
       </c>
       <c r="M53" t="n">
-        <v>4591.25</v>
+        <v>4486.8</v>
       </c>
       <c r="N53" t="n">
-        <v>4722.27</v>
+        <v>4563.7</v>
       </c>
       <c r="O53" t="n">
-        <v>4787.8</v>
+        <v>4644.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4943,12 +4935,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4974,65 +4966,67 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4375</v>
+        <v>4413</v>
       </c>
       <c r="C54" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D54" t="n">
-        <v>4273.3</v>
+        <v>4278.3</v>
       </c>
       <c r="E54" t="n">
-        <v>4424.9</v>
+        <v>4321.2</v>
       </c>
       <c r="F54" t="n">
-        <v>16</v>
+        <v>-103.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0234</v>
       </c>
       <c r="H54" t="n">
-        <v>166.5</v>
+        <v>143.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4177.2</v>
+        <v>4106.8</v>
       </c>
       <c r="J54" t="n">
-        <v>4252.1</v>
+        <v>4292.57</v>
       </c>
       <c r="K54" t="n">
-        <v>4331</v>
+        <v>4341.65</v>
       </c>
       <c r="L54" t="n">
-        <v>4409.9</v>
+        <v>4390.72</v>
       </c>
       <c r="M54" t="n">
-        <v>4486.8</v>
+        <v>4508.15</v>
       </c>
       <c r="N54" t="n">
-        <v>4563.7</v>
+        <v>4625.57</v>
       </c>
       <c r="O54" t="n">
-        <v>4644.6</v>
+        <v>4606.3</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5058,64 +5052,64 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4413</v>
+        <v>4315</v>
       </c>
       <c r="C55" t="n">
-        <v>4422.1</v>
+        <v>4315.6</v>
       </c>
       <c r="D55" t="n">
-        <v>4278.3</v>
+        <v>4143.1</v>
       </c>
       <c r="E55" t="n">
-        <v>4321.2</v>
+        <v>4162.3</v>
       </c>
       <c r="F55" t="n">
-        <v>-103.7</v>
+        <v>-158.9</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0234</v>
+        <v>-0.0368</v>
       </c>
       <c r="H55" t="n">
-        <v>143.8</v>
+        <v>172.5</v>
       </c>
       <c r="I55" t="n">
-        <v>4106.8</v>
+        <v>4134.5</v>
       </c>
       <c r="J55" t="n">
-        <v>4292.57</v>
+        <v>4162.9</v>
       </c>
       <c r="K55" t="n">
-        <v>4341.65</v>
+        <v>4249.3</v>
       </c>
       <c r="L55" t="n">
-        <v>4390.72</v>
+        <v>4335.7</v>
       </c>
       <c r="M55" t="n">
-        <v>4508.15</v>
+        <v>4393.1</v>
       </c>
       <c r="N55" t="n">
-        <v>4625.57</v>
+        <v>4450.5</v>
       </c>
       <c r="O55" t="n">
-        <v>4606.3</v>
+        <v>4565.9</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5130,81 +5124,73 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4315</v>
+        <v>4169.4</v>
       </c>
       <c r="C56" t="n">
-        <v>4315.6</v>
+        <v>4233.7</v>
       </c>
       <c r="D56" t="n">
-        <v>4143.1</v>
+        <v>4091.2</v>
       </c>
       <c r="E56" t="n">
-        <v>4162.3</v>
+        <v>4216.3</v>
       </c>
       <c r="F56" t="n">
-        <v>-158.9</v>
+        <v>54</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0368</v>
+        <v>0.013</v>
       </c>
       <c r="H56" t="n">
-        <v>172.5</v>
+        <v>142.5</v>
       </c>
       <c r="I56" t="n">
-        <v>4134.5</v>
+        <v>3970.6</v>
       </c>
       <c r="J56" t="n">
-        <v>4162.9</v>
+        <v>3956.27</v>
       </c>
       <c r="K56" t="n">
-        <v>4249.3</v>
+        <v>4076.05</v>
       </c>
       <c r="L56" t="n">
-        <v>4335.7</v>
+        <v>4195.82</v>
       </c>
       <c r="M56" t="n">
-        <v>4393.1</v>
+        <v>4248.55</v>
       </c>
       <c r="N56" t="n">
-        <v>4450.5</v>
+        <v>4301.27</v>
       </c>
       <c r="O56" t="n">
-        <v>4565.9</v>
+        <v>4488.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5221,68 +5207,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4169.4</v>
+        <v>4220.8</v>
       </c>
       <c r="C57" t="n">
-        <v>4233.7</v>
+        <v>4242.3</v>
       </c>
       <c r="D57" t="n">
-        <v>4091.2</v>
+        <v>4095</v>
       </c>
       <c r="E57" t="n">
-        <v>4216.3</v>
+        <v>4186.7</v>
       </c>
       <c r="F57" t="n">
-        <v>54</v>
+        <v>-29.6</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.007</v>
       </c>
       <c r="H57" t="n">
-        <v>142.5</v>
+        <v>147.3</v>
       </c>
       <c r="I57" t="n">
-        <v>3970.6</v>
+        <v>3948.7</v>
       </c>
       <c r="J57" t="n">
-        <v>3956.27</v>
+        <v>4100.72</v>
       </c>
       <c r="K57" t="n">
-        <v>4076.05</v>
+        <v>4145.05</v>
       </c>
       <c r="L57" t="n">
-        <v>4195.82</v>
+        <v>4189.37</v>
       </c>
       <c r="M57" t="n">
-        <v>4248.55</v>
+        <v>4287.55</v>
       </c>
       <c r="N57" t="n">
-        <v>4301.27</v>
+        <v>4385.72</v>
       </c>
       <c r="O57" t="n">
-        <v>4488.1</v>
+        <v>4376.2</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5300,92 +5294,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4220.8</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4242.3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>4095</v>
-      </c>
-      <c r="E58" t="n">
-        <v>4176.9</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-39.4</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.009299999999999999</v>
-      </c>
-      <c r="H58" t="n">
-        <v>147.3</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3948.7</v>
-      </c>
-      <c r="J58" t="n">
-        <v>4100.72</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4145.05</v>
-      </c>
-      <c r="L58" t="n">
-        <v>4189.37</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4287.55</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4385.72</v>
-      </c>
-      <c r="O58" t="n">
-        <v>4376.2</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5229,13 +5229,13 @@
         <v>4095</v>
       </c>
       <c r="E57" t="n">
-        <v>4186.7</v>
+        <v>4181.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-29.6</v>
+        <v>-35.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.007</v>
+        <v>-0.0083</v>
       </c>
       <c r="H57" t="n">
         <v>147.3</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5229,13 +5229,13 @@
         <v>4095</v>
       </c>
       <c r="E57" t="n">
-        <v>4181.1</v>
+        <v>4202.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-35.2</v>
+        <v>-14.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0034</v>
       </c>
       <c r="H57" t="n">
         <v>147.3</v>
@@ -5274,9 +5274,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5229,13 +5229,13 @@
         <v>4095</v>
       </c>
       <c r="E57" t="n">
-        <v>4202.1</v>
+        <v>4194</v>
       </c>
       <c r="F57" t="n">
-        <v>-14.2</v>
+        <v>-22.3</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0053</v>
       </c>
       <c r="H57" t="n">
         <v>147.3</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5229,13 +5232,13 @@
         <v>4095</v>
       </c>
       <c r="E57" t="n">
-        <v>4194</v>
+        <v>4181.1</v>
       </c>
       <c r="F57" t="n">
-        <v>-22.3</v>
+        <v>-35.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0053</v>
+        <v>-0.0083</v>
       </c>
       <c r="H57" t="n">
         <v>147.3</v>
@@ -5274,9 +5277,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5296,6 +5299,90 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4162.4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4163.3</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4148.6</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3947.7</v>
+      </c>
+      <c r="J58" t="n">
+        <v>4040.03</v>
+      </c>
+      <c r="K58" t="n">
+        <v>4107.45</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4174.88</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4254.75</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4334.62</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4389.6</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5315,7 +5315,7 @@
         <v>4163.3</v>
       </c>
       <c r="D58" t="n">
-        <v>4148.6</v>
+        <v>4134.5</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5327,7 +5327,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>14.7</v>
+        <v>28.8</v>
       </c>
       <c r="I58" t="n">
         <v>3947.7</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5309,25 +5306,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4162.4</v>
+        <v>4185</v>
       </c>
       <c r="C58" t="n">
-        <v>4163.3</v>
+        <v>4211.2</v>
       </c>
       <c r="D58" t="n">
-        <v>4134.5</v>
+        <v>4124.4</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>4127</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-54.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0129</v>
       </c>
       <c r="H58" t="n">
-        <v>28.8</v>
+        <v>86.8</v>
       </c>
       <c r="I58" t="n">
         <v>3947.7</v>
@@ -5350,20 +5347,20 @@
       <c r="O58" t="n">
         <v>4389.6</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>106.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3577</v>
+        <v>3601.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3624.08</v>
+        <v>3654.57</v>
       </c>
       <c r="K2" t="n">
-        <v>3664.05</v>
+        <v>3676.25</v>
       </c>
       <c r="L2" t="n">
-        <v>3704.03</v>
+        <v>3697.93</v>
       </c>
       <c r="M2" t="n">
-        <v>3747.55</v>
+        <v>3735.35</v>
       </c>
       <c r="N2" t="n">
-        <v>3791.08</v>
+        <v>3772.78</v>
       </c>
       <c r="O2" t="n">
-        <v>3827.5</v>
+        <v>3778.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,11 +700,13 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5312,19 +5314,19 @@
         <v>4211.2</v>
       </c>
       <c r="D58" t="n">
-        <v>4124.4</v>
+        <v>4127.2</v>
       </c>
       <c r="E58" t="n">
-        <v>4127</v>
+        <v>4128.1</v>
       </c>
       <c r="F58" t="n">
-        <v>-54.1</v>
+        <v>-53</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0127</v>
       </c>
       <c r="H58" t="n">
-        <v>86.8</v>
+        <v>84</v>
       </c>
       <c r="I58" t="n">
         <v>3947.7</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5314,19 +5314,19 @@
         <v>4211.2</v>
       </c>
       <c r="D58" t="n">
-        <v>4127.2</v>
+        <v>4116.2</v>
       </c>
       <c r="E58" t="n">
-        <v>4128.1</v>
+        <v>4122.3</v>
       </c>
       <c r="F58" t="n">
-        <v>-53</v>
+        <v>-58.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.0141</v>
       </c>
       <c r="H58" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I58" t="n">
         <v>3947.7</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>106.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3601.4</v>
+        <v>3609.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3654.57</v>
+        <v>3657.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3676.25</v>
+        <v>3678.2</v>
       </c>
       <c r="L2" t="n">
-        <v>3697.93</v>
+        <v>3698.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3735.35</v>
+        <v>3733.4</v>
       </c>
       <c r="N2" t="n">
-        <v>3772.78</v>
+        <v>3767.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3778.7</v>
+        <v>3774.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5314,19 +5314,19 @@
         <v>4211.2</v>
       </c>
       <c r="D58" t="n">
-        <v>4116.2</v>
+        <v>4028.7</v>
       </c>
       <c r="E58" t="n">
-        <v>4122.3</v>
+        <v>4034.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-58.8</v>
+        <v>-146.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.035</v>
       </c>
       <c r="H58" t="n">
-        <v>95</v>
+        <v>182.5</v>
       </c>
       <c r="I58" t="n">
         <v>3947.7</v>
@@ -5352,12 +5352,14 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
@@ -5379,11 +5381,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3721.3</v>
+        <v>3788.8</v>
       </c>
       <c r="C2" t="n">
-        <v>3824.6</v>
+        <v>3923.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3718.1</v>
+        <v>3785.5</v>
       </c>
       <c r="E2" t="n">
-        <v>3809</v>
+        <v>3908.9</v>
       </c>
       <c r="F2" t="n">
-        <v>103.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0278</v>
+        <v>0.0262</v>
       </c>
       <c r="H2" t="n">
-        <v>106.5</v>
+        <v>137.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3609.2</v>
+        <v>3611.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3657.5</v>
+        <v>3721.32</v>
       </c>
       <c r="K2" t="n">
-        <v>3678.2</v>
+        <v>3755.75</v>
       </c>
       <c r="L2" t="n">
-        <v>3698.9</v>
+        <v>3790.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3733.4</v>
+        <v>3862.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3767.9</v>
+        <v>3934.32</v>
       </c>
       <c r="O2" t="n">
-        <v>3774.8</v>
+        <v>3931.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,10 +698,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="inlineStr">
         <is>
@@ -718,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3788.8</v>
+        <v>3913.5</v>
       </c>
       <c r="C3" t="n">
-        <v>3923.3</v>
+        <v>4081</v>
       </c>
       <c r="D3" t="n">
-        <v>3785.5</v>
+        <v>3909.2</v>
       </c>
       <c r="E3" t="n">
-        <v>3908.9</v>
+        <v>4000.4</v>
       </c>
       <c r="F3" t="n">
-        <v>99.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0262</v>
+        <v>0.0234</v>
       </c>
       <c r="H3" t="n">
-        <v>137.8</v>
+        <v>171.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3611.6</v>
+        <v>3647.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3721.32</v>
+        <v>3798.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3755.75</v>
+        <v>3840</v>
       </c>
       <c r="L3" t="n">
-        <v>3790.18</v>
+        <v>3881.65</v>
       </c>
       <c r="M3" t="n">
-        <v>3862.25</v>
+        <v>3977.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3934.32</v>
+        <v>4073.95</v>
       </c>
       <c r="O3" t="n">
-        <v>3931.1</v>
+        <v>4061.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,15 +777,17 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
@@ -800,50 +800,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3913.5</v>
+        <v>4018.3</v>
       </c>
       <c r="C4" t="n">
-        <v>4081</v>
+        <v>4392</v>
       </c>
       <c r="D4" t="n">
-        <v>3909.2</v>
+        <v>4011.3</v>
       </c>
       <c r="E4" t="n">
-        <v>4000.4</v>
+        <v>4213.3</v>
       </c>
       <c r="F4" t="n">
-        <v>91.5</v>
+        <v>212.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0532</v>
       </c>
       <c r="H4" t="n">
-        <v>171.8</v>
+        <v>380.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3647.7</v>
+        <v>3737.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3798.35</v>
+        <v>3831.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3840</v>
+        <v>3914.5</v>
       </c>
       <c r="L4" t="n">
-        <v>3881.65</v>
+        <v>3997.75</v>
       </c>
       <c r="M4" t="n">
-        <v>3977.8</v>
+        <v>4086.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4073.95</v>
+        <v>4174.85</v>
       </c>
       <c r="O4" t="n">
-        <v>4061.1</v>
+        <v>4252.8</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -861,12 +861,12 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V4" s="8" t="inlineStr">
@@ -884,50 +884,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4018.3</v>
+        <v>4269</v>
       </c>
       <c r="C5" t="n">
-        <v>4392</v>
+        <v>4398</v>
       </c>
       <c r="D5" t="n">
-        <v>4011.3</v>
+        <v>4021.2</v>
       </c>
       <c r="E5" t="n">
-        <v>4213.3</v>
+        <v>4137.8</v>
       </c>
       <c r="F5" t="n">
-        <v>212.9</v>
+        <v>-75.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0532</v>
+        <v>-0.0179</v>
       </c>
       <c r="H5" t="n">
-        <v>380.7</v>
+        <v>376.8</v>
       </c>
       <c r="I5" t="n">
-        <v>3737.4</v>
+        <v>3630.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3831.25</v>
+        <v>3838.42</v>
       </c>
       <c r="K5" t="n">
-        <v>3914.5</v>
+        <v>4022.95</v>
       </c>
       <c r="L5" t="n">
-        <v>3997.75</v>
+        <v>4207.47</v>
       </c>
       <c r="M5" t="n">
-        <v>4086.3</v>
+        <v>4403.65</v>
       </c>
       <c r="N5" t="n">
-        <v>4174.85</v>
+        <v>4599.82</v>
       </c>
       <c r="O5" t="n">
-        <v>4252.8</v>
+        <v>4772.7</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,83 +935,83 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4269</v>
+        <v>4103.2</v>
       </c>
       <c r="C6" t="n">
-        <v>4398</v>
+        <v>4123.8</v>
       </c>
       <c r="D6" t="n">
-        <v>4021.2</v>
+        <v>3901.3</v>
       </c>
       <c r="E6" t="n">
-        <v>4137.8</v>
+        <v>3996.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-75.5</v>
+        <v>-141.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0179</v>
+        <v>-0.0341</v>
       </c>
       <c r="H6" t="n">
-        <v>376.8</v>
+        <v>222.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3630.6</v>
+        <v>3644.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3838.42</v>
+        <v>3725.1</v>
       </c>
       <c r="K6" t="n">
-        <v>4022.95</v>
+        <v>3949.4</v>
       </c>
       <c r="L6" t="n">
-        <v>4207.47</v>
+        <v>4173.7</v>
       </c>
       <c r="M6" t="n">
-        <v>4403.65</v>
+        <v>4326.2</v>
       </c>
       <c r="N6" t="n">
-        <v>4599.82</v>
+        <v>4478.7</v>
       </c>
       <c r="O6" t="n">
-        <v>4772.7</v>
+        <v>4774.8</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1045,57 +1045,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4103.2</v>
+        <v>4001</v>
       </c>
       <c r="C7" t="n">
-        <v>4123.8</v>
+        <v>4043.1</v>
       </c>
       <c r="D7" t="n">
-        <v>3901.3</v>
+        <v>3935.7</v>
       </c>
       <c r="E7" t="n">
-        <v>3996.5</v>
+        <v>4009.8</v>
       </c>
       <c r="F7" t="n">
-        <v>-141.3</v>
+        <v>13.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0341</v>
+        <v>0.0033</v>
       </c>
       <c r="H7" t="n">
-        <v>222.5</v>
+        <v>107.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3644.4</v>
+        <v>3678.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3725.1</v>
+        <v>3765.98</v>
       </c>
       <c r="K7" t="n">
-        <v>3949.4</v>
+        <v>3885.25</v>
       </c>
       <c r="L7" t="n">
-        <v>4173.7</v>
+        <v>4004.52</v>
       </c>
       <c r="M7" t="n">
-        <v>4326.2</v>
+        <v>4107.75</v>
       </c>
       <c r="N7" t="n">
-        <v>4478.7</v>
+        <v>4210.97</v>
       </c>
       <c r="O7" t="n">
-        <v>4774.8</v>
+        <v>4346.3</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,14 +1103,12 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1129,57 +1127,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4001</v>
+        <v>4007.2</v>
       </c>
       <c r="C8" t="n">
-        <v>4043.1</v>
+        <v>4250</v>
       </c>
       <c r="D8" t="n">
-        <v>3935.7</v>
+        <v>4004.2</v>
       </c>
       <c r="E8" t="n">
-        <v>4009.8</v>
+        <v>4094.2</v>
       </c>
       <c r="F8" t="n">
-        <v>13.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.021</v>
       </c>
       <c r="H8" t="n">
-        <v>107.4</v>
+        <v>245.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3678.8</v>
+        <v>3828.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3765.98</v>
+        <v>3912.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3885.25</v>
+        <v>3956.1</v>
       </c>
       <c r="L8" t="n">
-        <v>4004.52</v>
+        <v>3999.6</v>
       </c>
       <c r="M8" t="n">
-        <v>4107.75</v>
+        <v>4063.5</v>
       </c>
       <c r="N8" t="n">
-        <v>4210.97</v>
+        <v>4127.4</v>
       </c>
       <c r="O8" t="n">
-        <v>4346.3</v>
+        <v>4150.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1192,76 +1190,78 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4007.2</v>
+        <v>4084.4</v>
       </c>
       <c r="C9" t="n">
-        <v>4250</v>
+        <v>4134.3</v>
       </c>
       <c r="D9" t="n">
-        <v>4004.2</v>
+        <v>3997.4</v>
       </c>
       <c r="E9" t="n">
-        <v>4094.2</v>
+        <v>4079.5</v>
       </c>
       <c r="F9" t="n">
-        <v>84.40000000000001</v>
+        <v>-14.7</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.0036</v>
       </c>
       <c r="H9" t="n">
-        <v>245.8</v>
+        <v>136.9</v>
       </c>
       <c r="I9" t="n">
-        <v>3828.3</v>
+        <v>3758.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3912.6</v>
+        <v>3831.95</v>
       </c>
       <c r="K9" t="n">
-        <v>3956.1</v>
+        <v>3971.3</v>
       </c>
       <c r="L9" t="n">
-        <v>3999.6</v>
+        <v>4110.65</v>
       </c>
       <c r="M9" t="n">
-        <v>4063.5</v>
+        <v>4217.1</v>
       </c>
       <c r="N9" t="n">
-        <v>4127.4</v>
+        <v>4323.55</v>
       </c>
       <c r="O9" t="n">
-        <v>4150.5</v>
+        <v>4495.8</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,80 +1272,78 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4084.4</v>
+        <v>4069.2</v>
       </c>
       <c r="C10" t="n">
-        <v>4134.3</v>
+        <v>4263.1</v>
       </c>
       <c r="D10" t="n">
-        <v>3997.4</v>
+        <v>4036.4</v>
       </c>
       <c r="E10" t="n">
-        <v>4079.5</v>
+        <v>4254.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-14.7</v>
+        <v>175.4</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.043</v>
       </c>
       <c r="H10" t="n">
-        <v>136.9</v>
+        <v>226.7</v>
       </c>
       <c r="I10" t="n">
-        <v>3758.4</v>
+        <v>3860.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3831.95</v>
+        <v>3949.43</v>
       </c>
       <c r="K10" t="n">
-        <v>3971.3</v>
+        <v>4011.05</v>
       </c>
       <c r="L10" t="n">
-        <v>4110.65</v>
+        <v>4072.67</v>
       </c>
       <c r="M10" t="n">
-        <v>4217.1</v>
+        <v>4147.95</v>
       </c>
       <c r="N10" t="n">
-        <v>4323.55</v>
+        <v>4223.22</v>
       </c>
       <c r="O10" t="n">
-        <v>4495.8</v>
+        <v>4271.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,78 +1354,80 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4069.2</v>
+        <v>4258.5</v>
       </c>
       <c r="C11" t="n">
-        <v>4263.1</v>
+        <v>4299.6</v>
       </c>
       <c r="D11" t="n">
-        <v>4036.4</v>
+        <v>4194</v>
       </c>
       <c r="E11" t="n">
-        <v>4254.9</v>
+        <v>4243</v>
       </c>
       <c r="F11" t="n">
-        <v>175.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.043</v>
+        <v>-0.0028</v>
       </c>
       <c r="H11" t="n">
-        <v>226.7</v>
+        <v>105.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3860.5</v>
+        <v>3809.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3949.43</v>
+        <v>4080.77</v>
       </c>
       <c r="K11" t="n">
-        <v>4011.05</v>
+        <v>4141.55</v>
       </c>
       <c r="L11" t="n">
-        <v>4072.67</v>
+        <v>4202.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4147.95</v>
+        <v>4368.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4223.22</v>
+        <v>4534.18</v>
       </c>
       <c r="O11" t="n">
-        <v>4271.2</v>
+        <v>4489.8</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,78 +1440,76 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4258.5</v>
+        <v>4228.1</v>
       </c>
       <c r="C12" t="n">
-        <v>4299.6</v>
+        <v>4387.8</v>
       </c>
       <c r="D12" t="n">
-        <v>4194</v>
+        <v>4197.8</v>
       </c>
       <c r="E12" t="n">
-        <v>4243</v>
+        <v>4328.3</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.9</v>
+        <v>85.3</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0201</v>
       </c>
       <c r="H12" t="n">
-        <v>105.6</v>
+        <v>190</v>
       </c>
       <c r="I12" t="n">
-        <v>3809.7</v>
+        <v>4088.4</v>
       </c>
       <c r="J12" t="n">
-        <v>4080.77</v>
+        <v>4135.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4141.55</v>
+        <v>4190.2</v>
       </c>
       <c r="L12" t="n">
-        <v>4202.32</v>
+        <v>4244.9</v>
       </c>
       <c r="M12" t="n">
-        <v>4368.25</v>
+        <v>4295.8</v>
       </c>
       <c r="N12" t="n">
-        <v>4534.18</v>
+        <v>4346.7</v>
       </c>
       <c r="O12" t="n">
-        <v>4489.8</v>
+        <v>4405.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,14 +1522,18 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1541,59 +1543,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4228.1</v>
+        <v>4330</v>
       </c>
       <c r="C13" t="n">
-        <v>4387.8</v>
+        <v>4409.5</v>
       </c>
       <c r="D13" t="n">
-        <v>4197.8</v>
+        <v>4297.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4328.3</v>
+        <v>4387.3</v>
       </c>
       <c r="F13" t="n">
-        <v>85.3</v>
+        <v>59</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0136</v>
       </c>
       <c r="H13" t="n">
-        <v>190</v>
+        <v>112.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4088.4</v>
+        <v>4007.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4135.5</v>
+        <v>4156.05</v>
       </c>
       <c r="K13" t="n">
-        <v>4190.2</v>
+        <v>4233.3</v>
       </c>
       <c r="L13" t="n">
-        <v>4244.9</v>
+        <v>4310.55</v>
       </c>
       <c r="M13" t="n">
-        <v>4295.8</v>
+        <v>4423.3</v>
       </c>
       <c r="N13" t="n">
-        <v>4346.7</v>
+        <v>4536.05</v>
       </c>
       <c r="O13" t="n">
-        <v>4405.2</v>
+        <v>4577.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1611,13 +1609,11 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1632,50 +1628,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4330</v>
+        <v>4369.9</v>
       </c>
       <c r="C14" t="n">
-        <v>4409.5</v>
+        <v>4584</v>
       </c>
       <c r="D14" t="n">
-        <v>4297.4</v>
+        <v>4367.9</v>
       </c>
       <c r="E14" t="n">
-        <v>4387.3</v>
+        <v>4552.7</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>165.4</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0377</v>
       </c>
       <c r="H14" t="n">
-        <v>112.1</v>
+        <v>216.1</v>
       </c>
       <c r="I14" t="n">
-        <v>4007.8</v>
+        <v>4185.3</v>
       </c>
       <c r="J14" t="n">
-        <v>4156.05</v>
+        <v>4292.12</v>
       </c>
       <c r="K14" t="n">
-        <v>4233.3</v>
+        <v>4331.25</v>
       </c>
       <c r="L14" t="n">
-        <v>4310.55</v>
+        <v>4370.37</v>
       </c>
       <c r="M14" t="n">
-        <v>4423.3</v>
+        <v>4443.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4536.05</v>
+        <v>4516.32</v>
       </c>
       <c r="O14" t="n">
-        <v>4577.8</v>
+        <v>4521.6</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,14 +1689,18 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1712,83 +1712,81 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4369.9</v>
+        <v>4568</v>
       </c>
       <c r="C15" t="n">
-        <v>4584</v>
+        <v>4581.3</v>
       </c>
       <c r="D15" t="n">
-        <v>4367.9</v>
+        <v>4284.3</v>
       </c>
       <c r="E15" t="n">
-        <v>4552.7</v>
+        <v>4329.6</v>
       </c>
       <c r="F15" t="n">
-        <v>165.4</v>
+        <v>-223.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.049</v>
       </c>
       <c r="H15" t="n">
-        <v>216.1</v>
+        <v>297</v>
       </c>
       <c r="I15" t="n">
-        <v>4185.3</v>
+        <v>4151.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4292.12</v>
+        <v>4374.98</v>
       </c>
       <c r="K15" t="n">
-        <v>4331.25</v>
+        <v>4444.65</v>
       </c>
       <c r="L15" t="n">
-        <v>4370.37</v>
+        <v>4514.33</v>
       </c>
       <c r="M15" t="n">
-        <v>4443.35</v>
+        <v>4660.75</v>
       </c>
       <c r="N15" t="n">
-        <v>4516.32</v>
+        <v>4807.18</v>
       </c>
       <c r="O15" t="n">
-        <v>4521.6</v>
+        <v>4800.1</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1796,72 +1794,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4568</v>
+        <v>4368.3</v>
       </c>
       <c r="C16" t="n">
-        <v>4581.3</v>
+        <v>4527</v>
       </c>
       <c r="D16" t="n">
-        <v>4284.3</v>
+        <v>4354.6</v>
       </c>
       <c r="E16" t="n">
-        <v>4329.6</v>
+        <v>4500.9</v>
       </c>
       <c r="F16" t="n">
-        <v>-223.1</v>
+        <v>171.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.049</v>
+        <v>0.0396</v>
       </c>
       <c r="H16" t="n">
-        <v>297</v>
+        <v>172.4</v>
       </c>
       <c r="I16" t="n">
-        <v>4151.8</v>
+        <v>3987.3</v>
       </c>
       <c r="J16" t="n">
-        <v>4374.98</v>
+        <v>3981</v>
       </c>
       <c r="K16" t="n">
-        <v>4444.65</v>
+        <v>4181.1</v>
       </c>
       <c r="L16" t="n">
-        <v>4514.33</v>
+        <v>4381.2</v>
       </c>
       <c r="M16" t="n">
-        <v>4660.75</v>
+        <v>4478.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4807.18</v>
+        <v>4575</v>
       </c>
       <c r="O16" t="n">
-        <v>4800.1</v>
+        <v>4878.3</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1873,55 +1869,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4368.3</v>
+        <v>4529.1</v>
       </c>
       <c r="C17" t="n">
-        <v>4527</v>
+        <v>4650.5</v>
       </c>
       <c r="D17" t="n">
-        <v>4354.6</v>
+        <v>4520.8</v>
       </c>
       <c r="E17" t="n">
-        <v>4500.9</v>
+        <v>4595.4</v>
       </c>
       <c r="F17" t="n">
-        <v>171.3</v>
+        <v>94.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.021</v>
       </c>
       <c r="H17" t="n">
-        <v>172.4</v>
+        <v>129.7</v>
       </c>
       <c r="I17" t="n">
-        <v>3987.3</v>
+        <v>4182.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3981</v>
+        <v>4358.55</v>
       </c>
       <c r="K17" t="n">
-        <v>4181.1</v>
+        <v>4414.7</v>
       </c>
       <c r="L17" t="n">
-        <v>4381.2</v>
+        <v>4470.85</v>
       </c>
       <c r="M17" t="n">
-        <v>4478.1</v>
+        <v>4587.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4575</v>
+        <v>4703.35</v>
       </c>
       <c r="O17" t="n">
-        <v>4878.3</v>
+        <v>4699.4</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1955,57 +1955,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4529.1</v>
+        <v>4633.7</v>
       </c>
       <c r="C18" t="n">
-        <v>4650.5</v>
+        <v>4991.4</v>
       </c>
       <c r="D18" t="n">
-        <v>4520.8</v>
+        <v>4622.2</v>
       </c>
       <c r="E18" t="n">
-        <v>4595.4</v>
+        <v>4979.7</v>
       </c>
       <c r="F18" t="n">
-        <v>94.5</v>
+        <v>384.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.021</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>129.7</v>
+        <v>369.2</v>
       </c>
       <c r="I18" t="n">
-        <v>4182.2</v>
+        <v>4391.1</v>
       </c>
       <c r="J18" t="n">
-        <v>4358.55</v>
+        <v>4470.57</v>
       </c>
       <c r="K18" t="n">
-        <v>4414.7</v>
+        <v>4530.55</v>
       </c>
       <c r="L18" t="n">
-        <v>4470.85</v>
+        <v>4590.52</v>
       </c>
       <c r="M18" t="n">
-        <v>4587.1</v>
+        <v>4660.25</v>
       </c>
       <c r="N18" t="n">
-        <v>4703.35</v>
+        <v>4729.98</v>
       </c>
       <c r="O18" t="n">
-        <v>4699.4</v>
+        <v>4780.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2023,86 +2023,90 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4633.7</v>
+        <v>5013.4</v>
       </c>
       <c r="C19" t="n">
-        <v>4991.4</v>
+        <v>5586.2</v>
       </c>
       <c r="D19" t="n">
-        <v>4622.2</v>
+        <v>4700.4</v>
       </c>
       <c r="E19" t="n">
-        <v>4979.7</v>
+        <v>4745.1</v>
       </c>
       <c r="F19" t="n">
-        <v>384.3</v>
+        <v>-234.6</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.0471</v>
       </c>
       <c r="H19" t="n">
-        <v>369.2</v>
+        <v>885.8</v>
       </c>
       <c r="I19" t="n">
-        <v>4391.1</v>
+        <v>4253</v>
       </c>
       <c r="J19" t="n">
-        <v>4470.57</v>
+        <v>4696.95</v>
       </c>
       <c r="K19" t="n">
-        <v>4530.55</v>
+        <v>4795.1</v>
       </c>
       <c r="L19" t="n">
-        <v>4590.52</v>
+        <v>4893.25</v>
       </c>
       <c r="M19" t="n">
-        <v>4660.25</v>
+        <v>5164.3</v>
       </c>
       <c r="N19" t="n">
-        <v>4729.98</v>
+        <v>5435.35</v>
       </c>
       <c r="O19" t="n">
-        <v>4780.2</v>
+        <v>5360.6</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2117,7 +2121,7 @@
       </c>
       <c r="V19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
@@ -2125,88 +2129,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5013.4</v>
+        <v>4816</v>
       </c>
       <c r="C20" t="n">
-        <v>5586.2</v>
+        <v>5113.9</v>
       </c>
       <c r="D20" t="n">
-        <v>4700.4</v>
+        <v>4423.2</v>
       </c>
       <c r="E20" t="n">
-        <v>4745.1</v>
+        <v>4979.8</v>
       </c>
       <c r="F20" t="n">
-        <v>-234.6</v>
+        <v>234.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0471</v>
+        <v>0.0495</v>
       </c>
       <c r="H20" t="n">
-        <v>885.8</v>
+        <v>690.7</v>
       </c>
       <c r="I20" t="n">
-        <v>4253</v>
+        <v>3814.6</v>
       </c>
       <c r="J20" t="n">
-        <v>4696.95</v>
+        <v>3660.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4795.1</v>
+        <v>4302.2</v>
       </c>
       <c r="L20" t="n">
-        <v>4893.25</v>
+        <v>4944.2</v>
       </c>
       <c r="M20" t="n">
-        <v>5164.3</v>
+        <v>5188</v>
       </c>
       <c r="N20" t="n">
-        <v>5435.35</v>
+        <v>5431.8</v>
       </c>
       <c r="O20" t="n">
-        <v>5360.6</v>
+        <v>6472</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2215,57 +2213,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4816</v>
+        <v>5003.6</v>
       </c>
       <c r="C21" t="n">
-        <v>5113.9</v>
+        <v>5144.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4423.2</v>
+        <v>4900</v>
       </c>
       <c r="E21" t="n">
-        <v>4979.8</v>
+        <v>5046.3</v>
       </c>
       <c r="F21" t="n">
-        <v>234.7</v>
+        <v>66.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0495</v>
+        <v>0.0134</v>
       </c>
       <c r="H21" t="n">
-        <v>690.7</v>
+        <v>244.5</v>
       </c>
       <c r="I21" t="n">
-        <v>3814.6</v>
+        <v>3732.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3660.2</v>
+        <v>4394.72</v>
       </c>
       <c r="K21" t="n">
-        <v>4302.2</v>
+        <v>4634.45</v>
       </c>
       <c r="L21" t="n">
-        <v>4944.2</v>
+        <v>4874.17</v>
       </c>
       <c r="M21" t="n">
-        <v>5188</v>
+        <v>5325.15</v>
       </c>
       <c r="N21" t="n">
-        <v>5431.8</v>
+        <v>5776.12</v>
       </c>
       <c r="O21" t="n">
-        <v>6472</v>
+        <v>5804.6</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2295,59 +2293,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5003.6</v>
+        <v>5050</v>
       </c>
       <c r="C22" t="n">
-        <v>5144.5</v>
+        <v>5131</v>
       </c>
       <c r="D22" t="n">
-        <v>4900</v>
+        <v>4854.2</v>
       </c>
       <c r="E22" t="n">
-        <v>5046.3</v>
+        <v>5080.9</v>
       </c>
       <c r="F22" t="n">
-        <v>66.5</v>
+        <v>34.6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0069</v>
       </c>
       <c r="H22" t="n">
-        <v>244.5</v>
+        <v>276.8</v>
       </c>
       <c r="I22" t="n">
-        <v>3732.5</v>
+        <v>4655.5</v>
       </c>
       <c r="J22" t="n">
-        <v>4394.72</v>
+        <v>4813.82</v>
       </c>
       <c r="K22" t="n">
-        <v>4634.45</v>
+        <v>4924.05</v>
       </c>
       <c r="L22" t="n">
-        <v>4874.17</v>
+        <v>5034.27</v>
       </c>
       <c r="M22" t="n">
-        <v>5325.15</v>
+        <v>5168.55</v>
       </c>
       <c r="N22" t="n">
-        <v>5776.12</v>
+        <v>5302.82</v>
       </c>
       <c r="O22" t="n">
-        <v>5804.6</v>
+        <v>5389</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,8 +2349,10 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
@@ -2377,55 +2373,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5050</v>
+        <v>5128.8</v>
       </c>
       <c r="C23" t="n">
-        <v>5131</v>
+        <v>5299</v>
       </c>
       <c r="D23" t="n">
-        <v>4854.2</v>
+        <v>5109.5</v>
       </c>
       <c r="E23" t="n">
-        <v>5080.9</v>
+        <v>5247.9</v>
       </c>
       <c r="F23" t="n">
-        <v>34.6</v>
+        <v>167</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0329</v>
       </c>
       <c r="H23" t="n">
-        <v>276.8</v>
+        <v>189.5</v>
       </c>
       <c r="I23" t="n">
-        <v>4655.5</v>
+        <v>4577.4</v>
       </c>
       <c r="J23" t="n">
-        <v>4813.82</v>
+        <v>4848.25</v>
       </c>
       <c r="K23" t="n">
-        <v>4924.05</v>
+        <v>4942.5</v>
       </c>
       <c r="L23" t="n">
-        <v>5034.27</v>
+        <v>5036.75</v>
       </c>
       <c r="M23" t="n">
-        <v>5168.55</v>
+        <v>5219.3</v>
       </c>
       <c r="N23" t="n">
-        <v>5302.82</v>
+        <v>5401.85</v>
       </c>
       <c r="O23" t="n">
-        <v>5389</v>
+        <v>5407.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2433,18 +2433,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2457,77 +2457,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5128.8</v>
+        <v>5360</v>
       </c>
       <c r="C24" t="n">
-        <v>5299</v>
+        <v>5434.1</v>
       </c>
       <c r="D24" t="n">
-        <v>5109.5</v>
+        <v>5005</v>
       </c>
       <c r="E24" t="n">
-        <v>5247.9</v>
+        <v>5158.7</v>
       </c>
       <c r="F24" t="n">
-        <v>167</v>
+        <v>-89.2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0329</v>
+        <v>-0.017</v>
       </c>
       <c r="H24" t="n">
-        <v>189.5</v>
+        <v>429.1</v>
       </c>
       <c r="I24" t="n">
-        <v>4577.4</v>
+        <v>4920</v>
       </c>
       <c r="J24" t="n">
-        <v>4848.25</v>
+        <v>5080.22</v>
       </c>
       <c r="K24" t="n">
-        <v>4942.5</v>
+        <v>5153.15</v>
       </c>
       <c r="L24" t="n">
-        <v>5036.75</v>
+        <v>5226.07</v>
       </c>
       <c r="M24" t="n">
-        <v>5219.3</v>
+        <v>5342.65</v>
       </c>
       <c r="N24" t="n">
-        <v>5401.85</v>
+        <v>5459.22</v>
       </c>
       <c r="O24" t="n">
-        <v>5407.8</v>
+        <v>5488.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U24" s="8" t="n">
@@ -2541,63 +2541,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5360</v>
+        <v>5186.7</v>
       </c>
       <c r="C25" t="n">
-        <v>5434.1</v>
+        <v>5248.7</v>
       </c>
       <c r="D25" t="n">
-        <v>5005</v>
+        <v>5014.1</v>
       </c>
       <c r="E25" t="n">
-        <v>5158.7</v>
+        <v>5061.7</v>
       </c>
       <c r="F25" t="n">
-        <v>-89.2</v>
+        <v>-97</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0188</v>
       </c>
       <c r="H25" t="n">
-        <v>429.1</v>
+        <v>234.6</v>
       </c>
       <c r="I25" t="n">
-        <v>4920</v>
+        <v>4575.9</v>
       </c>
       <c r="J25" t="n">
-        <v>5080.22</v>
+        <v>4699.18</v>
       </c>
       <c r="K25" t="n">
-        <v>5153.15</v>
+        <v>4944.15</v>
       </c>
       <c r="L25" t="n">
-        <v>5226.07</v>
+        <v>5189.13</v>
       </c>
       <c r="M25" t="n">
-        <v>5342.65</v>
+        <v>5373.25</v>
       </c>
       <c r="N25" t="n">
-        <v>5459.22</v>
+        <v>5557.38</v>
       </c>
       <c r="O25" t="n">
-        <v>5488.5</v>
+        <v>5863.2</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q25" s="6" t="n">
+        <v/>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2609,10 +2611,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2634,60 +2634,64 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5186.7</v>
+        <v>5010</v>
       </c>
       <c r="C26" t="n">
-        <v>5248.7</v>
+        <v>5049.4</v>
       </c>
       <c r="D26" t="n">
-        <v>5014.1</v>
+        <v>4478.4</v>
       </c>
       <c r="E26" t="n">
-        <v>5061.7</v>
+        <v>4574.9</v>
       </c>
       <c r="F26" t="n">
-        <v>-97</v>
+        <v>-486.8</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0188</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>234.6</v>
+        <v>571</v>
       </c>
       <c r="I26" t="n">
-        <v>4575.9</v>
+        <v>4779.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4699.18</v>
+        <v>4792.25</v>
       </c>
       <c r="K26" t="n">
-        <v>4944.15</v>
+        <v>4944.4</v>
       </c>
       <c r="L26" t="n">
-        <v>5189.13</v>
+        <v>5096.55</v>
       </c>
       <c r="M26" t="n">
-        <v>5373.25</v>
+        <v>5179</v>
       </c>
       <c r="N26" t="n">
-        <v>5557.38</v>
+        <v>5261.45</v>
       </c>
       <c r="O26" t="n">
-        <v>5863.2</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+        <v>5483.3</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
@@ -2704,83 +2708,75 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5010</v>
+        <v>4450</v>
       </c>
       <c r="C27" t="n">
-        <v>5049.4</v>
+        <v>4601</v>
       </c>
       <c r="D27" t="n">
-        <v>4478.4</v>
+        <v>4100</v>
       </c>
       <c r="E27" t="n">
-        <v>4574.9</v>
+        <v>4492.5</v>
       </c>
       <c r="F27" t="n">
-        <v>-486.8</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="H27" t="n">
-        <v>571</v>
+        <v>501</v>
       </c>
       <c r="I27" t="n">
-        <v>4779.5</v>
+        <v>3907.4</v>
       </c>
       <c r="J27" t="n">
-        <v>4792.25</v>
+        <v>3909.4</v>
       </c>
       <c r="K27" t="n">
-        <v>4944.4</v>
+        <v>4289.4</v>
       </c>
       <c r="L27" t="n">
-        <v>5096.55</v>
+        <v>4669.4</v>
       </c>
       <c r="M27" t="n">
-        <v>5179</v>
+        <v>4860.4</v>
       </c>
       <c r="N27" t="n">
-        <v>5261.45</v>
+        <v>5051.4</v>
       </c>
       <c r="O27" t="n">
-        <v>5483.3</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
+        <v>5620.4</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2802,50 +2798,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4450</v>
+        <v>4482.8</v>
       </c>
       <c r="C28" t="n">
-        <v>4601</v>
+        <v>4825.9</v>
       </c>
       <c r="D28" t="n">
-        <v>4100</v>
+        <v>4413.4</v>
       </c>
       <c r="E28" t="n">
-        <v>4492.5</v>
+        <v>4679.7</v>
       </c>
       <c r="F28" t="n">
-        <v>-82.40000000000001</v>
+        <v>187.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0417</v>
       </c>
       <c r="H28" t="n">
-        <v>501</v>
+        <v>412.5</v>
       </c>
       <c r="I28" t="n">
-        <v>3907.4</v>
+        <v>3599</v>
       </c>
       <c r="J28" t="n">
-        <v>3909.4</v>
+        <v>4062.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4289.4</v>
+        <v>4242</v>
       </c>
       <c r="L28" t="n">
-        <v>4669.4</v>
+        <v>4421.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4860.4</v>
+        <v>4743</v>
       </c>
       <c r="N28" t="n">
-        <v>5051.4</v>
+        <v>5064.5</v>
       </c>
       <c r="O28" t="n">
-        <v>5620.4</v>
+        <v>5102</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2853,18 +2849,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2877,55 +2873,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4482.8</v>
+        <v>4675</v>
       </c>
       <c r="C29" t="n">
-        <v>4825.9</v>
+        <v>4888</v>
       </c>
       <c r="D29" t="n">
-        <v>4413.4</v>
+        <v>4626.2</v>
       </c>
       <c r="E29" t="n">
-        <v>4679.7</v>
+        <v>4787.4</v>
       </c>
       <c r="F29" t="n">
-        <v>187.2</v>
+        <v>107.7</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0417</v>
+        <v>0.023</v>
       </c>
       <c r="H29" t="n">
-        <v>412.5</v>
+        <v>261.8</v>
       </c>
       <c r="I29" t="n">
-        <v>3599</v>
+        <v>4000.9</v>
       </c>
       <c r="J29" t="n">
-        <v>4062.5</v>
+        <v>4297.23</v>
       </c>
       <c r="K29" t="n">
-        <v>4242</v>
+        <v>4473.45</v>
       </c>
       <c r="L29" t="n">
-        <v>4421.5</v>
+        <v>4649.68</v>
       </c>
       <c r="M29" t="n">
-        <v>4743</v>
+        <v>4885.95</v>
       </c>
       <c r="N29" t="n">
-        <v>5064.5</v>
+        <v>5122.23</v>
       </c>
       <c r="O29" t="n">
-        <v>5102</v>
+        <v>5238.4</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2966,50 +2966,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4675</v>
+        <v>4710</v>
       </c>
       <c r="C30" t="n">
-        <v>4888</v>
+        <v>4917.7</v>
       </c>
       <c r="D30" t="n">
-        <v>4626.2</v>
+        <v>4626</v>
       </c>
       <c r="E30" t="n">
-        <v>4787.4</v>
+        <v>4879.6</v>
       </c>
       <c r="F30" t="n">
-        <v>107.7</v>
+        <v>92.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0193</v>
       </c>
       <c r="H30" t="n">
-        <v>261.8</v>
+        <v>291.7</v>
       </c>
       <c r="I30" t="n">
-        <v>4000.9</v>
+        <v>4364.4</v>
       </c>
       <c r="J30" t="n">
-        <v>4297.23</v>
+        <v>4540.75</v>
       </c>
       <c r="K30" t="n">
-        <v>4473.45</v>
+        <v>4656.5</v>
       </c>
       <c r="L30" t="n">
-        <v>4649.68</v>
+        <v>4772.25</v>
       </c>
       <c r="M30" t="n">
-        <v>4885.95</v>
+        <v>4918.3</v>
       </c>
       <c r="N30" t="n">
-        <v>5122.23</v>
+        <v>5064.35</v>
       </c>
       <c r="O30" t="n">
-        <v>5238.4</v>
+        <v>5149.8</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3017,8 +3017,10 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
@@ -3043,57 +3045,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4710</v>
+        <v>4811.8</v>
       </c>
       <c r="C31" t="n">
-        <v>4917.7</v>
+        <v>4854.8</v>
       </c>
       <c r="D31" t="n">
-        <v>4626</v>
+        <v>4672.2</v>
       </c>
       <c r="E31" t="n">
-        <v>4879.6</v>
+        <v>4740.9</v>
       </c>
       <c r="F31" t="n">
-        <v>92.2</v>
+        <v>-138.7</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0193</v>
+        <v>-0.0284</v>
       </c>
       <c r="H31" t="n">
-        <v>291.7</v>
+        <v>182.6</v>
       </c>
       <c r="I31" t="n">
-        <v>4364.4</v>
+        <v>4334.3</v>
       </c>
       <c r="J31" t="n">
-        <v>4540.75</v>
+        <v>4641.77</v>
       </c>
       <c r="K31" t="n">
-        <v>4656.5</v>
+        <v>4733.75</v>
       </c>
       <c r="L31" t="n">
-        <v>4772.25</v>
+        <v>4825.73</v>
       </c>
       <c r="M31" t="n">
-        <v>4918.3</v>
+        <v>5025.45</v>
       </c>
       <c r="N31" t="n">
-        <v>5064.35</v>
+        <v>5225.18</v>
       </c>
       <c r="O31" t="n">
-        <v>5149.8</v>
+        <v>5209.4</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3103,19 +3105,17 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3129,63 +3129,65 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4811.8</v>
+        <v>4713.1</v>
       </c>
       <c r="C32" t="n">
-        <v>4854.8</v>
+        <v>4745.8</v>
       </c>
       <c r="D32" t="n">
-        <v>4672.2</v>
+        <v>4522.2</v>
       </c>
       <c r="E32" t="n">
-        <v>4740.9</v>
+        <v>4644.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-138.7</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0284</v>
+        <v>-0.0203</v>
       </c>
       <c r="H32" t="n">
-        <v>182.6</v>
+        <v>223.6</v>
       </c>
       <c r="I32" t="n">
-        <v>4334.3</v>
+        <v>4489.6</v>
       </c>
       <c r="J32" t="n">
-        <v>4641.77</v>
+        <v>4547</v>
       </c>
       <c r="K32" t="n">
-        <v>4733.75</v>
+        <v>4649.6</v>
       </c>
       <c r="L32" t="n">
-        <v>4825.73</v>
+        <v>4752.2</v>
       </c>
       <c r="M32" t="n">
-        <v>5025.45</v>
+        <v>4832.2</v>
       </c>
       <c r="N32" t="n">
-        <v>5225.18</v>
+        <v>4912.2</v>
       </c>
       <c r="O32" t="n">
-        <v>5209.4</v>
+        <v>5037.4</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
@@ -3211,81 +3213,77 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4713.1</v>
+        <v>4644</v>
       </c>
       <c r="C33" t="n">
-        <v>4745.8</v>
+        <v>4775.2</v>
       </c>
       <c r="D33" t="n">
-        <v>4522.2</v>
+        <v>4510.1</v>
       </c>
       <c r="E33" t="n">
-        <v>4644.5</v>
+        <v>4730.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-96.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0186</v>
       </c>
       <c r="H33" t="n">
-        <v>223.6</v>
+        <v>265.1</v>
       </c>
       <c r="I33" t="n">
-        <v>4489.6</v>
+        <v>4298.6</v>
       </c>
       <c r="J33" t="n">
-        <v>4547</v>
+        <v>4426.15</v>
       </c>
       <c r="K33" t="n">
-        <v>4649.6</v>
+        <v>4532.7</v>
       </c>
       <c r="L33" t="n">
-        <v>4752.2</v>
+        <v>4639.25</v>
       </c>
       <c r="M33" t="n">
-        <v>4832.2</v>
+        <v>4756.3</v>
       </c>
       <c r="N33" t="n">
-        <v>4912.2</v>
+        <v>4873.35</v>
       </c>
       <c r="O33" t="n">
-        <v>5037.4</v>
+        <v>4969.4</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3297,55 +3295,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4644</v>
+        <v>4690</v>
       </c>
       <c r="C34" t="n">
-        <v>4775.2</v>
+        <v>4783.4</v>
       </c>
       <c r="D34" t="n">
-        <v>4510.1</v>
+        <v>4513.8</v>
       </c>
       <c r="E34" t="n">
-        <v>4730.7</v>
+        <v>4561.9</v>
       </c>
       <c r="F34" t="n">
-        <v>86.2</v>
+        <v>-168.8</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0357</v>
       </c>
       <c r="H34" t="n">
-        <v>265.1</v>
+        <v>269.6</v>
       </c>
       <c r="I34" t="n">
-        <v>4298.6</v>
+        <v>4245</v>
       </c>
       <c r="J34" t="n">
-        <v>4426.15</v>
+        <v>4509.63</v>
       </c>
       <c r="K34" t="n">
-        <v>4532.7</v>
+        <v>4598.15</v>
       </c>
       <c r="L34" t="n">
-        <v>4639.25</v>
+        <v>4686.68</v>
       </c>
       <c r="M34" t="n">
-        <v>4756.3</v>
+        <v>4863.25</v>
       </c>
       <c r="N34" t="n">
-        <v>4873.35</v>
+        <v>5039.83</v>
       </c>
       <c r="O34" t="n">
-        <v>4969.4</v>
+        <v>5040.3</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,18 +3357,16 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3388,50 +3388,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4690</v>
+        <v>4547.6</v>
       </c>
       <c r="C35" t="n">
-        <v>4783.4</v>
+        <v>4593.2</v>
       </c>
       <c r="D35" t="n">
-        <v>4513.8</v>
+        <v>4455</v>
       </c>
       <c r="E35" t="n">
-        <v>4561.9</v>
+        <v>4523.2</v>
       </c>
       <c r="F35" t="n">
-        <v>-168.8</v>
+        <v>-38.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0357</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>269.6</v>
+        <v>138.2</v>
       </c>
       <c r="I35" t="n">
-        <v>4245</v>
+        <v>4244.2</v>
       </c>
       <c r="J35" t="n">
-        <v>4509.63</v>
+        <v>4248.95</v>
       </c>
       <c r="K35" t="n">
-        <v>4598.15</v>
+        <v>4427.1</v>
       </c>
       <c r="L35" t="n">
-        <v>4686.68</v>
+        <v>4605.25</v>
       </c>
       <c r="M35" t="n">
-        <v>4863.25</v>
+        <v>4696.7</v>
       </c>
       <c r="N35" t="n">
-        <v>5039.83</v>
+        <v>4788.15</v>
       </c>
       <c r="O35" t="n">
-        <v>5040.3</v>
+        <v>5053</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3439,14 +3439,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3463,76 +3461,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4547.6</v>
+        <v>4532</v>
       </c>
       <c r="C36" t="n">
-        <v>4593.2</v>
+        <v>4627.1</v>
       </c>
       <c r="D36" t="n">
-        <v>4455</v>
+        <v>4363.5</v>
       </c>
       <c r="E36" t="n">
-        <v>4523.2</v>
+        <v>4593</v>
       </c>
       <c r="F36" t="n">
-        <v>-38.7</v>
+        <v>69.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H36" t="n">
-        <v>138.2</v>
+        <v>263.6</v>
       </c>
       <c r="I36" t="n">
-        <v>4244.2</v>
+        <v>4316.8</v>
       </c>
       <c r="J36" t="n">
-        <v>4248.95</v>
+        <v>4384.55</v>
       </c>
       <c r="K36" t="n">
-        <v>4427.1</v>
+        <v>4454.1</v>
       </c>
       <c r="L36" t="n">
-        <v>4605.25</v>
+        <v>4523.65</v>
       </c>
       <c r="M36" t="n">
-        <v>4696.7</v>
+        <v>4592.3</v>
       </c>
       <c r="N36" t="n">
-        <v>4788.15</v>
+        <v>4660.95</v>
       </c>
       <c r="O36" t="n">
-        <v>5053</v>
+        <v>4731.4</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3545,78 +3545,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4532</v>
+        <v>4575.2</v>
       </c>
       <c r="C37" t="n">
-        <v>4627.1</v>
+        <v>4577.3</v>
       </c>
       <c r="D37" t="n">
-        <v>4363.5</v>
+        <v>4336.6</v>
       </c>
       <c r="E37" t="n">
-        <v>4593</v>
+        <v>4365.3</v>
       </c>
       <c r="F37" t="n">
-        <v>69.8</v>
+        <v>-227.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0154</v>
+        <v>-0.0496</v>
       </c>
       <c r="H37" t="n">
-        <v>263.6</v>
+        <v>240.7</v>
       </c>
       <c r="I37" t="n">
-        <v>4316.8</v>
+        <v>4099.9</v>
       </c>
       <c r="J37" t="n">
-        <v>4384.55</v>
+        <v>4378.25</v>
       </c>
       <c r="K37" t="n">
-        <v>4454.1</v>
+        <v>4461.2</v>
       </c>
       <c r="L37" t="n">
-        <v>4523.65</v>
+        <v>4544.15</v>
       </c>
       <c r="M37" t="n">
-        <v>4592.3</v>
+        <v>4724.8</v>
       </c>
       <c r="N37" t="n">
-        <v>4660.95</v>
+        <v>4905.45</v>
       </c>
       <c r="O37" t="n">
-        <v>4731.4</v>
+        <v>4890.7</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3629,71 +3631,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4575.2</v>
+        <v>4354</v>
       </c>
       <c r="C38" t="n">
-        <v>4577.3</v>
+        <v>4388.6</v>
       </c>
       <c r="D38" t="n">
-        <v>4336.6</v>
+        <v>4046.2</v>
       </c>
       <c r="E38" t="n">
-        <v>4365.3</v>
+        <v>4238.8</v>
       </c>
       <c r="F38" t="n">
-        <v>-227.7</v>
+        <v>-126.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0496</v>
+        <v>-0.029</v>
       </c>
       <c r="H38" t="n">
-        <v>240.7</v>
+        <v>342.4</v>
       </c>
       <c r="I38" t="n">
-        <v>4099.9</v>
+        <v>4095.9</v>
       </c>
       <c r="J38" t="n">
-        <v>4378.25</v>
+        <v>4078.78</v>
       </c>
       <c r="K38" t="n">
-        <v>4461.2</v>
+        <v>4244.95</v>
       </c>
       <c r="L38" t="n">
-        <v>4544.15</v>
+        <v>4411.12</v>
       </c>
       <c r="M38" t="n">
-        <v>4724.8</v>
+        <v>4485.65</v>
       </c>
       <c r="N38" t="n">
-        <v>4905.45</v>
+        <v>4560.17</v>
       </c>
       <c r="O38" t="n">
-        <v>4890.7</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
+        <v>4818</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
@@ -3720,69 +3720,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4354</v>
+        <v>4289.4</v>
       </c>
       <c r="C39" t="n">
-        <v>4388.6</v>
+        <v>4403.6</v>
       </c>
       <c r="D39" t="n">
-        <v>4046.2</v>
+        <v>4138.7</v>
       </c>
       <c r="E39" t="n">
-        <v>4238.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F39" t="n">
-        <v>-126.5</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0155</v>
       </c>
       <c r="H39" t="n">
-        <v>342.4</v>
+        <v>264.9</v>
       </c>
       <c r="I39" t="n">
-        <v>4095.9</v>
+        <v>3703.8</v>
       </c>
       <c r="J39" t="n">
-        <v>4078.78</v>
+        <v>3907.1</v>
       </c>
       <c r="K39" t="n">
-        <v>4244.95</v>
+        <v>4067.6</v>
       </c>
       <c r="L39" t="n">
-        <v>4411.12</v>
+        <v>4228.1</v>
       </c>
       <c r="M39" t="n">
-        <v>4485.65</v>
+        <v>4410</v>
       </c>
       <c r="N39" t="n">
-        <v>4560.17</v>
+        <v>4591.9</v>
       </c>
       <c r="O39" t="n">
-        <v>4818</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4731</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3799,55 +3793,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4289.4</v>
+        <v>4163.9</v>
       </c>
       <c r="C40" t="n">
-        <v>4403.6</v>
+        <v>4238.1</v>
       </c>
       <c r="D40" t="n">
-        <v>4138.7</v>
+        <v>3975.7</v>
       </c>
       <c r="E40" t="n">
-        <v>4172.9</v>
+        <v>4096.3</v>
       </c>
       <c r="F40" t="n">
-        <v>-65.90000000000001</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0184</v>
       </c>
       <c r="H40" t="n">
-        <v>264.9</v>
+        <v>262.4</v>
       </c>
       <c r="I40" t="n">
-        <v>3703.8</v>
+        <v>3873.8</v>
       </c>
       <c r="J40" t="n">
-        <v>3907.1</v>
+        <v>3858.87</v>
       </c>
       <c r="K40" t="n">
-        <v>4067.6</v>
+        <v>4040.45</v>
       </c>
       <c r="L40" t="n">
-        <v>4228.1</v>
+        <v>4222.03</v>
       </c>
       <c r="M40" t="n">
-        <v>4410</v>
+        <v>4305.35</v>
       </c>
       <c r="N40" t="n">
-        <v>4591.9</v>
+        <v>4388.67</v>
       </c>
       <c r="O40" t="n">
-        <v>4731</v>
+        <v>4668.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,12 +3853,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3877,59 +3877,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4163.9</v>
+        <v>4101.1</v>
       </c>
       <c r="C41" t="n">
-        <v>4238.1</v>
+        <v>4208.3</v>
       </c>
       <c r="D41" t="n">
-        <v>3975.7</v>
+        <v>3955.4</v>
       </c>
       <c r="E41" t="n">
-        <v>4096.3</v>
+        <v>4187.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-76.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0222</v>
       </c>
       <c r="H41" t="n">
-        <v>262.4</v>
+        <v>252.9</v>
       </c>
       <c r="I41" t="n">
-        <v>3873.8</v>
+        <v>3713.3</v>
       </c>
       <c r="J41" t="n">
-        <v>3858.87</v>
+        <v>3828.6</v>
       </c>
       <c r="K41" t="n">
-        <v>4040.45</v>
+        <v>3965.1</v>
       </c>
       <c r="L41" t="n">
-        <v>4222.03</v>
+        <v>4101.6</v>
       </c>
       <c r="M41" t="n">
-        <v>4305.35</v>
+        <v>4227.5</v>
       </c>
       <c r="N41" t="n">
-        <v>4388.67</v>
+        <v>4353.4</v>
       </c>
       <c r="O41" t="n">
-        <v>4668.5</v>
+        <v>4500.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3939,17 +3935,19 @@
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3961,55 +3959,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4101.1</v>
+        <v>4187.5</v>
       </c>
       <c r="C42" t="n">
-        <v>4208.3</v>
+        <v>4215.5</v>
       </c>
       <c r="D42" t="n">
-        <v>3955.4</v>
+        <v>4032.5</v>
       </c>
       <c r="E42" t="n">
-        <v>4187.3</v>
+        <v>4113.7</v>
       </c>
       <c r="F42" t="n">
-        <v>91</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0176</v>
       </c>
       <c r="H42" t="n">
-        <v>252.9</v>
+        <v>183</v>
       </c>
       <c r="I42" t="n">
-        <v>3713.3</v>
+        <v>3702.5</v>
       </c>
       <c r="J42" t="n">
-        <v>3828.6</v>
+        <v>3987.12</v>
       </c>
       <c r="K42" t="n">
-        <v>3965.1</v>
+        <v>4060.85</v>
       </c>
       <c r="L42" t="n">
-        <v>4101.6</v>
+        <v>4134.57</v>
       </c>
       <c r="M42" t="n">
-        <v>4227.5</v>
+        <v>4313.75</v>
       </c>
       <c r="N42" t="n">
-        <v>4353.4</v>
+        <v>4492.92</v>
       </c>
       <c r="O42" t="n">
-        <v>4500.5</v>
+        <v>4461.2</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4022,15 +4024,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4045,57 +4045,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4187.5</v>
+        <v>4106.6</v>
       </c>
       <c r="C43" t="n">
-        <v>4215.5</v>
+        <v>4112.5</v>
       </c>
       <c r="D43" t="n">
-        <v>4032.5</v>
+        <v>3963</v>
       </c>
       <c r="E43" t="n">
-        <v>4113.7</v>
+        <v>4018.8</v>
       </c>
       <c r="F43" t="n">
-        <v>-73.59999999999999</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0176</v>
+        <v>-0.0231</v>
       </c>
       <c r="H43" t="n">
-        <v>183</v>
+        <v>149.5</v>
       </c>
       <c r="I43" t="n">
-        <v>3702.5</v>
+        <v>3849.5</v>
       </c>
       <c r="J43" t="n">
-        <v>3987.12</v>
+        <v>3925.55</v>
       </c>
       <c r="K43" t="n">
-        <v>4060.85</v>
+        <v>4022.2</v>
       </c>
       <c r="L43" t="n">
-        <v>4134.57</v>
+        <v>4118.85</v>
       </c>
       <c r="M43" t="n">
-        <v>4313.75</v>
+        <v>4205.2</v>
       </c>
       <c r="N43" t="n">
-        <v>4492.92</v>
+        <v>4291.55</v>
       </c>
       <c r="O43" t="n">
-        <v>4461.2</v>
+        <v>4398.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4105,12 +4105,12 @@
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4127,59 +4127,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4106.6</v>
+        <v>4005.6</v>
       </c>
       <c r="C44" t="n">
-        <v>4112.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D44" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E44" t="n">
-        <v>4018.8</v>
+        <v>4070.8</v>
       </c>
       <c r="F44" t="n">
-        <v>-94.90000000000001</v>
+        <v>52</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0129</v>
       </c>
       <c r="H44" t="n">
-        <v>149.5</v>
+        <v>184.9</v>
       </c>
       <c r="I44" t="n">
-        <v>3849.5</v>
+        <v>3813.5</v>
       </c>
       <c r="J44" t="n">
-        <v>3925.55</v>
+        <v>3859.83</v>
       </c>
       <c r="K44" t="n">
-        <v>4022.2</v>
+        <v>3944.05</v>
       </c>
       <c r="L44" t="n">
-        <v>4118.85</v>
+        <v>4028.28</v>
       </c>
       <c r="M44" t="n">
-        <v>4205.2</v>
+        <v>4093.55</v>
       </c>
       <c r="N44" t="n">
-        <v>4291.55</v>
+        <v>4158.83</v>
       </c>
       <c r="O44" t="n">
-        <v>4398.5</v>
+        <v>4262</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4187,21 +4183,23 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4211,55 +4209,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4005.6</v>
+        <v>4097.5</v>
       </c>
       <c r="C45" t="n">
-        <v>4171.4</v>
+        <v>4170.7</v>
       </c>
       <c r="D45" t="n">
-        <v>3986.5</v>
+        <v>3993.8</v>
       </c>
       <c r="E45" t="n">
-        <v>4070.8</v>
+        <v>4107</v>
       </c>
       <c r="F45" t="n">
-        <v>52</v>
+        <v>36.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0089</v>
       </c>
       <c r="H45" t="n">
-        <v>184.9</v>
+        <v>176.9</v>
       </c>
       <c r="I45" t="n">
-        <v>3813.5</v>
+        <v>3801.6</v>
       </c>
       <c r="J45" t="n">
-        <v>3859.83</v>
+        <v>3881.83</v>
       </c>
       <c r="K45" t="n">
-        <v>3944.05</v>
+        <v>3978.35</v>
       </c>
       <c r="L45" t="n">
-        <v>4028.28</v>
+        <v>4074.88</v>
       </c>
       <c r="M45" t="n">
-        <v>4093.55</v>
+        <v>4163.25</v>
       </c>
       <c r="N45" t="n">
-        <v>4158.83</v>
+        <v>4251.62</v>
       </c>
       <c r="O45" t="n">
-        <v>4262</v>
+        <v>4356.3</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4272,19 +4274,17 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4295,57 +4295,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4097.5</v>
+        <v>4135.2</v>
       </c>
       <c r="C46" t="n">
-        <v>4170.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D46" t="n">
-        <v>3993.8</v>
+        <v>4074</v>
       </c>
       <c r="E46" t="n">
-        <v>4107</v>
+        <v>4399.7</v>
       </c>
       <c r="F46" t="n">
-        <v>36.2</v>
+        <v>292.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0089</v>
+        <v>0.0713</v>
       </c>
       <c r="H46" t="n">
-        <v>176.9</v>
+        <v>358.3</v>
       </c>
       <c r="I46" t="n">
-        <v>3801.6</v>
+        <v>3816.9</v>
       </c>
       <c r="J46" t="n">
-        <v>3881.83</v>
+        <v>3942.47</v>
       </c>
       <c r="K46" t="n">
-        <v>3978.35</v>
+        <v>4018.55</v>
       </c>
       <c r="L46" t="n">
-        <v>4074.88</v>
+        <v>4094.63</v>
       </c>
       <c r="M46" t="n">
-        <v>4163.25</v>
+        <v>4195.45</v>
       </c>
       <c r="N46" t="n">
-        <v>4251.62</v>
+        <v>4296.28</v>
       </c>
       <c r="O46" t="n">
-        <v>4356.3</v>
+        <v>4347.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4366,70 +4366,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4135.2</v>
+        <v>4400</v>
       </c>
       <c r="C47" t="n">
-        <v>4432.3</v>
+        <v>4509.1</v>
       </c>
       <c r="D47" t="n">
-        <v>4074</v>
+        <v>4365.5</v>
       </c>
       <c r="E47" t="n">
-        <v>4399.7</v>
+        <v>4437.3</v>
       </c>
       <c r="F47" t="n">
-        <v>292.7</v>
+        <v>37.6</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0713</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>358.3</v>
+        <v>143.6</v>
       </c>
       <c r="I47" t="n">
-        <v>3816.9</v>
+        <v>3715.7</v>
       </c>
       <c r="J47" t="n">
-        <v>3942.47</v>
+        <v>4114.68</v>
       </c>
       <c r="K47" t="n">
-        <v>4018.55</v>
+        <v>4220.55</v>
       </c>
       <c r="L47" t="n">
-        <v>4094.63</v>
+        <v>4326.43</v>
       </c>
       <c r="M47" t="n">
-        <v>4195.45</v>
+        <v>4578.85</v>
       </c>
       <c r="N47" t="n">
-        <v>4296.28</v>
+        <v>4831.28</v>
       </c>
       <c r="O47" t="n">
-        <v>4347.6</v>
+        <v>4790.6</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4442,23 +4442,17 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4470,50 +4464,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4400</v>
+        <v>4440</v>
       </c>
       <c r="C48" t="n">
+        <v>4690.4</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4378</v>
+      </c>
+      <c r="E48" t="n">
+        <v>4680.6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>243.3</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H48" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4221.9</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4293.7</v>
+      </c>
+      <c r="K48" t="n">
+        <v>4365.5</v>
+      </c>
+      <c r="L48" t="n">
+        <v>4437.3</v>
+      </c>
+      <c r="M48" t="n">
         <v>4509.1</v>
       </c>
-      <c r="D48" t="n">
-        <v>4365.5</v>
-      </c>
-      <c r="E48" t="n">
-        <v>4437.3</v>
-      </c>
-      <c r="F48" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="H48" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="I48" t="n">
-        <v>3715.7</v>
-      </c>
-      <c r="J48" t="n">
-        <v>4114.68</v>
-      </c>
-      <c r="K48" t="n">
-        <v>4220.55</v>
-      </c>
-      <c r="L48" t="n">
-        <v>4326.43</v>
-      </c>
-      <c r="M48" t="n">
-        <v>4578.85</v>
-      </c>
       <c r="N48" t="n">
-        <v>4831.28</v>
+        <v>4580.9</v>
       </c>
       <c r="O48" t="n">
-        <v>4790.6</v>
+        <v>4652.7</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4526,17 +4520,23 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4548,50 +4548,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4440</v>
+        <v>4673.4</v>
       </c>
       <c r="C49" t="n">
-        <v>4690.4</v>
+        <v>4755</v>
       </c>
       <c r="D49" t="n">
-        <v>4378</v>
+        <v>4495</v>
       </c>
       <c r="E49" t="n">
-        <v>4680.6</v>
+        <v>4529.9</v>
       </c>
       <c r="F49" t="n">
-        <v>243.3</v>
+        <v>-150.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0548</v>
+        <v>-0.0322</v>
       </c>
       <c r="H49" t="n">
-        <v>312.4</v>
+        <v>260</v>
       </c>
       <c r="I49" t="n">
-        <v>4221.9</v>
+        <v>4065.6</v>
       </c>
       <c r="J49" t="n">
-        <v>4293.7</v>
+        <v>4441.4</v>
       </c>
       <c r="K49" t="n">
-        <v>4365.5</v>
+        <v>4524.4</v>
       </c>
       <c r="L49" t="n">
-        <v>4437.3</v>
+        <v>4607.4</v>
       </c>
       <c r="M49" t="n">
-        <v>4509.1</v>
+        <v>4836.8</v>
       </c>
       <c r="N49" t="n">
-        <v>4580.9</v>
+        <v>5066.2</v>
       </c>
       <c r="O49" t="n">
-        <v>4652.7</v>
+        <v>5002.8</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4599,83 +4599,83 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4673.4</v>
+        <v>4483.2</v>
       </c>
       <c r="C50" t="n">
-        <v>4755</v>
+        <v>4558.5</v>
       </c>
       <c r="D50" t="n">
-        <v>4495</v>
+        <v>4329.2</v>
       </c>
       <c r="E50" t="n">
-        <v>4529.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F50" t="n">
-        <v>-150.7</v>
+        <v>-53.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0118</v>
       </c>
       <c r="H50" t="n">
-        <v>260</v>
+        <v>229.3</v>
       </c>
       <c r="I50" t="n">
-        <v>4065.6</v>
+        <v>4235</v>
       </c>
       <c r="J50" t="n">
-        <v>4441.4</v>
+        <v>4222.35</v>
       </c>
       <c r="K50" t="n">
-        <v>4524.4</v>
+        <v>4399.9</v>
       </c>
       <c r="L50" t="n">
-        <v>4607.4</v>
+        <v>4577.45</v>
       </c>
       <c r="M50" t="n">
-        <v>4836.8</v>
+        <v>4659.9</v>
       </c>
       <c r="N50" t="n">
-        <v>5066.2</v>
+        <v>4742.35</v>
       </c>
       <c r="O50" t="n">
-        <v>5002.8</v>
+        <v>5015</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4709,57 +4709,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4483.2</v>
+        <v>4466.5</v>
       </c>
       <c r="C51" t="n">
-        <v>4558.5</v>
+        <v>4488.8</v>
       </c>
       <c r="D51" t="n">
-        <v>4329.2</v>
+        <v>4333</v>
       </c>
       <c r="E51" t="n">
-        <v>4476.6</v>
+        <v>4408.9</v>
       </c>
       <c r="F51" t="n">
-        <v>-53.3</v>
+        <v>-67.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0151</v>
       </c>
       <c r="H51" t="n">
-        <v>229.3</v>
+        <v>155.8</v>
       </c>
       <c r="I51" t="n">
-        <v>4235</v>
+        <v>4099.9</v>
       </c>
       <c r="J51" t="n">
-        <v>4222.35</v>
+        <v>4263.68</v>
       </c>
       <c r="K51" t="n">
-        <v>4399.9</v>
+        <v>4361.95</v>
       </c>
       <c r="L51" t="n">
-        <v>4577.45</v>
+        <v>4460.23</v>
       </c>
       <c r="M51" t="n">
-        <v>4659.9</v>
+        <v>4591.25</v>
       </c>
       <c r="N51" t="n">
-        <v>4742.35</v>
+        <v>4722.27</v>
       </c>
       <c r="O51" t="n">
-        <v>5015</v>
+        <v>4787.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4793,57 +4793,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4466.5</v>
+        <v>4375</v>
       </c>
       <c r="C52" t="n">
-        <v>4488.8</v>
+        <v>4439.8</v>
       </c>
       <c r="D52" t="n">
-        <v>4333</v>
+        <v>4273.3</v>
       </c>
       <c r="E52" t="n">
-        <v>4408.9</v>
+        <v>4424.9</v>
       </c>
       <c r="F52" t="n">
-        <v>-67.7</v>
+        <v>16</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0151</v>
+        <v>0.0036</v>
       </c>
       <c r="H52" t="n">
-        <v>155.8</v>
+        <v>166.5</v>
       </c>
       <c r="I52" t="n">
-        <v>4099.9</v>
+        <v>4177.2</v>
       </c>
       <c r="J52" t="n">
-        <v>4263.68</v>
+        <v>4252.1</v>
       </c>
       <c r="K52" t="n">
-        <v>4361.95</v>
+        <v>4331</v>
       </c>
       <c r="L52" t="n">
-        <v>4460.23</v>
+        <v>4409.9</v>
       </c>
       <c r="M52" t="n">
-        <v>4591.25</v>
+        <v>4486.8</v>
       </c>
       <c r="N52" t="n">
-        <v>4722.27</v>
+        <v>4563.7</v>
       </c>
       <c r="O52" t="n">
-        <v>4787.8</v>
+        <v>4644.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4884,65 +4884,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4375</v>
+        <v>4413</v>
       </c>
       <c r="C53" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D53" t="n">
-        <v>4273.3</v>
+        <v>4278.3</v>
       </c>
       <c r="E53" t="n">
-        <v>4424.9</v>
+        <v>4321.2</v>
       </c>
       <c r="F53" t="n">
-        <v>16</v>
+        <v>-103.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0234</v>
       </c>
       <c r="H53" t="n">
-        <v>166.5</v>
+        <v>143.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4177.2</v>
+        <v>4106.8</v>
       </c>
       <c r="J53" t="n">
-        <v>4252.1</v>
+        <v>4292.57</v>
       </c>
       <c r="K53" t="n">
-        <v>4331</v>
+        <v>4341.65</v>
       </c>
       <c r="L53" t="n">
-        <v>4409.9</v>
+        <v>4390.72</v>
       </c>
       <c r="M53" t="n">
-        <v>4486.8</v>
+        <v>4508.15</v>
       </c>
       <c r="N53" t="n">
-        <v>4563.7</v>
+        <v>4625.57</v>
       </c>
       <c r="O53" t="n">
-        <v>4644.6</v>
+        <v>4606.3</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4968,64 +4970,64 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4413</v>
+        <v>4315</v>
       </c>
       <c r="C54" t="n">
-        <v>4422.1</v>
+        <v>4315.6</v>
       </c>
       <c r="D54" t="n">
-        <v>4278.3</v>
+        <v>4143.1</v>
       </c>
       <c r="E54" t="n">
-        <v>4321.2</v>
+        <v>4162.3</v>
       </c>
       <c r="F54" t="n">
-        <v>-103.7</v>
+        <v>-158.9</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0234</v>
+        <v>-0.0368</v>
       </c>
       <c r="H54" t="n">
-        <v>143.8</v>
+        <v>172.5</v>
       </c>
       <c r="I54" t="n">
-        <v>4106.8</v>
+        <v>4134.5</v>
       </c>
       <c r="J54" t="n">
-        <v>4292.57</v>
+        <v>4162.9</v>
       </c>
       <c r="K54" t="n">
-        <v>4341.65</v>
+        <v>4249.3</v>
       </c>
       <c r="L54" t="n">
-        <v>4390.72</v>
+        <v>4335.7</v>
       </c>
       <c r="M54" t="n">
-        <v>4508.15</v>
+        <v>4393.1</v>
       </c>
       <c r="N54" t="n">
-        <v>4625.57</v>
+        <v>4450.5</v>
       </c>
       <c r="O54" t="n">
-        <v>4606.3</v>
+        <v>4565.9</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5040,81 +5042,73 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4315</v>
+        <v>4169.4</v>
       </c>
       <c r="C55" t="n">
-        <v>4315.6</v>
+        <v>4233.7</v>
       </c>
       <c r="D55" t="n">
-        <v>4143.1</v>
+        <v>4091.2</v>
       </c>
       <c r="E55" t="n">
-        <v>4162.3</v>
+        <v>4216.3</v>
       </c>
       <c r="F55" t="n">
-        <v>-158.9</v>
+        <v>54</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0368</v>
+        <v>0.013</v>
       </c>
       <c r="H55" t="n">
-        <v>172.5</v>
+        <v>142.5</v>
       </c>
       <c r="I55" t="n">
-        <v>4134.5</v>
+        <v>3970.6</v>
       </c>
       <c r="J55" t="n">
-        <v>4162.9</v>
+        <v>3956.27</v>
       </c>
       <c r="K55" t="n">
-        <v>4249.3</v>
+        <v>4076.05</v>
       </c>
       <c r="L55" t="n">
-        <v>4335.7</v>
+        <v>4195.82</v>
       </c>
       <c r="M55" t="n">
-        <v>4393.1</v>
+        <v>4248.55</v>
       </c>
       <c r="N55" t="n">
-        <v>4450.5</v>
+        <v>4301.27</v>
       </c>
       <c r="O55" t="n">
-        <v>4565.9</v>
+        <v>4488.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5131,68 +5125,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4169.4</v>
+        <v>4220.8</v>
       </c>
       <c r="C56" t="n">
-        <v>4233.7</v>
+        <v>4242.3</v>
       </c>
       <c r="D56" t="n">
-        <v>4091.2</v>
+        <v>4095</v>
       </c>
       <c r="E56" t="n">
-        <v>4216.3</v>
+        <v>4181.1</v>
       </c>
       <c r="F56" t="n">
-        <v>54</v>
+        <v>-35.2</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0083</v>
       </c>
       <c r="H56" t="n">
-        <v>142.5</v>
+        <v>147.3</v>
       </c>
       <c r="I56" t="n">
-        <v>3970.6</v>
+        <v>3948.7</v>
       </c>
       <c r="J56" t="n">
-        <v>3956.27</v>
+        <v>4100.72</v>
       </c>
       <c r="K56" t="n">
-        <v>4076.05</v>
+        <v>4145.05</v>
       </c>
       <c r="L56" t="n">
-        <v>4195.82</v>
+        <v>4189.37</v>
       </c>
       <c r="M56" t="n">
-        <v>4248.55</v>
+        <v>4287.55</v>
       </c>
       <c r="N56" t="n">
-        <v>4301.27</v>
+        <v>4385.72</v>
       </c>
       <c r="O56" t="n">
-        <v>4488.1</v>
+        <v>4376.2</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5211,74 +5213,74 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4220.8</v>
+        <v>4185</v>
       </c>
       <c r="C57" t="n">
-        <v>4242.3</v>
+        <v>4211.2</v>
       </c>
       <c r="D57" t="n">
-        <v>4095</v>
+        <v>3989.2</v>
       </c>
       <c r="E57" t="n">
-        <v>4181.1</v>
+        <v>4010</v>
       </c>
       <c r="F57" t="n">
-        <v>-35.2</v>
+        <v>-171.1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0409</v>
       </c>
       <c r="H57" t="n">
-        <v>147.3</v>
+        <v>222</v>
       </c>
       <c r="I57" t="n">
-        <v>3948.7</v>
+        <v>3947.7</v>
       </c>
       <c r="J57" t="n">
-        <v>4100.72</v>
+        <v>4040.03</v>
       </c>
       <c r="K57" t="n">
-        <v>4145.05</v>
+        <v>4107.45</v>
       </c>
       <c r="L57" t="n">
-        <v>4189.37</v>
+        <v>4174.88</v>
       </c>
       <c r="M57" t="n">
-        <v>4287.55</v>
+        <v>4254.75</v>
       </c>
       <c r="N57" t="n">
-        <v>4385.72</v>
+        <v>4334.62</v>
       </c>
       <c r="O57" t="n">
-        <v>4376.2</v>
+        <v>4389.6</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5295,93 +5297,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4185</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4211.2</v>
-      </c>
-      <c r="D58" t="n">
-        <v>4028.7</v>
-      </c>
-      <c r="E58" t="n">
-        <v>4034.7</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-146.4</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.035</v>
-      </c>
-      <c r="H58" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3947.7</v>
-      </c>
-      <c r="J58" t="n">
-        <v>4040.03</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4107.45</v>
-      </c>
-      <c r="L58" t="n">
-        <v>4174.88</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4254.75</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4334.62</v>
-      </c>
-      <c r="O58" t="n">
-        <v>4389.6</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -5230,19 +5230,19 @@
         <v>4211.2</v>
       </c>
       <c r="D57" t="n">
-        <v>3989.2</v>
+        <v>3989.1</v>
       </c>
       <c r="E57" t="n">
-        <v>4010</v>
+        <v>4000.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-171.1</v>
+        <v>-180.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0409</v>
+        <v>-0.0431</v>
       </c>
       <c r="H57" t="n">
-        <v>222</v>
+        <v>222.1</v>
       </c>
       <c r="I57" t="n">
         <v>3947.7</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +662,25 @@
         <v>137.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3611.6</v>
+        <v>3674.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3721.32</v>
+        <v>3745.02</v>
       </c>
       <c r="K2" t="n">
-        <v>3755.75</v>
+        <v>3771.55</v>
       </c>
       <c r="L2" t="n">
-        <v>3790.18</v>
+        <v>3798.08</v>
       </c>
       <c r="M2" t="n">
-        <v>3862.25</v>
+        <v>3846.45</v>
       </c>
       <c r="N2" t="n">
-        <v>3934.32</v>
+        <v>3894.83</v>
       </c>
       <c r="O2" t="n">
-        <v>3931.1</v>
+        <v>3899.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,8 +701,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="inlineStr">
         <is>
@@ -5233,13 +5238,13 @@
         <v>3989.1</v>
       </c>
       <c r="E57" t="n">
-        <v>4000.9</v>
+        <v>4007.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-180.2</v>
+        <v>-173.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0431</v>
+        <v>-0.0414</v>
       </c>
       <c r="H57" t="n">
         <v>222.1</v>
@@ -5298,6 +5303,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4032.8</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4033.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4016.7</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3767</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3739.67</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3896.85</v>
+      </c>
+      <c r="L58" t="n">
+        <v>4054.03</v>
+      </c>
+      <c r="M58" t="n">
+        <v>4118.95</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4183.87</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4433.3</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>137.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3674.8</v>
+        <v>3685</v>
       </c>
       <c r="J2" t="n">
-        <v>3745.02</v>
+        <v>3757.78</v>
       </c>
       <c r="K2" t="n">
-        <v>3771.55</v>
+        <v>3776.65</v>
       </c>
       <c r="L2" t="n">
-        <v>3798.08</v>
+        <v>3795.52</v>
       </c>
       <c r="M2" t="n">
-        <v>3846.45</v>
+        <v>3841.35</v>
       </c>
       <c r="N2" t="n">
-        <v>3894.83</v>
+        <v>3887.17</v>
       </c>
       <c r="O2" t="n">
-        <v>3899.5</v>
+        <v>3879.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -703,12 +700,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5311,25 +5308,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4032.8</v>
+        <v>4012.2</v>
       </c>
       <c r="C58" t="n">
-        <v>4033.5</v>
+        <v>4084.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4016.7</v>
+        <v>3990.9</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>4062.3</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>54.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0136</v>
       </c>
       <c r="H58" t="n">
-        <v>16.8</v>
+        <v>93.2</v>
       </c>
       <c r="I58" t="n">
         <v>3767</v>
@@ -5352,10 +5349,8 @@
       <c r="O58" t="n">
         <v>4433.3</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5363,9 +5358,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5384,7 +5379,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>137.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3685</v>
+        <v>3689.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3757.78</v>
+        <v>3759.43</v>
       </c>
       <c r="K2" t="n">
-        <v>3776.65</v>
+        <v>3777.75</v>
       </c>
       <c r="L2" t="n">
-        <v>3795.52</v>
+        <v>3796.07</v>
       </c>
       <c r="M2" t="n">
-        <v>3841.35</v>
+        <v>3840.25</v>
       </c>
       <c r="N2" t="n">
-        <v>3887.17</v>
+        <v>3884.43</v>
       </c>
       <c r="O2" t="n">
-        <v>3879.1</v>
+        <v>3876.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5311,22 +5311,22 @@
         <v>4012.2</v>
       </c>
       <c r="C58" t="n">
-        <v>4084.1</v>
+        <v>4097.2</v>
       </c>
       <c r="D58" t="n">
         <v>3990.9</v>
       </c>
       <c r="E58" t="n">
-        <v>4062.3</v>
+        <v>4074.1</v>
       </c>
       <c r="F58" t="n">
-        <v>54.4</v>
+        <v>66.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0165</v>
       </c>
       <c r="H58" t="n">
-        <v>93.2</v>
+        <v>106.3</v>
       </c>
       <c r="I58" t="n">
         <v>3767</v>

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>137.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3689.4</v>
+        <v>3713.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3759.43</v>
+        <v>3768.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3777.75</v>
+        <v>3783.8</v>
       </c>
       <c r="L2" t="n">
-        <v>3796.07</v>
+        <v>3799.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3840.25</v>
+        <v>3834.2</v>
       </c>
       <c r="N2" t="n">
-        <v>3884.43</v>
+        <v>3869.3</v>
       </c>
       <c r="O2" t="n">
-        <v>3876.9</v>
+        <v>3864.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5317,13 +5317,13 @@
         <v>3990.9</v>
       </c>
       <c r="E58" t="n">
-        <v>4074.1</v>
+        <v>4024.3</v>
       </c>
       <c r="F58" t="n">
-        <v>66.2</v>
+        <v>16.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0165</v>
+        <v>0.0041</v>
       </c>
       <c r="H58" t="n">
         <v>106.3</v>
@@ -5358,9 +5358,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/GC_weekly.xlsx
+++ b/three_gate/analysis/GC_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3788.8</v>
+        <v>3913.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3923.3</v>
+        <v>4081</v>
       </c>
       <c r="D2" t="n">
-        <v>3785.5</v>
+        <v>3909.2</v>
       </c>
       <c r="E2" t="n">
-        <v>3908.9</v>
+        <v>4000.4</v>
       </c>
       <c r="F2" t="n">
-        <v>99.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0262</v>
+        <v>0.0234</v>
       </c>
       <c r="H2" t="n">
-        <v>137.8</v>
+        <v>171.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3713.6</v>
+        <v>3647.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3768.5</v>
+        <v>3798.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3783.8</v>
+        <v>3840</v>
       </c>
       <c r="L2" t="n">
-        <v>3799.1</v>
+        <v>3881.65</v>
       </c>
       <c r="M2" t="n">
-        <v>3834.2</v>
+        <v>3977.8</v>
       </c>
       <c r="N2" t="n">
-        <v>3869.3</v>
+        <v>4073.95</v>
       </c>
       <c r="O2" t="n">
-        <v>3864.8</v>
+        <v>4061.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,12 +695,12 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="V2" s="8" t="inlineStr">
@@ -718,50 +718,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3913.5</v>
+        <v>4018.3</v>
       </c>
       <c r="C3" t="n">
-        <v>4081</v>
+        <v>4392</v>
       </c>
       <c r="D3" t="n">
-        <v>3909.2</v>
+        <v>4011.3</v>
       </c>
       <c r="E3" t="n">
-        <v>4000.4</v>
+        <v>4213.3</v>
       </c>
       <c r="F3" t="n">
-        <v>91.5</v>
+        <v>212.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0234</v>
+        <v>0.0532</v>
       </c>
       <c r="H3" t="n">
-        <v>171.8</v>
+        <v>380.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3647.7</v>
+        <v>3737.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3798.35</v>
+        <v>3831.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3840</v>
+        <v>3914.5</v>
       </c>
       <c r="L3" t="n">
-        <v>3881.65</v>
+        <v>3997.75</v>
       </c>
       <c r="M3" t="n">
-        <v>3977.8</v>
+        <v>4086.3</v>
       </c>
       <c r="N3" t="n">
-        <v>4073.95</v>
+        <v>4174.85</v>
       </c>
       <c r="O3" t="n">
-        <v>4061.1</v>
+        <v>4252.8</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,12 +779,12 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V3" s="8" t="inlineStr">
@@ -802,50 +802,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4018.3</v>
+        <v>4269</v>
       </c>
       <c r="C4" t="n">
-        <v>4392</v>
+        <v>4398</v>
       </c>
       <c r="D4" t="n">
-        <v>4011.3</v>
+        <v>4021.2</v>
       </c>
       <c r="E4" t="n">
-        <v>4213.3</v>
+        <v>4137.8</v>
       </c>
       <c r="F4" t="n">
-        <v>212.9</v>
+        <v>-75.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0532</v>
+        <v>-0.0179</v>
       </c>
       <c r="H4" t="n">
-        <v>380.7</v>
+        <v>376.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3737.4</v>
+        <v>3630.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3831.25</v>
+        <v>3838.42</v>
       </c>
       <c r="K4" t="n">
-        <v>3914.5</v>
+        <v>4022.95</v>
       </c>
       <c r="L4" t="n">
-        <v>3997.75</v>
+        <v>4207.47</v>
       </c>
       <c r="M4" t="n">
-        <v>4086.3</v>
+        <v>4403.65</v>
       </c>
       <c r="N4" t="n">
-        <v>4174.85</v>
+        <v>4599.82</v>
       </c>
       <c r="O4" t="n">
-        <v>4252.8</v>
+        <v>4772.7</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,83 +853,83 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4269</v>
+        <v>4103.2</v>
       </c>
       <c r="C5" t="n">
-        <v>4398</v>
+        <v>4123.8</v>
       </c>
       <c r="D5" t="n">
-        <v>4021.2</v>
+        <v>3901.3</v>
       </c>
       <c r="E5" t="n">
-        <v>4137.8</v>
+        <v>3996.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-75.5</v>
+        <v>-141.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0179</v>
+        <v>-0.0341</v>
       </c>
       <c r="H5" t="n">
-        <v>376.8</v>
+        <v>222.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3630.6</v>
+        <v>3644.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3838.42</v>
+        <v>3725.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4022.95</v>
+        <v>3949.4</v>
       </c>
       <c r="L5" t="n">
-        <v>4207.47</v>
+        <v>4173.7</v>
       </c>
       <c r="M5" t="n">
-        <v>4403.65</v>
+        <v>4326.2</v>
       </c>
       <c r="N5" t="n">
-        <v>4599.82</v>
+        <v>4478.7</v>
       </c>
       <c r="O5" t="n">
-        <v>4772.7</v>
+        <v>4774.8</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,12 +939,12 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -963,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4103.2</v>
+        <v>4001</v>
       </c>
       <c r="C6" t="n">
-        <v>4123.8</v>
+        <v>4043.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3901.3</v>
+        <v>3935.7</v>
       </c>
       <c r="E6" t="n">
-        <v>3996.5</v>
+        <v>4009.8</v>
       </c>
       <c r="F6" t="n">
-        <v>-141.3</v>
+        <v>13.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0341</v>
+        <v>0.0033</v>
       </c>
       <c r="H6" t="n">
-        <v>222.5</v>
+        <v>107.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3644.4</v>
+        <v>3678.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3725.1</v>
+        <v>3765.98</v>
       </c>
       <c r="K6" t="n">
-        <v>3949.4</v>
+        <v>3885.25</v>
       </c>
       <c r="L6" t="n">
-        <v>4173.7</v>
+        <v>4004.52</v>
       </c>
       <c r="M6" t="n">
-        <v>4326.2</v>
+        <v>4107.75</v>
       </c>
       <c r="N6" t="n">
-        <v>4478.7</v>
+        <v>4210.97</v>
       </c>
       <c r="O6" t="n">
-        <v>4774.8</v>
+        <v>4346.3</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,14 +1021,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1047,57 +1045,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4001</v>
+        <v>4007.2</v>
       </c>
       <c r="C7" t="n">
-        <v>4043.1</v>
+        <v>4250</v>
       </c>
       <c r="D7" t="n">
-        <v>3935.7</v>
+        <v>4004.2</v>
       </c>
       <c r="E7" t="n">
-        <v>4009.8</v>
+        <v>4094.2</v>
       </c>
       <c r="F7" t="n">
-        <v>13.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.021</v>
       </c>
       <c r="H7" t="n">
-        <v>107.4</v>
+        <v>245.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3678.8</v>
+        <v>3828.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3765.98</v>
+        <v>3912.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3885.25</v>
+        <v>3956.1</v>
       </c>
       <c r="L7" t="n">
-        <v>4004.52</v>
+        <v>3999.6</v>
       </c>
       <c r="M7" t="n">
-        <v>4107.75</v>
+        <v>4063.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4210.97</v>
+        <v>4127.4</v>
       </c>
       <c r="O7" t="n">
-        <v>4346.3</v>
+        <v>4150.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1110,76 +1108,78 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4007.2</v>
+        <v>4084.4</v>
       </c>
       <c r="C8" t="n">
-        <v>4250</v>
+        <v>4134.3</v>
       </c>
       <c r="D8" t="n">
-        <v>4004.2</v>
+        <v>3997.4</v>
       </c>
       <c r="E8" t="n">
-        <v>4094.2</v>
+        <v>4079.5</v>
       </c>
       <c r="F8" t="n">
-        <v>84.40000000000001</v>
+        <v>-14.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.021</v>
+        <v>-0.0036</v>
       </c>
       <c r="H8" t="n">
-        <v>245.8</v>
+        <v>136.9</v>
       </c>
       <c r="I8" t="n">
-        <v>3828.3</v>
+        <v>3758.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3912.6</v>
+        <v>3831.95</v>
       </c>
       <c r="K8" t="n">
-        <v>3956.1</v>
+        <v>3971.3</v>
       </c>
       <c r="L8" t="n">
-        <v>3999.6</v>
+        <v>4110.65</v>
       </c>
       <c r="M8" t="n">
-        <v>4063.5</v>
+        <v>4217.1</v>
       </c>
       <c r="N8" t="n">
-        <v>4127.4</v>
+        <v>4323.55</v>
       </c>
       <c r="O8" t="n">
-        <v>4150.5</v>
+        <v>4495.8</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,80 +1190,78 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4084.4</v>
+        <v>4069.2</v>
       </c>
       <c r="C9" t="n">
-        <v>4134.3</v>
+        <v>4263.1</v>
       </c>
       <c r="D9" t="n">
-        <v>3997.4</v>
+        <v>4036.4</v>
       </c>
       <c r="E9" t="n">
-        <v>4079.5</v>
+        <v>4254.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-14.7</v>
+        <v>175.4</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0036</v>
+        <v>0.043</v>
       </c>
       <c r="H9" t="n">
-        <v>136.9</v>
+        <v>226.7</v>
       </c>
       <c r="I9" t="n">
-        <v>3758.4</v>
+        <v>3860.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3831.95</v>
+        <v>3949.43</v>
       </c>
       <c r="K9" t="n">
-        <v>3971.3</v>
+        <v>4011.05</v>
       </c>
       <c r="L9" t="n">
-        <v>4110.65</v>
+        <v>4072.67</v>
       </c>
       <c r="M9" t="n">
-        <v>4217.1</v>
+        <v>4147.95</v>
       </c>
       <c r="N9" t="n">
-        <v>4323.55</v>
+        <v>4223.22</v>
       </c>
       <c r="O9" t="n">
-        <v>4495.8</v>
+        <v>4271.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,78 +1272,80 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4069.2</v>
+        <v>4258.5</v>
       </c>
       <c r="C10" t="n">
-        <v>4263.1</v>
+        <v>4299.6</v>
       </c>
       <c r="D10" t="n">
-        <v>4036.4</v>
+        <v>4194</v>
       </c>
       <c r="E10" t="n">
-        <v>4254.9</v>
+        <v>4243</v>
       </c>
       <c r="F10" t="n">
-        <v>175.4</v>
+        <v>-11.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.043</v>
+        <v>-0.0028</v>
       </c>
       <c r="H10" t="n">
-        <v>226.7</v>
+        <v>105.6</v>
       </c>
       <c r="I10" t="n">
-        <v>3860.5</v>
+        <v>3809.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3949.43</v>
+        <v>4080.77</v>
       </c>
       <c r="K10" t="n">
-        <v>4011.05</v>
+        <v>4141.55</v>
       </c>
       <c r="L10" t="n">
-        <v>4072.67</v>
+        <v>4202.32</v>
       </c>
       <c r="M10" t="n">
-        <v>4147.95</v>
+        <v>4368.25</v>
       </c>
       <c r="N10" t="n">
-        <v>4223.22</v>
+        <v>4534.18</v>
       </c>
       <c r="O10" t="n">
-        <v>4271.2</v>
+        <v>4489.8</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,78 +1358,76 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4258.5</v>
+        <v>4228.1</v>
       </c>
       <c r="C11" t="n">
-        <v>4299.6</v>
+        <v>4387.8</v>
       </c>
       <c r="D11" t="n">
-        <v>4194</v>
+        <v>4197.8</v>
       </c>
       <c r="E11" t="n">
-        <v>4243</v>
+        <v>4328.3</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.9</v>
+        <v>85.3</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0201</v>
       </c>
       <c r="H11" t="n">
-        <v>105.6</v>
+        <v>190</v>
       </c>
       <c r="I11" t="n">
-        <v>3809.7</v>
+        <v>4088.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4080.77</v>
+        <v>4135.5</v>
       </c>
       <c r="K11" t="n">
-        <v>4141.55</v>
+        <v>4190.2</v>
       </c>
       <c r="L11" t="n">
-        <v>4202.32</v>
+        <v>4244.9</v>
       </c>
       <c r="M11" t="n">
-        <v>4368.25</v>
+        <v>4295.8</v>
       </c>
       <c r="N11" t="n">
-        <v>4534.18</v>
+        <v>4346.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4489.8</v>
+        <v>4405.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,14 +1440,18 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1459,59 +1461,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4228.1</v>
+        <v>4330</v>
       </c>
       <c r="C12" t="n">
-        <v>4387.8</v>
+        <v>4409.5</v>
       </c>
       <c r="D12" t="n">
-        <v>4197.8</v>
+        <v>4297.4</v>
       </c>
       <c r="E12" t="n">
-        <v>4328.3</v>
+        <v>4387.3</v>
       </c>
       <c r="F12" t="n">
-        <v>85.3</v>
+        <v>59</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0201</v>
+        <v>0.0136</v>
       </c>
       <c r="H12" t="n">
-        <v>190</v>
+        <v>112.1</v>
       </c>
       <c r="I12" t="n">
-        <v>4088.4</v>
+        <v>4007.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4135.5</v>
+        <v>4156.05</v>
       </c>
       <c r="K12" t="n">
-        <v>4190.2</v>
+        <v>4233.3</v>
       </c>
       <c r="L12" t="n">
-        <v>4244.9</v>
+        <v>4310.55</v>
       </c>
       <c r="M12" t="n">
-        <v>4295.8</v>
+        <v>4423.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4346.7</v>
+        <v>4536.05</v>
       </c>
       <c r="O12" t="n">
-        <v>4405.2</v>
+        <v>4577.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1529,13 +1527,11 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1550,50 +1546,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4330</v>
+        <v>4369.9</v>
       </c>
       <c r="C13" t="n">
-        <v>4409.5</v>
+        <v>4584</v>
       </c>
       <c r="D13" t="n">
-        <v>4297.4</v>
+        <v>4367.9</v>
       </c>
       <c r="E13" t="n">
-        <v>4387.3</v>
+        <v>4552.7</v>
       </c>
       <c r="F13" t="n">
-        <v>59</v>
+        <v>165.4</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0136</v>
+        <v>0.0377</v>
       </c>
       <c r="H13" t="n">
-        <v>112.1</v>
+        <v>216.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4007.8</v>
+        <v>4185.3</v>
       </c>
       <c r="J13" t="n">
-        <v>4156.05</v>
+        <v>4292.12</v>
       </c>
       <c r="K13" t="n">
-        <v>4233.3</v>
+        <v>4331.25</v>
       </c>
       <c r="L13" t="n">
-        <v>4310.55</v>
+        <v>4370.37</v>
       </c>
       <c r="M13" t="n">
-        <v>4423.3</v>
+        <v>4443.35</v>
       </c>
       <c r="N13" t="n">
-        <v>4536.05</v>
+        <v>4516.32</v>
       </c>
       <c r="O13" t="n">
-        <v>4577.8</v>
+        <v>4521.6</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1611,14 +1607,18 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1630,83 +1630,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4369.9</v>
+        <v>4568</v>
       </c>
       <c r="C14" t="n">
-        <v>4584</v>
+        <v>4581.3</v>
       </c>
       <c r="D14" t="n">
-        <v>4367.9</v>
+        <v>4284.3</v>
       </c>
       <c r="E14" t="n">
-        <v>4552.7</v>
+        <v>4329.6</v>
       </c>
       <c r="F14" t="n">
-        <v>165.4</v>
+        <v>-223.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0377</v>
+        <v>-0.049</v>
       </c>
       <c r="H14" t="n">
-        <v>216.1</v>
+        <v>297</v>
       </c>
       <c r="I14" t="n">
-        <v>4185.3</v>
+        <v>4151.8</v>
       </c>
       <c r="J14" t="n">
-        <v>4292.12</v>
+        <v>4374.98</v>
       </c>
       <c r="K14" t="n">
-        <v>4331.25</v>
+        <v>4444.65</v>
       </c>
       <c r="L14" t="n">
-        <v>4370.37</v>
+        <v>4514.33</v>
       </c>
       <c r="M14" t="n">
-        <v>4443.35</v>
+        <v>4660.75</v>
       </c>
       <c r="N14" t="n">
-        <v>4516.32</v>
+        <v>4807.18</v>
       </c>
       <c r="O14" t="n">
-        <v>4521.6</v>
+        <v>4800.1</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1714,72 +1712,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4568</v>
+        <v>4368.3</v>
       </c>
       <c r="C15" t="n">
-        <v>4581.3</v>
+        <v>4527</v>
       </c>
       <c r="D15" t="n">
-        <v>4284.3</v>
+        <v>4354.6</v>
       </c>
       <c r="E15" t="n">
-        <v>4329.6</v>
+        <v>4500.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-223.1</v>
+        <v>171.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.049</v>
+        <v>0.0396</v>
       </c>
       <c r="H15" t="n">
-        <v>297</v>
+        <v>172.4</v>
       </c>
       <c r="I15" t="n">
-        <v>4151.8</v>
+        <v>3987.3</v>
       </c>
       <c r="J15" t="n">
-        <v>4374.98</v>
+        <v>3981</v>
       </c>
       <c r="K15" t="n">
-        <v>4444.65</v>
+        <v>4181.1</v>
       </c>
       <c r="L15" t="n">
-        <v>4514.33</v>
+        <v>4381.2</v>
       </c>
       <c r="M15" t="n">
-        <v>4660.75</v>
+        <v>4478.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4807.18</v>
+        <v>4575</v>
       </c>
       <c r="O15" t="n">
-        <v>4800.1</v>
+        <v>4878.3</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1791,55 +1787,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4368.3</v>
+        <v>4529.1</v>
       </c>
       <c r="C16" t="n">
-        <v>4527</v>
+        <v>4650.5</v>
       </c>
       <c r="D16" t="n">
-        <v>4354.6</v>
+        <v>4520.8</v>
       </c>
       <c r="E16" t="n">
-        <v>4500.9</v>
+        <v>4595.4</v>
       </c>
       <c r="F16" t="n">
-        <v>171.3</v>
+        <v>94.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0396</v>
+        <v>0.021</v>
       </c>
       <c r="H16" t="n">
-        <v>172.4</v>
+        <v>129.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3987.3</v>
+        <v>4182.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3981</v>
+        <v>4358.55</v>
       </c>
       <c r="K16" t="n">
-        <v>4181.1</v>
+        <v>4414.7</v>
       </c>
       <c r="L16" t="n">
-        <v>4381.2</v>
+        <v>4470.85</v>
       </c>
       <c r="M16" t="n">
-        <v>4478.1</v>
+        <v>4587.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4575</v>
+        <v>4703.35</v>
       </c>
       <c r="O16" t="n">
-        <v>4878.3</v>
+        <v>4699.4</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1873,57 +1873,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4529.1</v>
+        <v>4633.7</v>
       </c>
       <c r="C17" t="n">
-        <v>4650.5</v>
+        <v>4991.4</v>
       </c>
       <c r="D17" t="n">
-        <v>4520.8</v>
+        <v>4622.2</v>
       </c>
       <c r="E17" t="n">
-        <v>4595.4</v>
+        <v>4979.7</v>
       </c>
       <c r="F17" t="n">
-        <v>94.5</v>
+        <v>384.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.021</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>129.7</v>
+        <v>369.2</v>
       </c>
       <c r="I17" t="n">
-        <v>4182.2</v>
+        <v>4391.1</v>
       </c>
       <c r="J17" t="n">
-        <v>4358.55</v>
+        <v>4470.57</v>
       </c>
       <c r="K17" t="n">
-        <v>4414.7</v>
+        <v>4530.55</v>
       </c>
       <c r="L17" t="n">
-        <v>4470.85</v>
+        <v>4590.52</v>
       </c>
       <c r="M17" t="n">
-        <v>4587.1</v>
+        <v>4660.25</v>
       </c>
       <c r="N17" t="n">
-        <v>4703.35</v>
+        <v>4729.98</v>
       </c>
       <c r="O17" t="n">
-        <v>4699.4</v>
+        <v>4780.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1941,86 +1941,90 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4633.7</v>
+        <v>5013.4</v>
       </c>
       <c r="C18" t="n">
-        <v>4991.4</v>
+        <v>5586.2</v>
       </c>
       <c r="D18" t="n">
-        <v>4622.2</v>
+        <v>4700.4</v>
       </c>
       <c r="E18" t="n">
-        <v>4979.7</v>
+        <v>4745.1</v>
       </c>
       <c r="F18" t="n">
-        <v>384.3</v>
+        <v>-234.6</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.0471</v>
       </c>
       <c r="H18" t="n">
-        <v>369.2</v>
+        <v>885.8</v>
       </c>
       <c r="I18" t="n">
-        <v>4391.1</v>
+        <v>4253</v>
       </c>
       <c r="J18" t="n">
-        <v>4470.57</v>
+        <v>4696.95</v>
       </c>
       <c r="K18" t="n">
-        <v>4530.55</v>
+        <v>4795.1</v>
       </c>
       <c r="L18" t="n">
-        <v>4590.52</v>
+        <v>4893.25</v>
       </c>
       <c r="M18" t="n">
-        <v>4660.25</v>
+        <v>5164.3</v>
       </c>
       <c r="N18" t="n">
-        <v>4729.98</v>
+        <v>5435.35</v>
       </c>
       <c r="O18" t="n">
-        <v>4780.2</v>
+        <v>5360.6</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2035,7 +2039,7 @@
       </c>
       <c r="V18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
@@ -2043,88 +2047,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5013.4</v>
+        <v>4816</v>
       </c>
       <c r="C19" t="n">
-        <v>5586.2</v>
+        <v>5113.9</v>
       </c>
       <c r="D19" t="n">
-        <v>4700.4</v>
+        <v>4423.2</v>
       </c>
       <c r="E19" t="n">
-        <v>4745.1</v>
+        <v>4979.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-234.6</v>
+        <v>234.7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0471</v>
+        <v>0.0495</v>
       </c>
       <c r="H19" t="n">
-        <v>885.8</v>
+        <v>690.7</v>
       </c>
       <c r="I19" t="n">
-        <v>4253</v>
+        <v>3814.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4696.95</v>
+        <v>3660.2</v>
       </c>
       <c r="K19" t="n">
-        <v>4795.1</v>
+        <v>4302.2</v>
       </c>
       <c r="L19" t="n">
-        <v>4893.25</v>
+        <v>4944.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5164.3</v>
+        <v>5188</v>
       </c>
       <c r="N19" t="n">
-        <v>5435.35</v>
+        <v>5431.8</v>
       </c>
       <c r="O19" t="n">
-        <v>5360.6</v>
+        <v>6472</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2133,57 +2131,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4816</v>
+        <v>5003.6</v>
       </c>
       <c r="C20" t="n">
-        <v>5113.9</v>
+        <v>5144.5</v>
       </c>
       <c r="D20" t="n">
-        <v>4423.2</v>
+        <v>4900</v>
       </c>
       <c r="E20" t="n">
-        <v>4979.8</v>
+        <v>5046.3</v>
       </c>
       <c r="F20" t="n">
-        <v>234.7</v>
+        <v>66.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0495</v>
+        <v>0.0134</v>
       </c>
       <c r="H20" t="n">
-        <v>690.7</v>
+        <v>244.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3814.6</v>
+        <v>3732.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3660.2</v>
+        <v>4394.72</v>
       </c>
       <c r="K20" t="n">
-        <v>4302.2</v>
+        <v>4634.45</v>
       </c>
       <c r="L20" t="n">
-        <v>4944.2</v>
+        <v>4874.17</v>
       </c>
       <c r="M20" t="n">
-        <v>5188</v>
+        <v>5325.15</v>
       </c>
       <c r="N20" t="n">
-        <v>5431.8</v>
+        <v>5776.12</v>
       </c>
       <c r="O20" t="n">
-        <v>6472</v>
+        <v>5804.6</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2213,59 +2211,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5003.6</v>
+        <v>5050</v>
       </c>
       <c r="C21" t="n">
-        <v>5144.5</v>
+        <v>5131</v>
       </c>
       <c r="D21" t="n">
-        <v>4900</v>
+        <v>4854.2</v>
       </c>
       <c r="E21" t="n">
-        <v>5046.3</v>
+        <v>5080.9</v>
       </c>
       <c r="F21" t="n">
-        <v>66.5</v>
+        <v>34.6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0069</v>
       </c>
       <c r="H21" t="n">
-        <v>244.5</v>
+        <v>276.8</v>
       </c>
       <c r="I21" t="n">
-        <v>3732.5</v>
+        <v>4655.5</v>
       </c>
       <c r="J21" t="n">
-        <v>4394.72</v>
+        <v>4813.82</v>
       </c>
       <c r="K21" t="n">
-        <v>4634.45</v>
+        <v>4924.05</v>
       </c>
       <c r="L21" t="n">
-        <v>4874.17</v>
+        <v>5034.27</v>
       </c>
       <c r="M21" t="n">
-        <v>5325.15</v>
+        <v>5168.55</v>
       </c>
       <c r="N21" t="n">
-        <v>5776.12</v>
+        <v>5302.82</v>
       </c>
       <c r="O21" t="n">
-        <v>5804.6</v>
+        <v>5389</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,8 +2267,10 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
@@ -2295,55 +2291,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5050</v>
+        <v>5128.8</v>
       </c>
       <c r="C22" t="n">
-        <v>5131</v>
+        <v>5299</v>
       </c>
       <c r="D22" t="n">
-        <v>4854.2</v>
+        <v>5109.5</v>
       </c>
       <c r="E22" t="n">
-        <v>5080.9</v>
+        <v>5247.9</v>
       </c>
       <c r="F22" t="n">
-        <v>34.6</v>
+        <v>167</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0069</v>
+        <v>0.0329</v>
       </c>
       <c r="H22" t="n">
-        <v>276.8</v>
+        <v>189.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4655.5</v>
+        <v>4577.4</v>
       </c>
       <c r="J22" t="n">
-        <v>4813.82</v>
+        <v>4848.25</v>
       </c>
       <c r="K22" t="n">
-        <v>4924.05</v>
+        <v>4942.5</v>
       </c>
       <c r="L22" t="n">
-        <v>5034.27</v>
+        <v>5036.75</v>
       </c>
       <c r="M22" t="n">
-        <v>5168.55</v>
+        <v>5219.3</v>
       </c>
       <c r="N22" t="n">
-        <v>5302.82</v>
+        <v>5401.85</v>
       </c>
       <c r="O22" t="n">
-        <v>5389</v>
+        <v>5407.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2351,18 +2351,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2375,77 +2375,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5128.8</v>
+        <v>5360</v>
       </c>
       <c r="C23" t="n">
-        <v>5299</v>
+        <v>5434.1</v>
       </c>
       <c r="D23" t="n">
-        <v>5109.5</v>
+        <v>5005</v>
       </c>
       <c r="E23" t="n">
-        <v>5247.9</v>
+        <v>5158.7</v>
       </c>
       <c r="F23" t="n">
-        <v>167</v>
+        <v>-89.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0329</v>
+        <v>-0.017</v>
       </c>
       <c r="H23" t="n">
-        <v>189.5</v>
+        <v>429.1</v>
       </c>
       <c r="I23" t="n">
-        <v>4577.4</v>
+        <v>4920</v>
       </c>
       <c r="J23" t="n">
-        <v>4848.25</v>
+        <v>5080.22</v>
       </c>
       <c r="K23" t="n">
-        <v>4942.5</v>
+        <v>5153.15</v>
       </c>
       <c r="L23" t="n">
-        <v>5036.75</v>
+        <v>5226.07</v>
       </c>
       <c r="M23" t="n">
-        <v>5219.3</v>
+        <v>5342.65</v>
       </c>
       <c r="N23" t="n">
-        <v>5401.85</v>
+        <v>5459.22</v>
       </c>
       <c r="O23" t="n">
-        <v>5407.8</v>
+        <v>5488.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U23" s="8" t="n">
@@ -2459,63 +2459,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5360</v>
+        <v>5186.7</v>
       </c>
       <c r="C24" t="n">
-        <v>5434.1</v>
+        <v>5248.7</v>
       </c>
       <c r="D24" t="n">
-        <v>5005</v>
+        <v>5014.1</v>
       </c>
       <c r="E24" t="n">
-        <v>5158.7</v>
+        <v>5061.7</v>
       </c>
       <c r="F24" t="n">
-        <v>-89.2</v>
+        <v>-97</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.017</v>
+        <v>-0.0188</v>
       </c>
       <c r="H24" t="n">
-        <v>429.1</v>
+        <v>234.6</v>
       </c>
       <c r="I24" t="n">
-        <v>4920</v>
+        <v>4575.9</v>
       </c>
       <c r="J24" t="n">
-        <v>5080.22</v>
+        <v>4699.18</v>
       </c>
       <c r="K24" t="n">
-        <v>5153.15</v>
+        <v>4944.15</v>
       </c>
       <c r="L24" t="n">
-        <v>5226.07</v>
+        <v>5189.13</v>
       </c>
       <c r="M24" t="n">
-        <v>5342.65</v>
+        <v>5373.25</v>
       </c>
       <c r="N24" t="n">
-        <v>5459.22</v>
+        <v>5557.38</v>
       </c>
       <c r="O24" t="n">
-        <v>5488.5</v>
+        <v>5863.2</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
@@ -2527,10 +2529,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2552,60 +2552,64 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5186.7</v>
+        <v>5010</v>
       </c>
       <c r="C25" t="n">
-        <v>5248.7</v>
+        <v>5049.4</v>
       </c>
       <c r="D25" t="n">
-        <v>5014.1</v>
+        <v>4478.4</v>
       </c>
       <c r="E25" t="n">
-        <v>5061.7</v>
+        <v>4574.9</v>
       </c>
       <c r="F25" t="n">
-        <v>-97</v>
+        <v>-486.8</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0188</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>234.6</v>
+        <v>571</v>
       </c>
       <c r="I25" t="n">
-        <v>4575.9</v>
+        <v>4779.5</v>
       </c>
       <c r="J25" t="n">
-        <v>4699.18</v>
+        <v>4792.25</v>
       </c>
       <c r="K25" t="n">
-        <v>4944.15</v>
+        <v>4944.4</v>
       </c>
       <c r="L25" t="n">
-        <v>5189.13</v>
+        <v>5096.55</v>
       </c>
       <c r="M25" t="n">
-        <v>5373.25</v>
+        <v>5179</v>
       </c>
       <c r="N25" t="n">
-        <v>5557.38</v>
+        <v>5261.45</v>
       </c>
       <c r="O25" t="n">
-        <v>5863.2</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+        <v>5483.3</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
@@ -2622,83 +2626,75 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5010</v>
+        <v>4450</v>
       </c>
       <c r="C26" t="n">
-        <v>5049.4</v>
+        <v>4601</v>
       </c>
       <c r="D26" t="n">
-        <v>4478.4</v>
+        <v>4100</v>
       </c>
       <c r="E26" t="n">
-        <v>4574.9</v>
+        <v>4492.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-486.8</v>
+        <v>-82.40000000000001</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="H26" t="n">
-        <v>571</v>
+        <v>501</v>
       </c>
       <c r="I26" t="n">
-        <v>4779.5</v>
+        <v>3907.4</v>
       </c>
       <c r="J26" t="n">
-        <v>4792.25</v>
+        <v>3909.4</v>
       </c>
       <c r="K26" t="n">
-        <v>4944.4</v>
+        <v>4289.4</v>
       </c>
       <c r="L26" t="n">
-        <v>5096.55</v>
+        <v>4669.4</v>
       </c>
       <c r="M26" t="n">
-        <v>5179</v>
+        <v>4860.4</v>
       </c>
       <c r="N26" t="n">
-        <v>5261.45</v>
+        <v>5051.4</v>
       </c>
       <c r="O26" t="n">
-        <v>5483.3</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
+        <v>5620.4</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2720,50 +2716,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4450</v>
+        <v>4482.8</v>
       </c>
       <c r="C27" t="n">
-        <v>4601</v>
+        <v>4825.9</v>
       </c>
       <c r="D27" t="n">
-        <v>4100</v>
+        <v>4413.4</v>
       </c>
       <c r="E27" t="n">
-        <v>4492.5</v>
+        <v>4679.7</v>
       </c>
       <c r="F27" t="n">
-        <v>-82.40000000000001</v>
+        <v>187.2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0417</v>
       </c>
       <c r="H27" t="n">
-        <v>501</v>
+        <v>412.5</v>
       </c>
       <c r="I27" t="n">
-        <v>3907.4</v>
+        <v>3599</v>
       </c>
       <c r="J27" t="n">
-        <v>3909.4</v>
+        <v>4062.5</v>
       </c>
       <c r="K27" t="n">
-        <v>4289.4</v>
+        <v>4242</v>
       </c>
       <c r="L27" t="n">
-        <v>4669.4</v>
+        <v>4421.5</v>
       </c>
       <c r="M27" t="n">
-        <v>4860.4</v>
+        <v>4743</v>
       </c>
       <c r="N27" t="n">
-        <v>5051.4</v>
+        <v>5064.5</v>
       </c>
       <c r="O27" t="n">
-        <v>5620.4</v>
+        <v>5102</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2771,18 +2767,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2795,55 +2791,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4482.8</v>
+        <v>4675</v>
       </c>
       <c r="C28" t="n">
-        <v>4825.9</v>
+        <v>4888</v>
       </c>
       <c r="D28" t="n">
-        <v>4413.4</v>
+        <v>4626.2</v>
       </c>
       <c r="E28" t="n">
-        <v>4679.7</v>
+        <v>4787.4</v>
       </c>
       <c r="F28" t="n">
-        <v>187.2</v>
+        <v>107.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0417</v>
+        <v>0.023</v>
       </c>
       <c r="H28" t="n">
-        <v>412.5</v>
+        <v>261.8</v>
       </c>
       <c r="I28" t="n">
-        <v>3599</v>
+        <v>4000.9</v>
       </c>
       <c r="J28" t="n">
-        <v>4062.5</v>
+        <v>4297.23</v>
       </c>
       <c r="K28" t="n">
-        <v>4242</v>
+        <v>4473.45</v>
       </c>
       <c r="L28" t="n">
-        <v>4421.5</v>
+        <v>4649.68</v>
       </c>
       <c r="M28" t="n">
-        <v>4743</v>
+        <v>4885.95</v>
       </c>
       <c r="N28" t="n">
-        <v>5064.5</v>
+        <v>5122.23</v>
       </c>
       <c r="O28" t="n">
-        <v>5102</v>
+        <v>5238.4</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2884,50 +2884,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4675</v>
+        <v>4710</v>
       </c>
       <c r="C29" t="n">
-        <v>4888</v>
+        <v>4917.7</v>
       </c>
       <c r="D29" t="n">
-        <v>4626.2</v>
+        <v>4626</v>
       </c>
       <c r="E29" t="n">
-        <v>4787.4</v>
+        <v>4879.6</v>
       </c>
       <c r="F29" t="n">
-        <v>107.7</v>
+        <v>92.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.023</v>
+        <v>0.0193</v>
       </c>
       <c r="H29" t="n">
-        <v>261.8</v>
+        <v>291.7</v>
       </c>
       <c r="I29" t="n">
-        <v>4000.9</v>
+        <v>4364.4</v>
       </c>
       <c r="J29" t="n">
-        <v>4297.23</v>
+        <v>4540.75</v>
       </c>
       <c r="K29" t="n">
-        <v>4473.45</v>
+        <v>4656.5</v>
       </c>
       <c r="L29" t="n">
-        <v>4649.68</v>
+        <v>4772.25</v>
       </c>
       <c r="M29" t="n">
-        <v>4885.95</v>
+        <v>4918.3</v>
       </c>
       <c r="N29" t="n">
-        <v>5122.23</v>
+        <v>5064.35</v>
       </c>
       <c r="O29" t="n">
-        <v>5238.4</v>
+        <v>5149.8</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2935,8 +2935,10 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
@@ -2961,57 +2963,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4710</v>
+        <v>4811.8</v>
       </c>
       <c r="C30" t="n">
-        <v>4917.7</v>
+        <v>4854.8</v>
       </c>
       <c r="D30" t="n">
-        <v>4626</v>
+        <v>4672.2</v>
       </c>
       <c r="E30" t="n">
-        <v>4879.6</v>
+        <v>4740.9</v>
       </c>
       <c r="F30" t="n">
-        <v>92.2</v>
+        <v>-138.7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0193</v>
+        <v>-0.0284</v>
       </c>
       <c r="H30" t="n">
-        <v>291.7</v>
+        <v>182.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4364.4</v>
+        <v>4334.3</v>
       </c>
       <c r="J30" t="n">
-        <v>4540.75</v>
+        <v>4641.77</v>
       </c>
       <c r="K30" t="n">
-        <v>4656.5</v>
+        <v>4733.75</v>
       </c>
       <c r="L30" t="n">
-        <v>4772.25</v>
+        <v>4825.73</v>
       </c>
       <c r="M30" t="n">
-        <v>4918.3</v>
+        <v>5025.45</v>
       </c>
       <c r="N30" t="n">
-        <v>5064.35</v>
+        <v>5225.18</v>
       </c>
       <c r="O30" t="n">
-        <v>5149.8</v>
+        <v>5209.4</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3021,19 +3023,17 @@
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3047,63 +3047,65 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4811.8</v>
+        <v>4713.1</v>
       </c>
       <c r="C31" t="n">
-        <v>4854.8</v>
+        <v>4745.8</v>
       </c>
       <c r="D31" t="n">
-        <v>4672.2</v>
+        <v>4522.2</v>
       </c>
       <c r="E31" t="n">
-        <v>4740.9</v>
+        <v>4644.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-138.7</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0284</v>
+        <v>-0.0203</v>
       </c>
       <c r="H31" t="n">
-        <v>182.6</v>
+        <v>223.6</v>
       </c>
       <c r="I31" t="n">
-        <v>4334.3</v>
+        <v>4489.6</v>
       </c>
       <c r="J31" t="n">
-        <v>4641.77</v>
+        <v>4547</v>
       </c>
       <c r="K31" t="n">
-        <v>4733.75</v>
+        <v>4649.6</v>
       </c>
       <c r="L31" t="n">
-        <v>4825.73</v>
+        <v>4752.2</v>
       </c>
       <c r="M31" t="n">
-        <v>5025.45</v>
+        <v>4832.2</v>
       </c>
       <c r="N31" t="n">
-        <v>5225.18</v>
+        <v>4912.2</v>
       </c>
       <c r="O31" t="n">
-        <v>5209.4</v>
+        <v>5037.4</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
@@ -3129,81 +3131,77 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4713.1</v>
+        <v>4644</v>
       </c>
       <c r="C32" t="n">
-        <v>4745.8</v>
+        <v>4775.2</v>
       </c>
       <c r="D32" t="n">
-        <v>4522.2</v>
+        <v>4510.1</v>
       </c>
       <c r="E32" t="n">
-        <v>4644.5</v>
+        <v>4730.7</v>
       </c>
       <c r="F32" t="n">
-        <v>-96.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0186</v>
       </c>
       <c r="H32" t="n">
-        <v>223.6</v>
+        <v>265.1</v>
       </c>
       <c r="I32" t="n">
-        <v>4489.6</v>
+        <v>4298.6</v>
       </c>
       <c r="J32" t="n">
-        <v>4547</v>
+        <v>4426.15</v>
       </c>
       <c r="K32" t="n">
-        <v>4649.6</v>
+        <v>4532.7</v>
       </c>
       <c r="L32" t="n">
-        <v>4752.2</v>
+        <v>4639.25</v>
       </c>
       <c r="M32" t="n">
-        <v>4832.2</v>
+        <v>4756.3</v>
       </c>
       <c r="N32" t="n">
-        <v>4912.2</v>
+        <v>4873.35</v>
       </c>
       <c r="O32" t="n">
-        <v>5037.4</v>
+        <v>4969.4</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3215,55 +3213,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4644</v>
+        <v>4690</v>
       </c>
       <c r="C33" t="n">
-        <v>4775.2</v>
+        <v>4783.4</v>
       </c>
       <c r="D33" t="n">
-        <v>4510.1</v>
+        <v>4513.8</v>
       </c>
       <c r="E33" t="n">
-        <v>4730.7</v>
+        <v>4561.9</v>
       </c>
       <c r="F33" t="n">
-        <v>86.2</v>
+        <v>-168.8</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0357</v>
       </c>
       <c r="H33" t="n">
-        <v>265.1</v>
+        <v>269.6</v>
       </c>
       <c r="I33" t="n">
-        <v>4298.6</v>
+        <v>4245</v>
       </c>
       <c r="J33" t="n">
-        <v>4426.15</v>
+        <v>4509.63</v>
       </c>
       <c r="K33" t="n">
-        <v>4532.7</v>
+        <v>4598.15</v>
       </c>
       <c r="L33" t="n">
-        <v>4639.25</v>
+        <v>4686.68</v>
       </c>
       <c r="M33" t="n">
-        <v>4756.3</v>
+        <v>4863.25</v>
       </c>
       <c r="N33" t="n">
-        <v>4873.35</v>
+        <v>5039.83</v>
       </c>
       <c r="O33" t="n">
-        <v>4969.4</v>
+        <v>5040.3</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,18 +3275,16 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3306,50 +3306,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4690</v>
+        <v>4547.6</v>
       </c>
       <c r="C34" t="n">
-        <v>4783.4</v>
+        <v>4593.2</v>
       </c>
       <c r="D34" t="n">
-        <v>4513.8</v>
+        <v>4455</v>
       </c>
       <c r="E34" t="n">
-        <v>4561.9</v>
+        <v>4523.2</v>
       </c>
       <c r="F34" t="n">
-        <v>-168.8</v>
+        <v>-38.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0357</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>269.6</v>
+        <v>138.2</v>
       </c>
       <c r="I34" t="n">
-        <v>4245</v>
+        <v>4244.2</v>
       </c>
       <c r="J34" t="n">
-        <v>4509.63</v>
+        <v>4248.95</v>
       </c>
       <c r="K34" t="n">
-        <v>4598.15</v>
+        <v>4427.1</v>
       </c>
       <c r="L34" t="n">
-        <v>4686.68</v>
+        <v>4605.25</v>
       </c>
       <c r="M34" t="n">
-        <v>4863.25</v>
+        <v>4696.7</v>
       </c>
       <c r="N34" t="n">
-        <v>5039.83</v>
+        <v>4788.15</v>
       </c>
       <c r="O34" t="n">
-        <v>5040.3</v>
+        <v>5053</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3357,14 +3357,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3381,76 +3379,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4547.6</v>
+        <v>4532</v>
       </c>
       <c r="C35" t="n">
-        <v>4593.2</v>
+        <v>4627.1</v>
       </c>
       <c r="D35" t="n">
-        <v>4455</v>
+        <v>4363.5</v>
       </c>
       <c r="E35" t="n">
-        <v>4523.2</v>
+        <v>4593</v>
       </c>
       <c r="F35" t="n">
-        <v>-38.7</v>
+        <v>69.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H35" t="n">
-        <v>138.2</v>
+        <v>263.6</v>
       </c>
       <c r="I35" t="n">
-        <v>4244.2</v>
+        <v>4316.8</v>
       </c>
       <c r="J35" t="n">
-        <v>4248.95</v>
+        <v>4384.55</v>
       </c>
       <c r="K35" t="n">
-        <v>4427.1</v>
+        <v>4454.1</v>
       </c>
       <c r="L35" t="n">
-        <v>4605.25</v>
+        <v>4523.65</v>
       </c>
       <c r="M35" t="n">
-        <v>4696.7</v>
+        <v>4592.3</v>
       </c>
       <c r="N35" t="n">
-        <v>4788.15</v>
+        <v>4660.95</v>
       </c>
       <c r="O35" t="n">
-        <v>5053</v>
+        <v>4731.4</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3463,78 +3463,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4532</v>
+        <v>4575.2</v>
       </c>
       <c r="C36" t="n">
-        <v>4627.1</v>
+        <v>4577.3</v>
       </c>
       <c r="D36" t="n">
-        <v>4363.5</v>
+        <v>4336.6</v>
       </c>
       <c r="E36" t="n">
-        <v>4593</v>
+        <v>4365.3</v>
       </c>
       <c r="F36" t="n">
-        <v>69.8</v>
+        <v>-227.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0154</v>
+        <v>-0.0496</v>
       </c>
       <c r="H36" t="n">
-        <v>263.6</v>
+        <v>240.7</v>
       </c>
       <c r="I36" t="n">
-        <v>4316.8</v>
+        <v>4099.9</v>
       </c>
       <c r="J36" t="n">
-        <v>4384.55</v>
+        <v>4378.25</v>
       </c>
       <c r="K36" t="n">
-        <v>4454.1</v>
+        <v>4461.2</v>
       </c>
       <c r="L36" t="n">
-        <v>4523.65</v>
+        <v>4544.15</v>
       </c>
       <c r="M36" t="n">
-        <v>4592.3</v>
+        <v>4724.8</v>
       </c>
       <c r="N36" t="n">
-        <v>4660.95</v>
+        <v>4905.45</v>
       </c>
       <c r="O36" t="n">
-        <v>4731.4</v>
+        <v>4890.7</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3547,71 +3549,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4575.2</v>
+        <v>4354</v>
       </c>
       <c r="C37" t="n">
-        <v>4577.3</v>
+        <v>4388.6</v>
       </c>
       <c r="D37" t="n">
-        <v>4336.6</v>
+        <v>4046.2</v>
       </c>
       <c r="E37" t="n">
-        <v>4365.3</v>
+        <v>4238.8</v>
       </c>
       <c r="F37" t="n">
-        <v>-227.7</v>
+        <v>-126.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0496</v>
+        <v>-0.029</v>
       </c>
       <c r="H37" t="n">
-        <v>240.7</v>
+        <v>342.4</v>
       </c>
       <c r="I37" t="n">
-        <v>4099.9</v>
+        <v>4095.9</v>
       </c>
       <c r="J37" t="n">
-        <v>4378.25</v>
+        <v>4078.78</v>
       </c>
       <c r="K37" t="n">
-        <v>4461.2</v>
+        <v>4244.95</v>
       </c>
       <c r="L37" t="n">
-        <v>4544.15</v>
+        <v>4411.12</v>
       </c>
       <c r="M37" t="n">
-        <v>4724.8</v>
+        <v>4485.65</v>
       </c>
       <c r="N37" t="n">
-        <v>4905.45</v>
+        <v>4560.17</v>
       </c>
       <c r="O37" t="n">
-        <v>4890.7</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
+        <v>4818</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
@@ -3638,69 +3638,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4354</v>
+        <v>4289.4</v>
       </c>
       <c r="C38" t="n">
-        <v>4388.6</v>
+        <v>4403.6</v>
       </c>
       <c r="D38" t="n">
-        <v>4046.2</v>
+        <v>4138.7</v>
       </c>
       <c r="E38" t="n">
-        <v>4238.8</v>
+        <v>4172.9</v>
       </c>
       <c r="F38" t="n">
-        <v>-126.5</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.029</v>
+        <v>-0.0155</v>
       </c>
       <c r="H38" t="n">
-        <v>342.4</v>
+        <v>264.9</v>
       </c>
       <c r="I38" t="n">
-        <v>4095.9</v>
+        <v>3703.8</v>
       </c>
       <c r="J38" t="n">
-        <v>4078.78</v>
+        <v>3907.1</v>
       </c>
       <c r="K38" t="n">
-        <v>4244.95</v>
+        <v>4067.6</v>
       </c>
       <c r="L38" t="n">
-        <v>4411.12</v>
+        <v>4228.1</v>
       </c>
       <c r="M38" t="n">
-        <v>4485.65</v>
+        <v>4410</v>
       </c>
       <c r="N38" t="n">
-        <v>4560.17</v>
+        <v>4591.9</v>
       </c>
       <c r="O38" t="n">
-        <v>4818</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4731</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3717,55 +3711,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4289.4</v>
+        <v>4163.9</v>
       </c>
       <c r="C39" t="n">
-        <v>4403.6</v>
+        <v>4238.1</v>
       </c>
       <c r="D39" t="n">
-        <v>4138.7</v>
+        <v>3975.7</v>
       </c>
       <c r="E39" t="n">
-        <v>4172.9</v>
+        <v>4096.3</v>
       </c>
       <c r="F39" t="n">
-        <v>-65.90000000000001</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0184</v>
       </c>
       <c r="H39" t="n">
-        <v>264.9</v>
+        <v>262.4</v>
       </c>
       <c r="I39" t="n">
-        <v>3703.8</v>
+        <v>3873.8</v>
       </c>
       <c r="J39" t="n">
-        <v>3907.1</v>
+        <v>3858.87</v>
       </c>
       <c r="K39" t="n">
-        <v>4067.6</v>
+        <v>4040.45</v>
       </c>
       <c r="L39" t="n">
-        <v>4228.1</v>
+        <v>4222.03</v>
       </c>
       <c r="M39" t="n">
-        <v>4410</v>
+        <v>4305.35</v>
       </c>
       <c r="N39" t="n">
-        <v>4591.9</v>
+        <v>4388.67</v>
       </c>
       <c r="O39" t="n">
-        <v>4731</v>
+        <v>4668.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3773,12 +3771,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3795,59 +3795,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4163.9</v>
+        <v>4101.1</v>
       </c>
       <c r="C40" t="n">
-        <v>4238.1</v>
+        <v>4208.3</v>
       </c>
       <c r="D40" t="n">
-        <v>3975.7</v>
+        <v>3955.4</v>
       </c>
       <c r="E40" t="n">
-        <v>4096.3</v>
+        <v>4187.3</v>
       </c>
       <c r="F40" t="n">
-        <v>-76.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0222</v>
       </c>
       <c r="H40" t="n">
-        <v>262.4</v>
+        <v>252.9</v>
       </c>
       <c r="I40" t="n">
-        <v>3873.8</v>
+        <v>3713.3</v>
       </c>
       <c r="J40" t="n">
-        <v>3858.87</v>
+        <v>3828.6</v>
       </c>
       <c r="K40" t="n">
-        <v>4040.45</v>
+        <v>3965.1</v>
       </c>
       <c r="L40" t="n">
-        <v>4222.03</v>
+        <v>4101.6</v>
       </c>
       <c r="M40" t="n">
-        <v>4305.35</v>
+        <v>4227.5</v>
       </c>
       <c r="N40" t="n">
-        <v>4388.67</v>
+        <v>4353.4</v>
       </c>
       <c r="O40" t="n">
-        <v>4668.5</v>
+        <v>4500.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3857,17 +3853,19 @@
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3879,55 +3877,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4101.1</v>
+        <v>4187.5</v>
       </c>
       <c r="C41" t="n">
-        <v>4208.3</v>
+        <v>4215.5</v>
       </c>
       <c r="D41" t="n">
-        <v>3955.4</v>
+        <v>4032.5</v>
       </c>
       <c r="E41" t="n">
-        <v>4187.3</v>
+        <v>4113.7</v>
       </c>
       <c r="F41" t="n">
-        <v>91</v>
+        <v>-73.59999999999999</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0222</v>
+        <v>-0.0176</v>
       </c>
       <c r="H41" t="n">
-        <v>252.9</v>
+        <v>183</v>
       </c>
       <c r="I41" t="n">
-        <v>3713.3</v>
+        <v>3702.5</v>
       </c>
       <c r="J41" t="n">
-        <v>3828.6</v>
+        <v>3987.12</v>
       </c>
       <c r="K41" t="n">
-        <v>3965.1</v>
+        <v>4060.85</v>
       </c>
       <c r="L41" t="n">
-        <v>4101.6</v>
+        <v>4134.57</v>
       </c>
       <c r="M41" t="n">
-        <v>4227.5</v>
+        <v>4313.75</v>
       </c>
       <c r="N41" t="n">
-        <v>4353.4</v>
+        <v>4492.92</v>
       </c>
       <c r="O41" t="n">
-        <v>4500.5</v>
+        <v>4461.2</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3940,15 +3942,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3963,57 +3963,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4187.5</v>
+        <v>4106.6</v>
       </c>
       <c r="C42" t="n">
-        <v>4215.5</v>
+        <v>4112.5</v>
       </c>
       <c r="D42" t="n">
-        <v>4032.5</v>
+        <v>3963</v>
       </c>
       <c r="E42" t="n">
-        <v>4113.7</v>
+        <v>4018.8</v>
       </c>
       <c r="F42" t="n">
-        <v>-73.59999999999999</v>
+        <v>-94.90000000000001</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0176</v>
+        <v>-0.0231</v>
       </c>
       <c r="H42" t="n">
-        <v>183</v>
+        <v>149.5</v>
       </c>
       <c r="I42" t="n">
-        <v>3702.5</v>
+        <v>3849.5</v>
       </c>
       <c r="J42" t="n">
-        <v>3987.12</v>
+        <v>3925.55</v>
       </c>
       <c r="K42" t="n">
-        <v>4060.85</v>
+        <v>4022.2</v>
       </c>
       <c r="L42" t="n">
-        <v>4134.57</v>
+        <v>4118.85</v>
       </c>
       <c r="M42" t="n">
-        <v>4313.75</v>
+        <v>4205.2</v>
       </c>
       <c r="N42" t="n">
-        <v>4492.92</v>
+        <v>4291.55</v>
       </c>
       <c r="O42" t="n">
-        <v>4461.2</v>
+        <v>4398.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4045,59 +4045,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4106.6</v>
+        <v>4005.6</v>
       </c>
       <c r="C43" t="n">
-        <v>4112.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D43" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E43" t="n">
-        <v>4018.8</v>
+        <v>4070.8</v>
       </c>
       <c r="F43" t="n">
-        <v>-94.90000000000001</v>
+        <v>52</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0129</v>
       </c>
       <c r="H43" t="n">
-        <v>149.5</v>
+        <v>184.9</v>
       </c>
       <c r="I43" t="n">
-        <v>3849.5</v>
+        <v>3813.5</v>
       </c>
       <c r="J43" t="n">
-        <v>3925.55</v>
+        <v>3859.83</v>
       </c>
       <c r="K43" t="n">
-        <v>4022.2</v>
+        <v>3944.05</v>
       </c>
       <c r="L43" t="n">
-        <v>4118.85</v>
+        <v>4028.28</v>
       </c>
       <c r="M43" t="n">
-        <v>4205.2</v>
+        <v>4093.55</v>
       </c>
       <c r="N43" t="n">
-        <v>4291.55</v>
+        <v>4158.83</v>
       </c>
       <c r="O43" t="n">
-        <v>4398.5</v>
+        <v>4262</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4105,21 +4101,23 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4129,55 +4127,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4005.6</v>
+        <v>4097.5</v>
       </c>
       <c r="C44" t="n">
-        <v>4171.4</v>
+        <v>4170.7</v>
       </c>
       <c r="D44" t="n">
-        <v>3986.5</v>
+        <v>3993.8</v>
       </c>
       <c r="E44" t="n">
-        <v>4070.8</v>
+        <v>4107</v>
       </c>
       <c r="F44" t="n">
-        <v>52</v>
+        <v>36.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0089</v>
       </c>
       <c r="H44" t="n">
-        <v>184.9</v>
+        <v>176.9</v>
       </c>
       <c r="I44" t="n">
-        <v>3813.5</v>
+        <v>3801.6</v>
       </c>
       <c r="J44" t="n">
-        <v>3859.83</v>
+        <v>3881.83</v>
       </c>
       <c r="K44" t="n">
-        <v>3944.05</v>
+        <v>3978.35</v>
       </c>
       <c r="L44" t="n">
-        <v>4028.28</v>
+        <v>4074.88</v>
       </c>
       <c r="M44" t="n">
-        <v>4093.55</v>
+        <v>4163.25</v>
       </c>
       <c r="N44" t="n">
-        <v>4158.83</v>
+        <v>4251.62</v>
       </c>
       <c r="O44" t="n">
-        <v>4262</v>
+        <v>4356.3</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4190,19 +4192,17 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4213,57 +4213,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4097.5</v>
+        <v>4135.2</v>
       </c>
       <c r="C45" t="n">
-        <v>4170.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D45" t="n">
-        <v>3993.8</v>
+        <v>4074</v>
       </c>
       <c r="E45" t="n">
-        <v>4107</v>
+        <v>4399.7</v>
       </c>
       <c r="F45" t="n">
-        <v>36.2</v>
+        <v>292.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0089</v>
+        <v>0.0713</v>
       </c>
       <c r="H45" t="n">
-        <v>176.9</v>
+        <v>358.3</v>
       </c>
       <c r="I45" t="n">
-        <v>3801.6</v>
+        <v>3816.9</v>
       </c>
       <c r="J45" t="n">
-        <v>3881.83</v>
+        <v>3942.47</v>
       </c>
       <c r="K45" t="n">
-        <v>3978.35</v>
+        <v>4018.55</v>
       </c>
       <c r="L45" t="n">
-        <v>4074.88</v>
+        <v>4094.63</v>
       </c>
       <c r="M45" t="n">
-        <v>4163.25</v>
+        <v>4195.45</v>
       </c>
       <c r="N45" t="n">
-        <v>4251.62</v>
+        <v>4296.28</v>
       </c>
       <c r="O45" t="n">
-        <v>4356.3</v>
+        <v>4347.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4284,70 +4284,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4135.2</v>
+        <v>4400</v>
       </c>
       <c r="C46" t="n">
-        <v>4432.3</v>
+        <v>4509.1</v>
       </c>
       <c r="D46" t="n">
-        <v>4074</v>
+        <v>4365.5</v>
       </c>
       <c r="E46" t="n">
-        <v>4399.7</v>
+        <v>4437.3</v>
       </c>
       <c r="F46" t="n">
-        <v>292.7</v>
+        <v>37.6</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0713</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>358.3</v>
+        <v>143.6</v>
       </c>
       <c r="I46" t="n">
-        <v>3816.9</v>
+        <v>3715.7</v>
       </c>
       <c r="J46" t="n">
-        <v>3942.47</v>
+        <v>4114.68</v>
       </c>
       <c r="K46" t="n">
-        <v>4018.55</v>
+        <v>4220.55</v>
       </c>
       <c r="L46" t="n">
-        <v>4094.63</v>
+        <v>4326.43</v>
       </c>
       <c r="M46" t="n">
-        <v>4195.45</v>
+        <v>4578.85</v>
       </c>
       <c r="N46" t="n">
-        <v>4296.28</v>
+        <v>4831.28</v>
       </c>
       <c r="O46" t="n">
-        <v>4347.6</v>
+        <v>4790.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4360,23 +4360,17 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
@@ -4388,50 +4382,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4400</v>
+        <v>4440</v>
       </c>
       <c r="C47" t="n">
+        <v>4690.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4378</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4680.6</v>
+      </c>
+      <c r="F47" t="n">
+        <v>243.3</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="H47" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4221.9</v>
+      </c>
+      <c r="J47" t="n">
+        <v>4293.7</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4365.5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>4437.3</v>
+      </c>
+      <c r="M47" t="n">
         <v>4509.1</v>
       </c>
-      <c r="D47" t="n">
-        <v>4365.5</v>
-      </c>
-      <c r="E47" t="n">
-        <v>4437.3</v>
-      </c>
-      <c r="F47" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.008500000000000001</v>
-      </c>
-      <c r="H47" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="I47" t="n">
-        <v>3715.7</v>
-      </c>
-      <c r="J47" t="n">
-        <v>4114.68</v>
-      </c>
-      <c r="K47" t="n">
-        <v>4220.55</v>
-      </c>
-      <c r="L47" t="n">
-        <v>4326.43</v>
-      </c>
-      <c r="M47" t="n">
-        <v>4578.85</v>
-      </c>
       <c r="N47" t="n">
-        <v>4831.28</v>
+        <v>4580.9</v>
       </c>
       <c r="O47" t="n">
-        <v>4790.6</v>
+        <v>4652.7</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4444,17 +4438,23 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4466,50 +4466,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4440</v>
+        <v>4673.4</v>
       </c>
       <c r="C48" t="n">
-        <v>4690.4</v>
+        <v>4755</v>
       </c>
       <c r="D48" t="n">
-        <v>4378</v>
+        <v>4495</v>
       </c>
       <c r="E48" t="n">
-        <v>4680.6</v>
+        <v>4529.9</v>
       </c>
       <c r="F48" t="n">
-        <v>243.3</v>
+        <v>-150.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0548</v>
+        <v>-0.0322</v>
       </c>
       <c r="H48" t="n">
-        <v>312.4</v>
+        <v>260</v>
       </c>
       <c r="I48" t="n">
-        <v>4221.9</v>
+        <v>4065.6</v>
       </c>
       <c r="J48" t="n">
-        <v>4293.7</v>
+        <v>4441.4</v>
       </c>
       <c r="K48" t="n">
-        <v>4365.5</v>
+        <v>4524.4</v>
       </c>
       <c r="L48" t="n">
-        <v>4437.3</v>
+        <v>4607.4</v>
       </c>
       <c r="M48" t="n">
-        <v>4509.1</v>
+        <v>4836.8</v>
       </c>
       <c r="N48" t="n">
-        <v>4580.9</v>
+        <v>5066.2</v>
       </c>
       <c r="O48" t="n">
-        <v>4652.7</v>
+        <v>5002.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4517,83 +4517,83 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4673.4</v>
+        <v>4483.2</v>
       </c>
       <c r="C49" t="n">
-        <v>4755</v>
+        <v>4558.5</v>
       </c>
       <c r="D49" t="n">
-        <v>4495</v>
+        <v>4329.2</v>
       </c>
       <c r="E49" t="n">
-        <v>4529.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F49" t="n">
-        <v>-150.7</v>
+        <v>-53.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0118</v>
       </c>
       <c r="H49" t="n">
-        <v>260</v>
+        <v>229.3</v>
       </c>
       <c r="I49" t="n">
-        <v>4065.6</v>
+        <v>4235</v>
       </c>
       <c r="J49" t="n">
-        <v>4441.4</v>
+        <v>4222.35</v>
       </c>
       <c r="K49" t="n">
-        <v>4524.4</v>
+        <v>4399.9</v>
       </c>
       <c r="L49" t="n">
-        <v>4607.4</v>
+        <v>4577.45</v>
       </c>
       <c r="M49" t="n">
-        <v>4836.8</v>
+        <v>4659.9</v>
       </c>
       <c r="N49" t="n">
-        <v>5066.2</v>
+        <v>4742.35</v>
       </c>
       <c r="O49" t="n">
-        <v>5002.8</v>
+        <v>5015</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4627,57 +4627,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4483.2</v>
+        <v>4466.5</v>
       </c>
       <c r="C50" t="n">
-        <v>4558.5</v>
+        <v>4488.8</v>
       </c>
       <c r="D50" t="n">
-        <v>4329.2</v>
+        <v>4333</v>
       </c>
       <c r="E50" t="n">
-        <v>4476.6</v>
+        <v>4408.9</v>
       </c>
       <c r="F50" t="n">
-        <v>-53.3</v>
+        <v>-67.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0151</v>
       </c>
       <c r="H50" t="n">
-        <v>229.3</v>
+        <v>155.8</v>
       </c>
       <c r="I50" t="n">
-        <v>4235</v>
+        <v>4099.9</v>
       </c>
       <c r="J50" t="n">
-        <v>4222.35</v>
+        <v>4263.68</v>
       </c>
       <c r="K50" t="n">
-        <v>4399.9</v>
+        <v>4361.95</v>
       </c>
       <c r="L50" t="n">
-        <v>4577.45</v>
+        <v>4460.23</v>
       </c>
       <c r="M50" t="n">
-        <v>4659.9</v>
+        <v>4591.25</v>
       </c>
       <c r="N50" t="n">
-        <v>4742.35</v>
+        <v>4722.27</v>
       </c>
       <c r="O50" t="n">
-        <v>5015</v>
+        <v>4787.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4711,57 +4711,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4466.5</v>
+        <v>4375</v>
       </c>
       <c r="C51" t="n">
-        <v>4488.8</v>
+        <v>4439.8</v>
       </c>
       <c r="D51" t="n">
-        <v>4333</v>
+        <v>4273.3</v>
       </c>
       <c r="E51" t="n">
-        <v>4408.9</v>
+        <v>4424.9</v>
       </c>
       <c r="F51" t="n">
-        <v>-67.7</v>
+        <v>16</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0151</v>
+        <v>0.0036</v>
       </c>
       <c r="H51" t="n">
-        <v>155.8</v>
+        <v>166.5</v>
       </c>
       <c r="I51" t="n">
-        <v>4099.9</v>
+        <v>4177.2</v>
       </c>
       <c r="J51" t="n">
-        <v>4263.68</v>
+        <v>4252.1</v>
       </c>
       <c r="K51" t="n">
-        <v>4361.95</v>
+        <v>4331</v>
       </c>
       <c r="L51" t="n">
-        <v>4460.23</v>
+        <v>4409.9</v>
       </c>
       <c r="M51" t="n">
-        <v>4591.25</v>
+        <v>4486.8</v>
       </c>
       <c r="N51" t="n">
-        <v>4722.27</v>
+        <v>4563.7</v>
       </c>
       <c r="O51" t="n">
-        <v>4787.8</v>
+        <v>4644.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4802,65 +4802,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4375</v>
+        <v>4413</v>
       </c>
       <c r="C52" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D52" t="n">
-        <v>4273.3</v>
+        <v>4278.3</v>
       </c>
       <c r="E52" t="n">
-        <v>4424.9</v>
+        <v>4321.2</v>
       </c>
       <c r="F52" t="n">
-        <v>16</v>
+        <v>-103.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0234</v>
       </c>
       <c r="H52" t="n">
-        <v>166.5</v>
+        <v>143.8</v>
       </c>
       <c r="I52" t="n">
-        <v>4177.2</v>
+        <v>4106.8</v>
       </c>
       <c r="J52" t="n">
-        <v>4252.1</v>
+        <v>4292.57</v>
       </c>
       <c r="K52" t="n">
-        <v>4331</v>
+        <v>4341.65</v>
       </c>
       <c r="L52" t="n">
-        <v>4409.9</v>
+        <v>4390.72</v>
       </c>
       <c r="M52" t="n">
-        <v>4486.8</v>
+        <v>4508.15</v>
       </c>
       <c r="N52" t="n">
-        <v>4563.7</v>
+        <v>4625.57</v>
       </c>
       <c r="O52" t="n">
-        <v>4644.6</v>
+        <v>4606.3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4886,64 +4888,64 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4413</v>
+        <v>4315</v>
       </c>
       <c r="C53" t="n">
-        <v>4422.1</v>
+        <v>4315.6</v>
       </c>
       <c r="D53" t="n">
-        <v>4278.3</v>
+        <v>4143.1</v>
       </c>
       <c r="E53" t="n">
-        <v>4321.2</v>
+        <v>4162.3</v>
       </c>
       <c r="F53" t="n">
-        <v>-103.7</v>
+        <v>-158.9</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0234</v>
+        <v>-0.0368</v>
       </c>
       <c r="H53" t="n">
-        <v>143.8</v>
+        <v>172.5</v>
       </c>
       <c r="I53" t="n">
-        <v>4106.8</v>
+        <v>4134.5</v>
       </c>
       <c r="J53" t="n">
-        <v>4292.57</v>
+        <v>4162.9</v>
       </c>
       <c r="K53" t="n">
-        <v>4341.65</v>
+        <v>4249.3</v>
       </c>
       <c r="L53" t="n">
-        <v>4390.72</v>
+        <v>4335.7</v>
       </c>
       <c r="M53" t="n">
-        <v>4508.15</v>
+        <v>4393.1</v>
       </c>
       <c r="N53" t="n">
-        <v>4625.57</v>
+        <v>4450.5</v>
       </c>
       <c r="O53" t="n">
-        <v>4606.3</v>
+        <v>4565.9</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4958,81 +4960,73 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4315</v>
+        <v>4169.4</v>
       </c>
       <c r="C54" t="n">
-        <v>4315.6</v>
+        <v>4233.7</v>
       </c>
       <c r="D54" t="n">
-        <v>4143.1</v>
+        <v>4091.2</v>
       </c>
       <c r="E54" t="n">
-        <v>4162.3</v>
+        <v>4216.3</v>
       </c>
       <c r="F54" t="n">
-        <v>-158.9</v>
+        <v>54</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0368</v>
+        <v>0.013</v>
       </c>
       <c r="H54" t="n">
-        <v>172.5</v>
+        <v>142.5</v>
       </c>
       <c r="I54" t="n">
-        <v>4134.5</v>
+        <v>3970.6</v>
       </c>
       <c r="J54" t="n">
-        <v>4162.9</v>
+        <v>3956.27</v>
       </c>
       <c r="K54" t="n">
-        <v>4249.3</v>
+        <v>4076.05</v>
       </c>
       <c r="L54" t="n">
-        <v>4335.7</v>
+        <v>4195.82</v>
       </c>
       <c r="M54" t="n">
-        <v>4393.1</v>
+        <v>4248.55</v>
       </c>
       <c r="N54" t="n">
-        <v>4450.5</v>
+        <v>4301.27</v>
       </c>
       <c r="O54" t="n">
-        <v>4565.9</v>
+        <v>4488.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5049,68 +5043,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4169.4</v>
+        <v>4220.8</v>
       </c>
       <c r="C55" t="n">
-        <v>4233.7</v>
+        <v>4242.3</v>
       </c>
       <c r="D55" t="n">
-        <v>4091.2</v>
+        <v>4095</v>
       </c>
       <c r="E55" t="n">
-        <v>4216.3</v>
+        <v>4181.1</v>
       </c>
       <c r="F55" t="n">
-        <v>54</v>
+        <v>-35.2</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0083</v>
       </c>
       <c r="H55" t="n">
-        <v>142.5</v>
+        <v>147.3</v>
       </c>
       <c r="I55" t="n">
-        <v>3970.6</v>
+        <v>3948.7</v>
       </c>
       <c r="J55" t="n">
-        <v>3956.27</v>
+        <v>4100.72</v>
       </c>
       <c r="K55" t="n">
-        <v>4076.05</v>
+        <v>4145.05</v>
       </c>
       <c r="L55" t="n">
-        <v>4195.82</v>
+        <v>4189.37</v>
       </c>
       <c r="M55" t="n">
-        <v>4248.55</v>
+        <v>4287.55</v>
       </c>
       <c r="N55" t="n">
-        <v>4301.27</v>
+        <v>4385.72</v>
       </c>
       <c r="O55" t="n">
-        <v>4488.1</v>
+        <v>4376.2</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5129,74 +5131,74 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4220.8</v>
+        <v>4185</v>
       </c>
       <c r="C56" t="n">
-        <v>4242.3</v>
+        <v>4211.2</v>
       </c>
       <c r="D56" t="n">
-        <v>4095</v>
+        <v>3989.1</v>
       </c>
       <c r="E56" t="n">
-        <v>4181.1</v>
+        <v>4007.9</v>
       </c>
       <c r="F56" t="n">
-        <v>-35.2</v>
+        <v>-173.2</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0414</v>
       </c>
       <c r="H56" t="n">
-        <v>147.3</v>
+        <v>222.1</v>
       </c>
       <c r="I56" t="n">
-        <v>3948.7</v>
+        <v>3947.7</v>
       </c>
       <c r="J56" t="n">
-        <v>4100.72</v>
+        <v>4040.03</v>
       </c>
       <c r="K56" t="n">
-        <v>4145.05</v>
+        <v>4107.45</v>
       </c>
       <c r="L56" t="n">
-        <v>4189.37</v>
+        <v>4174.88</v>
       </c>
       <c r="M56" t="n">
-        <v>4287.55</v>
+        <v>4254.75</v>
       </c>
       <c r="N56" t="n">
-        <v>4385.72</v>
+        <v>4334.62</v>
       </c>
       <c r="O56" t="n">
-        <v>4376.2</v>
+        <v>4389.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5213,73 +5215,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4185</v>
+        <v>4012.2</v>
       </c>
       <c r="C57" t="n">
-        <v>4211.2</v>
+        <v>4097.2</v>
       </c>
       <c r="D57" t="n">
-        <v>3989.1</v>
+        <v>3879.3</v>
       </c>
       <c r="E57" t="n">
-        <v>4007.9</v>
+        <v>3884.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-173.2</v>
+        <v>-123</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0414</v>
+        <v>-0.0307</v>
       </c>
       <c r="H57" t="n">
-        <v>222.1</v>
+        <v>217.9</v>
       </c>
       <c r="I57" t="n">
-        <v>3947.7</v>
+        <v>3767</v>
       </c>
       <c r="J57" t="n">
-        <v>4040.03</v>
+        <v>3739.67</v>
       </c>
       <c r="K57" t="n">
-        <v>4107.45</v>
+        <v>3896.85</v>
       </c>
       <c r="L57" t="n">
-        <v>4174.88</v>
+        <v>4054.03</v>
       </c>
       <c r="M57" t="n">
-        <v>4254.75</v>
+        <v>4118.95</v>
       </c>
       <c r="N57" t="n">
-        <v>4334.62</v>
+        <v>4183.87</v>
       </c>
       <c r="O57" t="n">
-        <v>4389.6</v>
+        <v>4433.3</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5300,88 +5296,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>4012.2</v>
-      </c>
-      <c r="C58" t="n">
-        <v>4097.2</v>
-      </c>
-      <c r="D58" t="n">
-        <v>3990.9</v>
-      </c>
-      <c r="E58" t="n">
-        <v>4024.3</v>
-      </c>
-      <c r="F58" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0041</v>
-      </c>
-      <c r="H58" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3767</v>
-      </c>
-      <c r="J58" t="n">
-        <v>3739.67</v>
-      </c>
-      <c r="K58" t="n">
-        <v>3896.85</v>
-      </c>
-      <c r="L58" t="n">
-        <v>4054.03</v>
-      </c>
-      <c r="M58" t="n">
-        <v>4118.95</v>
-      </c>
-      <c r="N58" t="n">
-        <v>4183.87</v>
-      </c>
-      <c r="O58" t="n">
-        <v>4433.3</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
